--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="872" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFE2DA6E-DEBC-4CDB-9C94-0817BA184571}"/>
+  <xr:revisionPtr revIDLastSave="906" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C73FC94-1EBD-4C56-AEDE-F3207932C84F}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -149,6 +149,7 @@
     <author>tc={E674068C-9812-42A2-9151-17837D13ABB6}</author>
     <author>tc={ED249525-191C-4637-9D99-E242BDB6421A}</author>
     <author>tc={B304C0F3-0817-4A4E-853F-5F45E9E32DFD}</author>
+    <author>tc={DF19662E-D699-40A7-996A-7901BA4875E9}</author>
     <author>tc={1C68C472-CF02-4D39-A15B-ACD03122D4F0}</author>
     <author>tc={2330157A-B3C2-4789-96E1-9C8D2D80D7FE}</author>
     <author>tc={831B6259-37A3-4907-AE80-39991BDC7649}</author>
@@ -261,7 +262,15 @@
     Mila arketa, kinito, oriothetisi</t>
       </text>
     </comment>
-    <comment ref="C35" authorId="13" shapeId="0" xr:uid="{1C68C472-CF02-4D39-A15B-ACD03122D4F0}">
+    <comment ref="I34" authorId="13" shapeId="0" xr:uid="{DF19662E-D699-40A7-996A-7901BA4875E9}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    kataggelia</t>
+      </text>
+    </comment>
+    <comment ref="C35" authorId="14" shapeId="0" xr:uid="{1C68C472-CF02-4D39-A15B-ACD03122D4F0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -271,7 +280,7 @@
     Miazei tis Melias</t>
       </text>
     </comment>
-    <comment ref="C36" authorId="14" shapeId="0" xr:uid="{2330157A-B3C2-4789-96E1-9C8D2D80D7FE}">
+    <comment ref="C36" authorId="15" shapeId="0" xr:uid="{2330157A-B3C2-4789-96E1-9C8D2D80D7FE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -279,7 +288,7 @@
     zoiros</t>
       </text>
     </comment>
-    <comment ref="C37" authorId="15" shapeId="0" xr:uid="{831B6259-37A3-4907-AE80-39991BDC7649}">
+    <comment ref="C37" authorId="16" shapeId="0" xr:uid="{831B6259-37A3-4907-AE80-39991BDC7649}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -456,7 +465,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="299">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1350,6 +1359,9 @@
   </si>
   <si>
     <t>change sits</t>
+  </si>
+  <si>
+    <t>hw. Ask9, p13</t>
   </si>
 </sst>
 </file>
@@ -1985,6 +1997,9 @@
   <threadedComment ref="C34" dT="2026-09-20T17:10:57.03" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B304C0F3-0817-4A4E-853F-5F45E9E32DFD}">
     <text>Mila arketa, kinito, oriothetisi</text>
   </threadedComment>
+  <threadedComment ref="I34" dT="2026-09-29T09:23:10.29" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{DF19662E-D699-40A7-996A-7901BA4875E9}">
+    <text>kataggelia</text>
+  </threadedComment>
   <threadedComment ref="C35" dT="2026-09-22T09:37:54.19" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{1C68C472-CF02-4D39-A15B-ACD03122D4F0}">
     <text>Oreo m.</text>
   </threadedComment>
@@ -2187,7 +2202,7 @@
       <c r="G5" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="19" t="s">
         <v>258</v>
       </c>
       <c r="I5" s="4" t="s">
@@ -2368,7 +2383,7 @@
       <c r="H15" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="19" t="s">
         <v>263</v>
       </c>
     </row>
@@ -2410,7 +2425,7 @@
       <c r="G20" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="19" t="s">
         <v>243</v>
       </c>
       <c r="I20" s="17" t="s">
@@ -2460,7 +2475,7 @@
       <c r="G21" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="19" t="s">
         <v>240</v>
       </c>
       <c r="I21" s="17" t="s">
@@ -2513,7 +2528,7 @@
       <c r="G22" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="19" t="s">
         <v>243</v>
       </c>
       <c r="I22" s="17" t="s">
@@ -2888,6 +2903,9 @@
       <c r="B15" s="9" t="s">
         <v>283</v>
       </c>
+      <c r="H15" s="9" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A16" s="9">
@@ -2908,6 +2926,9 @@
       <c r="F16" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H16" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A17" s="9">
@@ -2928,6 +2949,7 @@
       <c r="F17" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H17" s="22"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A18" s="9">
@@ -2948,6 +2970,9 @@
       <c r="F18" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H18" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A19" s="9">
@@ -2968,6 +2993,9 @@
       <c r="F19" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H19" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A20" s="9">
@@ -2988,6 +3016,7 @@
       <c r="F20" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H20" s="22"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A21" s="9">
@@ -3008,6 +3037,7 @@
       <c r="F21" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H21" s="22"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A22" s="9">
@@ -3028,6 +3058,9 @@
       <c r="F22" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H22" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A23" s="9">
@@ -3048,6 +3081,9 @@
       <c r="F23" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H23" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A24" s="9">
@@ -3068,6 +3104,9 @@
       <c r="F24" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H24" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A26" s="9" t="s">
@@ -3075,9 +3114,6 @@
       </c>
       <c r="F26" s="9" t="s">
         <v>294</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.5">
@@ -3941,7 +3977,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A17" s="9">
         <v>1031619</v>
       </c>
@@ -3961,7 +3997,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A18" s="9">
         <v>1037608</v>
       </c>
@@ -3981,7 +4017,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A19" s="9">
         <v>1035515</v>
       </c>
@@ -4001,7 +4037,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A20" s="9">
         <v>1030772</v>
       </c>
@@ -4021,7 +4057,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A21" s="9">
         <v>1026742</v>
       </c>
@@ -4041,7 +4077,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A22" s="9">
         <v>1038924</v>
       </c>
@@ -4061,7 +4097,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A23" s="9">
         <v>1029508</v>
       </c>
@@ -4081,7 +4117,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A24" s="9">
         <v>1028849</v>
       </c>
@@ -4101,12 +4137,12 @@
         <v>236</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A27" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A28" s="9">
         <v>1027008</v>
       </c>
@@ -4128,8 +4164,11 @@
       <c r="H28" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I28" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A29" s="9">
         <v>1026200</v>
       </c>
@@ -4151,8 +4190,11 @@
       <c r="H29" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I29" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A30" s="9">
         <v>1025833</v>
       </c>
@@ -4174,8 +4216,11 @@
       <c r="H30" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I30" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A31" s="9">
         <v>1036053</v>
       </c>
@@ -4197,8 +4242,11 @@
       <c r="H31" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I31" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A32" s="9">
         <v>1029029</v>
       </c>
@@ -4220,8 +4268,11 @@
       <c r="H32" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I32" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A33" s="9">
         <v>1028278</v>
       </c>
@@ -4243,8 +4294,11 @@
       <c r="H33" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I33" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A34" s="9">
         <v>1025603</v>
       </c>
@@ -4266,8 +4320,11 @@
       <c r="H34" s="12" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I34" s="12" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A35" s="9">
         <v>1028053</v>
       </c>
@@ -4289,8 +4346,11 @@
       <c r="H35" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I35" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A36" s="9">
         <v>1027036</v>
       </c>
@@ -4312,8 +4372,11 @@
       <c r="H36" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I36" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A37" s="9">
         <v>1032361</v>
       </c>
@@ -4333,6 +4396,9 @@
         <v>173</v>
       </c>
       <c r="H37" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I37" s="12" t="s">
         <v>173</v>
       </c>
     </row>
@@ -4552,6 +4618,9 @@
       <c r="H4" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="I4" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -4578,6 +4647,9 @@
       <c r="H5" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="I5" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -4604,6 +4676,9 @@
       <c r="H6" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="I6" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7">
@@ -4630,6 +4705,9 @@
       <c r="H7" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="I7" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -4656,6 +4734,9 @@
       <c r="H8" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="I8" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9">
@@ -4682,6 +4763,9 @@
       <c r="H9" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="I9" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10">
@@ -4708,6 +4792,9 @@
       <c r="H10" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="I10" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A11">
@@ -4734,6 +4821,9 @@
       <c r="H11" s="24" t="s">
         <v>236</v>
       </c>
+      <c r="I11" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12">
@@ -4760,6 +4850,9 @@
       <c r="H12" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="I12" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13">
@@ -4786,6 +4879,9 @@
       <c r="H13" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="I13" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A14">
@@ -4812,6 +4908,9 @@
       <c r="H14" s="24" t="s">
         <v>236</v>
       </c>
+      <c r="I14" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15">
@@ -4838,6 +4937,9 @@
       <c r="H15" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="I15" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16">
@@ -4864,8 +4966,11 @@
       <c r="H16" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I16" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="C17" t="s">
         <v>229</v>
       </c>
@@ -4884,8 +4989,11 @@
       <c r="H17" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I17" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>230</v>
       </c>
@@ -4907,8 +5015,11 @@
       <c r="H18" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I18" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>232</v>
       </c>
@@ -4930,13 +5041,16 @@
       <c r="H19" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I19" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -4950,7 +5064,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A23">
         <v>9693404</v>
       </c>
@@ -4975,8 +5089,11 @@
       <c r="H23" s="22" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="I23" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A24">
         <v>222222</v>
       </c>
@@ -5001,8 +5118,11 @@
       <c r="H24" s="22" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="I24" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A25">
         <v>9743804</v>
       </c>
@@ -5027,8 +5147,11 @@
       <c r="H25" s="22" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="I25" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A26">
         <v>111111</v>
       </c>
@@ -5053,8 +5176,9 @@
       <c r="H26" s="22" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="I26" s="31"/>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A27">
         <v>9662304</v>
       </c>
@@ -5079,8 +5203,11 @@
       <c r="H27" s="22" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="I27" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B28" t="s">
         <v>277</v>
       </c>
@@ -5098,8 +5225,9 @@
       <c r="H28" s="22" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="I28" s="31"/>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B29" t="s">
         <v>277</v>
       </c>
@@ -5117,13 +5245,14 @@
       <c r="H29" s="22" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I29" s="31"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>3578804</v>
       </c>
@@ -5145,8 +5274,11 @@
       <c r="G32" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I32" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A33">
         <v>9289704</v>
       </c>
@@ -5168,8 +5300,9 @@
       <c r="G33" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I33" s="22"/>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A34">
         <v>9344404</v>
       </c>
@@ -5191,8 +5324,9 @@
       <c r="G34" s="14" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I34" s="31"/>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A35">
         <v>6746404</v>
       </c>
@@ -5214,8 +5348,9 @@
       <c r="G35" s="14" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I35" s="22"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>9257604</v>
       </c>
@@ -5237,8 +5372,11 @@
       <c r="G36" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="I36" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A37">
         <v>9717204</v>
       </c>
@@ -5260,8 +5398,9 @@
       <c r="G37" s="29" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I37" s="22"/>
+    </row>
+    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A38">
         <v>2298204</v>
       </c>
@@ -5283,8 +5422,9 @@
       <c r="G38" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I38" s="22"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>5784804</v>
       </c>
@@ -5306,8 +5446,11 @@
       <c r="G39" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I39" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>9321704</v>
       </c>
@@ -5329,8 +5472,11 @@
       <c r="G40" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I40" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A41">
         <v>9720304</v>
       </c>
@@ -5352,8 +5498,11 @@
       <c r="G41" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I41" s="28" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A42">
         <v>9317404</v>
       </c>
@@ -5375,8 +5524,9 @@
       <c r="G42" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I42" s="22"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>8333604</v>
       </c>
@@ -5396,6 +5546,9 @@
         <v>173</v>
       </c>
       <c r="G43" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="I43" s="14" t="s">
         <v>173</v>
       </c>
     </row>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="906" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C73FC94-1EBD-4C56-AEDE-F3207932C84F}"/>
+  <xr:revisionPtr revIDLastSave="919" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1E9BDC6-CBF3-421E-8AF7-DBAF39A5D8B0}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -465,7 +465,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="300">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1362,6 +1362,9 @@
   </si>
   <si>
     <t>hw. Ask9, p13</t>
+  </si>
+  <si>
+    <t>hw. Ask1 p121</t>
   </si>
 </sst>
 </file>
@@ -1623,13 +1626,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2106,34 +2109,34 @@
   <sheetData>
     <row r="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="34" t="s">
+      <c r="C1" s="34"/>
+      <c r="D1" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="34" t="s">
+      <c r="E1" s="34"/>
+      <c r="F1" s="33" t="s">
         <v>238</v>
       </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="34" t="s">
+      <c r="G1" s="34"/>
+      <c r="H1" s="33" t="s">
         <v>244</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="34" t="s">
+      <c r="I1" s="34"/>
+      <c r="J1" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="34" t="s">
+      <c r="K1" s="34"/>
+      <c r="L1" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="M1" s="35"/>
-      <c r="N1" s="34" t="s">
+      <c r="M1" s="34"/>
+      <c r="N1" s="33" t="s">
         <v>253</v>
       </c>
-      <c r="O1" s="35"/>
+      <c r="O1" s="34"/>
     </row>
     <row r="2" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -2668,7 +2671,8 @@
     <col min="6" max="6" width="13.53125" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.06640625" style="9"/>
     <col min="8" max="8" width="13.53125" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.06640625" style="9"/>
+    <col min="9" max="9" width="13.46484375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.06640625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="13" customFormat="1" x14ac:dyDescent="0.5">
@@ -2686,19 +2690,22 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33" t="s">
+      <c r="G2" s="35"/>
+      <c r="H2" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="I2" s="33"/>
+      <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A3" s="9" t="s">
         <v>121</v>
       </c>
+      <c r="I3" s="9" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A4" s="9">
@@ -2717,6 +2724,7 @@
         <v>173</v>
       </c>
       <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A5" s="9">
@@ -2737,6 +2745,9 @@
       <c r="H5" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I5" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A6" s="9">
@@ -2757,6 +2768,9 @@
       <c r="H6" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I6" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A7" s="9">
@@ -2777,6 +2791,9 @@
       <c r="H7" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I7" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A8" s="9">
@@ -2797,6 +2814,9 @@
       <c r="H8" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I8" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A9" s="9">
@@ -2817,6 +2837,9 @@
       <c r="H9" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I9" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A10" s="9">
@@ -2837,6 +2860,9 @@
       <c r="H10" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I10" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A11" s="9">
@@ -2857,6 +2883,9 @@
       <c r="H11" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I11" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A12" s="9">
@@ -2877,6 +2906,9 @@
       <c r="H12" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I12" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A13" s="9">
@@ -2895,6 +2927,9 @@
         <v>173</v>
       </c>
       <c r="H13" s="31"/>
+      <c r="I13" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A15" s="9" t="s">
@@ -2906,6 +2941,9 @@
       <c r="H15" s="9" t="s">
         <v>298</v>
       </c>
+      <c r="I15" s="9" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A16" s="9">
@@ -3114,6 +3152,9 @@
       </c>
       <c r="F26" s="9" t="s">
         <v>294</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.5">
@@ -3677,14 +3718,14 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33" t="s">
+      <c r="G2" s="35"/>
+      <c r="H2" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="I2" s="33"/>
+      <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A3" s="9" t="s">
@@ -3716,6 +3757,9 @@
       <c r="H4" s="32" t="s">
         <v>267</v>
       </c>
+      <c r="I4" s="32" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A5" s="9">
@@ -3742,6 +3786,7 @@
       <c r="H5" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A6" s="9">
@@ -3768,6 +3813,9 @@
       <c r="H6" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I6" s="32" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A7" s="9">
@@ -3792,6 +3840,9 @@
         <v>173</v>
       </c>
       <c r="H7" s="22"/>
+      <c r="I7" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A8" s="9">
@@ -3818,6 +3869,9 @@
       <c r="H8" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I8" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A9" s="9">
@@ -3844,6 +3898,9 @@
       <c r="H9" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I9" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A10" s="9">
@@ -3870,6 +3927,9 @@
       <c r="H10" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I10" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A11" s="9">
@@ -3896,6 +3956,9 @@
       <c r="H11" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I11" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A12" s="9">
@@ -3922,6 +3985,9 @@
       <c r="H12" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I12" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A13" s="9">
@@ -3946,6 +4012,9 @@
         <v>173</v>
       </c>
       <c r="H13" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I13" s="12" t="s">
         <v>173</v>
       </c>
     </row>
@@ -4437,14 +4506,14 @@
       <c r="D1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33" t="s">
+      <c r="F1" s="35"/>
+      <c r="G1" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="H1" s="33"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A3" s="9">
@@ -4579,14 +4648,14 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33" t="s">
+      <c r="H1" s="35"/>
+      <c r="I1" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="J1" s="33"/>
+      <c r="J1" s="35"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="919" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1E9BDC6-CBF3-421E-8AF7-DBAF39A5D8B0}"/>
+  <xr:revisionPtr revIDLastSave="945" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3725E0AB-7B78-43EE-853A-4DB56EAE7777}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="15" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="Monada" sheetId="5" r:id="rId4"/>
     <sheet name="A Lyceum" sheetId="4" r:id="rId5"/>
     <sheet name="anapliroseis" sheetId="7" r:id="rId6"/>
-    <sheet name="tests" sheetId="8" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId7"/>
+    <sheet name="Sheet1 (2)" sheetId="10" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -73,6 +74,13 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={8EB208C6-D456-45F0-A2B8-C4DE4FED70F2}</author>
+    <author>tc={6A7133F0-4BE8-480D-9B8D-ADB25AC1F901}</author>
+    <author>tc={E8997790-0783-4AD7-B20C-B787446F63EE}</author>
+    <author>tc={244BBB48-84AA-4D45-9224-37028E88ADE4}</author>
+    <author>tc={D00A9786-4371-4DDC-AF94-2EFF9B28A584}</author>
+    <author>tc={FB3DF04B-F31A-450A-AC26-8640F28C121C}</author>
+    <author>tc={0F5BD204-8223-4D3B-AFE2-EF5ECBE1DDD2}</author>
+    <author>tc={60BA8BDF-307A-4EAF-84FA-BF1FDAF46BFC}</author>
     <author>tc={DBA037C8-7BAC-4FA9-AE99-50153AA21B00}</author>
     <author>tc={AD4C8F15-E890-4B85-B1C2-93D5114E713A}</author>
     <author>tc={009D741D-5339-4620-BEF3-C76ECC0C19D0}</author>
@@ -88,7 +96,71 @@
     Seems good class</t>
       </text>
     </comment>
-    <comment ref="C16" authorId="1" shapeId="0" xr:uid="{DBA037C8-7BAC-4FA9-AE99-50153AA21B00}">
+    <comment ref="C4" authorId="1" shapeId="0" xr:uid="{6A7133F0-4BE8-480D-9B8D-ADB25AC1F901}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Bulgaria, thema me apousies</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="2" shapeId="0" xr:uid="{E8997790-0783-4AD7-B20C-B787446F63EE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Menei me mitera, vlepei patera.
+Reply:
+    sitisis
+Reply:
+    Mitera kypria</t>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="3" shapeId="0" xr:uid="{244BBB48-84AA-4D45-9224-37028E88ADE4}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Xorismenos me mitera</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="4" shapeId="0" xr:uid="{D00A9786-4371-4DDC-AF94-2EFF9B28A584}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Isos themata me ti glossa
+Reply:
+    roumania</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="5" shapeId="0" xr:uid="{FB3DF04B-F31A-450A-AC26-8640F28C121C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    monaxikos
+Reply:
+    roumania</t>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="6" shapeId="0" xr:uid="{0F5BD204-8223-4D3B-AFE2-EF5ECBE1DDD2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    roumania</t>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="7" shapeId="0" xr:uid="{60BA8BDF-307A-4EAF-84FA-BF1FDAF46BFC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Xasimoto, elleipsi prosoxis, astheneia cushing</t>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="8" shapeId="0" xr:uid="{DBA037C8-7BAC-4FA9-AE99-50153AA21B00}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -96,7 +168,7 @@
     Exei voitho</t>
       </text>
     </comment>
-    <comment ref="C22" authorId="2" shapeId="0" xr:uid="{AD4C8F15-E890-4B85-B1C2-93D5114E713A}">
+    <comment ref="C22" authorId="9" shapeId="0" xr:uid="{AD4C8F15-E890-4B85-B1C2-93D5114E713A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -104,7 +176,7 @@
     Special, pontios</t>
       </text>
     </comment>
-    <comment ref="C41" authorId="3" shapeId="0" xr:uid="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
+    <comment ref="C41" authorId="10" shapeId="0" xr:uid="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -112,7 +184,7 @@
     indefferent</t>
       </text>
     </comment>
-    <comment ref="E42" authorId="4" shapeId="0" xr:uid="{720F20F5-2744-4E03-9112-5151AF4ED353}">
+    <comment ref="E42" authorId="11" shapeId="0" xr:uid="{720F20F5-2744-4E03-9112-5151AF4ED353}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -120,7 +192,7 @@
     Indifferent, don't take book.</t>
       </text>
     </comment>
-    <comment ref="C49" authorId="5" shapeId="0" xr:uid="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
+    <comment ref="C49" authorId="12" shapeId="0" xr:uid="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -465,7 +537,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="299">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1356,9 +1428,6 @@
   </si>
   <si>
     <t>ask Jouliana for keyboard</t>
-  </si>
-  <si>
-    <t>change sits</t>
   </si>
   <si>
     <t>hw. Ask9, p13</t>
@@ -1371,7 +1440,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1417,6 +1486,12 @@
       <family val="2"/>
       <charset val="161"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="14">
@@ -1626,13 +1701,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1936,6 +2011,39 @@
   <threadedComment ref="A3" dT="2026-09-21T06:34:38.10" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{8EB208C6-D456-45F0-A2B8-C4DE4FED70F2}">
     <text>Seems good class</text>
   </threadedComment>
+  <threadedComment ref="C4" dT="2026-10-01T18:49:32.40" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{6A7133F0-4BE8-480D-9B8D-ADB25AC1F901}">
+    <text>Bulgaria, thema me apousies</text>
+  </threadedComment>
+  <threadedComment ref="C5" dT="2026-10-01T18:50:02.22" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{E8997790-0783-4AD7-B20C-B787446F63EE}">
+    <text>Menei me mitera, vlepei patera.</text>
+  </threadedComment>
+  <threadedComment ref="C5" dT="2026-10-01T18:50:07.72" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{4307B83C-28FA-442D-A28B-44F549436287}" parentId="{E8997790-0783-4AD7-B20C-B787446F63EE}">
+    <text>sitisis</text>
+  </threadedComment>
+  <threadedComment ref="C5" dT="2026-10-01T18:52:00.24" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{1DF0185B-008B-42C9-819F-860A0872EC8C}" parentId="{E8997790-0783-4AD7-B20C-B787446F63EE}">
+    <text>Mitera kypria</text>
+  </threadedComment>
+  <threadedComment ref="C6" dT="2026-10-01T18:50:40.65" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{244BBB48-84AA-4D45-9224-37028E88ADE4}">
+    <text>Xorismenos me mitera</text>
+  </threadedComment>
+  <threadedComment ref="C7" dT="2026-10-01T18:50:55.97" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D00A9786-4371-4DDC-AF94-2EFF9B28A584}">
+    <text>Isos themata me ti glossa</text>
+  </threadedComment>
+  <threadedComment ref="C7" dT="2026-10-01T18:52:12.55" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{A6F29A10-2440-4A7C-AC26-462284AAED33}" parentId="{D00A9786-4371-4DDC-AF94-2EFF9B28A584}">
+    <text>roumania</text>
+  </threadedComment>
+  <threadedComment ref="C8" dT="2026-10-01T18:51:09.16" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{FB3DF04B-F31A-450A-AC26-8640F28C121C}">
+    <text>monaxikos</text>
+  </threadedComment>
+  <threadedComment ref="C8" dT="2026-10-01T18:51:20.32" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{55E655A5-D2BE-413A-8819-7BC023909879}" parentId="{FB3DF04B-F31A-450A-AC26-8640F28C121C}">
+    <text>roumania</text>
+  </threadedComment>
+  <threadedComment ref="C10" dT="2026-10-01T18:52:40.56" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{0F5BD204-8223-4D3B-AFE2-EF5ECBE1DDD2}">
+    <text>roumania</text>
+  </threadedComment>
+  <threadedComment ref="C12" dT="2026-10-01T18:53:07.17" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{60BA8BDF-307A-4EAF-84FA-BF1FDAF46BFC}">
+    <text>Xasimoto, elleipsi prosoxis, astheneia cushing</text>
+  </threadedComment>
   <threadedComment ref="C16" dT="2026-09-22T09:38:48.85" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{DBA037C8-7BAC-4FA9-AE99-50153AA21B00}">
     <text>Exei voitho</text>
   </threadedComment>
@@ -2109,34 +2217,34 @@
   <sheetData>
     <row r="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="33" t="s">
+      <c r="C1" s="35"/>
+      <c r="D1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="34"/>
-      <c r="F1" s="33" t="s">
+      <c r="E1" s="35"/>
+      <c r="F1" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="G1" s="34"/>
-      <c r="H1" s="33" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>244</v>
       </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="33" t="s">
+      <c r="I1" s="35"/>
+      <c r="J1" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="K1" s="34"/>
-      <c r="L1" s="33" t="s">
+      <c r="K1" s="35"/>
+      <c r="L1" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="M1" s="34"/>
-      <c r="N1" s="33" t="s">
+      <c r="M1" s="35"/>
+      <c r="N1" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="O1" s="34"/>
+      <c r="O1" s="35"/>
     </row>
     <row r="2" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -2179,7 +2287,7 @@
       <c r="H4" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="19" t="s">
         <v>255</v>
       </c>
     </row>
@@ -2208,7 +2316,7 @@
       <c r="H5" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="19" t="s">
         <v>255</v>
       </c>
       <c r="J5" s="1" t="s">
@@ -2240,7 +2348,7 @@
       <c r="G6" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="19" t="s">
         <v>255</v>
       </c>
       <c r="I6" s="4" t="s">
@@ -2328,7 +2436,7 @@
       <c r="H13" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="19" t="s">
         <v>264</v>
       </c>
     </row>
@@ -2690,21 +2798,21 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="I2" s="35"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A3" s="9" t="s">
         <v>121</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.5">
@@ -2939,10 +3047,10 @@
         <v>283</v>
       </c>
       <c r="H15" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="I15" s="9" t="s">
         <v>298</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.5">
@@ -3154,7 +3262,7 @@
         <v>294</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.5">
@@ -3176,6 +3284,9 @@
       <c r="F27" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H27" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A28" s="9">
@@ -3196,6 +3307,9 @@
       <c r="F28" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H28" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A29" s="9">
@@ -3214,6 +3328,7 @@
         <v>173</v>
       </c>
       <c r="F29" s="22"/>
+      <c r="H29" s="22"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A30" s="9">
@@ -3234,6 +3349,9 @@
       <c r="F30" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H30" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A31" s="9">
@@ -3254,6 +3372,9 @@
       <c r="F31" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H31" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A32" s="9">
@@ -3274,6 +3395,9 @@
       <c r="F32" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H32" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A33" s="9">
@@ -3294,6 +3418,9 @@
       <c r="F33" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H33" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A34" s="9">
@@ -3314,6 +3441,9 @@
       <c r="F34" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H34" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A35" s="9">
@@ -3334,6 +3464,9 @@
       <c r="F35" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="H35" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A36" s="9">
@@ -3352,6 +3485,9 @@
         <v>173</v>
       </c>
       <c r="F36" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H36" s="12" t="s">
         <v>173</v>
       </c>
     </row>
@@ -3718,14 +3854,14 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="I2" s="35"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A3" s="9" t="s">
@@ -4021,9 +4157,6 @@
     <row r="15" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A15" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.5">
@@ -4506,14 +4639,14 @@
       <c r="D1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35" t="s">
+      <c r="F1" s="33"/>
+      <c r="G1" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A3" s="9">
@@ -4648,14 +4781,14 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35" t="s">
+      <c r="H1" s="33"/>
+      <c r="I1" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="J1" s="35"/>
+      <c r="J1" s="33"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
@@ -5655,116 +5788,19 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC2DFA1-0C86-4973-B1C5-27FCBC81C12B}">
-  <dimension ref="C5:G20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C172699-9C2F-4E67-A102-81BDA8494E34}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.45">
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="3:7" x14ac:dyDescent="0.45">
-      <c r="C6">
-        <v>56</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.45">
-      <c r="C7">
-        <v>34</v>
-      </c>
-      <c r="G7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.45">
-      <c r="C8">
-        <v>22</v>
-      </c>
-      <c r="G8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.45">
-      <c r="C9">
-        <v>45</v>
-      </c>
-      <c r="G9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.45">
-      <c r="C10">
-        <v>23</v>
-      </c>
-      <c r="G10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.45">
-      <c r="C11">
-        <v>123</v>
-      </c>
-      <c r="G11">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.45">
-      <c r="C12">
-        <f>SUM(C5:C11)</f>
-        <v>307</v>
-      </c>
-      <c r="G12">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="3:7" x14ac:dyDescent="0.45">
-      <c r="G13">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="3:7" x14ac:dyDescent="0.45">
-      <c r="G14">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="3:7" x14ac:dyDescent="0.45">
-      <c r="G15">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="3:7" x14ac:dyDescent="0.45">
-      <c r="G16">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.45">
-      <c r="G17">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.45">
-      <c r="G18">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.45">
-      <c r="G19">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.45">
-      <c r="G20">
-        <v>80</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{679D73DD-8522-407F-98CA-C4EDF40265F0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="945" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3725E0AB-7B78-43EE-853A-4DB56EAE7777}"/>
+  <xr:revisionPtr revIDLastSave="955" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23C6E4E2-E928-438E-8F3B-C429CEF3B3C2}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="15" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,12 @@
     <author>tc={0F5BD204-8223-4D3B-AFE2-EF5ECBE1DDD2}</author>
     <author>tc={60BA8BDF-307A-4EAF-84FA-BF1FDAF46BFC}</author>
     <author>tc={DBA037C8-7BAC-4FA9-AE99-50153AA21B00}</author>
+    <author>tc={FACE775A-C672-4B26-8A1E-47683B5B2F22}</author>
+    <author>tc={2467605D-399B-4869-A30B-7FE742BDF0DA}</author>
+    <author>tc={48BC95C2-E3C5-464E-B23C-508BA24D8245}</author>
     <author>tc={AD4C8F15-E890-4B85-B1C2-93D5114E713A}</author>
+    <author>tc={8F76B8B8-18EE-496F-A335-0321C1189047}</author>
+    <author>tc={E74507EC-BC04-4A9B-B15C-32C7F44E6109}</author>
     <author>tc={009D741D-5339-4620-BEF3-C76ECC0C19D0}</author>
     <author>tc={720F20F5-2744-4E03-9112-5151AF4ED353}</author>
     <author>tc={2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}</author>
@@ -165,10 +170,36 @@
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Exei voitho</t>
+    Exei voitho
+Reply:
+    stiriksi</t>
       </text>
     </comment>
-    <comment ref="C22" authorId="9" shapeId="0" xr:uid="{AD4C8F15-E890-4B85-B1C2-93D5114E713A}">
+    <comment ref="C17" authorId="9" shapeId="0" xr:uid="{FACE775A-C672-4B26-8A1E-47683B5B2F22}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Noxelikos, pithanos ethismos sta electronica paixnidia</t>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="10" shapeId="0" xr:uid="{2467605D-399B-4869-A30B-7FE742BDF0DA}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Poli evesthiti, kleei eukola, politekni</t>
+      </text>
+    </comment>
+    <comment ref="C21" authorId="11" shapeId="0" xr:uid="{48BC95C2-E3C5-464E-B23C-508BA24D8245}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    vogotonia</t>
+      </text>
+    </comment>
+    <comment ref="C22" authorId="12" shapeId="0" xr:uid="{AD4C8F15-E890-4B85-B1C2-93D5114E713A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -176,7 +207,23 @@
     Special, pontios</t>
       </text>
     </comment>
-    <comment ref="C41" authorId="10" shapeId="0" xr:uid="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
+    <comment ref="C24" authorId="13" shapeId="0" xr:uid="{8F76B8B8-18EE-496F-A335-0321C1189047}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    stiriksi</t>
+      </text>
+    </comment>
+    <comment ref="C25" authorId="14" shapeId="0" xr:uid="{E74507EC-BC04-4A9B-B15C-32C7F44E6109}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Stiriksi</t>
+      </text>
+    </comment>
+    <comment ref="C42" authorId="15" shapeId="0" xr:uid="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -184,7 +231,7 @@
     indefferent</t>
       </text>
     </comment>
-    <comment ref="E42" authorId="11" shapeId="0" xr:uid="{720F20F5-2744-4E03-9112-5151AF4ED353}">
+    <comment ref="E43" authorId="16" shapeId="0" xr:uid="{720F20F5-2744-4E03-9112-5151AF4ED353}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -192,7 +239,7 @@
     Indifferent, don't take book.</t>
       </text>
     </comment>
-    <comment ref="C49" authorId="12" shapeId="0" xr:uid="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
+    <comment ref="C50" authorId="17" shapeId="0" xr:uid="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -537,7 +584,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="302">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1434,6 +1481,15 @@
   </si>
   <si>
     <t>hw. Ask1 p121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Τρήφωνος </t>
+  </si>
+  <si>
+    <t>Αντρέας</t>
+  </si>
+  <si>
+    <t>A2</t>
   </si>
 </sst>
 </file>
@@ -2047,16 +2103,34 @@
   <threadedComment ref="C16" dT="2026-09-22T09:38:48.85" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{DBA037C8-7BAC-4FA9-AE99-50153AA21B00}">
     <text>Exei voitho</text>
   </threadedComment>
+  <threadedComment ref="C16" dT="2026-10-02T08:19:54.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AA4BCF28-05A2-4F9D-A4FD-D708A7DF3EB9}" parentId="{DBA037C8-7BAC-4FA9-AE99-50153AA21B00}">
+    <text>stiriksi</text>
+  </threadedComment>
+  <threadedComment ref="C17" dT="2026-10-02T08:20:20.01" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{FACE775A-C672-4B26-8A1E-47683B5B2F22}">
+    <text>Noxelikos, pithanos ethismos sta electronica paixnidia</text>
+  </threadedComment>
+  <threadedComment ref="C19" dT="2026-10-02T08:21:02.61" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2467605D-399B-4869-A30B-7FE742BDF0DA}">
+    <text>Poli evesthiti, kleei eukola, politekni</text>
+  </threadedComment>
+  <threadedComment ref="C21" dT="2026-10-02T08:21:14.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{48BC95C2-E3C5-464E-B23C-508BA24D8245}">
+    <text>vogotonia</text>
+  </threadedComment>
   <threadedComment ref="C22" dT="2026-09-22T09:31:53.95" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AD4C8F15-E890-4B85-B1C2-93D5114E713A}">
     <text>Special, pontios</text>
   </threadedComment>
-  <threadedComment ref="C41" dT="2026-09-25T14:55:37.89" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
+  <threadedComment ref="C24" dT="2026-10-02T08:21:35.28" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{8F76B8B8-18EE-496F-A335-0321C1189047}">
+    <text>stiriksi</text>
+  </threadedComment>
+  <threadedComment ref="C25" dT="2026-10-02T08:22:39.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{E74507EC-BC04-4A9B-B15C-32C7F44E6109}">
+    <text>Stiriksi</text>
+  </threadedComment>
+  <threadedComment ref="C42" dT="2026-09-25T14:55:37.89" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
     <text>indefferent</text>
   </threadedComment>
-  <threadedComment ref="E42" dT="2026-09-15T15:29:00.38" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{720F20F5-2744-4E03-9112-5151AF4ED353}">
+  <threadedComment ref="E43" dT="2026-09-15T15:29:00.38" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{720F20F5-2744-4E03-9112-5151AF4ED353}">
     <text>Indifferent, don't take book.</text>
   </threadedComment>
-  <threadedComment ref="C49" dT="2026-09-21T06:24:16.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
+  <threadedComment ref="C50" dT="2026-09-21T06:24:16.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
     <text xml:space="preserve">Little guy with glasses
 </text>
   </threadedComment>
@@ -2768,7 +2842,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0C9DD2-633E-44CA-9A93-86B2E2731C82}">
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="8.33203125" style="9" bestFit="1" customWidth="1"/>
@@ -3254,49 +3328,37 @@
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A26" s="9" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="B25" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A27" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F27" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H27" s="9" t="s">
         <v>298</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A27" s="9">
-        <v>9189004</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A28" s="9">
-        <v>5682904</v>
+        <v>9189004</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>143</v>
@@ -3313,13 +3375,13 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A29" s="9">
-        <v>9217204</v>
+        <v>5682904</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>143</v>
@@ -3327,18 +3389,22 @@
       <c r="E29" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="F29" s="22"/>
-      <c r="H29" s="22"/>
+      <c r="F29" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A30" s="9">
-        <v>7319504</v>
+        <v>9217204</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>49</v>
+        <v>147</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>143</v>
@@ -3346,22 +3412,18 @@
       <c r="E30" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="F30" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>173</v>
-      </c>
+      <c r="F30" s="22"/>
+      <c r="H30" s="22"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A31" s="9">
-        <v>9254304</v>
+        <v>7319504</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>143</v>
@@ -3378,13 +3440,13 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A32" s="9">
-        <v>2428404</v>
+        <v>9254304</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>143</v>
@@ -3401,13 +3463,13 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A33" s="9">
-        <v>2427904</v>
+        <v>2428404</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>151</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>143</v>
@@ -3424,13 +3486,13 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A34" s="9">
-        <v>8373704</v>
+        <v>2427904</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>151</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>143</v>
@@ -3447,13 +3509,13 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A35" s="9">
-        <v>5155004</v>
+        <v>8373704</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>143</v>
@@ -3470,13 +3532,13 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A36" s="9">
-        <v>1006390</v>
+        <v>5155004</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>47</v>
+        <v>156</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>143</v>
@@ -3491,54 +3553,51 @@
         <v>173</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="H38" s="9" t="s">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A37" s="9">
+        <v>1006390</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="H39" s="9" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A39" s="9" t="s">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A40" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="H40" s="9" t="s">
         <v>294</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A40" s="9">
-        <v>5324204</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="G40" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H40" s="12" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A41" s="9">
-        <v>5996604</v>
+        <v>5324204</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>159</v>
@@ -3550,7 +3609,7 @@
         <v>173</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>236</v>
+        <v>173</v>
       </c>
       <c r="H41" s="12" t="s">
         <v>173</v>
@@ -3558,65 +3617,65 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A42" s="9">
-        <v>7153704</v>
+        <v>5996604</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E42" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G42" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="F42" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H42" s="24" t="s">
-        <v>236</v>
+      <c r="H42" s="12" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A43" s="9">
-        <v>9185204</v>
+        <v>7153704</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="G43" s="25" t="s">
-        <v>271</v>
-      </c>
-      <c r="H43" s="12" t="s">
-        <v>173</v>
+      <c r="G43" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H43" s="24" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A44" s="9">
-        <v>9185504</v>
+        <v>9185204</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>159</v>
@@ -3627,8 +3686,8 @@
       <c r="F44" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="G44" s="12" t="s">
-        <v>173</v>
+      <c r="G44" s="25" t="s">
+        <v>271</v>
       </c>
       <c r="H44" s="12" t="s">
         <v>173</v>
@@ -3636,13 +3695,13 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A45" s="9">
-        <v>4913604</v>
+        <v>9185504</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>159</v>
@@ -3650,11 +3709,11 @@
       <c r="E45" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="F45" s="28" t="s">
-        <v>267</v>
-      </c>
-      <c r="G45" s="28" t="s">
-        <v>267</v>
+      <c r="F45" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>173</v>
       </c>
       <c r="H45" s="12" t="s">
         <v>173</v>
@@ -3662,13 +3721,13 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A46" s="9">
-        <v>5436204</v>
+        <v>4913604</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>159</v>
@@ -3676,11 +3735,11 @@
       <c r="E46" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="F46" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>173</v>
+      <c r="F46" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="G46" s="28" t="s">
+        <v>267</v>
       </c>
       <c r="H46" s="12" t="s">
         <v>173</v>
@@ -3688,13 +3747,13 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A47" s="9">
-        <v>3506004</v>
+        <v>5436204</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>50</v>
+        <v>167</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>159</v>
@@ -3714,13 +3773,13 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A48" s="9">
-        <v>6757304</v>
+        <v>3506004</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>159</v>
@@ -3740,13 +3799,13 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A49" s="9">
-        <v>6390804</v>
+        <v>6757304</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>159</v>
@@ -3764,55 +3823,81 @@
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A53" s="22"/>
-      <c r="B53" s="12" t="s">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A50" s="9">
+        <v>6390804</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A54" s="22"/>
+      <c r="B54" s="12" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A54" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="B54" s="12" t="s">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A55" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B55" s="12" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A55" s="28" t="s">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A56" s="28" t="s">
         <v>267</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B56" s="12" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A56" s="31"/>
-      <c r="B56" s="12" t="s">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A57" s="31"/>
+      <c r="B57" s="12" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A57" s="24" t="s">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A58" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B58" s="12" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A58" s="25" t="s">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A59" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B59" s="12" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A59" s="26" t="s">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A60" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B60" s="12" t="s">
         <v>273</v>
       </c>
     </row>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="955" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23C6E4E2-E928-438E-8F3B-C429CEF3B3C2}"/>
+  <xr:revisionPtr revIDLastSave="981" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A04AEDA1-44F5-4A09-9AE7-C512CD357FB6}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -584,7 +584,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="306">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1474,9 +1474,6 @@
     <t>no participation</t>
   </si>
   <si>
-    <t>ask Jouliana for keyboard</t>
-  </si>
-  <si>
     <t>hw. Ask9, p13</t>
   </si>
   <si>
@@ -1490,13 +1487,28 @@
   </si>
   <si>
     <t>A2</t>
+  </si>
+  <si>
+    <t>A5.2 Μ1 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου</t>
+  </si>
+  <si>
+    <t>A5.2 Μ2 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου</t>
+  </si>
+  <si>
+    <t>A5.2 Μ3 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου</t>
+  </si>
+  <si>
+    <t>B41M8 - Επεξεργασία αριθμητικών δεδομένων και αναφορές κελιών</t>
+  </si>
+  <si>
+    <t>B41M9 - Εισαγωγή στις Συναρτήσεις</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1542,12 +1554,6 @@
       <family val="2"/>
       <charset val="161"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="14">
@@ -2280,10 +2286,9 @@
     <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="41.9296875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="42.19921875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="33" style="1" customWidth="1"/>
-    <col min="11" max="11" width="46.06640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.53125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="34.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="58.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="43.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="34.19921875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="34.19921875" style="1" customWidth="1"/>
     <col min="17" max="17" width="21.53125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="16384" width="9.06640625" style="1"/>
@@ -2364,6 +2369,12 @@
       <c r="I4" s="19" t="s">
         <v>255</v>
       </c>
+      <c r="J4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
@@ -2425,8 +2436,20 @@
       <c r="H6" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="19" t="s">
         <v>259</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.45">
@@ -2454,8 +2477,14 @@
       <c r="H7" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="19" t="s">
         <v>258</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.45">
@@ -2513,6 +2542,12 @@
       <c r="I13" s="19" t="s">
         <v>264</v>
       </c>
+      <c r="J13" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" s="5" t="s">
@@ -2539,8 +2574,14 @@
       <c r="H14" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="19" t="s">
         <v>263</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.45">
@@ -2570,6 +2611,12 @@
       </c>
       <c r="I15" s="19" t="s">
         <v>263</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.45">
@@ -2886,7 +2933,7 @@
         <v>121</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.5">
@@ -3121,10 +3168,10 @@
         <v>283</v>
       </c>
       <c r="H15" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="I15" s="9" t="s">
         <v>297</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.5">
@@ -3330,13 +3377,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.5">
       <c r="B25" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="D25" s="9" t="s">
         <v>300</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.5">
@@ -3347,7 +3394,7 @@
         <v>294</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.5">
@@ -3461,7 +3508,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A33" s="9">
         <v>2428404</v>
       </c>
@@ -3484,7 +3531,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A34" s="9">
         <v>2427904</v>
       </c>
@@ -3507,7 +3554,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A35" s="9">
         <v>8373704</v>
       </c>
@@ -3530,7 +3577,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A36" s="9">
         <v>5155004</v>
       </c>
@@ -3553,7 +3600,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A37" s="9">
         <v>1006390</v>
       </c>
@@ -3576,12 +3623,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="H39" s="9" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A40" s="9" t="s">
         <v>157</v>
       </c>
@@ -3589,7 +3631,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A41" s="9">
         <v>5324204</v>
       </c>
@@ -3614,8 +3656,11 @@
       <c r="H41" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I41" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A42" s="9">
         <v>5996604</v>
       </c>
@@ -3640,8 +3685,11 @@
       <c r="H42" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I42" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43" s="9">
         <v>7153704</v>
       </c>
@@ -3666,8 +3714,11 @@
       <c r="H43" s="24" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I43" s="24" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44" s="9">
         <v>9185204</v>
       </c>
@@ -3692,8 +3743,11 @@
       <c r="H44" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I44" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A45" s="9">
         <v>9185504</v>
       </c>
@@ -3718,8 +3772,11 @@
       <c r="H45" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I45" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A46" s="9">
         <v>4913604</v>
       </c>
@@ -3744,8 +3801,11 @@
       <c r="H46" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I46" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A47" s="9">
         <v>5436204</v>
       </c>
@@ -3770,8 +3830,11 @@
       <c r="H47" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I47" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48" s="9">
         <v>3506004</v>
       </c>
@@ -3796,8 +3859,11 @@
       <c r="H48" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I48" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49" s="9">
         <v>6757304</v>
       </c>
@@ -3822,8 +3888,11 @@
       <c r="H49" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I49" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" s="9">
         <v>6390804</v>
       </c>
@@ -3848,14 +3917,17 @@
       <c r="H50" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I50" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54" s="22"/>
       <c r="B54" s="12" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" s="27" t="s">
         <v>173</v>
       </c>
@@ -3863,7 +3935,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" s="28" t="s">
         <v>267</v>
       </c>
@@ -3871,13 +3943,13 @@
         <v>268</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" s="31"/>
       <c r="B57" s="12" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" s="24" t="s">
         <v>236</v>
       </c>
@@ -3885,7 +3957,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" s="25" t="s">
         <v>271</v>
       </c>
@@ -3893,7 +3965,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" s="26" t="s">
         <v>272</v>
       </c>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="981" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A04AEDA1-44F5-4A09-9AE7-C512CD357FB6}"/>
+  <xr:revisionPtr revIDLastSave="986" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BEAFA3B-6C61-48B1-A73B-2D55BE43B646}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <sheet name="A Lyceum" sheetId="4" r:id="rId5"/>
     <sheet name="anapliroseis" sheetId="7" r:id="rId6"/>
     <sheet name="Sheet1" sheetId="9" r:id="rId7"/>
-    <sheet name="Sheet1 (2)" sheetId="10" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1763,13 +1762,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2296,34 +2295,34 @@
   <sheetData>
     <row r="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="34" t="s">
+      <c r="C1" s="34"/>
+      <c r="D1" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="34" t="s">
+      <c r="E1" s="34"/>
+      <c r="F1" s="33" t="s">
         <v>238</v>
       </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="34" t="s">
+      <c r="G1" s="34"/>
+      <c r="H1" s="33" t="s">
         <v>244</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="34" t="s">
+      <c r="I1" s="34"/>
+      <c r="J1" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="34" t="s">
+      <c r="K1" s="34"/>
+      <c r="L1" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="M1" s="35"/>
-      <c r="N1" s="34" t="s">
+      <c r="M1" s="34"/>
+      <c r="N1" s="33" t="s">
         <v>253</v>
       </c>
-      <c r="O1" s="35"/>
+      <c r="O1" s="34"/>
     </row>
     <row r="2" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -2919,14 +2918,14 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33" t="s">
+      <c r="G2" s="35"/>
+      <c r="H2" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="I2" s="33"/>
+      <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A3" s="9" t="s">
@@ -4011,14 +4010,14 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33" t="s">
+      <c r="G2" s="35"/>
+      <c r="H2" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="I2" s="33"/>
+      <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A3" s="9" t="s">
@@ -4796,14 +4795,14 @@
       <c r="D1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33" t="s">
+      <c r="F1" s="35"/>
+      <c r="G1" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="H1" s="33"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A3" s="9">
@@ -4938,14 +4937,14 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33" t="s">
+      <c r="H1" s="35"/>
+      <c r="I1" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="J1" s="33"/>
+      <c r="J1" s="35"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
@@ -5946,18 +5945,22 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C172699-9C2F-4E67-A102-81BDA8494E34}">
-  <dimension ref="A1"/>
+  <dimension ref="G22:I22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{679D73DD-8522-407F-98CA-C4EDF40265F0}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="22" spans="7:9" x14ac:dyDescent="0.45">
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
+        <f>$G$22+H22</f>
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="986" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BEAFA3B-6C61-48B1-A73B-2D55BE43B646}"/>
+  <xr:revisionPtr revIDLastSave="992" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B795CAE-5674-44F9-9CD4-011A9E8A2FC9}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -583,7 +583,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="307">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1501,6 +1501,9 @@
   </si>
   <si>
     <t>B41M9 - Εισαγωγή στις Συναρτήσεις</t>
+  </si>
+  <si>
+    <t>5-9/10/2026</t>
   </si>
 </sst>
 </file>
@@ -1762,13 +1765,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2295,34 +2298,34 @@
   <sheetData>
     <row r="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="7"/>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="33" t="s">
+      <c r="C1" s="35"/>
+      <c r="D1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="34"/>
-      <c r="F1" s="33" t="s">
+      <c r="E1" s="35"/>
+      <c r="F1" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="G1" s="34"/>
-      <c r="H1" s="33" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>244</v>
       </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="33" t="s">
+      <c r="I1" s="35"/>
+      <c r="J1" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="K1" s="34"/>
-      <c r="L1" s="33" t="s">
+      <c r="K1" s="35"/>
+      <c r="L1" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="M1" s="34"/>
-      <c r="N1" s="33" t="s">
+      <c r="M1" s="35"/>
+      <c r="N1" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="O1" s="34"/>
+      <c r="O1" s="35"/>
     </row>
     <row r="2" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -2888,7 +2891,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0C9DD2-633E-44CA-9A93-86B2E2731C82}">
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:P60"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="8.33203125" style="9" bestFit="1" customWidth="1"/>
@@ -2903,7 +2906,7 @@
     <col min="10" max="16384" width="9.06640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="13" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="13" t="s">
         <v>57</v>
       </c>
@@ -2917,17 +2920,21 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="F2" s="35" t="s">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.5">
+      <c r="F2" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="I2" s="35"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="I2" s="33"/>
+      <c r="J2" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="K2" s="33"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A3" s="9" t="s">
         <v>121</v>
       </c>
@@ -2935,7 +2942,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A4" s="9">
         <v>9285104</v>
       </c>
@@ -2954,7 +2961,7 @@
       <c r="H4" s="22"/>
       <c r="I4" s="22"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A5" s="9">
         <v>8324104</v>
       </c>
@@ -2977,7 +2984,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A6" s="9">
         <v>6811804</v>
       </c>
@@ -2999,8 +3006,11 @@
       <c r="I6" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="P6" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A7" s="9">
         <v>5436904</v>
       </c>
@@ -3022,8 +3032,11 @@
       <c r="I7" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="P7" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A8" s="9">
         <v>7025704</v>
       </c>
@@ -3045,8 +3058,11 @@
       <c r="I8" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="P8" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A9" s="9">
         <v>8435804</v>
       </c>
@@ -3068,8 +3084,11 @@
       <c r="I9" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="P9" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A10" s="9">
         <v>5069104</v>
       </c>
@@ -3091,8 +3110,11 @@
       <c r="I10" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="P10" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A11" s="9">
         <v>5222304</v>
       </c>
@@ -3114,8 +3136,11 @@
       <c r="I11" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="P11" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A12" s="9">
         <v>1981204</v>
       </c>
@@ -3137,8 +3162,11 @@
       <c r="I12" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="P12" s="9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A13" s="9">
         <v>3766704</v>
       </c>
@@ -3158,8 +3186,16 @@
       <c r="I13" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="P13" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.5">
+      <c r="P14" s="9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A15" s="9" t="s">
         <v>72</v>
       </c>
@@ -3172,8 +3208,11 @@
       <c r="I15" s="9" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="P15" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A16" s="9">
         <v>5551204</v>
       </c>
@@ -3195,8 +3234,11 @@
       <c r="H16" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P16" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A17" s="9">
         <v>2056004</v>
       </c>
@@ -3216,8 +3258,11 @@
         <v>173</v>
       </c>
       <c r="H17" s="22"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P17" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A18" s="9">
         <v>3318504</v>
       </c>
@@ -3239,8 +3284,11 @@
       <c r="H18" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P18" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A19" s="9">
         <v>4926804</v>
       </c>
@@ -3262,8 +3310,11 @@
       <c r="H19" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P19" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A20" s="9">
         <v>7568204</v>
       </c>
@@ -3283,8 +3334,11 @@
         <v>173</v>
       </c>
       <c r="H20" s="22"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P20" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A21" s="9">
         <v>5111404</v>
       </c>
@@ -3304,8 +3358,11 @@
         <v>173</v>
       </c>
       <c r="H21" s="22"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P21" s="9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A22" s="9">
         <v>4332504</v>
       </c>
@@ -3327,8 +3384,11 @@
       <c r="H22" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P22" s="9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A23" s="9">
         <v>4424904</v>
       </c>
@@ -3350,8 +3410,11 @@
       <c r="H23" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P23" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A24" s="9">
         <v>4934404</v>
       </c>
@@ -3373,8 +3436,11 @@
       <c r="H24" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P24" s="9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.5">
       <c r="B25" s="9" t="s">
         <v>298</v>
       </c>
@@ -3384,8 +3450,16 @@
       <c r="D25" s="9" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P25" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.5">
+      <c r="P26" s="9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A27" s="9" t="s">
         <v>140</v>
       </c>
@@ -3395,8 +3469,11 @@
       <c r="H27" s="9" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P27" s="9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A28" s="9">
         <v>9189004</v>
       </c>
@@ -3418,8 +3495,11 @@
       <c r="H28" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P28" s="9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A29" s="9">
         <v>5682904</v>
       </c>
@@ -3441,8 +3521,11 @@
       <c r="H29" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P29" s="9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A30" s="9">
         <v>9217204</v>
       </c>
@@ -3460,8 +3543,11 @@
       </c>
       <c r="F30" s="22"/>
       <c r="H30" s="22"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P30" s="9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A31" s="9">
         <v>7319504</v>
       </c>
@@ -3483,8 +3569,11 @@
       <c r="H31" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="P31" s="9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A32" s="9">
         <v>9254304</v>
       </c>
@@ -3506,8 +3595,11 @@
       <c r="H32" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="P32" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A33" s="9">
         <v>2428404</v>
       </c>
@@ -3529,8 +3621,11 @@
       <c r="H33" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="P33" s="9">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A34" s="9">
         <v>2427904</v>
       </c>
@@ -3553,7 +3648,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A35" s="9">
         <v>8373704</v>
       </c>
@@ -3576,7 +3671,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A36" s="9">
         <v>5155004</v>
       </c>
@@ -3599,7 +3694,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A37" s="9">
         <v>1006390</v>
       </c>
@@ -3622,7 +3717,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A40" s="9" t="s">
         <v>157</v>
       </c>
@@ -3630,7 +3725,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A41" s="9">
         <v>5324204</v>
       </c>
@@ -3659,7 +3754,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A42" s="9">
         <v>5996604</v>
       </c>
@@ -3688,7 +3783,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A43" s="9">
         <v>7153704</v>
       </c>
@@ -3717,7 +3812,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A44" s="9">
         <v>9185204</v>
       </c>
@@ -3746,7 +3841,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A45" s="9">
         <v>9185504</v>
       </c>
@@ -3775,7 +3870,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A46" s="9">
         <v>4913604</v>
       </c>
@@ -3804,7 +3899,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A47" s="9">
         <v>5436204</v>
       </c>
@@ -3833,7 +3928,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A48" s="9">
         <v>3506004</v>
       </c>
@@ -3973,9 +4068,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4010,14 +4106,14 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="I2" s="35"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A3" s="9" t="s">
@@ -4795,14 +4891,14 @@
       <c r="D1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35" t="s">
+      <c r="F1" s="33"/>
+      <c r="G1" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A3" s="9">
@@ -4937,14 +5033,14 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35" t="s">
+      <c r="H1" s="33"/>
+      <c r="I1" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="J1" s="35"/>
+      <c r="J1" s="33"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="992" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B795CAE-5674-44F9-9CD4-011A9E8A2FC9}"/>
+  <xr:revisionPtr revIDLastSave="1060" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82A7610A-D711-4B46-9C7C-DD3E4A14C406}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -87,8 +87,22 @@
     <author>tc={AD4C8F15-E890-4B85-B1C2-93D5114E713A}</author>
     <author>tc={8F76B8B8-18EE-496F-A335-0321C1189047}</author>
     <author>tc={E74507EC-BC04-4A9B-B15C-32C7F44E6109}</author>
+    <author>tc={0E374CA0-3C13-436D-9FAC-14F6B920C675}</author>
+    <author>tc={0E1BF347-0EA3-4549-B042-BCD495D8C495}</author>
+    <author>tc={77742E87-EB5D-4747-811D-D6052514F58A}</author>
+    <author>tc={221FDEED-1145-48B8-93A0-518076128BE1}</author>
+    <author>tc={06E68A77-02D9-459A-AE13-BD4D2460CF82}</author>
+    <author>tc={B3A23F0F-0E01-41A2-8966-76A587BA515C}</author>
+    <author>tc={AA3BDBA2-8267-4A69-A689-551224F645D9}</author>
+    <author>tc={FCE8BE01-CFDB-4E54-9051-44ADC799EE83}</author>
+    <author>tc={98BD6B5F-37EB-41FA-B971-80255C43C024}</author>
+    <author>tc={3FB9C602-3AA9-40D1-97B5-331230499AE8}</author>
     <author>tc={009D741D-5339-4620-BEF3-C76ECC0C19D0}</author>
+    <author>tc={86B9678A-C29A-446D-AACA-74A7C503B71B}</author>
     <author>tc={720F20F5-2744-4E03-9112-5151AF4ED353}</author>
+    <author>tc={7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}</author>
+    <author>tc={8F4D57B3-2C90-4744-BFEF-99E499E55142}</author>
+    <author>tc={37F71BFC-AE14-49EC-B2B2-49697A83F48F}</author>
     <author>tc={2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}</author>
   </authors>
   <commentList>
@@ -222,29 +236,143 @@
     Stiriksi</t>
       </text>
     </comment>
-    <comment ref="C42" authorId="15" shapeId="0" xr:uid="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
+    <comment ref="C28" authorId="15" shapeId="0" xr:uid="{0E374CA0-3C13-436D-9FAC-14F6B920C675}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
+    Roumania, diskolies sta ellinika</t>
+      </text>
+    </comment>
+    <comment ref="C29" authorId="16" shapeId="0" xr:uid="{0E1BF347-0EA3-4549-B042-BCD495D8C495}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Xorismenoi goneis</t>
+      </text>
+    </comment>
+    <comment ref="C30" authorId="17" shapeId="0" xr:uid="{77742E87-EB5D-4747-811D-D6052514F58A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Skaki, mathimatika olympiades</t>
+      </text>
+    </comment>
+    <comment ref="C31" authorId="18" shapeId="0" xr:uid="{221FDEED-1145-48B8-93A0-518076128BE1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Sitisi, papapona gia bullying sto dimotiko</t>
+      </text>
+    </comment>
+    <comment ref="C32" authorId="19" shapeId="0" xr:uid="{06E68A77-02D9-459A-AE13-BD4D2460CF82}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Sitisi, stiriksi
+</t>
+      </text>
+    </comment>
+    <comment ref="C33" authorId="20" shapeId="0" xr:uid="{B3A23F0F-0E01-41A2-8966-76A587BA515C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Didimoi me Kimona</t>
+      </text>
+    </comment>
+    <comment ref="C34" authorId="21" shapeId="0" xr:uid="{AA3BDBA2-8267-4A69-A689-551224F645D9}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Ypermetropia, astigmatismos</t>
+      </text>
+    </comment>
+    <comment ref="C36" authorId="22" shapeId="0" xr:uid="{FCE8BE01-CFDB-4E54-9051-44ADC799EE83}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Sitisi, orfanos apo patera sti Syria</t>
+      </text>
+    </comment>
+    <comment ref="C37" authorId="23" shapeId="0" xr:uid="{98BD6B5F-37EB-41FA-B971-80255C43C024}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Spazei sixna h miti tis</t>
+      </text>
+    </comment>
+    <comment ref="C41" authorId="24" shapeId="0" xr:uid="{3FB9C602-3AA9-40D1-97B5-331230499AE8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Xorismeni, apoklisitiki h mitera</t>
+      </text>
+    </comment>
+    <comment ref="C42" authorId="25" shapeId="0" xr:uid="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     indefferent</t>
       </text>
     </comment>
-    <comment ref="E43" authorId="16" shapeId="0" xr:uid="{720F20F5-2744-4E03-9112-5151AF4ED353}">
+    <comment ref="C43" authorId="26" shapeId="0" xr:uid="{86B9678A-C29A-446D-AACA-74A7C503B71B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
+    Depy, sitisi, sinesthimatikes diskolies</t>
+      </text>
+    </comment>
+    <comment ref="E43" authorId="27" shapeId="0" xr:uid="{720F20F5-2744-4E03-9112-5151AF4ED353}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Indifferent, don't take book.</t>
       </text>
     </comment>
-    <comment ref="C50" authorId="17" shapeId="0" xr:uid="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
+    <comment ref="C44" authorId="28" shapeId="0" xr:uid="{7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Stiriksi, sitisi, menei me patera, oxi epaphi me mitera, o pateras fetos irthe, emenas me giagia kai pappou</t>
+      </text>
+    </comment>
+    <comment ref="C48" authorId="29" shapeId="0" xr:uid="{8F4D57B3-2C90-4744-BFEF-99E499E55142}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Dropalos, thelei enisxisi</t>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="30" shapeId="0" xr:uid="{37F71BFC-AE14-49EC-B2B2-49697A83F48F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Stiriksi, mathisiakes adinamies</t>
+      </text>
+    </comment>
+    <comment ref="C50" authorId="31" shapeId="0" xr:uid="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
+      <text>
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Little guy with glasses
-</t>
+Reply:
+    alpabitismos</t>
       </text>
     </comment>
   </commentList>
@@ -260,7 +388,10 @@
     <author>tc={D061CE57-8AF4-47A9-90BD-BA76DE8360E4}</author>
     <author>tc={323A21AB-C8B1-49E9-B0D2-C3EDEE435FC5}</author>
     <author>tc={51EF4A43-CB2C-4BF9-A554-78A9E1EF56AC}</author>
+    <author>tc={7067F77C-035C-496C-86AB-3C2E5C6DF949}</author>
+    <author>tc={DCAFAF19-D942-4ACA-9758-79DA09558F55}</author>
     <author>tc={63E1D257-C3B7-435A-A4B3-4F6EA6F7AC25}</author>
+    <author>tc={DDB96904-162D-419D-BF36-AC7C7955C53E}</author>
     <author>tc={08EEC001-3001-4E58-A957-556D8883327A}</author>
     <author>tc={8AC19454-30E3-45D9-9597-E3A2E37CFF9A}</author>
     <author>tc={CA6B0F40-6EF4-4274-8867-21553D999551}</author>
@@ -324,23 +455,47 @@
     Pateras sto eksoteriko</t>
       </text>
     </comment>
-    <comment ref="C19" authorId="6" shapeId="0" xr:uid="{63E1D257-C3B7-435A-A4B3-4F6EA6F7AC25}">
+    <comment ref="J17" authorId="6" shapeId="0" xr:uid="{7067F77C-035C-496C-86AB-3C2E5C6DF949}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
+    kataggelia</t>
+      </text>
+    </comment>
+    <comment ref="J18" authorId="7" shapeId="0" xr:uid="{DCAFAF19-D942-4ACA-9758-79DA09558F55}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    kataggelia</t>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="8" shapeId="0" xr:uid="{63E1D257-C3B7-435A-A4B3-4F6EA6F7AC25}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Me mitera, oxi epaphi me patera.</t>
       </text>
     </comment>
-    <comment ref="C20" authorId="7" shapeId="0" xr:uid="{08EEC001-3001-4E58-A957-556D8883327A}">
+    <comment ref="J19" authorId="9" shapeId="0" xr:uid="{DDB96904-162D-419D-BF36-AC7C7955C53E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
+    kataggelia</t>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="10" shapeId="0" xr:uid="{08EEC001-3001-4E58-A957-556D8883327A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Mono me mitera</t>
       </text>
     </comment>
-    <comment ref="C24" authorId="8" shapeId="0" xr:uid="{8AC19454-30E3-45D9-9597-E3A2E37CFF9A}">
+    <comment ref="C24" authorId="11" shapeId="0" xr:uid="{8AC19454-30E3-45D9-9597-E3A2E37CFF9A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -348,7 +503,7 @@
     Aporos, sitisis</t>
       </text>
     </comment>
-    <comment ref="C28" authorId="9" shapeId="0" xr:uid="{CA6B0F40-6EF4-4274-8867-21553D999551}">
+    <comment ref="C28" authorId="12" shapeId="0" xr:uid="{CA6B0F40-6EF4-4274-8867-21553D999551}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -356,7 +511,7 @@
     Ntrepete, xamilon tonon</t>
       </text>
     </comment>
-    <comment ref="C31" authorId="10" shapeId="0" xr:uid="{E674068C-9812-42A2-9151-17837D13ABB6}">
+    <comment ref="C31" authorId="13" shapeId="0" xr:uid="{E674068C-9812-42A2-9151-17837D13ABB6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -364,7 +519,7 @@
     Isixi, thelei entharinsi</t>
       </text>
     </comment>
-    <comment ref="C32" authorId="11" shapeId="0" xr:uid="{ED249525-191C-4637-9D99-E242BDB6421A}">
+    <comment ref="C32" authorId="14" shapeId="0" xr:uid="{ED249525-191C-4637-9D99-E242BDB6421A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -372,7 +527,7 @@
     Xasimoto, pernei thiroksini</t>
       </text>
     </comment>
-    <comment ref="C34" authorId="12" shapeId="0" xr:uid="{B304C0F3-0817-4A4E-853F-5F45E9E32DFD}">
+    <comment ref="C34" authorId="15" shapeId="0" xr:uid="{B304C0F3-0817-4A4E-853F-5F45E9E32DFD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -380,7 +535,7 @@
     Mila arketa, kinito, oriothetisi</t>
       </text>
     </comment>
-    <comment ref="I34" authorId="13" shapeId="0" xr:uid="{DF19662E-D699-40A7-996A-7901BA4875E9}">
+    <comment ref="I34" authorId="16" shapeId="0" xr:uid="{DF19662E-D699-40A7-996A-7901BA4875E9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -388,7 +543,7 @@
     kataggelia</t>
       </text>
     </comment>
-    <comment ref="C35" authorId="14" shapeId="0" xr:uid="{1C68C472-CF02-4D39-A15B-ACD03122D4F0}">
+    <comment ref="C35" authorId="17" shapeId="0" xr:uid="{1C68C472-CF02-4D39-A15B-ACD03122D4F0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -398,7 +553,7 @@
     Miazei tis Melias</t>
       </text>
     </comment>
-    <comment ref="C36" authorId="15" shapeId="0" xr:uid="{2330157A-B3C2-4789-96E1-9C8D2D80D7FE}">
+    <comment ref="C36" authorId="18" shapeId="0" xr:uid="{2330157A-B3C2-4789-96E1-9C8D2D80D7FE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -406,7 +561,7 @@
     zoiros</t>
       </text>
     </comment>
-    <comment ref="C37" authorId="16" shapeId="0" xr:uid="{831B6259-37A3-4907-AE80-39991BDC7649}">
+    <comment ref="C37" authorId="19" shapeId="0" xr:uid="{831B6259-37A3-4907-AE80-39991BDC7649}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -583,7 +738,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="309">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1504,13 +1659,19 @@
   </si>
   <si>
     <t>5-9/10/2026</t>
+  </si>
+  <si>
+    <t>REVISION</t>
+  </si>
+  <si>
+    <t>5-9/10 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1556,6 +1717,12 @@
       <family val="2"/>
       <charset val="161"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="14">
@@ -2132,15 +2299,61 @@
   <threadedComment ref="C25" dT="2026-10-02T08:22:39.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{E74507EC-BC04-4A9B-B15C-32C7F44E6109}">
     <text>Stiriksi</text>
   </threadedComment>
+  <threadedComment ref="C28" dT="2026-10-05T07:13:32.27" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{0E374CA0-3C13-436D-9FAC-14F6B920C675}">
+    <text>Roumania, diskolies sta ellinika</text>
+  </threadedComment>
+  <threadedComment ref="C29" dT="2026-10-05T07:13:44.64" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{0E1BF347-0EA3-4549-B042-BCD495D8C495}">
+    <text>Xorismenoi goneis</text>
+  </threadedComment>
+  <threadedComment ref="C30" dT="2026-10-05T07:14:01.31" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{77742E87-EB5D-4747-811D-D6052514F58A}">
+    <text>Skaki, mathimatika olympiades</text>
+  </threadedComment>
+  <threadedComment ref="C31" dT="2026-10-05T07:14:18.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{221FDEED-1145-48B8-93A0-518076128BE1}">
+    <text>Sitisi, papapona gia bullying sto dimotiko</text>
+  </threadedComment>
+  <threadedComment ref="C32" dT="2026-10-05T07:14:34.50" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{06E68A77-02D9-459A-AE13-BD4D2460CF82}">
+    <text xml:space="preserve">Sitisi, stiriksi
+</text>
+  </threadedComment>
+  <threadedComment ref="C33" dT="2026-10-05T07:14:51.75" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B3A23F0F-0E01-41A2-8966-76A587BA515C}">
+    <text>Didimoi me Kimona</text>
+  </threadedComment>
+  <threadedComment ref="C34" dT="2026-10-05T07:15:08.05" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AA3BDBA2-8267-4A69-A689-551224F645D9}">
+    <text>Ypermetropia, astigmatismos</text>
+  </threadedComment>
+  <threadedComment ref="C36" dT="2026-10-05T07:15:27.54" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{FCE8BE01-CFDB-4E54-9051-44ADC799EE83}">
+    <text>Sitisi, orfanos apo patera sti Syria</text>
+  </threadedComment>
+  <threadedComment ref="C37" dT="2026-10-05T07:15:40.47" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{98BD6B5F-37EB-41FA-B971-80255C43C024}">
+    <text>Spazei sixna h miti tis</text>
+  </threadedComment>
+  <threadedComment ref="C41" dT="2026-10-05T09:04:32.37" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3FB9C602-3AA9-40D1-97B5-331230499AE8}">
+    <text>Xorismeni, apoklisitiki h mitera</text>
+  </threadedComment>
   <threadedComment ref="C42" dT="2026-09-25T14:55:37.89" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
     <text>indefferent</text>
   </threadedComment>
+  <threadedComment ref="C43" dT="2026-10-05T09:04:58.84" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{86B9678A-C29A-446D-AACA-74A7C503B71B}">
+    <text>Depy, sitisi, sinesthimatikes diskolies</text>
+  </threadedComment>
   <threadedComment ref="E43" dT="2026-09-15T15:29:00.38" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{720F20F5-2744-4E03-9112-5151AF4ED353}">
     <text>Indifferent, don't take book.</text>
+  </threadedComment>
+  <threadedComment ref="C44" dT="2026-10-05T09:05:48.06" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}">
+    <text>Stiriksi, sitisi, menei me patera, oxi epaphi me mitera, o pateras fetos irthe, emenas me giagia kai pappou</text>
+  </threadedComment>
+  <threadedComment ref="C48" dT="2026-10-05T09:06:03.45" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{8F4D57B3-2C90-4744-BFEF-99E499E55142}">
+    <text>Dropalos, thelei enisxisi</text>
+  </threadedComment>
+  <threadedComment ref="C49" dT="2026-10-05T09:06:27.63" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{37F71BFC-AE14-49EC-B2B2-49697A83F48F}">
+    <text>Stiriksi, mathisiakes adinamies</text>
   </threadedComment>
   <threadedComment ref="C50" dT="2026-09-21T06:24:16.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
     <text xml:space="preserve">Little guy with glasses
 </text>
+  </threadedComment>
+  <threadedComment ref="C50" dT="2026-10-05T09:06:44.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{98AF0D30-4238-4DB6-AEB6-E46495700012}" parentId="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
+    <text>alpabitismos</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -2169,8 +2382,17 @@
   <threadedComment ref="C17" dT="2026-09-23T07:03:34.08" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{9D3CB741-6499-491E-8D1E-B393FE999F93}" parentId="{51EF4A43-CB2C-4BF9-A554-78A9E1EF56AC}">
     <text>Pateras sto eksoteriko</text>
   </threadedComment>
+  <threadedComment ref="J17" dT="2026-10-05T17:19:37.59" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7067F77C-035C-496C-86AB-3C2E5C6DF949}">
+    <text>kataggelia</text>
+  </threadedComment>
+  <threadedComment ref="J18" dT="2026-10-05T17:19:47.12" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{DCAFAF19-D942-4ACA-9758-79DA09558F55}">
+    <text>kataggelia</text>
+  </threadedComment>
   <threadedComment ref="C19" dT="2026-09-23T07:03:19.98" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{63E1D257-C3B7-435A-A4B3-4F6EA6F7AC25}">
     <text>Me mitera, oxi epaphi me patera.</text>
+  </threadedComment>
+  <threadedComment ref="J19" dT="2026-10-05T17:19:58.07" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{DDB96904-162D-419D-BF36-AC7C7955C53E}">
+    <text>kataggelia</text>
   </threadedComment>
   <threadedComment ref="C20" dT="2026-09-23T07:05:00.47" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{08EEC001-3001-4E58-A957-556D8883327A}">
     <text>Mono me mitera</text>
@@ -2278,7 +2500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="5" bestFit="1" customWidth="1"/>
@@ -2371,7 +2593,7 @@
       <c r="I4" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="19" t="s">
         <v>259</v>
       </c>
       <c r="K4" s="1" t="s">
@@ -2482,7 +2704,7 @@
       <c r="I7" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="19" t="s">
         <v>255</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -2544,7 +2766,7 @@
       <c r="I13" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="19" t="s">
         <v>304</v>
       </c>
       <c r="K13" s="1" t="s">
@@ -2579,7 +2801,7 @@
       <c r="I14" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="19" t="s">
         <v>264</v>
       </c>
       <c r="K14" s="1" t="s">
@@ -2614,14 +2836,14 @@
       <c r="I15" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="19" t="s">
         <v>264</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
@@ -2632,12 +2854,12 @@
         <v>241</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
       <c r="H19" s="30" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A20" s="5" t="s">
         <v>14</v>
       </c>
@@ -2677,19 +2899,22 @@
       <c r="M20" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="N20" s="18" t="s">
+      <c r="N20" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="O20" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="P20" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="P20" s="4" t="s">
+      <c r="Q20" s="4" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A21" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>9</v>
@@ -2706,29 +2931,29 @@
       <c r="F21" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="G21" s="17" t="s">
-        <v>287</v>
+      <c r="G21" s="21" t="s">
+        <v>240</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I21" s="17" t="s">
         <v>291</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="O21" s="18" t="s">
         <v>254</v>
@@ -2740,9 +2965,9 @@
         <v>251</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A22" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>9</v>
@@ -2759,38 +2984,62 @@
       <c r="F22" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="G22" s="21" t="s">
+      <c r="G22" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="H22" s="19" t="s">
         <v>240</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>243</v>
       </c>
       <c r="I22" s="17" t="s">
         <v>291</v>
       </c>
       <c r="J22" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="K22" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="L22" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="M22" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="M22" s="4" t="s">
+      <c r="N22" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="N22" s="18" t="s">
+      <c r="O22" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="P22" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="Q22" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="P22" s="4" t="s">
+      <c r="R22" s="4" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="B23" s="2"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A24" s="5" t="s">
         <v>10</v>
       </c>
@@ -2811,27 +3060,27 @@
         <v>288</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.45">
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.45">
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.45">
       <c r="B27" s="11"/>
       <c r="C27" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.45">
       <c r="B28" s="3"/>
       <c r="C28" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.45">
       <c r="B29" s="4"/>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -2960,6 +3209,9 @@
       </c>
       <c r="H4" s="22"/>
       <c r="I4" s="22"/>
+      <c r="J4" s="24" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A5" s="9">
@@ -2983,6 +3235,9 @@
       <c r="I5" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J5" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A6" s="9">
@@ -3006,6 +3261,9 @@
       <c r="I6" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J6" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P6" s="9">
         <v>1</v>
       </c>
@@ -3032,6 +3290,9 @@
       <c r="I7" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J7" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P7" s="9">
         <v>2</v>
       </c>
@@ -3058,6 +3319,9 @@
       <c r="I8" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J8" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P8" s="9">
         <v>3</v>
       </c>
@@ -3084,6 +3348,9 @@
       <c r="I9" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J9" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P9" s="9">
         <v>4</v>
       </c>
@@ -3110,6 +3377,9 @@
       <c r="I10" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J10" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P10" s="9">
         <v>5</v>
       </c>
@@ -3136,6 +3406,9 @@
       <c r="I11" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J11" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P11" s="9">
         <v>6</v>
       </c>
@@ -3162,6 +3435,9 @@
       <c r="I12" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J12" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P12" s="9">
         <v>7</v>
       </c>
@@ -3184,6 +3460,9 @@
       </c>
       <c r="H13" s="31"/>
       <c r="I13" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J13" s="12" t="s">
         <v>173</v>
       </c>
       <c r="P13" s="9">
@@ -3753,6 +4032,9 @@
       <c r="I41" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J41" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A42" s="9">
@@ -3782,6 +4064,9 @@
       <c r="I42" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J42" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A43" s="9">
@@ -3811,6 +4096,9 @@
       <c r="I43" s="24" t="s">
         <v>236</v>
       </c>
+      <c r="J43" s="24" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A44" s="9">
@@ -3840,6 +4128,9 @@
       <c r="I44" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J44" s="24" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A45" s="9">
@@ -3869,6 +4160,9 @@
       <c r="I45" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J45" s="24" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A46" s="9">
@@ -3898,6 +4192,9 @@
       <c r="I46" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J46" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A47" s="9">
@@ -3927,6 +4224,9 @@
       <c r="I47" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J47" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A48" s="9">
@@ -3956,8 +4256,11 @@
       <c r="I48" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J48" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A49" s="9">
         <v>6757304</v>
       </c>
@@ -3985,8 +4288,11 @@
       <c r="I49" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J49" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A50" s="9">
         <v>6390804</v>
       </c>
@@ -4014,14 +4320,17 @@
       <c r="I50" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J50" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A54" s="22"/>
       <c r="B54" s="12" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A55" s="27" t="s">
         <v>173</v>
       </c>
@@ -4029,7 +4338,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A56" s="28" t="s">
         <v>267</v>
       </c>
@@ -4037,13 +4346,13 @@
         <v>268</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A57" s="31"/>
       <c r="B57" s="12" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A58" s="24" t="s">
         <v>236</v>
       </c>
@@ -4051,7 +4360,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A59" s="25" t="s">
         <v>271</v>
       </c>
@@ -4059,7 +4368,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A60" s="26" t="s">
         <v>272</v>
       </c>
@@ -4081,7 +4390,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A321353-3FB1-4427-84C3-E63782B65799}">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="8.33203125" style="9" bestFit="1" customWidth="1"/>
@@ -4091,7 +4400,7 @@
     <col min="5" max="16384" width="9.06640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="10" t="s">
         <v>57</v>
       </c>
@@ -4105,7 +4414,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
       <c r="F2" s="33" t="s">
         <v>292</v>
       </c>
@@ -4114,13 +4423,17 @@
         <v>293</v>
       </c>
       <c r="I2" s="33"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J2" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="K2" s="33"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A3" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A4" s="9">
         <v>1025518</v>
       </c>
@@ -4149,7 +4462,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A5" s="9">
         <v>4298104</v>
       </c>
@@ -4176,7 +4489,7 @@
       </c>
       <c r="I5" s="22"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A6" s="9">
         <v>1033606</v>
       </c>
@@ -4205,7 +4518,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A7" s="9">
         <v>1033506</v>
       </c>
@@ -4232,7 +4545,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A8" s="9">
         <v>1026254</v>
       </c>
@@ -4261,7 +4574,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A9" s="9">
         <v>1028366</v>
       </c>
@@ -4290,7 +4603,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A10" s="9">
         <v>1033023</v>
       </c>
@@ -4319,7 +4632,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A11" s="9">
         <v>1032554</v>
       </c>
@@ -4348,7 +4661,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A12" s="9">
         <v>1026281</v>
       </c>
@@ -4377,7 +4690,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A13" s="9">
         <v>1029057</v>
       </c>
@@ -4406,12 +4719,12 @@
         <v>173</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A15" s="9" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A16" s="9">
         <v>1035828</v>
       </c>
@@ -4430,8 +4743,11 @@
       <c r="H16" s="12" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J16" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A17" s="9">
         <v>1031619</v>
       </c>
@@ -4450,8 +4766,11 @@
       <c r="H17" s="12" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J17" s="26" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A18" s="9">
         <v>1037608</v>
       </c>
@@ -4470,8 +4789,11 @@
       <c r="H18" s="12" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J18" s="26" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A19" s="9">
         <v>1035515</v>
       </c>
@@ -4490,8 +4812,11 @@
       <c r="H19" s="12" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J19" s="26" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A20" s="9">
         <v>1030772</v>
       </c>
@@ -4510,8 +4835,11 @@
       <c r="H20" s="12" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J20" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A21" s="9">
         <v>1026742</v>
       </c>
@@ -4530,8 +4858,11 @@
       <c r="H21" s="12" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J21" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A22" s="9">
         <v>1038924</v>
       </c>
@@ -4550,8 +4881,11 @@
       <c r="H22" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J22" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A23" s="9">
         <v>1029508</v>
       </c>
@@ -4570,8 +4904,11 @@
       <c r="H23" s="12" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J23" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A24" s="9">
         <v>1028849</v>
       </c>
@@ -4590,13 +4927,16 @@
       <c r="H24" s="12" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J24" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A27" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A28" s="9">
         <v>1027008</v>
       </c>
@@ -4621,8 +4961,11 @@
       <c r="I28" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J28" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A29" s="9">
         <v>1026200</v>
       </c>
@@ -4647,8 +4990,11 @@
       <c r="I29" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J29" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A30" s="9">
         <v>1025833</v>
       </c>
@@ -4673,8 +5019,11 @@
       <c r="I30" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J30" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A31" s="9">
         <v>1036053</v>
       </c>
@@ -4699,8 +5048,11 @@
       <c r="I31" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J31" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A32" s="9">
         <v>1029029</v>
       </c>
@@ -4725,8 +5077,11 @@
       <c r="I32" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J32" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A33" s="9">
         <v>1028278</v>
       </c>
@@ -4751,8 +5106,11 @@
       <c r="I33" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J33" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A34" s="9">
         <v>1025603</v>
       </c>
@@ -4777,8 +5135,9 @@
       <c r="I34" s="12" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J34" s="22"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A35" s="9">
         <v>1028053</v>
       </c>
@@ -4803,8 +5162,11 @@
       <c r="I35" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J35" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A36" s="9">
         <v>1027036</v>
       </c>
@@ -4829,8 +5191,11 @@
       <c r="I36" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="J36" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A37" s="9">
         <v>1032361</v>
       </c>
@@ -4855,11 +5220,15 @@
       <c r="I37" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="J37" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4869,7 +5238,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82B87684-E387-4B51-9ECE-3C23F4BC9CBD}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="10.46484375" style="9" bestFit="1" customWidth="1"/>
@@ -4878,7 +5247,7 @@
     <col min="4" max="16384" width="9.06640625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A1" s="9" t="s">
         <v>57</v>
       </c>
@@ -4899,8 +5268,12 @@
         <v>293</v>
       </c>
       <c r="H1" s="33"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="I1" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="J1" s="33"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A3" s="9">
         <v>400002110</v>
       </c>
@@ -4920,7 +5293,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A4" s="9">
         <v>400002100</v>
       </c>
@@ -4940,7 +5313,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A5" s="9">
         <v>405136704</v>
       </c>
@@ -4960,7 +5333,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A6" s="9">
         <v>400002095</v>
       </c>
@@ -4980,7 +5353,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A7" s="9">
         <v>400002064</v>
       </c>
@@ -5001,9 +5374,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5011,7 +5385,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF640171-D19A-4A22-AEE9-A5E7AF0F79D2}">
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7.73046875" bestFit="1" customWidth="1"/>
@@ -5020,7 +5394,7 @@
     <col min="4" max="4" width="6.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -5041,13 +5415,17 @@
         <v>293</v>
       </c>
       <c r="J1" s="33"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K1" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="L1" s="33"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A4">
         <v>4206804</v>
       </c>
@@ -5075,8 +5453,11 @@
       <c r="I4" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J4" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A5">
         <v>9307104</v>
       </c>
@@ -5104,8 +5485,11 @@
       <c r="I5" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J5" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A6">
         <v>2173704</v>
       </c>
@@ -5133,8 +5517,11 @@
       <c r="I6" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J6" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A7">
         <v>9257304</v>
       </c>
@@ -5162,8 +5549,11 @@
       <c r="I7" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J7" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A8">
         <v>2915404</v>
       </c>
@@ -5191,8 +5581,11 @@
       <c r="I8" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J8" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A9">
         <v>2836604</v>
       </c>
@@ -5220,8 +5613,11 @@
       <c r="I9" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J9" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A10">
         <v>1274904</v>
       </c>
@@ -5249,8 +5645,11 @@
       <c r="I10" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J10" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A11">
         <v>3863304</v>
       </c>
@@ -5278,8 +5677,11 @@
       <c r="I11" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J11" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A12">
         <v>3403504</v>
       </c>
@@ -5307,8 +5709,11 @@
       <c r="I12" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J12" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A13">
         <v>4721304</v>
       </c>
@@ -5336,8 +5741,11 @@
       <c r="I13" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J13" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A14">
         <v>3924304</v>
       </c>
@@ -5365,8 +5773,11 @@
       <c r="I14" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J14" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A15">
         <v>4041704</v>
       </c>
@@ -5394,8 +5805,11 @@
       <c r="I15" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J15" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A16">
         <v>9280704</v>
       </c>
@@ -5423,8 +5837,11 @@
       <c r="I16" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J16" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="C17" t="s">
         <v>229</v>
       </c>
@@ -5446,8 +5863,11 @@
       <c r="I17" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J17" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B18" t="s">
         <v>230</v>
       </c>
@@ -5472,8 +5892,11 @@
       <c r="I18" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J18" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B19" t="s">
         <v>232</v>
       </c>
@@ -5498,13 +5921,16 @@
       <c r="I19" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J19" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -5518,7 +5944,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A23">
         <v>9693404</v>
       </c>
@@ -5546,8 +5972,11 @@
       <c r="I23" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J23" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A24">
         <v>222222</v>
       </c>
@@ -5575,8 +6004,11 @@
       <c r="I24" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J24" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A25">
         <v>9743804</v>
       </c>
@@ -5604,8 +6036,11 @@
       <c r="I25" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J25" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A26">
         <v>111111</v>
       </c>
@@ -5631,8 +6066,11 @@
         <v>287</v>
       </c>
       <c r="I26" s="31"/>
-    </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J26" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A27">
         <v>9662304</v>
       </c>
@@ -5660,8 +6098,11 @@
       <c r="I27" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J27" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B28" t="s">
         <v>277</v>
       </c>
@@ -5680,8 +6121,11 @@
         <v>287</v>
       </c>
       <c r="I28" s="31"/>
-    </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J28" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B29" t="s">
         <v>277</v>
       </c>
@@ -5700,13 +6144,16 @@
         <v>287</v>
       </c>
       <c r="I29" s="31"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J29" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A32">
         <v>3578804</v>
       </c>
@@ -5731,8 +6178,11 @@
       <c r="I32" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J32" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A33">
         <v>9289704</v>
       </c>
@@ -5755,8 +6205,11 @@
         <v>173</v>
       </c>
       <c r="I33" s="22"/>
-    </row>
-    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J33" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A34">
         <v>9344404</v>
       </c>
@@ -5779,8 +6232,11 @@
         <v>236</v>
       </c>
       <c r="I34" s="31"/>
-    </row>
-    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J34" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A35">
         <v>6746404</v>
       </c>
@@ -5803,8 +6259,11 @@
         <v>236</v>
       </c>
       <c r="I35" s="22"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J35" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A36">
         <v>9257604</v>
       </c>
@@ -5829,8 +6288,11 @@
       <c r="I36" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J36" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A37">
         <v>9717204</v>
       </c>
@@ -5853,8 +6315,11 @@
         <v>236</v>
       </c>
       <c r="I37" s="22"/>
-    </row>
-    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J37" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A38">
         <v>2298204</v>
       </c>
@@ -5877,8 +6342,11 @@
         <v>173</v>
       </c>
       <c r="I38" s="22"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J38" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A39">
         <v>5784804</v>
       </c>
@@ -5903,8 +6371,11 @@
       <c r="I39" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J39" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A40">
         <v>9321704</v>
       </c>
@@ -5929,8 +6400,11 @@
       <c r="I40" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J40" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A41">
         <v>9720304</v>
       </c>
@@ -5955,8 +6429,11 @@
       <c r="I41" s="28" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="J41" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A42">
         <v>9317404</v>
       </c>
@@ -5979,8 +6456,11 @@
         <v>173</v>
       </c>
       <c r="I42" s="22"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J42" s="29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A43">
         <v>8333604</v>
       </c>
@@ -6005,15 +6485,20 @@
       <c r="I43" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="J43" s="29" t="s">
+        <v>291</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1060" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82A7610A-D711-4B46-9C7C-DD3E4A14C406}"/>
+  <xr:revisionPtr revIDLastSave="1101" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AA3E364-8BCC-4412-A3C8-69C236C71117}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -503,7 +503,7 @@
     Aporos, sitisis</t>
       </text>
     </comment>
-    <comment ref="C28" authorId="12" shapeId="0" xr:uid="{CA6B0F40-6EF4-4274-8867-21553D999551}">
+    <comment ref="C29" authorId="12" shapeId="0" xr:uid="{CA6B0F40-6EF4-4274-8867-21553D999551}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -511,7 +511,7 @@
     Ntrepete, xamilon tonon</t>
       </text>
     </comment>
-    <comment ref="C31" authorId="13" shapeId="0" xr:uid="{E674068C-9812-42A2-9151-17837D13ABB6}">
+    <comment ref="C32" authorId="13" shapeId="0" xr:uid="{E674068C-9812-42A2-9151-17837D13ABB6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -519,7 +519,7 @@
     Isixi, thelei entharinsi</t>
       </text>
     </comment>
-    <comment ref="C32" authorId="14" shapeId="0" xr:uid="{ED249525-191C-4637-9D99-E242BDB6421A}">
+    <comment ref="C33" authorId="14" shapeId="0" xr:uid="{ED249525-191C-4637-9D99-E242BDB6421A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -527,7 +527,7 @@
     Xasimoto, pernei thiroksini</t>
       </text>
     </comment>
-    <comment ref="C34" authorId="15" shapeId="0" xr:uid="{B304C0F3-0817-4A4E-853F-5F45E9E32DFD}">
+    <comment ref="C35" authorId="15" shapeId="0" xr:uid="{B304C0F3-0817-4A4E-853F-5F45E9E32DFD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -535,7 +535,7 @@
     Mila arketa, kinito, oriothetisi</t>
       </text>
     </comment>
-    <comment ref="I34" authorId="16" shapeId="0" xr:uid="{DF19662E-D699-40A7-996A-7901BA4875E9}">
+    <comment ref="I35" authorId="16" shapeId="0" xr:uid="{DF19662E-D699-40A7-996A-7901BA4875E9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -543,7 +543,7 @@
     kataggelia</t>
       </text>
     </comment>
-    <comment ref="C35" authorId="17" shapeId="0" xr:uid="{1C68C472-CF02-4D39-A15B-ACD03122D4F0}">
+    <comment ref="C36" authorId="17" shapeId="0" xr:uid="{1C68C472-CF02-4D39-A15B-ACD03122D4F0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -553,7 +553,7 @@
     Miazei tis Melias</t>
       </text>
     </comment>
-    <comment ref="C36" authorId="18" shapeId="0" xr:uid="{2330157A-B3C2-4789-96E1-9C8D2D80D7FE}">
+    <comment ref="C37" authorId="18" shapeId="0" xr:uid="{2330157A-B3C2-4789-96E1-9C8D2D80D7FE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -561,7 +561,7 @@
     zoiros</t>
       </text>
     </comment>
-    <comment ref="C37" authorId="19" shapeId="0" xr:uid="{831B6259-37A3-4907-AE80-39991BDC7649}">
+    <comment ref="C38" authorId="19" shapeId="0" xr:uid="{831B6259-37A3-4907-AE80-39991BDC7649}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -738,7 +738,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="313">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1665,13 +1665,25 @@
   </si>
   <si>
     <t>5-9/10 2026</t>
+  </si>
+  <si>
+    <t>did in class ask 1,2,3</t>
+  </si>
+  <si>
+    <t>hw ask 2,3 p 122</t>
+  </si>
+  <si>
+    <t>Λούβαρης</t>
+  </si>
+  <si>
+    <t>Ιωάννης</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1717,12 +1729,6 @@
       <family val="2"/>
       <charset val="161"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="14">
@@ -1932,13 +1938,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2400,31 +2406,31 @@
   <threadedComment ref="C24" dT="2026-09-23T07:02:08.99" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{8AC19454-30E3-45D9-9597-E3A2E37CFF9A}">
     <text>Aporos, sitisis</text>
   </threadedComment>
-  <threadedComment ref="C28" dT="2026-09-20T17:09:45.79" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{CA6B0F40-6EF4-4274-8867-21553D999551}">
+  <threadedComment ref="C29" dT="2026-09-20T17:09:45.79" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{CA6B0F40-6EF4-4274-8867-21553D999551}">
     <text>Ntrepete, xamilon tonon</text>
   </threadedComment>
-  <threadedComment ref="C31" dT="2026-09-20T17:10:08.12" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{E674068C-9812-42A2-9151-17837D13ABB6}">
+  <threadedComment ref="C32" dT="2026-09-20T17:10:08.12" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{E674068C-9812-42A2-9151-17837D13ABB6}">
     <text>Isixi, thelei entharinsi</text>
   </threadedComment>
-  <threadedComment ref="C32" dT="2026-09-20T17:10:27.77" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{ED249525-191C-4637-9D99-E242BDB6421A}">
+  <threadedComment ref="C33" dT="2026-09-20T17:10:27.77" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{ED249525-191C-4637-9D99-E242BDB6421A}">
     <text>Xasimoto, pernei thiroksini</text>
   </threadedComment>
-  <threadedComment ref="C34" dT="2026-09-20T17:10:57.03" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B304C0F3-0817-4A4E-853F-5F45E9E32DFD}">
+  <threadedComment ref="C35" dT="2026-09-20T17:10:57.03" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B304C0F3-0817-4A4E-853F-5F45E9E32DFD}">
     <text>Mila arketa, kinito, oriothetisi</text>
   </threadedComment>
-  <threadedComment ref="I34" dT="2026-09-29T09:23:10.29" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{DF19662E-D699-40A7-996A-7901BA4875E9}">
+  <threadedComment ref="I35" dT="2026-09-29T09:23:10.29" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{DF19662E-D699-40A7-996A-7901BA4875E9}">
     <text>kataggelia</text>
   </threadedComment>
-  <threadedComment ref="C35" dT="2026-09-22T09:37:54.19" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{1C68C472-CF02-4D39-A15B-ACD03122D4F0}">
+  <threadedComment ref="C36" dT="2026-09-22T09:37:54.19" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{1C68C472-CF02-4D39-A15B-ACD03122D4F0}">
     <text>Oreo m.</text>
   </threadedComment>
-  <threadedComment ref="C35" dT="2026-09-28T13:49:17.74" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B1F323BE-4949-4763-BB39-48857EEB06DA}" parentId="{1C68C472-CF02-4D39-A15B-ACD03122D4F0}">
+  <threadedComment ref="C36" dT="2026-09-28T13:49:17.74" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B1F323BE-4949-4763-BB39-48857EEB06DA}" parentId="{1C68C472-CF02-4D39-A15B-ACD03122D4F0}">
     <text>Miazei tis Melias</text>
   </threadedComment>
-  <threadedComment ref="C36" dT="2026-09-20T17:11:14.69" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2330157A-B3C2-4789-96E1-9C8D2D80D7FE}">
+  <threadedComment ref="C37" dT="2026-09-20T17:11:14.69" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2330157A-B3C2-4789-96E1-9C8D2D80D7FE}">
     <text>zoiros</text>
   </threadedComment>
-  <threadedComment ref="C37" dT="2026-09-20T17:11:23.87" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{831B6259-37A3-4907-AE80-39991BDC7649}">
+  <threadedComment ref="C38" dT="2026-09-20T17:11:23.87" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{831B6259-37A3-4907-AE80-39991BDC7649}">
     <text>zoiros</text>
   </threadedComment>
 </ThreadedComments>
@@ -2501,60 +2507,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R36"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.9296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.41015625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.8203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.52734375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="41.9296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42.19921875" style="1" customWidth="1"/>
-    <col min="10" max="11" width="58.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="43.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="34.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34.19921875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="21.53125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.06640625" style="1"/>
+    <col min="6" max="8" width="41.9375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42.17578125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="58.5859375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="43.41015625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="34.17578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="34.17578125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="21.52734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.05859375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="7"/>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="34" t="s">
+      <c r="C1" s="34"/>
+      <c r="D1" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="35"/>
-      <c r="F1" s="34" t="s">
+      <c r="E1" s="34"/>
+      <c r="F1" s="33" t="s">
         <v>238</v>
       </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="34" t="s">
+      <c r="G1" s="34"/>
+      <c r="H1" s="33" t="s">
         <v>244</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="34" t="s">
+      <c r="I1" s="34"/>
+      <c r="J1" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="34" t="s">
+      <c r="K1" s="34"/>
+      <c r="L1" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="M1" s="35"/>
-      <c r="N1" s="34" t="s">
+      <c r="M1" s="34"/>
+      <c r="N1" s="33" t="s">
         <v>253</v>
       </c>
-      <c r="O1" s="35"/>
-    </row>
-    <row r="2" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="O1" s="34"/>
+    </row>
+    <row r="2" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2565,7 +2571,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -2596,11 +2602,11 @@
       <c r="J4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="4" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -2628,14 +2634,14 @@
       <c r="I5" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="4" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
@@ -2663,10 +2669,10 @@
       <c r="I6" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="4" t="s">
         <v>301</v>
       </c>
       <c r="L6" s="1" t="s">
@@ -2676,7 +2682,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
@@ -2707,11 +2713,11 @@
       <c r="J7" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" s="4" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
         <v>285</v>
       </c>
@@ -2719,7 +2725,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>286</v>
       </c>
@@ -2727,7 +2733,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A12" s="5" t="s">
         <v>1</v>
       </c>
@@ -2738,7 +2744,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
@@ -2769,11 +2775,11 @@
       <c r="J13" s="19" t="s">
         <v>304</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" s="4" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A14" s="5" t="s">
         <v>7</v>
       </c>
@@ -2804,11 +2810,11 @@
       <c r="J14" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" s="4" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
@@ -2839,11 +2845,11 @@
       <c r="J15" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" s="19" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
@@ -2854,12 +2860,12 @@
         <v>241</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.5">
       <c r="H19" s="30" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A20" s="5" t="s">
         <v>14</v>
       </c>
@@ -2887,7 +2893,7 @@
       <c r="I20" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="19" t="s">
         <v>245</v>
       </c>
       <c r="K20" s="4" t="s">
@@ -2912,7 +2918,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A21" s="5" t="s">
         <v>16</v>
       </c>
@@ -2940,7 +2946,7 @@
       <c r="I21" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J21" s="19" t="s">
         <v>245</v>
       </c>
       <c r="K21" s="4" t="s">
@@ -2965,7 +2971,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A22" s="5" t="s">
         <v>15</v>
       </c>
@@ -2993,7 +2999,7 @@
       <c r="I22" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J22" s="19" t="s">
         <v>243</v>
       </c>
       <c r="K22" s="4" t="s">
@@ -3021,7 +3027,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.5">
       <c r="B23" s="2"/>
       <c r="C23" s="3"/>
       <c r="D23" s="21"/>
@@ -3039,7 +3045,7 @@
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A24" s="5" t="s">
         <v>10</v>
       </c>
@@ -3060,33 +3066,33 @@
         <v>288</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.5">
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.5">
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.5">
       <c r="B27" s="11"/>
       <c r="C27" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.5">
       <c r="B28" s="3"/>
       <c r="C28" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.5">
       <c r="B29" s="4"/>
       <c r="C29" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
         <v>21</v>
       </c>
@@ -3097,7 +3103,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
         <v>22</v>
       </c>
@@ -3105,7 +3111,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
         <v>23</v>
       </c>
@@ -3113,7 +3119,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
         <v>24</v>
       </c>
@@ -3141,21 +3147,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0C9DD2-633E-44CA-9A93-86B2E2731C82}">
   <dimension ref="A1:P60"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.46484375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.53125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.19921875" style="9" customWidth="1"/>
-    <col min="5" max="5" width="9.06640625" style="9"/>
-    <col min="6" max="6" width="13.53125" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.06640625" style="9"/>
-    <col min="8" max="8" width="13.53125" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.46484375" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.06640625" style="9"/>
+    <col min="1" max="1" width="8.3515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.46875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.52734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.17578125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="9.05859375" style="9"/>
+    <col min="6" max="6" width="13.52734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.05859375" style="9"/>
+    <col min="8" max="8" width="13.52734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.17578125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="14.52734375" style="9" customWidth="1"/>
+    <col min="11" max="16384" width="9.05859375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="13" t="s">
         <v>57</v>
       </c>
@@ -3169,21 +3176,21 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="F2" s="33" t="s">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="F2" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33" t="s">
+      <c r="G2" s="35"/>
+      <c r="H2" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33" t="s">
+      <c r="I2" s="35"/>
+      <c r="J2" s="35" t="s">
         <v>306</v>
       </c>
-      <c r="K2" s="33"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.5">
+      <c r="K2" s="35"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9" t="s">
         <v>121</v>
       </c>
@@ -3191,7 +3198,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="9">
         <v>9285104</v>
       </c>
@@ -3213,7 +3220,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="9">
         <v>8324104</v>
       </c>
@@ -3239,7 +3246,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="9">
         <v>6811804</v>
       </c>
@@ -3268,7 +3275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="9">
         <v>5436904</v>
       </c>
@@ -3297,7 +3304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="9">
         <v>7025704</v>
       </c>
@@ -3326,7 +3333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="9">
         <v>8435804</v>
       </c>
@@ -3355,7 +3362,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="9">
         <v>5069104</v>
       </c>
@@ -3384,7 +3391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="9">
         <v>5222304</v>
       </c>
@@ -3413,7 +3420,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="9">
         <v>1981204</v>
       </c>
@@ -3442,7 +3449,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="9">
         <v>3766704</v>
       </c>
@@ -3469,12 +3476,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="P14" s="9">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="9" t="s">
         <v>72</v>
       </c>
@@ -3487,11 +3494,14 @@
       <c r="I15" s="9" t="s">
         <v>297</v>
       </c>
+      <c r="J15" s="9" t="s">
+        <v>310</v>
+      </c>
       <c r="P15" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="9">
         <v>5551204</v>
       </c>
@@ -3513,11 +3523,17 @@
       <c r="H16" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I16" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P16" s="9">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="9">
         <v>2056004</v>
       </c>
@@ -3537,11 +3553,17 @@
         <v>173</v>
       </c>
       <c r="H17" s="22"/>
+      <c r="I17" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P17" s="9">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="9">
         <v>3318504</v>
       </c>
@@ -3563,11 +3585,17 @@
       <c r="H18" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I18" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P18" s="9">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="9">
         <v>4926804</v>
       </c>
@@ -3589,11 +3617,17 @@
       <c r="H19" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I19" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P19" s="9">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="9">
         <v>7568204</v>
       </c>
@@ -3613,11 +3647,17 @@
         <v>173</v>
       </c>
       <c r="H20" s="22"/>
+      <c r="I20" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P20" s="9">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="9">
         <v>5111404</v>
       </c>
@@ -3637,11 +3677,17 @@
         <v>173</v>
       </c>
       <c r="H21" s="22"/>
+      <c r="I21" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P21" s="9">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="9">
         <v>4332504</v>
       </c>
@@ -3663,11 +3709,17 @@
       <c r="H22" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I22" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P22" s="9">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="9">
         <v>4424904</v>
       </c>
@@ -3689,11 +3741,17 @@
       <c r="H23" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I23" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P23" s="9">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="9">
         <v>4934404</v>
       </c>
@@ -3715,11 +3773,17 @@
       <c r="H24" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I24" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P24" s="9">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="9" t="s">
         <v>298</v>
       </c>
@@ -3729,16 +3793,31 @@
       <c r="D25" s="9" t="s">
         <v>300</v>
       </c>
+      <c r="E25" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P25" s="9">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="P26" s="9">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="9" t="s">
         <v>140</v>
       </c>
@@ -3752,7 +3831,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="9">
         <v>9189004</v>
       </c>
@@ -3778,7 +3857,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="9">
         <v>5682904</v>
       </c>
@@ -3804,7 +3883,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="9">
         <v>9217204</v>
       </c>
@@ -3826,7 +3905,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="9">
         <v>7319504</v>
       </c>
@@ -3852,7 +3931,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="9">
         <v>9254304</v>
       </c>
@@ -3878,7 +3957,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="9">
         <v>2428404</v>
       </c>
@@ -3904,7 +3983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="9">
         <v>2427904</v>
       </c>
@@ -3927,7 +4006,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="9">
         <v>8373704</v>
       </c>
@@ -3950,7 +4029,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="9">
         <v>5155004</v>
       </c>
@@ -3973,7 +4052,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="9">
         <v>1006390</v>
       </c>
@@ -3996,7 +4075,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="9" t="s">
         <v>157</v>
       </c>
@@ -4004,7 +4083,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="9">
         <v>5324204</v>
       </c>
@@ -4036,7 +4115,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="9">
         <v>5996604</v>
       </c>
@@ -4068,7 +4147,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="9">
         <v>7153704</v>
       </c>
@@ -4100,7 +4179,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="9">
         <v>9185204</v>
       </c>
@@ -4132,7 +4211,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="9">
         <v>9185504</v>
       </c>
@@ -4164,7 +4243,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="9">
         <v>4913604</v>
       </c>
@@ -4196,7 +4275,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="9">
         <v>5436204</v>
       </c>
@@ -4228,7 +4307,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="9">
         <v>3506004</v>
       </c>
@@ -4260,7 +4339,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="9">
         <v>6757304</v>
       </c>
@@ -4292,7 +4371,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="9">
         <v>6390804</v>
       </c>
@@ -4324,13 +4403,13 @@
         <v>173</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="22"/>
       <c r="B54" s="12" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="27" t="s">
         <v>173</v>
       </c>
@@ -4338,7 +4417,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="28" t="s">
         <v>267</v>
       </c>
@@ -4346,13 +4425,13 @@
         <v>268</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="31"/>
       <c r="B57" s="12" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="24" t="s">
         <v>236</v>
       </c>
@@ -4360,7 +4439,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="25" t="s">
         <v>271</v>
       </c>
@@ -4368,7 +4447,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="26" t="s">
         <v>272</v>
       </c>
@@ -4390,17 +4469,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A321353-3FB1-4427-84C3-E63782B65799}">
-  <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:K38"/>
+  <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.06640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.796875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="6.73046875" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.06640625" style="9"/>
+    <col min="1" max="1" width="8.3515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.05859375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.8203125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="6.703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.05859375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="10" t="s">
         <v>57</v>
       </c>
@@ -4414,26 +4493,26 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
-      <c r="F2" s="33" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="F2" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33" t="s">
+      <c r="G2" s="35"/>
+      <c r="H2" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33" t="s">
+      <c r="I2" s="35"/>
+      <c r="J2" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="K2" s="33"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="K2" s="35"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="9">
         <v>1025518</v>
       </c>
@@ -4462,7 +4541,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="9">
         <v>4298104</v>
       </c>
@@ -4489,7 +4568,7 @@
       </c>
       <c r="I5" s="22"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="9">
         <v>1033606</v>
       </c>
@@ -4518,7 +4597,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="9">
         <v>1033506</v>
       </c>
@@ -4545,7 +4624,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="9">
         <v>1026254</v>
       </c>
@@ -4574,7 +4653,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="9">
         <v>1028366</v>
       </c>
@@ -4603,7 +4682,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="9">
         <v>1033023</v>
       </c>
@@ -4632,7 +4711,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="9">
         <v>1032554</v>
       </c>
@@ -4661,7 +4740,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="9">
         <v>1026281</v>
       </c>
@@ -4690,7 +4769,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="9">
         <v>1029057</v>
       </c>
@@ -4719,12 +4798,12 @@
         <v>173</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="9" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="9">
         <v>1035828</v>
       </c>
@@ -4747,7 +4826,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="9">
         <v>1031619</v>
       </c>
@@ -4770,7 +4849,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="9">
         <v>1037608</v>
       </c>
@@ -4793,7 +4872,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="9">
         <v>1035515</v>
       </c>
@@ -4816,7 +4895,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="9">
         <v>1030772</v>
       </c>
@@ -4839,7 +4918,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="9">
         <v>1026742</v>
       </c>
@@ -4862,7 +4941,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="9">
         <v>1038924</v>
       </c>
@@ -4885,7 +4964,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="9">
         <v>1029508</v>
       </c>
@@ -4908,7 +4987,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="9">
         <v>1028849</v>
       </c>
@@ -4931,30 +5010,21 @@
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.5">
-      <c r="A28" s="9">
-        <v>1027008</v>
-      </c>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="9" t="s">
-        <v>37</v>
+        <v>311</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>38</v>
+        <v>312</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>173</v>
-      </c>
       <c r="H28" s="12" t="s">
         <v>173</v>
       </c>
@@ -4964,22 +5034,25 @@
       <c r="J28" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="K28" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="9">
-        <v>1026200</v>
+        <v>1027008</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>173</v>
@@ -4993,16 +5066,19 @@
       <c r="J29" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="K29" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="9">
-        <v>1025833</v>
+        <v>1026200</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>39</v>
@@ -5022,16 +5098,19 @@
       <c r="J30" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="K30" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="9">
-        <v>1036053</v>
+        <v>1025833</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>39</v>
@@ -5051,16 +5130,19 @@
       <c r="J31" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="K31" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="9">
-        <v>1029029</v>
+        <v>1036053</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>39</v>
@@ -5080,16 +5162,19 @@
       <c r="J32" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="K32" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="9">
-        <v>1028278</v>
+        <v>1029029</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>39</v>
@@ -5109,16 +5194,19 @@
       <c r="J33" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="K33" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="9">
-        <v>1025603</v>
+        <v>1028278</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>39</v>
@@ -5127,25 +5215,30 @@
         <v>173</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>236</v>
+        <v>173</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>236</v>
+        <v>173</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="J34" s="22"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.5">
+        <v>173</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="K34" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="9">
-        <v>1028053</v>
+        <v>1025603</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>39</v>
@@ -5154,27 +5247,28 @@
         <v>173</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="J35" s="12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.5">
+        <v>236</v>
+      </c>
+      <c r="J35" s="22"/>
+      <c r="K35" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="9">
-        <v>1027036</v>
+        <v>1028053</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>39</v>
@@ -5194,10 +5288,13 @@
       <c r="J36" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="K36" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="9">
-        <v>1032361</v>
+        <v>1027036</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>54</v>
@@ -5221,6 +5318,41 @@
         <v>173</v>
       </c>
       <c r="J37" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="9">
+        <v>1032361</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="K38" s="12" t="s">
         <v>173</v>
       </c>
     </row>
@@ -5239,15 +5371,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82B87684-E387-4B51-9ECE-3C23F4BC9CBD}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="10.46484375" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.06640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" style="9" customWidth="1"/>
-    <col min="4" max="16384" width="9.06640625" style="9"/>
+    <col min="1" max="1" width="10.46875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.05859375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.17578125" style="9" customWidth="1"/>
+    <col min="4" max="16384" width="9.05859375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="9" t="s">
         <v>57</v>
       </c>
@@ -5260,20 +5392,20 @@
       <c r="D1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33" t="s">
+      <c r="F1" s="35"/>
+      <c r="G1" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33" t="s">
+      <c r="H1" s="35"/>
+      <c r="I1" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="J1" s="33"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.5">
+      <c r="J1" s="35"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9">
         <v>400002110</v>
       </c>
@@ -5293,7 +5425,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="9">
         <v>400002100</v>
       </c>
@@ -5313,7 +5445,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="9">
         <v>405136704</v>
       </c>
@@ -5333,7 +5465,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="9">
         <v>400002095</v>
       </c>
@@ -5353,7 +5485,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="9">
         <v>400002064</v>
       </c>
@@ -5386,15 +5518,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF640171-D19A-4A22-AEE9-A5E7AF0F79D2}">
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.41015625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.9375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.17578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -5407,25 +5540,28 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33" t="s">
+      <c r="H1" s="35"/>
+      <c r="I1" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33" t="s">
+      <c r="J1" s="35"/>
+      <c r="K1" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="L1" s="33"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="L1" s="35"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>4206804</v>
       </c>
@@ -5456,8 +5592,11 @@
       <c r="J4" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K4" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>9307104</v>
       </c>
@@ -5488,8 +5627,11 @@
       <c r="J5" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K5" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>2173704</v>
       </c>
@@ -5520,8 +5662,11 @@
       <c r="J6" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K6" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>9257304</v>
       </c>
@@ -5552,8 +5697,11 @@
       <c r="J7" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K7" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>2915404</v>
       </c>
@@ -5584,8 +5732,11 @@
       <c r="J8" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K8" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>2836604</v>
       </c>
@@ -5616,8 +5767,11 @@
       <c r="J9" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K9" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>1274904</v>
       </c>
@@ -5648,8 +5802,11 @@
       <c r="J10" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K10" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>3863304</v>
       </c>
@@ -5680,8 +5837,9 @@
       <c r="J11" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K11" s="22"/>
+    </row>
+    <row r="12" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>3403504</v>
       </c>
@@ -5712,8 +5870,11 @@
       <c r="J12" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K12" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>4721304</v>
       </c>
@@ -5744,8 +5905,11 @@
       <c r="J13" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K13" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>3924304</v>
       </c>
@@ -5776,8 +5940,11 @@
       <c r="J14" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K14" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>4041704</v>
       </c>
@@ -5808,8 +5975,11 @@
       <c r="J15" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K15" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>9280704</v>
       </c>
@@ -5840,8 +6010,11 @@
       <c r="J16" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K16" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="C17" t="s">
         <v>229</v>
       </c>
@@ -5866,8 +6039,11 @@
       <c r="J17" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K17" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
         <v>230</v>
       </c>
@@ -5895,8 +6071,11 @@
       <c r="J18" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K18" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" t="s">
         <v>232</v>
       </c>
@@ -5924,13 +6103,16 @@
       <c r="J19" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K19" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -5944,7 +6126,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>9693404</v>
       </c>
@@ -5975,8 +6157,11 @@
       <c r="J23" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K23" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>222222</v>
       </c>
@@ -6007,8 +6192,11 @@
       <c r="J24" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K24" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>9743804</v>
       </c>
@@ -6039,8 +6227,11 @@
       <c r="J25" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K25" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>111111</v>
       </c>
@@ -6069,8 +6260,9 @@
       <c r="J26" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K26" s="22"/>
+    </row>
+    <row r="27" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>9662304</v>
       </c>
@@ -6101,8 +6293,11 @@
       <c r="J27" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K27" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
         <v>277</v>
       </c>
@@ -6124,8 +6319,11 @@
       <c r="J28" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K28" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" t="s">
         <v>277</v>
       </c>
@@ -6147,13 +6345,16 @@
       <c r="J29" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K29" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>3578804</v>
       </c>
@@ -6181,8 +6382,11 @@
       <c r="J32" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K32" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>9289704</v>
       </c>
@@ -6208,8 +6412,11 @@
       <c r="J33" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K33" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>9344404</v>
       </c>
@@ -6235,8 +6442,11 @@
       <c r="J34" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K34" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>6746404</v>
       </c>
@@ -6262,8 +6472,11 @@
       <c r="J35" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K35" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>9257604</v>
       </c>
@@ -6291,8 +6504,11 @@
       <c r="J36" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K36" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>9717204</v>
       </c>
@@ -6318,8 +6534,11 @@
       <c r="J37" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K37" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>2298204</v>
       </c>
@@ -6345,8 +6564,9 @@
       <c r="J38" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K38" s="22"/>
+    </row>
+    <row r="39" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>5784804</v>
       </c>
@@ -6374,8 +6594,11 @@
       <c r="J39" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K39" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>9321704</v>
       </c>
@@ -6403,8 +6626,9 @@
       <c r="J40" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K40" s="22"/>
+    </row>
+    <row r="41" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>9720304</v>
       </c>
@@ -6432,8 +6656,11 @@
       <c r="J41" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K41" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>9317404</v>
       </c>
@@ -6459,8 +6686,11 @@
       <c r="J42" s="29" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="K42" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>8333604</v>
       </c>
@@ -6487,6 +6717,9 @@
       </c>
       <c r="J43" s="29" t="s">
         <v>291</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -6505,13 +6738,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC563BF-C300-44C1-88F1-5244DF9366D6}">
   <dimension ref="A3:B3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.64453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>274</v>
       </c>
@@ -6527,9 +6760,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C172699-9C2F-4E67-A102-81BDA8494E34}">
   <dimension ref="G22:I22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
-    <row r="22" spans="7:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="7:9" x14ac:dyDescent="0.5">
       <c r="G22">
         <v>2</v>
       </c>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1101" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AA3E364-8BCC-4412-A3C8-69C236C71117}"/>
+  <xr:revisionPtr revIDLastSave="1111" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF88D81C-C390-4DC2-AE4B-3F5EABFDE565}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -738,7 +738,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="315">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1677,6 +1677,12 @@
   </si>
   <si>
     <t>Ιωάννης</t>
+  </si>
+  <si>
+    <t>powerpoint introduction</t>
+  </si>
+  <si>
+    <t>REDO - CREATE MY OWN FYLLO ERGASIAS</t>
   </si>
 </sst>
 </file>
@@ -2602,7 +2608,7 @@
       <c r="J4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="19" t="s">
         <v>260</v>
       </c>
     </row>
@@ -2637,7 +2643,7 @@
       <c r="J5" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="19" t="s">
         <v>260</v>
       </c>
     </row>
@@ -2669,7 +2675,7 @@
       <c r="I6" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="19" t="s">
         <v>260</v>
       </c>
       <c r="K6" s="4" t="s">
@@ -2721,8 +2727,11 @@
       <c r="B9" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>257</v>
+      <c r="C9" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.5">
@@ -2775,7 +2784,7 @@
       <c r="J13" s="19" t="s">
         <v>304</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="19" t="s">
         <v>305</v>
       </c>
     </row>
@@ -3036,8 +3045,6 @@
       <c r="G23" s="17"/>
       <c r="H23" s="19"/>
       <c r="I23" s="17"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
@@ -3064,6 +3071,9 @@
       </c>
       <c r="G24" s="21" t="s">
         <v>288</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.5">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1111" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF88D81C-C390-4DC2-AE4B-3F5EABFDE565}"/>
+  <xr:revisionPtr revIDLastSave="1133" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{112FB27E-D345-4AB7-B44B-6AE03B77E9D0}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Monada" sheetId="5" r:id="rId4"/>
     <sheet name="A Lyceum" sheetId="4" r:id="rId5"/>
     <sheet name="anapliroseis" sheetId="7" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="9" r:id="rId7"/>
+    <sheet name="notes" sheetId="10" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -738,7 +738,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="320">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1683,6 +1683,21 @@
   </si>
   <si>
     <t>REDO - CREATE MY OWN FYLLO ERGASIAS</t>
+  </si>
+  <si>
+    <t>na ginei erevna sto B1, B2</t>
+  </si>
+  <si>
+    <t>ΠΡΟΣΦΟΡΑ ΓΙΑ ΤΗΝ ΕΚΔΟΣΗ ΤΟΥ ΠΕΡΙΟΔΙΚΟΥ ΤΟΥ ΣΧΟΛΕΙΟΥ</t>
+  </si>
+  <si>
+    <t>ΠΡΟΚΗΡΥΞΗ ΠΡΟΣΦΟΡΑΣ ΓΙΑ ΦΩΤΟΓΡΑΦΙΣΗ</t>
+  </si>
+  <si>
+    <t>erevva B1, B2:</t>
+  </si>
+  <si>
+    <t>https://forms.cloud.microsoft/e/tmx2WgGAj2</t>
   </si>
 </sst>
 </file>
@@ -2522,8 +2537,9 @@
     <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="41.9375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="42.17578125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="58.5859375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="43.41015625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="58.5859375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="56" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="43.41015625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="34.17578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="34.17578125" style="1" customWidth="1"/>
     <col min="17" max="17" width="21.52734375" style="1" bestFit="1" customWidth="1"/>
@@ -2719,7 +2735,10 @@
       <c r="J7" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>260</v>
       </c>
     </row>
@@ -2752,6 +2771,9 @@
       <c r="C12" s="1" t="s">
         <v>176</v>
       </c>
+      <c r="L12" s="1" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A13" s="5" t="s">
@@ -2854,7 +2876,10 @@
       <c r="J15" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="K15" s="19" t="s">
+      <c r="K15" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>304</v>
       </c>
     </row>
@@ -6768,23 +6793,30 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C172699-9C2F-4E67-A102-81BDA8494E34}">
-  <dimension ref="G22:I22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23D143C4-24B5-4F25-A9AC-CA5F9ACC8C3E}">
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
-    <row r="22" spans="7:9" x14ac:dyDescent="0.5">
-      <c r="G22">
-        <v>2</v>
-      </c>
-      <c r="H22">
-        <v>3</v>
-      </c>
-      <c r="I22">
-        <f>$G$22+H22</f>
-        <v>5</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C3" t="s">
+        <v>319</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1133" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{112FB27E-D345-4AB7-B44B-6AE03B77E9D0}"/>
+  <xr:revisionPtr revIDLastSave="1175" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17765811-35DD-42E3-BB1C-A0D9A669DEA0}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
     <sheet name="A Gymansiou" sheetId="2" r:id="rId2"/>
-    <sheet name="B Gymnasiou" sheetId="3" r:id="rId3"/>
-    <sheet name="Monada" sheetId="5" r:id="rId4"/>
-    <sheet name="A Lyceum" sheetId="4" r:id="rId5"/>
-    <sheet name="anapliroseis" sheetId="7" r:id="rId6"/>
-    <sheet name="notes" sheetId="10" r:id="rId7"/>
+    <sheet name="notes" sheetId="10" r:id="rId3"/>
+    <sheet name="B Gymnasiou" sheetId="3" r:id="rId4"/>
+    <sheet name="Monada" sheetId="5" r:id="rId5"/>
+    <sheet name="A Lyceum" sheetId="4" r:id="rId6"/>
+    <sheet name="anapliroseis" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -738,7 +738,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="329">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1698,6 +1698,33 @@
   </si>
   <si>
     <t>https://forms.cloud.microsoft/e/tmx2WgGAj2</t>
+  </si>
+  <si>
+    <t>hw: ask 4-5, p.82</t>
+  </si>
+  <si>
+    <t>A5.1 Μ3 - Εντοπισμός Πληροφοριών από το Διαδίκτυο(ξανά με ενεργοποιητή)</t>
+  </si>
+  <si>
+    <t>hw. Ex 1,2,3 p.81</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/O-g5-swe1fM?si=taB7tom-iAyLPLpO</t>
+  </si>
+  <si>
+    <t>what is the internet backbone:</t>
+  </si>
+  <si>
+    <t>how are cables installed</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/Mv2VcOZjn64?si=W8Em1jqp1O75MGiX</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/TuSTnOwhStg?si=o5EOIprdTtIusChy</t>
+  </si>
+  <si>
+    <t>how to fix internet cables</t>
   </si>
 </sst>
 </file>
@@ -2538,7 +2565,8 @@
     <col min="6" max="8" width="41.9375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="42.17578125" style="1" customWidth="1"/>
     <col min="10" max="10" width="58.5859375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="56" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="65.5859375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="56" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="43.41015625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="34.17578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="34.17578125" style="1" customWidth="1"/>
@@ -2694,13 +2722,16 @@
       <c r="J6" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>303</v>
       </c>
     </row>
@@ -3888,6 +3919,9 @@
       <c r="H28" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I28" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P28" s="9">
         <v>23</v>
       </c>
@@ -3914,6 +3948,9 @@
       <c r="H29" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I29" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P29" s="9">
         <v>24</v>
       </c>
@@ -3936,6 +3973,9 @@
       </c>
       <c r="F30" s="22"/>
       <c r="H30" s="22"/>
+      <c r="I30" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P30" s="9">
         <v>25</v>
       </c>
@@ -3962,6 +4002,9 @@
       <c r="H31" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I31" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P31" s="9">
         <v>26</v>
       </c>
@@ -3988,6 +4031,9 @@
       <c r="H32" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I32" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P32" s="9">
         <v>27</v>
       </c>
@@ -4014,6 +4060,9 @@
       <c r="H33" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I33" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="P33" s="9">
         <v>28</v>
       </c>
@@ -4040,6 +4089,9 @@
       <c r="H34" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I34" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="9">
@@ -4063,6 +4115,9 @@
       <c r="H35" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I35" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="9">
@@ -4086,6 +4141,9 @@
       <c r="H36" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="I36" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="9">
@@ -4107,6 +4165,9 @@
         <v>173</v>
       </c>
       <c r="H37" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I37" s="12" t="s">
         <v>173</v>
       </c>
     </row>
@@ -4503,6 +4564,129 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23D143C4-24B5-4F25-A9AC-CA5F9ACC8C3E}">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="49.87890625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.234375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
+        <v>316</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C3" t="s">
+        <v>319</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="H4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="H5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C6" t="s">
+        <v>323</v>
+      </c>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A7" t="s">
+        <v>325</v>
+      </c>
+      <c r="C7" t="s">
+        <v>326</v>
+      </c>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C8" t="s">
+        <v>327</v>
+      </c>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="H10" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="H11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="H12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="H13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>264</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A321353-3FB1-4427-84C3-E63782B65799}">
   <dimension ref="A1:K38"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
@@ -5403,7 +5587,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82B87684-E387-4B51-9ECE-3C23F4BC9CBD}">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
@@ -5550,7 +5734,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF640171-D19A-4A22-AEE9-A5E7AF0F79D2}">
   <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
@@ -5559,7 +5743,8 @@
     <col min="2" max="2" width="19.41015625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.9375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.17578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.29296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.3515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -5595,6 +5780,9 @@
       <c r="K3" t="s">
         <v>309</v>
       </c>
+      <c r="L3" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="4" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
@@ -5630,6 +5818,9 @@
       <c r="K4" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="L4" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="5" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
@@ -5665,6 +5856,9 @@
       <c r="K5" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="L5" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
@@ -5700,6 +5894,9 @@
       <c r="K6" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="L6" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
@@ -5735,6 +5932,9 @@
       <c r="K7" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="L7" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="8" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
@@ -5770,6 +5970,9 @@
       <c r="K8" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="L8" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
@@ -5805,6 +6008,9 @@
       <c r="K9" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="L9" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="10" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
@@ -5840,6 +6046,9 @@
       <c r="K10" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="L10" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="11" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
@@ -5873,6 +6082,9 @@
         <v>291</v>
       </c>
       <c r="K11" s="22"/>
+      <c r="L11" s="24" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="12" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
@@ -5908,6 +6120,9 @@
       <c r="K12" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="L12" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="13" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
@@ -5943,6 +6158,9 @@
       <c r="K13" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="L13" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="14" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
@@ -5978,6 +6196,9 @@
       <c r="K14" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="L14" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="15" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
@@ -6013,6 +6234,9 @@
       <c r="K15" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="L15" s="14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="16" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
@@ -6048,8 +6272,11 @@
       <c r="K16" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L16" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="C17" t="s">
         <v>229</v>
       </c>
@@ -6077,8 +6304,11 @@
       <c r="K17" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L17" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
         <v>230</v>
       </c>
@@ -6109,8 +6339,11 @@
       <c r="K18" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L18" s="24" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" t="s">
         <v>232</v>
       </c>
@@ -6141,13 +6374,16 @@
       <c r="K19" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="L19" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -6160,8 +6396,11 @@
       <c r="D22" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L22" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>9693404</v>
       </c>
@@ -6195,8 +6434,11 @@
       <c r="K23" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L23" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>222222</v>
       </c>
@@ -6230,8 +6472,11 @@
       <c r="K24" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L24" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>9743804</v>
       </c>
@@ -6265,8 +6510,11 @@
       <c r="K25" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L25" s="25" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>111111</v>
       </c>
@@ -6296,8 +6544,11 @@
         <v>291</v>
       </c>
       <c r="K26" s="22"/>
-    </row>
-    <row r="27" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L26" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>9662304</v>
       </c>
@@ -6331,8 +6582,11 @@
       <c r="K27" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L27" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
         <v>277</v>
       </c>
@@ -6357,8 +6611,11 @@
       <c r="K28" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L28" s="25" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" t="s">
         <v>277</v>
       </c>
@@ -6383,13 +6640,16 @@
       <c r="K29" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.5">
+      <c r="L29" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>3578804</v>
       </c>
@@ -6770,7 +7030,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC563BF-C300-44C1-88F1-5244DF9366D6}">
   <dimension ref="A3:B3"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
@@ -6790,33 +7050,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23D143C4-24B5-4F25-A9AC-CA5F9ACC8C3E}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
 </file>
--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1175" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17765811-35DD-42E3-BB1C-A0D9A669DEA0}"/>
+  <xr:revisionPtr revIDLastSave="1197" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FEA22CA-8968-4E51-825E-63A1637ABBDE}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -662,7 +662,7 @@
     Good student</t>
       </text>
     </comment>
-    <comment ref="C33" authorId="8" shapeId="0" xr:uid="{598384F6-CAC4-4E14-937B-755974DF65A2}">
+    <comment ref="C34" authorId="8" shapeId="0" xr:uid="{598384F6-CAC4-4E14-937B-755974DF65A2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -672,7 +672,7 @@
     Ligo prixtissa, alla kali.</t>
       </text>
     </comment>
-    <comment ref="C34" authorId="9" shapeId="0" xr:uid="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
+    <comment ref="C35" authorId="9" shapeId="0" xr:uid="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -684,7 +684,7 @@
     Keep an eye on him.</t>
       </text>
     </comment>
-    <comment ref="G34" authorId="10" shapeId="0" xr:uid="{05F8CCDA-D71B-40DF-B68D-97E9813023D7}">
+    <comment ref="G35" authorId="10" shapeId="0" xr:uid="{05F8CCDA-D71B-40DF-B68D-97E9813023D7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -692,7 +692,7 @@
     Epiase to kinito tou simmathiti tou, kai mou eipe psemata otan ton rotisa.</t>
       </text>
     </comment>
-    <comment ref="C35" authorId="11" shapeId="0" xr:uid="{B7F8AA97-EF7A-4346-BFE7-BFF2EEB2C1DB}">
+    <comment ref="C36" authorId="11" shapeId="0" xr:uid="{B7F8AA97-EF7A-4346-BFE7-BFF2EEB2C1DB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -700,7 +700,7 @@
     Fenete filotimos, with some knowledge</t>
       </text>
     </comment>
-    <comment ref="E37" authorId="12" shapeId="0" xr:uid="{D7246692-A47D-44D0-B75A-AD5BAC8A45F7}">
+    <comment ref="E38" authorId="12" shapeId="0" xr:uid="{D7246692-A47D-44D0-B75A-AD5BAC8A45F7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -708,7 +708,7 @@
     No effort, left class without asking permission, opened her phone, but I didn't says anything because they said some of their friends died from motorcycle accident.</t>
       </text>
     </comment>
-    <comment ref="C38" authorId="13" shapeId="0" xr:uid="{7768E2F5-6F98-401C-9CE0-F5514C8493B1}">
+    <comment ref="C39" authorId="13" shapeId="0" xr:uid="{7768E2F5-6F98-401C-9CE0-F5514C8493B1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -716,7 +716,7 @@
     Kori tis Lelias</t>
       </text>
     </comment>
-    <comment ref="C42" authorId="14" shapeId="0" xr:uid="{2EB8A751-6FC9-43E4-BEFE-D7B2A37941A4}">
+    <comment ref="C43" authorId="14" shapeId="0" xr:uid="{2EB8A751-6FC9-43E4-BEFE-D7B2A37941A4}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -725,7 +725,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="C43" authorId="15" shapeId="0" xr:uid="{BEA4804D-72CD-494C-BE39-4999EABE6959}">
+    <comment ref="C44" authorId="15" shapeId="0" xr:uid="{BEA4804D-72CD-494C-BE39-4999EABE6959}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -738,7 +738,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="332">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1481,9 +1481,6 @@
     <t>A.5.M1 Εισαγωγή - Μέρος 2</t>
   </si>
   <si>
-    <t>Α.5.M2 Έλεγχος Λειτουργίας Δικτύου</t>
-  </si>
-  <si>
     <t>Α.5.M5 Ασφάλεια</t>
   </si>
   <si>
@@ -1725,6 +1722,18 @@
   </si>
   <si>
     <t>how to fix internet cables</t>
+  </si>
+  <si>
+    <t>show videos</t>
+  </si>
+  <si>
+    <t>put hw ex.1,2,3 p.81</t>
+  </si>
+  <si>
+    <t>Α.5.M2 Έλεγχος Λειτουργίας Δικτύου - Μέρος 1</t>
+  </si>
+  <si>
+    <t>Α.5.M2 Έλεγχος Λειτουργίας Δικτύου - Μέρος 2</t>
   </si>
 </sst>
 </file>
@@ -2515,38 +2524,38 @@
   <threadedComment ref="C24" dT="2026-09-22T09:31:23.10" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D1B5C973-E93C-423C-8CC6-340934B20F0E}">
     <text>Good student</text>
   </threadedComment>
-  <threadedComment ref="C33" dT="2026-09-17T05:56:45.08" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{598384F6-CAC4-4E14-937B-755974DF65A2}">
+  <threadedComment ref="C34" dT="2026-09-17T05:56:45.08" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{598384F6-CAC4-4E14-937B-755974DF65A2}">
     <text>Not very careful</text>
   </threadedComment>
-  <threadedComment ref="C33" dT="2026-09-22T09:33:55.26" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{ABE83869-780E-416C-839B-791C9FC8D78D}" parentId="{598384F6-CAC4-4E14-937B-755974DF65A2}">
+  <threadedComment ref="C34" dT="2026-09-22T09:33:55.26" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{ABE83869-780E-416C-839B-791C9FC8D78D}" parentId="{598384F6-CAC4-4E14-937B-755974DF65A2}">
     <text>Ligo prixtissa, alla kali.</text>
   </threadedComment>
-  <threadedComment ref="C34" dT="2026-09-17T05:57:00.11" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
+  <threadedComment ref="C35" dT="2026-09-17T05:57:00.11" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
     <text>Get bored, starts playing games</text>
   </threadedComment>
-  <threadedComment ref="C34" dT="2026-09-22T09:34:55.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{13FEE7CC-818A-4309-AB99-FB756416F0D5}" parentId="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
+  <threadedComment ref="C35" dT="2026-09-22T09:34:55.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{13FEE7CC-818A-4309-AB99-FB756416F0D5}" parentId="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
     <text>Not paying attention</text>
   </threadedComment>
-  <threadedComment ref="C34" dT="2026-09-22T15:27:55.30" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{A8F8C615-6F8E-4F6F-9D9D-27AE9362CCDE}" parentId="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
+  <threadedComment ref="C35" dT="2026-09-22T15:27:55.30" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{A8F8C615-6F8E-4F6F-9D9D-27AE9362CCDE}" parentId="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
     <text>Keep an eye on him.</text>
   </threadedComment>
-  <threadedComment ref="G34" dT="2026-09-22T15:27:37.74" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{05F8CCDA-D71B-40DF-B68D-97E9813023D7}">
+  <threadedComment ref="G35" dT="2026-09-22T15:27:37.74" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{05F8CCDA-D71B-40DF-B68D-97E9813023D7}">
     <text>Epiase to kinito tou simmathiti tou, kai mou eipe psemata otan ton rotisa.</text>
   </threadedComment>
-  <threadedComment ref="C35" dT="2026-09-17T05:56:20.80" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B7F8AA97-EF7A-4346-BFE7-BFF2EEB2C1DB}">
+  <threadedComment ref="C36" dT="2026-09-17T05:56:20.80" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B7F8AA97-EF7A-4346-BFE7-BFF2EEB2C1DB}">
     <text>Fenete filotimos, with some knowledge</text>
   </threadedComment>
-  <threadedComment ref="E37" dT="2026-09-15T15:38:58.71" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D7246692-A47D-44D0-B75A-AD5BAC8A45F7}">
+  <threadedComment ref="E38" dT="2026-09-15T15:38:58.71" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D7246692-A47D-44D0-B75A-AD5BAC8A45F7}">
     <text>No effort, left class without asking permission, opened her phone, but I didn't says anything because they said some of their friends died from motorcycle accident.</text>
   </threadedComment>
-  <threadedComment ref="C38" dT="2026-09-22T09:33:38.73" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7768E2F5-6F98-401C-9CE0-F5514C8493B1}">
+  <threadedComment ref="C39" dT="2026-09-22T09:33:38.73" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7768E2F5-6F98-401C-9CE0-F5514C8493B1}">
     <text>Kori tis Lelias</text>
   </threadedComment>
-  <threadedComment ref="C42" dT="2026-09-17T05:53:15.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2EB8A751-6FC9-43E4-BEFE-D7B2A37941A4}">
+  <threadedComment ref="C43" dT="2026-09-17T05:53:15.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2EB8A751-6FC9-43E4-BEFE-D7B2A37941A4}">
     <text xml:space="preserve">Filotimos
 </text>
   </threadedComment>
-  <threadedComment ref="C43" dT="2026-09-17T05:55:56.16" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{BEA4804D-72CD-494C-BE39-4999EABE6959}">
+  <threadedComment ref="C44" dT="2026-09-17T05:55:56.16" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{BEA4804D-72CD-494C-BE39-4999EABE6959}">
     <text>With glasses</text>
   </threadedComment>
 </ThreadedComments>
@@ -2554,7 +2563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="11.41015625" style="5" bestFit="1" customWidth="1"/>
@@ -2568,7 +2577,8 @@
     <col min="11" max="11" width="65.5859375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="56" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="43.41015625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="34.17578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="43.05859375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="34.17578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="34.17578125" style="1" customWidth="1"/>
     <col min="17" max="17" width="21.52734375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="16384" width="9.05859375" style="1"/>
@@ -2593,15 +2603,15 @@
       </c>
       <c r="I1" s="34"/>
       <c r="J1" s="33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K1" s="34"/>
       <c r="L1" s="33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M1" s="34"/>
       <c r="N1" s="33" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O1" s="34"/>
     </row>
@@ -2626,7 +2636,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
@@ -2641,19 +2651,22 @@
         <v>31</v>
       </c>
       <c r="G4" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="H4" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="I4" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="J4" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="I4" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="J4" s="19" t="s">
+      <c r="K4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="K4" s="19" t="s">
-        <v>260</v>
+      <c r="L4" s="4" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.5">
@@ -2676,19 +2689,22 @@
         <v>31</v>
       </c>
       <c r="G5" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="H5" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="I5" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="J5" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="I5" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="J5" s="19" t="s">
+      <c r="K5" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="K5" s="19" t="s">
-        <v>260</v>
+      <c r="L5" s="4" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.5">
@@ -2708,31 +2724,31 @@
         <v>31</v>
       </c>
       <c r="F6" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="G6" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="H6" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="I6" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="H6" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="I6" s="19" t="s">
+      <c r="J6" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="J6" s="19" t="s">
-        <v>260</v>
-      </c>
       <c r="K6" s="19" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L6" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.5">
@@ -2740,7 +2756,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
@@ -2752,44 +2768,44 @@
         <v>242</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G7" s="19" t="s">
         <v>31</v>
       </c>
       <c r="H7" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="I7" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="I7" s="19" t="s">
-        <v>258</v>
-      </c>
       <c r="J7" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K7" s="17" t="s">
         <v>242</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.5">
@@ -2803,7 +2819,7 @@
         <v>176</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.5">
@@ -2823,22 +2839,22 @@
         <v>32</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G13" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="H13" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="I13" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="I13" s="19" t="s">
-        <v>264</v>
-      </c>
       <c r="J13" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="K13" s="19" t="s">
         <v>304</v>
-      </c>
-      <c r="K13" s="19" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.5">
@@ -2861,19 +2877,22 @@
         <v>32</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H14" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="I14" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="J14" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="J14" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>304</v>
+      <c r="K14" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.5">
@@ -2896,25 +2915,22 @@
         <v>32</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H15" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="I15" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="I15" s="19" t="s">
+      <c r="J15" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="J15" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="K15" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="K15" s="19" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
@@ -2925,12 +2941,12 @@
         <v>241</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.5">
       <c r="H19" s="30" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.5">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A20" s="5" t="s">
         <v>14</v>
       </c>
@@ -2956,34 +2972,37 @@
         <v>243</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J20" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="19" t="s">
         <v>246</v>
       </c>
       <c r="L20" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="N20" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="M20" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="O20" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="P20" s="4" t="s">
+      <c r="O20" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="P20" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="R20" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="Q20" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.5">
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A21" s="5" t="s">
         <v>16</v>
       </c>
@@ -3009,34 +3028,37 @@
         <v>243</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J21" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="K21" s="19" t="s">
         <v>246</v>
       </c>
       <c r="L21" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="N21" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="M21" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="O21" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="P21" s="4" t="s">
+      <c r="O21" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="P21" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="R21" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="Q21" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.5">
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A22" s="5" t="s">
         <v>15</v>
       </c>
@@ -3056,43 +3078,46 @@
         <v>239</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H22" s="19" t="s">
         <v>240</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J22" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="19" t="s">
         <v>245</v>
       </c>
       <c r="L22" s="4" t="s">
         <v>246</v>
       </c>
       <c r="M22" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="O22" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="N22" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="O22" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="P22" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q22" s="4" t="s">
+      <c r="P22" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q22" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="S22" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="R22" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.5">
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B23" s="2"/>
       <c r="C23" s="3"/>
       <c r="D23" s="21"/>
@@ -3108,7 +3133,7 @@
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A24" s="5" t="s">
         <v>10</v>
       </c>
@@ -3123,36 +3148,39 @@
         <v>242</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.5">
+        <v>312</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B27" s="11"/>
       <c r="C27" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B28" s="3"/>
       <c r="C28" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B29" s="4"/>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -3174,7 +3202,7 @@
         <v>22</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.5">
@@ -3190,7 +3218,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -3244,15 +3272,15 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="F2" s="35" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G2" s="35"/>
       <c r="H2" s="35" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I2" s="35"/>
       <c r="J2" s="35" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K2" s="35"/>
     </row>
@@ -3261,7 +3289,7 @@
         <v>121</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -3552,16 +3580,16 @@
         <v>72</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H15" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="I15" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="I15" s="9" t="s">
-        <v>297</v>
-      </c>
       <c r="J15" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P15" s="9">
         <v>10</v>
@@ -3851,13 +3879,13 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="D25" s="9" t="s">
         <v>299</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>300</v>
       </c>
       <c r="E25" s="12" t="s">
         <v>173</v>
@@ -3888,10 +3916,10 @@
         <v>140</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P27" s="9">
         <v>22</v>
@@ -4176,7 +4204,7 @@
         <v>157</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -4295,7 +4323,7 @@
         <v>236</v>
       </c>
       <c r="G44" s="25" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H44" s="12" t="s">
         <v>173</v>
@@ -4356,10 +4384,10 @@
         <v>173</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G46" s="28" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H46" s="12" t="s">
         <v>173</v>
@@ -4502,7 +4530,7 @@
     <row r="54" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="22"/>
       <c r="B54" s="12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -4510,21 +4538,21 @@
         <v>173</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="B56" s="12" t="s">
         <v>267</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="31"/>
       <c r="B57" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -4532,23 +4560,23 @@
         <v>236</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="25" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="B60" s="12" t="s">
         <v>272</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -4574,7 +4602,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>0</v>
@@ -4582,27 +4610,27 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="I2" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C3" t="s">
         <v>318</v>
-      </c>
-      <c r="C3" t="s">
-        <v>319</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.5">
@@ -4610,7 +4638,7 @@
         <v>4</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>301</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.5">
@@ -4618,33 +4646,33 @@
         <v>5</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
+        <v>324</v>
+      </c>
+      <c r="C7" t="s">
         <v>325</v>
-      </c>
-      <c r="C7" t="s">
-        <v>326</v>
       </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -4661,7 +4689,7 @@
         <v>6</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.5">
@@ -4669,7 +4697,7 @@
         <v>7</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.5">
@@ -4677,7 +4705,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4714,15 +4742,15 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="F2" s="35" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G2" s="35"/>
       <c r="H2" s="35" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I2" s="35"/>
       <c r="J2" s="35" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K2" s="35"/>
     </row>
@@ -4754,10 +4782,10 @@
         <v>173</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -4813,7 +4841,7 @@
         <v>173</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -5065,7 +5093,7 @@
         <v>236</v>
       </c>
       <c r="J17" s="26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -5088,7 +5116,7 @@
         <v>236</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -5111,7 +5139,7 @@
         <v>236</v>
       </c>
       <c r="J19" s="26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -5236,10 +5264,10 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>311</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>312</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>39</v>
@@ -5612,15 +5640,15 @@
         <v>60</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F1" s="35"/>
       <c r="G1" s="35" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1" s="35"/>
       <c r="I1" s="35" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J1" s="35"/>
     </row>
@@ -5736,7 +5764,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF640171-D19A-4A22-AEE9-A5E7AF0F79D2}">
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="7.703125" bestFit="1" customWidth="1"/>
@@ -5761,15 +5789,15 @@
         <v>60</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1" s="35"/>
       <c r="I1" s="35" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J1" s="35"/>
       <c r="K1" s="35" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L1" s="35"/>
     </row>
@@ -5778,10 +5806,10 @@
         <v>14</v>
       </c>
       <c r="K3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -5813,7 +5841,7 @@
         <v>173</v>
       </c>
       <c r="J4" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K4" s="14" t="s">
         <v>173</v>
@@ -5851,7 +5879,7 @@
         <v>173</v>
       </c>
       <c r="J5" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K5" s="14" t="s">
         <v>173</v>
@@ -5889,7 +5917,7 @@
         <v>173</v>
       </c>
       <c r="J6" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K6" s="14" t="s">
         <v>173</v>
@@ -5927,7 +5955,7 @@
         <v>173</v>
       </c>
       <c r="J7" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K7" s="14" t="s">
         <v>173</v>
@@ -5965,7 +5993,7 @@
         <v>173</v>
       </c>
       <c r="J8" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K8" s="14" t="s">
         <v>173</v>
@@ -6003,7 +6031,7 @@
         <v>173</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K9" s="14" t="s">
         <v>173</v>
@@ -6041,7 +6069,7 @@
         <v>173</v>
       </c>
       <c r="J10" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K10" s="14" t="s">
         <v>173</v>
@@ -6079,7 +6107,7 @@
         <v>173</v>
       </c>
       <c r="J11" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K11" s="22"/>
       <c r="L11" s="24" t="s">
@@ -6115,7 +6143,7 @@
         <v>173</v>
       </c>
       <c r="J12" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K12" s="14" t="s">
         <v>173</v>
@@ -6153,7 +6181,7 @@
         <v>173</v>
       </c>
       <c r="J13" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>173</v>
@@ -6191,7 +6219,7 @@
         <v>173</v>
       </c>
       <c r="J14" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K14" s="14" t="s">
         <v>173</v>
@@ -6229,7 +6257,7 @@
         <v>173</v>
       </c>
       <c r="J15" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>173</v>
@@ -6267,7 +6295,7 @@
         <v>173</v>
       </c>
       <c r="J16" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K16" s="14" t="s">
         <v>173</v>
@@ -6299,7 +6327,7 @@
         <v>173</v>
       </c>
       <c r="J17" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K17" s="14" t="s">
         <v>173</v>
@@ -6334,7 +6362,7 @@
         <v>173</v>
       </c>
       <c r="J18" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K18" s="14" t="s">
         <v>173</v>
@@ -6369,7 +6397,7 @@
         <v>173</v>
       </c>
       <c r="J19" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K19" s="14" t="s">
         <v>173</v>
@@ -6397,7 +6425,7 @@
         <v>60</v>
       </c>
       <c r="L22" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -6423,13 +6451,13 @@
         <v>173</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>173</v>
       </c>
       <c r="J23" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K23" s="14" t="s">
         <v>173</v>
@@ -6461,13 +6489,13 @@
         <v>173</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I24" s="14" t="s">
         <v>173</v>
       </c>
       <c r="J24" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K24" s="14" t="s">
         <v>173</v>
@@ -6499,19 +6527,19 @@
         <v>173</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I25" s="14" t="s">
         <v>173</v>
       </c>
       <c r="J25" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K25" s="14" t="s">
         <v>173</v>
       </c>
       <c r="L25" s="25" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -6537,11 +6565,11 @@
         <v>173</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I26" s="31"/>
       <c r="J26" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K26" s="22"/>
       <c r="L26" s="14" t="s">
@@ -6571,13 +6599,13 @@
         <v>173</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I27" s="14" t="s">
         <v>173</v>
       </c>
       <c r="J27" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K27" s="14" t="s">
         <v>173</v>
@@ -6588,13 +6616,13 @@
     </row>
     <row r="28" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
+        <v>276</v>
+      </c>
+      <c r="C28" t="s">
         <v>277</v>
       </c>
-      <c r="C28" t="s">
-        <v>278</v>
-      </c>
       <c r="D28" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
@@ -6602,28 +6630,28 @@
         <v>173</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I28" s="31"/>
       <c r="J28" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K28" s="14" t="s">
         <v>173</v>
       </c>
       <c r="L28" s="25" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E29" s="22"/>
       <c r="F29" s="22"/>
@@ -6631,11 +6659,11 @@
         <v>173</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I29" s="31"/>
       <c r="J29" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K29" s="14" t="s">
         <v>173</v>
@@ -6645,51 +6673,27 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A31" t="s">
+      <c r="L31" s="14" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A32" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32">
+      <c r="L32" s="14" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33">
         <v>3578804</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>177</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>128</v>
-      </c>
-      <c r="D32" t="s">
-        <v>178</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="I32" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="J32" s="29" t="s">
-        <v>291</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33">
-        <v>9289704</v>
-      </c>
-      <c r="B33" t="s">
-        <v>179</v>
-      </c>
-      <c r="C33" t="s">
-        <v>49</v>
       </c>
       <c r="D33" t="s">
         <v>178</v>
@@ -6703,23 +6707,28 @@
       <c r="G33" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="I33" s="22"/>
+      <c r="I33" s="14" t="s">
+        <v>173</v>
+      </c>
       <c r="J33" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K33" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L33" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
-        <v>9344404</v>
+        <v>9289704</v>
       </c>
       <c r="B34" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C34" t="s">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="D34" t="s">
         <v>178</v>
@@ -6731,25 +6740,28 @@
         <v>173</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="I34" s="31"/>
+        <v>173</v>
+      </c>
+      <c r="I34" s="22"/>
       <c r="J34" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K34" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L34" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
-        <v>6746404</v>
+        <v>9344404</v>
       </c>
       <c r="B35" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C35" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D35" t="s">
         <v>178</v>
@@ -6763,23 +6775,24 @@
       <c r="G35" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="I35" s="22"/>
+      <c r="I35" s="31"/>
       <c r="J35" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K35" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L35" s="22"/>
+    </row>
+    <row r="36" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
-        <v>9257604</v>
+        <v>6746404</v>
       </c>
       <c r="B36" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C36" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D36" t="s">
         <v>178</v>
@@ -6791,85 +6804,96 @@
         <v>173</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="I36" s="14" t="s">
-        <v>173</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="I36" s="22"/>
       <c r="J36" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K36" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L36" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
-        <v>9717204</v>
+        <v>9257604</v>
       </c>
       <c r="B37" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C37" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D37" t="s">
         <v>178</v>
       </c>
-      <c r="E37" s="15" t="s">
-        <v>236</v>
+      <c r="E37" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="F37" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="G37" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="I37" s="22"/>
+      <c r="G37" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>173</v>
+      </c>
       <c r="J37" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K37" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L37" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
-        <v>2298204</v>
+        <v>9717204</v>
       </c>
       <c r="B38" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C38" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D38" t="s">
         <v>178</v>
       </c>
-      <c r="E38" s="14" t="s">
-        <v>173</v>
+      <c r="E38" s="15" t="s">
+        <v>236</v>
       </c>
       <c r="F38" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="G38" s="14" t="s">
-        <v>173</v>
+      <c r="G38" s="29" t="s">
+        <v>236</v>
       </c>
       <c r="I38" s="22"/>
       <c r="J38" s="29" t="s">
-        <v>291</v>
-      </c>
-      <c r="K38" s="22"/>
-    </row>
-    <row r="39" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>290</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="L38" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
-        <v>5784804</v>
+        <v>2298204</v>
       </c>
       <c r="B39" t="s">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="C39" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D39" t="s">
         <v>178</v>
@@ -6883,25 +6907,24 @@
       <c r="G39" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="I39" s="14" t="s">
-        <v>173</v>
-      </c>
+      <c r="I39" s="22"/>
       <c r="J39" s="29" t="s">
-        <v>291</v>
-      </c>
-      <c r="K39" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>290</v>
+      </c>
+      <c r="K39" s="22"/>
+      <c r="L39" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
-        <v>9321704</v>
+        <v>5784804</v>
       </c>
       <c r="B40" t="s">
-        <v>191</v>
+        <v>98</v>
       </c>
       <c r="C40" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D40" t="s">
         <v>178</v>
@@ -6919,19 +6942,24 @@
         <v>173</v>
       </c>
       <c r="J40" s="29" t="s">
-        <v>291</v>
-      </c>
-      <c r="K40" s="22"/>
-    </row>
-    <row r="41" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>290</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="L40" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
-        <v>9720304</v>
+        <v>9321704</v>
       </c>
       <c r="B41" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C41" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D41" t="s">
         <v>178</v>
@@ -6945,25 +6973,26 @@
       <c r="G41" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="I41" s="28" t="s">
-        <v>267</v>
+      <c r="I41" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="J41" s="29" t="s">
-        <v>291</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>290</v>
+      </c>
+      <c r="K41" s="22"/>
+      <c r="L41" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
-        <v>9317404</v>
+        <v>9720304</v>
       </c>
       <c r="B42" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C42" t="s">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="D42" t="s">
         <v>178</v>
@@ -6977,20 +7006,25 @@
       <c r="G42" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="I42" s="22"/>
+      <c r="I42" s="28" t="s">
+        <v>266</v>
+      </c>
       <c r="J42" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K42" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L42" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
-        <v>8333604</v>
+        <v>9317404</v>
       </c>
       <c r="B43" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C43" t="s">
         <v>67</v>
@@ -7007,13 +7041,49 @@
       <c r="G43" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="I43" s="14" t="s">
-        <v>173</v>
-      </c>
+      <c r="I43" s="22"/>
       <c r="J43" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K43" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="L43" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44">
+        <v>8333604</v>
+      </c>
+      <c r="B44" t="s">
+        <v>196</v>
+      </c>
+      <c r="C44" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" t="s">
+        <v>178</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="J44" s="29" t="s">
+        <v>290</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="L44" s="14" t="s">
         <v>173</v>
       </c>
     </row>
@@ -7041,10 +7111,10 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B3" t="s">
         <v>274</v>
-      </c>
-      <c r="B3" t="s">
-        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1197" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FEA22CA-8968-4E51-825E-63A1637ABBDE}"/>
+  <xr:revisionPtr revIDLastSave="1218" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08C6F171-EA88-4293-8718-AD7293440054}"/>
   <bookViews>
     <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -738,7 +738,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="338">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1734,6 +1734,24 @@
   </si>
   <si>
     <t>Α.5.M2 Έλεγχος Λειτουργίας Δικτύου - Μέρος 2</t>
+  </si>
+  <si>
+    <t>12-17/10/2026</t>
+  </si>
+  <si>
+    <t>B41M10 - Συναρτήσεις</t>
+  </si>
+  <si>
+    <t>B41M11 - Βασική Μορφοποίηση Υπολογιστικού Φύλλου</t>
+  </si>
+  <si>
+    <t>B41M12 - Μορφοποίηση Υπολογιστικού Φύλλου</t>
+  </si>
+  <si>
+    <t>Erevna - Kahoot B41M9</t>
+  </si>
+  <si>
+    <t>Erevna - kahoot B41M8</t>
   </si>
 </sst>
 </file>
@@ -2576,7 +2594,7 @@
     <col min="10" max="10" width="58.5859375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="65.5859375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="56" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="43.41015625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="47.8203125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="43.05859375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="34.17578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="34.17578125" style="1" customWidth="1"/>
@@ -2856,6 +2874,18 @@
       <c r="K13" s="19" t="s">
         <v>304</v>
       </c>
+      <c r="L13" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A14" s="5" t="s">
@@ -2891,7 +2921,10 @@
       <c r="K14" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>303</v>
       </c>
     </row>
@@ -2928,6 +2961,18 @@
       </c>
       <c r="K15" s="19" t="s">
         <v>303</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.5">
@@ -3283,6 +3328,10 @@
         <v>305</v>
       </c>
       <c r="K2" s="35"/>
+      <c r="L2" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="M2" s="35"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9" t="s">
@@ -4580,10 +4629,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4593,119 +4643,55 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23D143C4-24B5-4F25-A9AC-CA5F9ACC8C3E}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="49.87890625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.76171875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.9375" customWidth="1"/>
     <col min="9" max="9" width="44.234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>315</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>316</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>317</v>
       </c>
       <c r="C3" t="s">
         <v>318</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="H4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="H5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" s="19" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.5">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>323</v>
       </c>
       <c r="C6" t="s">
         <v>322</v>
       </c>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.5">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
         <v>324</v>
       </c>
       <c r="C7" t="s">
         <v>325</v>
       </c>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.5">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>327</v>
       </c>
       <c r="C8" t="s">
         <v>326</v>
-      </c>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="H10" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="H11" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="H12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="H13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I13" s="19" t="s">
-        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1218" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08C6F171-EA88-4293-8718-AD7293440054}"/>
+  <xr:revisionPtr revIDLastSave="1242" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26EC57FD-9CE8-40E7-A25E-F22CF0798A2A}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -738,7 +738,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="340">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1752,13 +1752,19 @@
   </si>
   <si>
     <t>Erevna - kahoot B41M8</t>
+  </si>
+  <si>
+    <t>how satelline internet works</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/POplsN2fjB8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1803,6 +1809,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="161"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1936,10 +1950,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2022,8 +2037,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2602,7 +2619,7 @@
     <col min="18" max="16384" width="9.05859375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="7"/>
       <c r="B1" s="33" t="s">
         <v>33</v>
@@ -2633,12 +2650,12 @@
       </c>
       <c r="O1" s="34"/>
     </row>
-    <row r="2" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2649,7 +2666,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -2683,11 +2700,14 @@
       <c r="K4" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="M4" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -2724,8 +2744,11 @@
       <c r="L5" s="4" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.5">
+      <c r="M5" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
@@ -2769,7 +2792,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
@@ -2803,11 +2826,14 @@
       <c r="K7" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="M7" s="4" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
         <v>284</v>
       </c>
@@ -2818,7 +2844,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>285</v>
       </c>
@@ -2826,7 +2852,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A12" s="5" t="s">
         <v>1</v>
       </c>
@@ -2836,11 +2862,11 @@
       <c r="C12" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
@@ -2874,20 +2900,23 @@
       <c r="K13" s="19" t="s">
         <v>304</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="L13" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="O13" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A14" s="5" t="s">
         <v>7</v>
       </c>
@@ -2921,14 +2950,17 @@
       <c r="K14" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="L14" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="N14" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
@@ -2962,16 +2994,19 @@
       <c r="K15" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="L15" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="M15" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="O15" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="O15" s="1" t="s">
+      <c r="P15" s="1" t="s">
         <v>335</v>
       </c>
     </row>
@@ -4643,7 +4678,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23D143C4-24B5-4F25-A9AC-CA5F9ACC8C3E}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="49.87890625" bestFit="1" customWidth="1"/>
@@ -4666,7 +4701,7 @@
       <c r="A3" t="s">
         <v>317</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="36" t="s">
         <v>318</v>
       </c>
     </row>
@@ -4694,9 +4729,20 @@
         <v>326</v>
       </c>
     </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C9" t="s">
+        <v>339</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{2329A344-AF26-4B9C-98D4-47024E1629FE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1242" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26EC57FD-9CE8-40E7-A25E-F22CF0798A2A}"/>
+  <xr:revisionPtr revIDLastSave="1320" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{508FD441-286B-4530-BAB9-502536B5EB91}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -581,8 +581,6 @@
     <author>tc={81BD84F6-8A20-4389-8E36-72D27C355E7D}</author>
     <author>tc={1C5012ED-C19D-4FFE-B3C1-C22FC7299932}</author>
     <author>tc={B1153885-2C0F-4184-AEAF-6AEB6FB8C116}</author>
-    <author>tc={13BAF8B4-566F-4259-B437-A7E77861B871}</author>
-    <author>tc={EA0DFC21-2EEC-4333-BA25-5580879FF4BF}</author>
     <author>tc={D1B5C973-E93C-423C-8CC6-340934B20F0E}</author>
     <author>tc={598384F6-CAC4-4E14-937B-755974DF65A2}</author>
     <author>tc={261E6CBF-FE75-4CEB-AA30-1B52D29531DF}</author>
@@ -637,24 +635,7 @@
     Blond, quiet</t>
       </text>
     </comment>
-    <comment ref="C18" authorId="5" shapeId="0" xr:uid="{13BAF8B4-566F-4259-B437-A7E77861B871}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Indifferent
-</t>
-      </text>
-    </comment>
-    <comment ref="F18" authorId="6" shapeId="0" xr:uid="{EA0DFC21-2EEC-4333-BA25-5580879FF4BF}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    No effort, left class without asking permission, opened her phone, but I didn't says anything because they said some of their friends died from motorcycle accident.</t>
-      </text>
-    </comment>
-    <comment ref="C24" authorId="7" shapeId="0" xr:uid="{D1B5C973-E93C-423C-8CC6-340934B20F0E}">
+    <comment ref="C23" authorId="5" shapeId="0" xr:uid="{D1B5C973-E93C-423C-8CC6-340934B20F0E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -662,7 +643,7 @@
     Good student</t>
       </text>
     </comment>
-    <comment ref="C34" authorId="8" shapeId="0" xr:uid="{598384F6-CAC4-4E14-937B-755974DF65A2}">
+    <comment ref="C33" authorId="6" shapeId="0" xr:uid="{598384F6-CAC4-4E14-937B-755974DF65A2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -672,7 +653,7 @@
     Ligo prixtissa, alla kali.</t>
       </text>
     </comment>
-    <comment ref="C35" authorId="9" shapeId="0" xr:uid="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
+    <comment ref="C34" authorId="7" shapeId="0" xr:uid="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -684,7 +665,7 @@
     Keep an eye on him.</t>
       </text>
     </comment>
-    <comment ref="G35" authorId="10" shapeId="0" xr:uid="{05F8CCDA-D71B-40DF-B68D-97E9813023D7}">
+    <comment ref="G34" authorId="8" shapeId="0" xr:uid="{05F8CCDA-D71B-40DF-B68D-97E9813023D7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -692,7 +673,7 @@
     Epiase to kinito tou simmathiti tou, kai mou eipe psemata otan ton rotisa.</t>
       </text>
     </comment>
-    <comment ref="C36" authorId="11" shapeId="0" xr:uid="{B7F8AA97-EF7A-4346-BFE7-BFF2EEB2C1DB}">
+    <comment ref="C35" authorId="9" shapeId="0" xr:uid="{B7F8AA97-EF7A-4346-BFE7-BFF2EEB2C1DB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -700,7 +681,7 @@
     Fenete filotimos, with some knowledge</t>
       </text>
     </comment>
-    <comment ref="E38" authorId="12" shapeId="0" xr:uid="{D7246692-A47D-44D0-B75A-AD5BAC8A45F7}">
+    <comment ref="E37" authorId="10" shapeId="0" xr:uid="{D7246692-A47D-44D0-B75A-AD5BAC8A45F7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -708,7 +689,7 @@
     No effort, left class without asking permission, opened her phone, but I didn't says anything because they said some of their friends died from motorcycle accident.</t>
       </text>
     </comment>
-    <comment ref="C39" authorId="13" shapeId="0" xr:uid="{7768E2F5-6F98-401C-9CE0-F5514C8493B1}">
+    <comment ref="C38" authorId="11" shapeId="0" xr:uid="{7768E2F5-6F98-401C-9CE0-F5514C8493B1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -716,7 +697,7 @@
     Kori tis Lelias</t>
       </text>
     </comment>
-    <comment ref="C43" authorId="14" shapeId="0" xr:uid="{2EB8A751-6FC9-43E4-BEFE-D7B2A37941A4}">
+    <comment ref="C42" authorId="12" shapeId="0" xr:uid="{2EB8A751-6FC9-43E4-BEFE-D7B2A37941A4}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -725,7 +706,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="C44" authorId="15" shapeId="0" xr:uid="{BEA4804D-72CD-494C-BE39-4999EABE6959}">
+    <comment ref="C43" authorId="13" shapeId="0" xr:uid="{BEA4804D-72CD-494C-BE39-4999EABE6959}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -738,7 +719,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="342">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1430,12 +1411,6 @@
     <t>Ραμόνα</t>
   </si>
   <si>
-    <t>Μαρκουλή</t>
-  </si>
-  <si>
-    <t>Ελένη</t>
-  </si>
-  <si>
     <t xml:space="preserve">Φιλιππός </t>
   </si>
   <si>
@@ -1748,9 +1723,6 @@
     <t>B41M12 - Μορφοποίηση Υπολογιστικού Φύλλου</t>
   </si>
   <si>
-    <t>Erevna - Kahoot B41M9</t>
-  </si>
-  <si>
     <t>Erevna - kahoot B41M8</t>
   </si>
   <si>
@@ -1758,6 +1730,21 @@
   </si>
   <si>
     <t>https://www.youtube.com/shorts/POplsN2fjB8</t>
+  </si>
+  <si>
+    <t>12-16/10  2026</t>
+  </si>
+  <si>
+    <t>A5.2 Μ1 - Proton mail - Νοήτικό στήριγμα - Δημιουργία και αποστολή εμαιλ</t>
+  </si>
+  <si>
+    <t>hw: sent me email</t>
+  </si>
+  <si>
+    <t>οι βαθμοί μου στο excel</t>
+  </si>
+  <si>
+    <t>Erevna - Kahoot B41M9 aksiologisis</t>
   </si>
 </sst>
 </file>
@@ -1954,7 +1941,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2028,16 +2015,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2549,48 +2539,41 @@
   <threadedComment ref="C16" dT="2026-09-17T05:12:57.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B1153885-2C0F-4184-AEAF-6AEB6FB8C116}">
     <text>Blond, quiet</text>
   </threadedComment>
-  <threadedComment ref="C18" dT="2026-09-17T05:16:25.25" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{13BAF8B4-566F-4259-B437-A7E77861B871}">
-    <text xml:space="preserve">Indifferent
-</text>
-  </threadedComment>
-  <threadedComment ref="F18" dT="2026-09-15T15:38:58.71" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{EA0DFC21-2EEC-4333-BA25-5580879FF4BF}">
+  <threadedComment ref="C23" dT="2026-09-22T09:31:23.10" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D1B5C973-E93C-423C-8CC6-340934B20F0E}">
+    <text>Good student</text>
+  </threadedComment>
+  <threadedComment ref="C33" dT="2026-09-17T05:56:45.08" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{598384F6-CAC4-4E14-937B-755974DF65A2}">
+    <text>Not very careful</text>
+  </threadedComment>
+  <threadedComment ref="C33" dT="2026-09-22T09:33:55.26" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{ABE83869-780E-416C-839B-791C9FC8D78D}" parentId="{598384F6-CAC4-4E14-937B-755974DF65A2}">
+    <text>Ligo prixtissa, alla kali.</text>
+  </threadedComment>
+  <threadedComment ref="C34" dT="2026-09-17T05:57:00.11" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
+    <text>Get bored, starts playing games</text>
+  </threadedComment>
+  <threadedComment ref="C34" dT="2026-09-22T09:34:55.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{13FEE7CC-818A-4309-AB99-FB756416F0D5}" parentId="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
+    <text>Not paying attention</text>
+  </threadedComment>
+  <threadedComment ref="C34" dT="2026-09-22T15:27:55.30" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{A8F8C615-6F8E-4F6F-9D9D-27AE9362CCDE}" parentId="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
+    <text>Keep an eye on him.</text>
+  </threadedComment>
+  <threadedComment ref="G34" dT="2026-09-22T15:27:37.74" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{05F8CCDA-D71B-40DF-B68D-97E9813023D7}">
+    <text>Epiase to kinito tou simmathiti tou, kai mou eipe psemata otan ton rotisa.</text>
+  </threadedComment>
+  <threadedComment ref="C35" dT="2026-09-17T05:56:20.80" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B7F8AA97-EF7A-4346-BFE7-BFF2EEB2C1DB}">
+    <text>Fenete filotimos, with some knowledge</text>
+  </threadedComment>
+  <threadedComment ref="E37" dT="2026-09-15T15:38:58.71" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D7246692-A47D-44D0-B75A-AD5BAC8A45F7}">
     <text>No effort, left class without asking permission, opened her phone, but I didn't says anything because they said some of their friends died from motorcycle accident.</text>
   </threadedComment>
-  <threadedComment ref="C24" dT="2026-09-22T09:31:23.10" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D1B5C973-E93C-423C-8CC6-340934B20F0E}">
-    <text>Good student</text>
-  </threadedComment>
-  <threadedComment ref="C34" dT="2026-09-17T05:56:45.08" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{598384F6-CAC4-4E14-937B-755974DF65A2}">
-    <text>Not very careful</text>
-  </threadedComment>
-  <threadedComment ref="C34" dT="2026-09-22T09:33:55.26" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{ABE83869-780E-416C-839B-791C9FC8D78D}" parentId="{598384F6-CAC4-4E14-937B-755974DF65A2}">
-    <text>Ligo prixtissa, alla kali.</text>
-  </threadedComment>
-  <threadedComment ref="C35" dT="2026-09-17T05:57:00.11" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
-    <text>Get bored, starts playing games</text>
-  </threadedComment>
-  <threadedComment ref="C35" dT="2026-09-22T09:34:55.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{13FEE7CC-818A-4309-AB99-FB756416F0D5}" parentId="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
-    <text>Not paying attention</text>
-  </threadedComment>
-  <threadedComment ref="C35" dT="2026-09-22T15:27:55.30" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{A8F8C615-6F8E-4F6F-9D9D-27AE9362CCDE}" parentId="{261E6CBF-FE75-4CEB-AA30-1B52D29531DF}">
-    <text>Keep an eye on him.</text>
-  </threadedComment>
-  <threadedComment ref="G35" dT="2026-09-22T15:27:37.74" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{05F8CCDA-D71B-40DF-B68D-97E9813023D7}">
-    <text>Epiase to kinito tou simmathiti tou, kai mou eipe psemata otan ton rotisa.</text>
-  </threadedComment>
-  <threadedComment ref="C36" dT="2026-09-17T05:56:20.80" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B7F8AA97-EF7A-4346-BFE7-BFF2EEB2C1DB}">
-    <text>Fenete filotimos, with some knowledge</text>
-  </threadedComment>
-  <threadedComment ref="E38" dT="2026-09-15T15:38:58.71" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D7246692-A47D-44D0-B75A-AD5BAC8A45F7}">
-    <text>No effort, left class without asking permission, opened her phone, but I didn't says anything because they said some of their friends died from motorcycle accident.</text>
-  </threadedComment>
-  <threadedComment ref="C39" dT="2026-09-22T09:33:38.73" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7768E2F5-6F98-401C-9CE0-F5514C8493B1}">
+  <threadedComment ref="C38" dT="2026-09-22T09:33:38.73" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7768E2F5-6F98-401C-9CE0-F5514C8493B1}">
     <text>Kori tis Lelias</text>
   </threadedComment>
-  <threadedComment ref="C43" dT="2026-09-17T05:53:15.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2EB8A751-6FC9-43E4-BEFE-D7B2A37941A4}">
+  <threadedComment ref="C42" dT="2026-09-17T05:53:15.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2EB8A751-6FC9-43E4-BEFE-D7B2A37941A4}">
     <text xml:space="preserve">Filotimos
 </text>
   </threadedComment>
-  <threadedComment ref="C44" dT="2026-09-17T05:55:56.16" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{BEA4804D-72CD-494C-BE39-4999EABE6959}">
+  <threadedComment ref="C43" dT="2026-09-17T05:55:56.16" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{BEA4804D-72CD-494C-BE39-4999EABE6959}">
     <text>With glasses</text>
   </threadedComment>
 </ThreadedComments>
@@ -2610,45 +2593,45 @@
     <col min="9" max="9" width="42.17578125" style="1" customWidth="1"/>
     <col min="10" max="10" width="58.5859375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="65.5859375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="56" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="47.8203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="61.87890625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="64.234375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="43.05859375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="34.17578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34.17578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="47.8203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="41.64453125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="21.52734375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="16384" width="9.05859375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="7"/>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="33" t="s">
+      <c r="C1" s="37"/>
+      <c r="D1" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="34"/>
-      <c r="F1" s="33" t="s">
-        <v>238</v>
-      </c>
-      <c r="G1" s="34"/>
-      <c r="H1" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="K1" s="34"/>
-      <c r="L1" s="33" t="s">
-        <v>251</v>
-      </c>
-      <c r="M1" s="34"/>
-      <c r="N1" s="33" t="s">
-        <v>252</v>
-      </c>
-      <c r="O1" s="34"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="G1" s="37"/>
+      <c r="H1" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1" s="37"/>
+      <c r="J1" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="K1" s="37"/>
+      <c r="L1" s="36" t="s">
+        <v>249</v>
+      </c>
+      <c r="M1" s="37"/>
+      <c r="N1" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="O1" s="37"/>
     </row>
     <row r="2" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
@@ -2671,7 +2654,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
@@ -2686,25 +2669,25 @@
         <v>31</v>
       </c>
       <c r="G4" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="J4" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="K4" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="I4" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="K4" s="19" t="s">
-        <v>259</v>
-      </c>
       <c r="L4" s="17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>300</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.5">
@@ -2721,31 +2704,34 @@
         <v>30</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>31</v>
       </c>
       <c r="G5" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="J5" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="K5" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="I5" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="J5" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="K5" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>301</v>
+      <c r="L5" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.5">
@@ -2765,31 +2751,34 @@
         <v>31</v>
       </c>
       <c r="F6" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="I6" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="J6" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="H6" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>259</v>
-      </c>
       <c r="K6" s="19" t="s">
-        <v>320</v>
-      </c>
-      <c r="L6" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.5">
@@ -2797,7 +2786,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
@@ -2806,50 +2795,50 @@
         <v>18</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G7" s="19" t="s">
         <v>31</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I7" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="M7" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.5">
@@ -2863,7 +2852,7 @@
         <v>176</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.5">
@@ -2883,37 +2872,37 @@
         <v>32</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G13" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="I13" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="H13" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="I13" s="19" t="s">
-        <v>263</v>
-      </c>
       <c r="J13" s="19" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L13" s="17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="N13" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="P13" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.5">
@@ -2930,34 +2919,34 @@
         <v>28</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F14" s="19" t="s">
         <v>32</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H14" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="J14" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="I14" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>263</v>
-      </c>
       <c r="K14" s="17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L14" s="17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.5">
@@ -2974,40 +2963,40 @@
         <v>28</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F15" s="19" t="s">
         <v>32</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H15" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="J15" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="I15" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="J15" s="19" t="s">
-        <v>263</v>
-      </c>
       <c r="K15" s="19" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L15" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>304</v>
+        <v>240</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>302</v>
       </c>
       <c r="N15" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="P15" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.5">
@@ -3018,12 +3007,12 @@
         <v>35</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.5">
       <c r="H19" s="30" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.5">
@@ -3040,46 +3029,46 @@
         <v>174</v>
       </c>
       <c r="E20" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="F20" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="F20" s="21" t="s">
-        <v>239</v>
-      </c>
       <c r="G20" s="21" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H20" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="J20" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="I20" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="J20" s="19" t="s">
+      <c r="K20" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="N20" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="K20" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="N20" s="4" t="s">
+      <c r="O20" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="P20" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q20" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="O20" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="P20" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q20" s="4" t="s">
-        <v>249</v>
-      </c>
       <c r="R20" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.5">
@@ -3096,46 +3085,46 @@
         <v>174</v>
       </c>
       <c r="E21" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="F21" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="F21" s="21" t="s">
-        <v>239</v>
-      </c>
       <c r="G21" s="21" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H21" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="J21" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="I21" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="J21" s="19" t="s">
+      <c r="K21" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="N21" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="K21" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="N21" s="4" t="s">
+      <c r="O21" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="P21" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q21" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="O21" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="P21" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q21" s="4" t="s">
-        <v>249</v>
-      </c>
       <c r="R21" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.5">
@@ -3152,49 +3141,49 @@
         <v>174</v>
       </c>
       <c r="E22" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="F22" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="F22" s="21" t="s">
-        <v>239</v>
-      </c>
       <c r="G22" s="17" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J22" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="K22" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="K22" s="19" t="s">
+      <c r="L22" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="O22" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="L22" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="O22" s="4" t="s">
+      <c r="P22" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q22" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="R22" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="P22" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q22" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="R22" s="4" t="s">
-        <v>249</v>
-      </c>
       <c r="S22" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.5">
@@ -3225,19 +3214,22 @@
         <v>172</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="K24" s="19" t="s">
         <v>172</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.5">
@@ -3282,7 +3274,7 @@
         <v>22</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.5">
@@ -3298,7 +3290,7 @@
         <v>24</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -3320,7 +3312,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0C9DD2-633E-44CA-9A93-86B2E2731C82}">
-  <dimension ref="A1:P60"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.3515625" style="9" bestFit="1" customWidth="1"/>
@@ -3333,10 +3325,12 @@
     <col min="8" max="8" width="13.52734375" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.17578125" style="9" customWidth="1"/>
     <col min="10" max="10" width="14.52734375" style="9" customWidth="1"/>
-    <col min="11" max="16384" width="9.05859375" style="9"/>
+    <col min="11" max="11" width="18.9375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.64453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.05859375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="13" t="s">
         <v>57</v>
       </c>
@@ -3350,33 +3344,33 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="35" t="s">
-        <v>291</v>
-      </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35" t="s">
-        <v>292</v>
-      </c>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35" t="s">
-        <v>305</v>
-      </c>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35" t="s">
-        <v>332</v>
-      </c>
-      <c r="M2" s="35"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="F2" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="M2" s="34"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9" t="s">
         <v>121</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="9">
         <v>9285104</v>
       </c>
@@ -3395,10 +3389,13 @@
       <c r="H4" s="22"/>
       <c r="I4" s="22"/>
       <c r="J4" s="24" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>234</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="9">
         <v>8324104</v>
       </c>
@@ -3423,8 +3420,11 @@
       <c r="J5" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L5" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="9">
         <v>6811804</v>
       </c>
@@ -3449,11 +3449,11 @@
       <c r="J6" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P6" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L6" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="9">
         <v>5436904</v>
       </c>
@@ -3478,11 +3478,11 @@
       <c r="J7" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P7" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L7" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="9">
         <v>7025704</v>
       </c>
@@ -3507,11 +3507,11 @@
       <c r="J8" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P8" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L8" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="9">
         <v>8435804</v>
       </c>
@@ -3536,11 +3536,11 @@
       <c r="J9" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P9" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L9" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="9">
         <v>5069104</v>
       </c>
@@ -3565,11 +3565,11 @@
       <c r="J10" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P10" s="9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L10" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="9">
         <v>5222304</v>
       </c>
@@ -3594,11 +3594,11 @@
       <c r="J11" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P11" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L11" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="9">
         <v>1981204</v>
       </c>
@@ -3623,11 +3623,11 @@
       <c r="J12" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P12" s="9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L12" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="9">
         <v>3766704</v>
       </c>
@@ -3650,36 +3650,31 @@
       <c r="J13" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P13" s="9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="P14" s="9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L13" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="9" t="s">
         <v>72</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="P15" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>307</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="9">
         <v>5551204</v>
       </c>
@@ -3707,11 +3702,11 @@
       <c r="J16" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P16" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L16" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="9">
         <v>2056004</v>
       </c>
@@ -3737,11 +3732,11 @@
       <c r="J17" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P17" s="9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L17" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="9">
         <v>3318504</v>
       </c>
@@ -3769,11 +3764,11 @@
       <c r="J18" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P18" s="9">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L18" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="9">
         <v>4926804</v>
       </c>
@@ -3801,11 +3796,11 @@
       <c r="J19" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P19" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L19" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="9">
         <v>7568204</v>
       </c>
@@ -3831,11 +3826,11 @@
       <c r="J20" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P20" s="9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L20" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="9">
         <v>5111404</v>
       </c>
@@ -3861,11 +3856,11 @@
       <c r="J21" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P21" s="9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L21" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="9">
         <v>4332504</v>
       </c>
@@ -3893,11 +3888,11 @@
       <c r="J22" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P22" s="9">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L22" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="9">
         <v>4424904</v>
       </c>
@@ -3925,11 +3920,11 @@
       <c r="J23" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P23" s="9">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L23" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="9">
         <v>4934404</v>
       </c>
@@ -3957,20 +3952,20 @@
       <c r="J24" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P24" s="9">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L24" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>299</v>
-      </c>
       <c r="E25" s="12" t="s">
         <v>173</v>
       </c>
@@ -3986,30 +3981,22 @@
       <c r="J25" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P25" s="9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="P26" s="9">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="L25" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="9" t="s">
         <v>140</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="P27" s="9">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="9">
         <v>9189004</v>
       </c>
@@ -4034,11 +4021,8 @@
       <c r="I28" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P28" s="9">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="9">
         <v>5682904</v>
       </c>
@@ -4063,11 +4047,8 @@
       <c r="I29" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P29" s="9">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="9">
         <v>9217204</v>
       </c>
@@ -4088,11 +4069,8 @@
       <c r="I30" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P30" s="9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="9">
         <v>7319504</v>
       </c>
@@ -4117,11 +4095,8 @@
       <c r="I31" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P31" s="9">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="9">
         <v>9254304</v>
       </c>
@@ -4146,11 +4121,8 @@
       <c r="I32" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P32" s="9">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="9">
         <v>2428404</v>
       </c>
@@ -4175,11 +4147,8 @@
       <c r="I33" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P33" s="9">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="9">
         <v>2427904</v>
       </c>
@@ -4205,7 +4174,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="9">
         <v>8373704</v>
       </c>
@@ -4231,7 +4200,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="9">
         <v>5155004</v>
       </c>
@@ -4257,7 +4226,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="9">
         <v>1006390</v>
       </c>
@@ -4283,15 +4252,15 @@
         <v>173</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="9" t="s">
         <v>157</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="9">
         <v>5324204</v>
       </c>
@@ -4322,8 +4291,14 @@
       <c r="J41" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="K41" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L41" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="9">
         <v>5996604</v>
       </c>
@@ -4343,7 +4318,7 @@
         <v>173</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H42" s="12" t="s">
         <v>173</v>
@@ -4354,8 +4329,14 @@
       <c r="J42" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="K42" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L42" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="9">
         <v>7153704</v>
       </c>
@@ -4369,25 +4350,31 @@
         <v>159</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G43" s="12" t="s">
         <v>173</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I43" s="24" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J43" s="24" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>234</v>
+      </c>
+      <c r="K43" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L43" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="9">
         <v>9185204</v>
       </c>
@@ -4404,10 +4391,10 @@
         <v>173</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G44" s="25" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H44" s="12" t="s">
         <v>173</v>
@@ -4416,10 +4403,16 @@
         <v>173</v>
       </c>
       <c r="J44" s="24" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>234</v>
+      </c>
+      <c r="K44" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L44" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="9">
         <v>9185504</v>
       </c>
@@ -4436,7 +4429,7 @@
         <v>173</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>173</v>
@@ -4448,10 +4441,16 @@
         <v>173</v>
       </c>
       <c r="J45" s="24" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>234</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L45" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="9">
         <v>4913604</v>
       </c>
@@ -4468,10 +4467,10 @@
         <v>173</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G46" s="28" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H46" s="12" t="s">
         <v>173</v>
@@ -4482,8 +4481,14 @@
       <c r="J46" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="K46" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L46" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="9">
         <v>5436204</v>
       </c>
@@ -4514,8 +4519,14 @@
       <c r="J47" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="K47" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L47" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="9">
         <v>3506004</v>
       </c>
@@ -4546,8 +4557,14 @@
       <c r="J48" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K48" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L48" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="9">
         <v>6757304</v>
       </c>
@@ -4578,8 +4595,14 @@
       <c r="J49" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K49" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L49" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="9">
         <v>6390804</v>
       </c>
@@ -4610,57 +4633,63 @@
       <c r="J50" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K50" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L50" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="22"/>
       <c r="B54" s="12" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="27" t="s">
         <v>173</v>
       </c>
       <c r="B55" s="12" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B56" s="12" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="31"/>
       <c r="B57" s="12" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="24" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B58" s="12" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="26" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="25" t="s">
+      <c r="B60" s="12" t="s">
         <v>270</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -4689,52 +4718,52 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C3" s="36" t="s">
-        <v>318</v>
+        <v>315</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C9" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -4748,17 +4777,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A321353-3FB1-4427-84C3-E63782B65799}">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.3515625" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.05859375" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.8203125" style="9" customWidth="1"/>
     <col min="4" max="4" width="6.703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.05859375" style="9"/>
+    <col min="5" max="10" width="9.05859375" style="9"/>
+    <col min="11" max="11" width="9.8203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.05859375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="10" t="s">
         <v>57</v>
       </c>
@@ -4772,26 +4803,30 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="35" t="s">
-        <v>291</v>
-      </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35" t="s">
-        <v>292</v>
-      </c>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35" t="s">
-        <v>307</v>
-      </c>
-      <c r="K2" s="35"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="F2" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="M2" s="34"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="9">
         <v>1025518</v>
       </c>
@@ -4814,13 +4849,16 @@
         <v>173</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>264</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="9">
         <v>4298104</v>
       </c>
@@ -4846,8 +4884,11 @@
         <v>173</v>
       </c>
       <c r="I5" s="22"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L5" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="9">
         <v>1033606</v>
       </c>
@@ -4867,16 +4908,19 @@
         <v>173</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>173</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>264</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="9">
         <v>1033506</v>
       </c>
@@ -4902,8 +4946,11 @@
       <c r="I7" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L7" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="9">
         <v>1026254</v>
       </c>
@@ -4931,8 +4978,11 @@
       <c r="I8" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L8" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="9">
         <v>1028366</v>
       </c>
@@ -4952,7 +5002,7 @@
         <v>173</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>173</v>
@@ -4960,8 +5010,11 @@
       <c r="I9" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L9" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="9">
         <v>1033023</v>
       </c>
@@ -4989,8 +5042,11 @@
       <c r="I10" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L10" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="9">
         <v>1032554</v>
       </c>
@@ -5018,8 +5074,11 @@
       <c r="I11" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L11" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="9">
         <v>1026281</v>
       </c>
@@ -5047,8 +5106,11 @@
       <c r="I12" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L12" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="9">
         <v>1029057</v>
       </c>
@@ -5076,13 +5138,16 @@
       <c r="I13" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L13" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="9" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="9">
         <v>1035828</v>
       </c>
@@ -5099,13 +5164,19 @@
         <v>173</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J16" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="K16" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L16" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="9">
         <v>1031619</v>
       </c>
@@ -5122,13 +5193,19 @@
         <v>173</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J17" s="26" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>269</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="9">
         <v>1037608</v>
       </c>
@@ -5145,13 +5222,19 @@
         <v>173</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>269</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L18" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="9">
         <v>1035515</v>
       </c>
@@ -5168,13 +5251,19 @@
         <v>173</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J19" s="26" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>269</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L19" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="9">
         <v>1030772</v>
       </c>
@@ -5191,13 +5280,19 @@
         <v>173</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J20" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="K20" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="9">
         <v>1026742</v>
       </c>
@@ -5214,13 +5309,19 @@
         <v>173</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J21" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="K21" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="9">
         <v>1038924</v>
       </c>
@@ -5242,8 +5343,14 @@
       <c r="J22" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="K22" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="9">
         <v>1029508</v>
       </c>
@@ -5260,13 +5367,19 @@
         <v>173</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J23" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="K23" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="9">
         <v>1028849</v>
       </c>
@@ -5283,23 +5396,29 @@
         <v>173</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J24" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="K24" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>39</v>
@@ -5316,8 +5435,14 @@
       <c r="K28" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L28" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="M28" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="9">
         <v>1027008</v>
       </c>
@@ -5331,7 +5456,7 @@
         <v>39</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>173</v>
@@ -5348,8 +5473,14 @@
       <c r="K29" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L29" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="M29" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="9">
         <v>1026200</v>
       </c>
@@ -5380,8 +5511,14 @@
       <c r="K30" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L30" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="M30" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="9">
         <v>1025833</v>
       </c>
@@ -5412,8 +5549,14 @@
       <c r="K31" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L31" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="M31" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="9">
         <v>1036053</v>
       </c>
@@ -5444,8 +5587,14 @@
       <c r="K32" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L32" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="M32" s="24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="9">
         <v>1029029</v>
       </c>
@@ -5476,8 +5625,14 @@
       <c r="K33" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L33" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="M33" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="9">
         <v>1028278</v>
       </c>
@@ -5508,8 +5663,14 @@
       <c r="K34" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L34" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="M34" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="9">
         <v>1025603</v>
       </c>
@@ -5526,20 +5687,26 @@
         <v>173</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J35" s="22"/>
       <c r="K35" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L35" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="M35" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="9">
         <v>1028053</v>
       </c>
@@ -5570,8 +5737,14 @@
       <c r="K36" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L36" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="M36" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="9">
         <v>1027036</v>
       </c>
@@ -5602,8 +5775,14 @@
       <c r="K37" s="12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="L37" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="M37" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="9">
         <v>1032361</v>
       </c>
@@ -5634,12 +5813,19 @@
       <c r="K38" s="12" t="s">
         <v>173</v>
       </c>
+      <c r="L38" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="M38" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5671,18 +5857,18 @@
       <c r="D1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="35" t="s">
-        <v>291</v>
-      </c>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35" t="s">
-        <v>292</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35" t="s">
-        <v>307</v>
-      </c>
-      <c r="J1" s="35"/>
+      <c r="E1" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="J1" s="34"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9">
@@ -5761,7 +5947,7 @@
         <v>173</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -5796,7 +5982,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF640171-D19A-4A22-AEE9-A5E7AF0F79D2}">
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="7.703125" bestFit="1" customWidth="1"/>
@@ -5804,10 +5990,10 @@
     <col min="3" max="3" width="17.9375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.17578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.29296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.3515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.3515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -5820,31 +6006,35 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="35" t="s">
-        <v>291</v>
-      </c>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35" t="s">
-        <v>292</v>
-      </c>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35" t="s">
-        <v>307</v>
-      </c>
-      <c r="L1" s="35"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="G1" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="L1" s="34"/>
+      <c r="M1" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="N1" s="35"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="K3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="L3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>4206804</v>
       </c>
@@ -5873,7 +6063,7 @@
         <v>173</v>
       </c>
       <c r="J4" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K4" s="14" t="s">
         <v>173</v>
@@ -5881,8 +6071,11 @@
       <c r="L4" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M4" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>9307104</v>
       </c>
@@ -5911,7 +6104,7 @@
         <v>173</v>
       </c>
       <c r="J5" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K5" s="14" t="s">
         <v>173</v>
@@ -5919,8 +6112,11 @@
       <c r="L5" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M5" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>2173704</v>
       </c>
@@ -5949,7 +6145,7 @@
         <v>173</v>
       </c>
       <c r="J6" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K6" s="14" t="s">
         <v>173</v>
@@ -5957,8 +6153,11 @@
       <c r="L6" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M6" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>9257304</v>
       </c>
@@ -5987,7 +6186,7 @@
         <v>173</v>
       </c>
       <c r="J7" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K7" s="14" t="s">
         <v>173</v>
@@ -5995,8 +6194,11 @@
       <c r="L7" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M7" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>2915404</v>
       </c>
@@ -6025,7 +6227,7 @@
         <v>173</v>
       </c>
       <c r="J8" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K8" s="14" t="s">
         <v>173</v>
@@ -6033,8 +6235,11 @@
       <c r="L8" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M8" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>2836604</v>
       </c>
@@ -6063,7 +6268,7 @@
         <v>173</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K9" s="14" t="s">
         <v>173</v>
@@ -6071,8 +6276,11 @@
       <c r="L9" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M9" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>1274904</v>
       </c>
@@ -6101,7 +6309,7 @@
         <v>173</v>
       </c>
       <c r="J10" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K10" s="14" t="s">
         <v>173</v>
@@ -6109,8 +6317,11 @@
       <c r="L10" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M10" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>3863304</v>
       </c>
@@ -6133,20 +6344,23 @@
         <v>173</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>173</v>
       </c>
       <c r="J11" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K11" s="22"/>
       <c r="L11" s="24" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>234</v>
+      </c>
+      <c r="M11" s="24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>3403504</v>
       </c>
@@ -6175,7 +6389,7 @@
         <v>173</v>
       </c>
       <c r="J12" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K12" s="14" t="s">
         <v>173</v>
@@ -6183,8 +6397,11 @@
       <c r="L12" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M12" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>4721304</v>
       </c>
@@ -6213,16 +6430,17 @@
         <v>173</v>
       </c>
       <c r="J13" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="L13" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L13" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="M13" s="31"/>
+    </row>
+    <row r="14" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>3924304</v>
       </c>
@@ -6245,13 +6463,13 @@
         <v>173</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I14" s="14" t="s">
         <v>173</v>
       </c>
       <c r="J14" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K14" s="14" t="s">
         <v>173</v>
@@ -6259,8 +6477,11 @@
       <c r="L14" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M14" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>4041704</v>
       </c>
@@ -6289,7 +6510,7 @@
         <v>173</v>
       </c>
       <c r="J15" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>173</v>
@@ -6297,8 +6518,11 @@
       <c r="L15" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M15" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>9280704</v>
       </c>
@@ -6327,7 +6551,7 @@
         <v>173</v>
       </c>
       <c r="J16" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K16" s="14" t="s">
         <v>173</v>
@@ -6335,13 +6559,16 @@
       <c r="L16" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M16" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="C17" t="s">
         <v>229</v>
       </c>
       <c r="D17" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>173</v>
@@ -6359,7 +6586,7 @@
         <v>173</v>
       </c>
       <c r="J17" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K17" s="14" t="s">
         <v>173</v>
@@ -6367,8 +6594,11 @@
       <c r="L17" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M17" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
         <v>230</v>
       </c>
@@ -6376,13 +6606,13 @@
         <v>231</v>
       </c>
       <c r="D18" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="F18" s="15" t="s">
-        <v>236</v>
+      <c r="F18" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="G18" s="14" t="s">
         <v>173</v>
@@ -6394,81 +6624,93 @@
         <v>173</v>
       </c>
       <c r="J18" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K18" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="L18" s="24" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" t="s">
-        <v>232</v>
-      </c>
-      <c r="C19" t="s">
-        <v>233</v>
-      </c>
-      <c r="D19" t="s">
-        <v>209</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="J19" s="29" t="s">
-        <v>290</v>
-      </c>
-      <c r="K19" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="L19" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="L18" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A22" t="s">
         <v>57</v>
       </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L21" t="s">
+        <v>319</v>
+      </c>
+      <c r="M21" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22">
+        <v>9693404</v>
+      </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>197</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>198</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
-      </c>
-      <c r="L22" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>199</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="J22" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
-        <v>9693404</v>
+        <v>222222</v>
       </c>
       <c r="B23" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C23" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D23" t="s">
         <v>199</v>
@@ -6483,13 +6725,13 @@
         <v>173</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>173</v>
       </c>
       <c r="J23" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K23" s="14" t="s">
         <v>173</v>
@@ -6497,16 +6739,19 @@
       <c r="L23" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M23" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
-        <v>222222</v>
+        <v>9743804</v>
       </c>
       <c r="B24" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C24" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D24" t="s">
         <v>199</v>
@@ -6521,36 +6766,39 @@
         <v>173</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I24" s="14" t="s">
         <v>173</v>
       </c>
       <c r="J24" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K24" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="L24" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L24" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="M24" s="25" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
-        <v>9743804</v>
+        <v>111111</v>
       </c>
       <c r="B25" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C25" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D25" t="s">
         <v>199</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>173</v>
+        <v>233</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>173</v>
@@ -6559,102 +6807,102 @@
         <v>173</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>173</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="I25" s="31"/>
       <c r="J25" s="29" t="s">
-        <v>290</v>
-      </c>
-      <c r="K25" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="L25" s="25" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>288</v>
+      </c>
+      <c r="K25" s="22"/>
+      <c r="L25" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="M25" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
-        <v>111111</v>
+        <v>9662304</v>
       </c>
       <c r="B26" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C26" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D26" t="s">
         <v>199</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="F26" s="14" t="s">
-        <v>173</v>
+        <v>173</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>234</v>
       </c>
       <c r="G26" s="14" t="s">
         <v>173</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="I26" s="31"/>
+        <v>284</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>173</v>
+      </c>
       <c r="J26" s="29" t="s">
-        <v>290</v>
-      </c>
-      <c r="K26" s="22"/>
+        <v>288</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>173</v>
+      </c>
       <c r="L26" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27">
-        <v>9662304</v>
-      </c>
+      <c r="M26" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" t="s">
-        <v>206</v>
+        <v>274</v>
       </c>
       <c r="C27" t="s">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="D27" t="s">
-        <v>199</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>236</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
       <c r="G27" s="14" t="s">
         <v>173</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>173</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="I27" s="31"/>
       <c r="J27" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K27" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="L27" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L27" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="M27" s="25" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
+        <v>274</v>
+      </c>
+      <c r="C28" t="s">
         <v>276</v>
       </c>
-      <c r="C28" t="s">
-        <v>277</v>
-      </c>
       <c r="D28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
@@ -6662,70 +6910,82 @@
         <v>173</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I28" s="31"/>
       <c r="J28" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K28" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="L28" s="25" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" t="s">
-        <v>276</v>
-      </c>
-      <c r="C29" t="s">
-        <v>278</v>
-      </c>
-      <c r="D29" t="s">
-        <v>280</v>
-      </c>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="I29" s="31"/>
-      <c r="J29" s="29" t="s">
-        <v>290</v>
-      </c>
-      <c r="K29" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="L29" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="L28" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="L30" s="14" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.5">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
       <c r="L31" s="14" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.5">
-      <c r="A32" t="s">
-        <v>16</v>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32">
+        <v>3578804</v>
+      </c>
+      <c r="B32" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" t="s">
+        <v>178</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="J32" s="29" t="s">
+        <v>288</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="L32" s="14" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+        <v>173</v>
+      </c>
+      <c r="M32" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
-        <v>3578804</v>
+        <v>9289704</v>
       </c>
       <c r="B33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="D33" t="s">
         <v>178</v>
@@ -6739,11 +6999,9 @@
       <c r="G33" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="I33" s="14" t="s">
-        <v>173</v>
-      </c>
+      <c r="I33" s="22"/>
       <c r="J33" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K33" s="14" t="s">
         <v>173</v>
@@ -6751,16 +7009,19 @@
       <c r="L33" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M33" s="24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
-        <v>9289704</v>
+        <v>9344404</v>
       </c>
       <c r="B34" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="D34" t="s">
         <v>178</v>
@@ -6772,28 +7033,29 @@
         <v>173</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="I34" s="22"/>
+        <v>234</v>
+      </c>
+      <c r="I34" s="31"/>
       <c r="J34" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K34" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="L34" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L34" s="22"/>
+      <c r="M34" s="24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
-        <v>9344404</v>
+        <v>6746404</v>
       </c>
       <c r="B35" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C35" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D35" t="s">
         <v>178</v>
@@ -6805,26 +7067,31 @@
         <v>173</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="I35" s="31"/>
+        <v>234</v>
+      </c>
+      <c r="I35" s="22"/>
       <c r="J35" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K35" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="L35" s="22"/>
-    </row>
-    <row r="36" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="L35" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="M35" s="24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
-        <v>6746404</v>
+        <v>9257604</v>
       </c>
       <c r="B36" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C36" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D36" t="s">
         <v>178</v>
@@ -6836,11 +7103,13 @@
         <v>173</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="I36" s="22"/>
+        <v>173</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>173</v>
+      </c>
       <c r="J36" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K36" s="14" t="s">
         <v>173</v>
@@ -6848,34 +7117,35 @@
       <c r="L36" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M36" s="24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
-        <v>9257604</v>
+        <v>9717204</v>
       </c>
       <c r="B37" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C37" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D37" t="s">
         <v>178</v>
       </c>
-      <c r="E37" s="14" t="s">
-        <v>173</v>
+      <c r="E37" s="15" t="s">
+        <v>234</v>
       </c>
       <c r="F37" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="G37" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>173</v>
-      </c>
+      <c r="G37" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="I37" s="22"/>
       <c r="J37" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K37" s="14" t="s">
         <v>173</v>
@@ -6883,49 +7153,53 @@
       <c r="L37" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M37" s="24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
-        <v>9717204</v>
+        <v>2298204</v>
       </c>
       <c r="B38" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C38" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D38" t="s">
         <v>178</v>
       </c>
-      <c r="E38" s="15" t="s">
-        <v>236</v>
+      <c r="E38" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="F38" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="G38" s="29" t="s">
-        <v>236</v>
+      <c r="G38" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="I38" s="22"/>
       <c r="J38" s="29" t="s">
-        <v>290</v>
-      </c>
-      <c r="K38" s="14" t="s">
-        <v>173</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="K38" s="22"/>
       <c r="L38" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M38" s="24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
-        <v>2298204</v>
+        <v>5784804</v>
       </c>
       <c r="B39" t="s">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="C39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D39" t="s">
         <v>178</v>
@@ -6939,24 +7213,31 @@
       <c r="G39" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="I39" s="22"/>
+      <c r="I39" s="14" t="s">
+        <v>173</v>
+      </c>
       <c r="J39" s="29" t="s">
-        <v>290</v>
-      </c>
-      <c r="K39" s="22"/>
+        <v>288</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>173</v>
+      </c>
       <c r="L39" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M39" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
-        <v>5784804</v>
+        <v>9321704</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>191</v>
       </c>
       <c r="C40" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D40" t="s">
         <v>178</v>
@@ -6974,24 +7255,25 @@
         <v>173</v>
       </c>
       <c r="J40" s="29" t="s">
-        <v>290</v>
-      </c>
-      <c r="K40" s="14" t="s">
-        <v>173</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="K40" s="22"/>
       <c r="L40" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M40" s="24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
-        <v>9321704</v>
+        <v>9720304</v>
       </c>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C41" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D41" t="s">
         <v>178</v>
@@ -7005,26 +7287,31 @@
       <c r="G41" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="I41" s="14" t="s">
-        <v>173</v>
+      <c r="I41" s="28" t="s">
+        <v>264</v>
       </c>
       <c r="J41" s="29" t="s">
-        <v>290</v>
-      </c>
-      <c r="K41" s="22"/>
+        <v>288</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>173</v>
+      </c>
       <c r="L41" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M41" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
-        <v>9720304</v>
+        <v>9317404</v>
       </c>
       <c r="B42" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C42" t="s">
-        <v>194</v>
+        <v>67</v>
       </c>
       <c r="D42" t="s">
         <v>178</v>
@@ -7038,11 +7325,9 @@
       <c r="G42" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="I42" s="28" t="s">
-        <v>266</v>
-      </c>
+      <c r="I42" s="22"/>
       <c r="J42" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K42" s="14" t="s">
         <v>173</v>
@@ -7050,13 +7335,16 @@
       <c r="L42" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="M42" s="24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
-        <v>9317404</v>
+        <v>8333604</v>
       </c>
       <c r="B43" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C43" t="s">
         <v>67</v>
@@ -7073,9 +7361,11 @@
       <c r="G43" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="I43" s="22"/>
+      <c r="I43" s="14" t="s">
+        <v>173</v>
+      </c>
       <c r="J43" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K43" s="14" t="s">
         <v>173</v>
@@ -7083,47 +7373,16 @@
       <c r="L43" s="14" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44">
-        <v>8333604</v>
-      </c>
-      <c r="B44" t="s">
-        <v>196</v>
-      </c>
-      <c r="C44" t="s">
-        <v>67</v>
-      </c>
-      <c r="D44" t="s">
-        <v>178</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="I44" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="J44" s="29" t="s">
-        <v>290</v>
-      </c>
-      <c r="K44" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="L44" s="14" t="s">
-        <v>173</v>
+      <c r="M43" s="24" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7143,10 +7402,10 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1320" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{508FD441-286B-4530-BAB9-502536B5EB91}"/>
+  <xr:revisionPtr revIDLastSave="1377" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47A4F416-CF10-484C-B408-65DF19EE0B5C}"/>
   <bookViews>
     <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,8 @@
     <sheet name="Monada" sheetId="5" r:id="rId5"/>
     <sheet name="A Lyceum" sheetId="4" r:id="rId6"/>
     <sheet name="anapliroseis" sheetId="7" r:id="rId7"/>
+    <sheet name="A Lyceum - tests" sheetId="12" r:id="rId8"/>
+    <sheet name="A Gymansiou - tests" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -85,8 +87,8 @@
     <author>tc={2467605D-399B-4869-A30B-7FE742BDF0DA}</author>
     <author>tc={48BC95C2-E3C5-464E-B23C-508BA24D8245}</author>
     <author>tc={AD4C8F15-E890-4B85-B1C2-93D5114E713A}</author>
+    <author>tc={3D2570EE-C1C0-4D2F-A268-8D52210E5513}</author>
     <author>tc={8F76B8B8-18EE-496F-A335-0321C1189047}</author>
-    <author>tc={E74507EC-BC04-4A9B-B15C-32C7F44E6109}</author>
     <author>tc={0E374CA0-3C13-436D-9FAC-14F6B920C675}</author>
     <author>tc={0E1BF347-0EA3-4549-B042-BCD495D8C495}</author>
     <author>tc={77742E87-EB5D-4747-811D-D6052514F58A}</author>
@@ -220,7 +222,15 @@
     Special, pontios</t>
       </text>
     </comment>
-    <comment ref="C24" authorId="13" shapeId="0" xr:uid="{8F76B8B8-18EE-496F-A335-0321C1189047}">
+    <comment ref="C23" authorId="13" shapeId="0" xr:uid="{3D2570EE-C1C0-4D2F-A268-8D52210E5513}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Stiriksi</t>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="14" shapeId="0" xr:uid="{8F76B8B8-18EE-496F-A335-0321C1189047}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -228,15 +238,7 @@
     stiriksi</t>
       </text>
     </comment>
-    <comment ref="C25" authorId="14" shapeId="0" xr:uid="{E74507EC-BC04-4A9B-B15C-32C7F44E6109}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Stiriksi</t>
-      </text>
-    </comment>
-    <comment ref="C28" authorId="15" shapeId="0" xr:uid="{0E374CA0-3C13-436D-9FAC-14F6B920C675}">
+    <comment ref="C30" authorId="15" shapeId="0" xr:uid="{0E374CA0-3C13-436D-9FAC-14F6B920C675}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -244,7 +246,7 @@
     Roumania, diskolies sta ellinika</t>
       </text>
     </comment>
-    <comment ref="C29" authorId="16" shapeId="0" xr:uid="{0E1BF347-0EA3-4549-B042-BCD495D8C495}">
+    <comment ref="C31" authorId="16" shapeId="0" xr:uid="{0E1BF347-0EA3-4549-B042-BCD495D8C495}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -252,7 +254,7 @@
     Xorismenoi goneis</t>
       </text>
     </comment>
-    <comment ref="C30" authorId="17" shapeId="0" xr:uid="{77742E87-EB5D-4747-811D-D6052514F58A}">
+    <comment ref="C32" authorId="17" shapeId="0" xr:uid="{77742E87-EB5D-4747-811D-D6052514F58A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -260,7 +262,7 @@
     Skaki, mathimatika olympiades</t>
       </text>
     </comment>
-    <comment ref="C31" authorId="18" shapeId="0" xr:uid="{221FDEED-1145-48B8-93A0-518076128BE1}">
+    <comment ref="C33" authorId="18" shapeId="0" xr:uid="{221FDEED-1145-48B8-93A0-518076128BE1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -268,7 +270,7 @@
     Sitisi, papapona gia bullying sto dimotiko</t>
       </text>
     </comment>
-    <comment ref="C32" authorId="19" shapeId="0" xr:uid="{06E68A77-02D9-459A-AE13-BD4D2460CF82}">
+    <comment ref="C34" authorId="19" shapeId="0" xr:uid="{06E68A77-02D9-459A-AE13-BD4D2460CF82}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -277,7 +279,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="C33" authorId="20" shapeId="0" xr:uid="{B3A23F0F-0E01-41A2-8966-76A587BA515C}">
+    <comment ref="C35" authorId="20" shapeId="0" xr:uid="{B3A23F0F-0E01-41A2-8966-76A587BA515C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -285,7 +287,7 @@
     Didimoi me Kimona</t>
       </text>
     </comment>
-    <comment ref="C34" authorId="21" shapeId="0" xr:uid="{AA3BDBA2-8267-4A69-A689-551224F645D9}">
+    <comment ref="C36" authorId="21" shapeId="0" xr:uid="{AA3BDBA2-8267-4A69-A689-551224F645D9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -293,7 +295,7 @@
     Ypermetropia, astigmatismos</t>
       </text>
     </comment>
-    <comment ref="C36" authorId="22" shapeId="0" xr:uid="{FCE8BE01-CFDB-4E54-9051-44ADC799EE83}">
+    <comment ref="C38" authorId="22" shapeId="0" xr:uid="{FCE8BE01-CFDB-4E54-9051-44ADC799EE83}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -301,7 +303,7 @@
     Sitisi, orfanos apo patera sti Syria</t>
       </text>
     </comment>
-    <comment ref="C37" authorId="23" shapeId="0" xr:uid="{98BD6B5F-37EB-41FA-B971-80255C43C024}">
+    <comment ref="C39" authorId="23" shapeId="0" xr:uid="{98BD6B5F-37EB-41FA-B971-80255C43C024}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -309,7 +311,7 @@
     Spazei sixna h miti tis</t>
       </text>
     </comment>
-    <comment ref="C41" authorId="24" shapeId="0" xr:uid="{3FB9C602-3AA9-40D1-97B5-331230499AE8}">
+    <comment ref="C43" authorId="24" shapeId="0" xr:uid="{3FB9C602-3AA9-40D1-97B5-331230499AE8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -317,7 +319,7 @@
     Xorismeni, apoklisitiki h mitera</t>
       </text>
     </comment>
-    <comment ref="C42" authorId="25" shapeId="0" xr:uid="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
+    <comment ref="C44" authorId="25" shapeId="0" xr:uid="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -325,7 +327,7 @@
     indefferent</t>
       </text>
     </comment>
-    <comment ref="C43" authorId="26" shapeId="0" xr:uid="{86B9678A-C29A-446D-AACA-74A7C503B71B}">
+    <comment ref="C45" authorId="26" shapeId="0" xr:uid="{86B9678A-C29A-446D-AACA-74A7C503B71B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -333,7 +335,7 @@
     Depy, sitisi, sinesthimatikes diskolies</t>
       </text>
     </comment>
-    <comment ref="E43" authorId="27" shapeId="0" xr:uid="{720F20F5-2744-4E03-9112-5151AF4ED353}">
+    <comment ref="E45" authorId="27" shapeId="0" xr:uid="{720F20F5-2744-4E03-9112-5151AF4ED353}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -341,7 +343,7 @@
     Indifferent, don't take book.</t>
       </text>
     </comment>
-    <comment ref="C44" authorId="28" shapeId="0" xr:uid="{7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}">
+    <comment ref="C46" authorId="28" shapeId="0" xr:uid="{7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -349,7 +351,7 @@
     Stiriksi, sitisi, menei me patera, oxi epaphi me mitera, o pateras fetos irthe, emenas me giagia kai pappou</t>
       </text>
     </comment>
-    <comment ref="C48" authorId="29" shapeId="0" xr:uid="{8F4D57B3-2C90-4744-BFEF-99E499E55142}">
+    <comment ref="C50" authorId="29" shapeId="0" xr:uid="{8F4D57B3-2C90-4744-BFEF-99E499E55142}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -357,7 +359,7 @@
     Dropalos, thelei enisxisi</t>
       </text>
     </comment>
-    <comment ref="C49" authorId="30" shapeId="0" xr:uid="{37F71BFC-AE14-49EC-B2B2-49697A83F48F}">
+    <comment ref="C51" authorId="30" shapeId="0" xr:uid="{37F71BFC-AE14-49EC-B2B2-49697A83F48F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -365,7 +367,7 @@
     Stiriksi, mathisiakes adinamies</t>
       </text>
     </comment>
-    <comment ref="C50" authorId="31" shapeId="0" xr:uid="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
+    <comment ref="C52" authorId="31" shapeId="0" xr:uid="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -393,6 +395,7 @@
     <author>tc={63E1D257-C3B7-435A-A4B3-4F6EA6F7AC25}</author>
     <author>tc={DDB96904-162D-419D-BF36-AC7C7955C53E}</author>
     <author>tc={08EEC001-3001-4E58-A957-556D8883327A}</author>
+    <author>tc={A89EB0FE-9FD4-49AE-BB82-4055CE84C862}</author>
     <author>tc={8AC19454-30E3-45D9-9597-E3A2E37CFF9A}</author>
     <author>tc={CA6B0F40-6EF4-4274-8867-21553D999551}</author>
     <author>tc={E674068C-9812-42A2-9151-17837D13ABB6}</author>
@@ -495,7 +498,17 @@
     Mono me mitera</t>
       </text>
     </comment>
-    <comment ref="C24" authorId="11" shapeId="0" xr:uid="{8AC19454-30E3-45D9-9597-E3A2E37CFF9A}">
+    <comment ref="C23" authorId="11" shapeId="0" xr:uid="{A89EB0FE-9FD4-49AE-BB82-4055CE84C862}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Diefkolinseis, stiriksi
+Reply:
+    Mitera karkino</t>
+      </text>
+    </comment>
+    <comment ref="C24" authorId="12" shapeId="0" xr:uid="{8AC19454-30E3-45D9-9597-E3A2E37CFF9A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -503,7 +516,7 @@
     Aporos, sitisis</t>
       </text>
     </comment>
-    <comment ref="C29" authorId="12" shapeId="0" xr:uid="{CA6B0F40-6EF4-4274-8867-21553D999551}">
+    <comment ref="C29" authorId="13" shapeId="0" xr:uid="{CA6B0F40-6EF4-4274-8867-21553D999551}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -511,7 +524,7 @@
     Ntrepete, xamilon tonon</t>
       </text>
     </comment>
-    <comment ref="C32" authorId="13" shapeId="0" xr:uid="{E674068C-9812-42A2-9151-17837D13ABB6}">
+    <comment ref="C32" authorId="14" shapeId="0" xr:uid="{E674068C-9812-42A2-9151-17837D13ABB6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -519,7 +532,7 @@
     Isixi, thelei entharinsi</t>
       </text>
     </comment>
-    <comment ref="C33" authorId="14" shapeId="0" xr:uid="{ED249525-191C-4637-9D99-E242BDB6421A}">
+    <comment ref="C33" authorId="15" shapeId="0" xr:uid="{ED249525-191C-4637-9D99-E242BDB6421A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -527,7 +540,7 @@
     Xasimoto, pernei thiroksini</t>
       </text>
     </comment>
-    <comment ref="C35" authorId="15" shapeId="0" xr:uid="{B304C0F3-0817-4A4E-853F-5F45E9E32DFD}">
+    <comment ref="C35" authorId="16" shapeId="0" xr:uid="{B304C0F3-0817-4A4E-853F-5F45E9E32DFD}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -535,7 +548,7 @@
     Mila arketa, kinito, oriothetisi</t>
       </text>
     </comment>
-    <comment ref="I35" authorId="16" shapeId="0" xr:uid="{DF19662E-D699-40A7-996A-7901BA4875E9}">
+    <comment ref="I35" authorId="17" shapeId="0" xr:uid="{DF19662E-D699-40A7-996A-7901BA4875E9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -543,7 +556,7 @@
     kataggelia</t>
       </text>
     </comment>
-    <comment ref="C36" authorId="17" shapeId="0" xr:uid="{1C68C472-CF02-4D39-A15B-ACD03122D4F0}">
+    <comment ref="C36" authorId="18" shapeId="0" xr:uid="{1C68C472-CF02-4D39-A15B-ACD03122D4F0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -553,7 +566,7 @@
     Miazei tis Melias</t>
       </text>
     </comment>
-    <comment ref="C37" authorId="18" shapeId="0" xr:uid="{2330157A-B3C2-4789-96E1-9C8D2D80D7FE}">
+    <comment ref="C37" authorId="19" shapeId="0" xr:uid="{2330157A-B3C2-4789-96E1-9C8D2D80D7FE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -561,7 +574,7 @@
     zoiros</t>
       </text>
     </comment>
-    <comment ref="C38" authorId="19" shapeId="0" xr:uid="{831B6259-37A3-4907-AE80-39991BDC7649}">
+    <comment ref="C38" authorId="20" shapeId="0" xr:uid="{831B6259-37A3-4907-AE80-39991BDC7649}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -718,8 +731,436 @@
 </comments>
 </file>
 
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={376EB8CC-624A-4905-943C-003667EB4EEA}</author>
+    <author>tc={DC46CFF3-F130-4C35-ADEF-5A1F821781A9}</author>
+    <author>tc={B7A43FBB-5038-4FC3-8FAD-07EE5143A1F8}</author>
+    <author>tc={63C17029-8F90-4253-9CA7-E994CFD5D5A2}</author>
+    <author>tc={AA276D36-BF21-4BF1-B4EE-CFB1644CC25A}</author>
+    <author>tc={E15DDDED-B2BA-4607-867F-BB836742B4CF}</author>
+    <author>tc={959932C7-E7CF-4613-A506-DF1AB6866DD6}</author>
+    <author>tc={A44E3110-99FE-4968-95C4-FBBC90EA44AB}</author>
+    <author>tc={2FB97B2F-685A-47AD-B451-26CE099B5CDE}</author>
+    <author>tc={49700AAE-FBF5-4AF6-8413-5CA5A784A6FE}</author>
+    <author>tc={C1108176-F43A-484D-8C9A-1ABAB3DE80B2}</author>
+    <author>tc={F444680E-9CC4-4A89-898A-5ABDCDB06F58}</author>
+  </authors>
+  <commentList>
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{376EB8CC-624A-4905-943C-003667EB4EEA}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Seems like  a good kid</t>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="1" shapeId="0" xr:uid="{DC46CFF3-F130-4C35-ADEF-5A1F821781A9}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    indifferent
+Reply:
+    Mourmouros
+</t>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="2" shapeId="0" xr:uid="{B7A43FBB-5038-4FC3-8FAD-07EE5143A1F8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Fili tou konstantinou</t>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="3" shapeId="0" xr:uid="{63C17029-8F90-4253-9CA7-E994CFD5D5A2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Quiet but tries</t>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="4" shapeId="0" xr:uid="{AA276D36-BF21-4BF1-B4EE-CFB1644CC25A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Blond, quiet</t>
+      </text>
+    </comment>
+    <comment ref="C23" authorId="5" shapeId="0" xr:uid="{E15DDDED-B2BA-4607-867F-BB836742B4CF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Good student</t>
+      </text>
+    </comment>
+    <comment ref="C33" authorId="6" shapeId="0" xr:uid="{959932C7-E7CF-4613-A506-DF1AB6866DD6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Not very careful
+Reply:
+    Ligo prixtissa, alla kali.</t>
+      </text>
+    </comment>
+    <comment ref="C34" authorId="7" shapeId="0" xr:uid="{A44E3110-99FE-4968-95C4-FBBC90EA44AB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Get bored, starts playing games
+Reply:
+    Not paying attention
+Reply:
+    Keep an eye on him.</t>
+      </text>
+    </comment>
+    <comment ref="C35" authorId="8" shapeId="0" xr:uid="{2FB97B2F-685A-47AD-B451-26CE099B5CDE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Fenete filotimos, with some knowledge</t>
+      </text>
+    </comment>
+    <comment ref="C38" authorId="9" shapeId="0" xr:uid="{49700AAE-FBF5-4AF6-8413-5CA5A784A6FE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Kori tis Lelias</t>
+      </text>
+    </comment>
+    <comment ref="C42" authorId="10" shapeId="0" xr:uid="{C1108176-F43A-484D-8C9A-1ABAB3DE80B2}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Filotimos
+</t>
+      </text>
+    </comment>
+    <comment ref="C43" authorId="11" shapeId="0" xr:uid="{F444680E-9CC4-4A89-898A-5ABDCDB06F58}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    With glasses</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={2D3AFF17-C5DC-42F1-900D-6D2DDCDEDE40}</author>
+    <author>tc={5AEB12AC-CF6F-4769-B6EC-6CD91A0CD2B2}</author>
+    <author>tc={378E7594-8484-4AB0-9234-B7D16F63965E}</author>
+    <author>tc={411A9399-939F-4CF3-84DE-E99276BDD5F1}</author>
+    <author>tc={653A25CE-F853-41CD-A80C-071E9A56C03D}</author>
+    <author>tc={CBC4FE66-6F10-4A75-8F50-45357D88B4F9}</author>
+    <author>tc={3CE025BD-885B-4BB4-8153-5BC45D96E63A}</author>
+    <author>tc={59815D4B-84E2-4C30-910E-50D01C3C6ED7}</author>
+    <author>tc={4647EABC-BD0A-4287-98AE-93002CBD969E}</author>
+    <author>tc={D0C2496A-FD3A-4795-86E4-65A32C49D3BB}</author>
+    <author>tc={CD7FCC05-427C-4B42-A9A7-2AFEEF3F93F9}</author>
+    <author>tc={61FB07C0-0E78-4C8B-AA14-9FC2FF75EB53}</author>
+    <author>tc={A20A5040-4856-4E57-BDA4-AE16EF61198C}</author>
+    <author>tc={5B59CB62-C4AC-414E-99F2-9D3F0BAE7F43}</author>
+    <author>tc={0F457041-30F1-42D5-86AA-827F66CF5BFF}</author>
+    <author>tc={3AB30EA2-F1F4-4B35-A695-4BD343EDA7AB}</author>
+    <author>tc={43A0AE65-034A-43EB-BC59-C4E0B72EF263}</author>
+    <author>tc={D4F088E1-432B-4086-AA01-1CA80A1DAD01}</author>
+    <author>tc={003CF2AA-8884-4C36-88CB-5F0850865977}</author>
+    <author>tc={1F0FEE88-81AC-4F0C-A40A-208A40518123}</author>
+    <author>tc={BAD03DE3-79F7-4ED6-BBEE-A216F4A0CF81}</author>
+    <author>tc={328D28C5-39DF-4E43-9191-E0347C55DC85}</author>
+    <author>tc={CCF5C47C-DAC9-4163-911E-D25575FED191}</author>
+    <author>tc={1BCE4285-4670-48B9-A6C0-A7ACB02EB42C}</author>
+    <author>tc={1BA79E55-D3B6-4B95-8DA1-57CBF311C4CC}</author>
+    <author>tc={2B329A84-0BDF-4381-88A4-81550D5EEF38}</author>
+    <author>tc={AAFA0838-65EA-4623-BC08-12544B2903FB}</author>
+    <author>tc={4D05AFA5-576B-4955-8CD5-510AFC85FC66}</author>
+    <author>tc={C94A78CF-2F80-4B38-B2A4-3CC0C4D9E0E4}</author>
+    <author>tc={D7EB80D4-5CFD-425F-B3B4-EB0A0BE048F6}</author>
+    <author>tc={222055CB-C6B5-4FA3-91EE-184B465B0798}</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{2D3AFF17-C5DC-42F1-900D-6D2DDCDEDE40}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Seems good class</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="1" shapeId="0" xr:uid="{5AEB12AC-CF6F-4769-B6EC-6CD91A0CD2B2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Bulgaria, thema me apousies</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="2" shapeId="0" xr:uid="{378E7594-8484-4AB0-9234-B7D16F63965E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Menei me mitera, vlepei patera.
+Reply:
+    sitisis
+Reply:
+    Mitera kypria</t>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="3" shapeId="0" xr:uid="{411A9399-939F-4CF3-84DE-E99276BDD5F1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Xorismenos me mitera</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="4" shapeId="0" xr:uid="{653A25CE-F853-41CD-A80C-071E9A56C03D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Isos themata me ti glossa
+Reply:
+    roumania</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="5" shapeId="0" xr:uid="{CBC4FE66-6F10-4A75-8F50-45357D88B4F9}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    monaxikos
+Reply:
+    roumania</t>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="6" shapeId="0" xr:uid="{3CE025BD-885B-4BB4-8153-5BC45D96E63A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    roumania</t>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="7" shapeId="0" xr:uid="{59815D4B-84E2-4C30-910E-50D01C3C6ED7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Xasimoto, elleipsi prosoxis, astheneia cushing</t>
+      </text>
+    </comment>
+    <comment ref="C17" authorId="8" shapeId="0" xr:uid="{4647EABC-BD0A-4287-98AE-93002CBD969E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Exei voitho
+Reply:
+    stiriksi</t>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="9" shapeId="0" xr:uid="{D0C2496A-FD3A-4795-86E4-65A32C49D3BB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Noxelikos, pithanos ethismos sta electronica paixnidia</t>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="10" shapeId="0" xr:uid="{CD7FCC05-427C-4B42-A9A7-2AFEEF3F93F9}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Poli evesthiti, kleei eukola, politekni</t>
+      </text>
+    </comment>
+    <comment ref="C22" authorId="11" shapeId="0" xr:uid="{61FB07C0-0E78-4C8B-AA14-9FC2FF75EB53}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    vogotonia</t>
+      </text>
+    </comment>
+    <comment ref="C23" authorId="12" shapeId="0" xr:uid="{A20A5040-4856-4E57-BDA4-AE16EF61198C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Special, pontios</t>
+      </text>
+    </comment>
+    <comment ref="C24" authorId="13" shapeId="0" xr:uid="{5B59CB62-C4AC-414E-99F2-9D3F0BAE7F43}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Stiriksi</t>
+      </text>
+    </comment>
+    <comment ref="C27" authorId="14" shapeId="0" xr:uid="{0F457041-30F1-42D5-86AA-827F66CF5BFF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    stiriksi</t>
+      </text>
+    </comment>
+    <comment ref="C30" authorId="15" shapeId="0" xr:uid="{3AB30EA2-F1F4-4B35-A695-4BD343EDA7AB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Roumania, diskolies sta ellinika</t>
+      </text>
+    </comment>
+    <comment ref="C31" authorId="16" shapeId="0" xr:uid="{43A0AE65-034A-43EB-BC59-C4E0B72EF263}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Xorismenoi goneis</t>
+      </text>
+    </comment>
+    <comment ref="C32" authorId="17" shapeId="0" xr:uid="{D4F088E1-432B-4086-AA01-1CA80A1DAD01}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Skaki, mathimatika olympiades</t>
+      </text>
+    </comment>
+    <comment ref="C33" authorId="18" shapeId="0" xr:uid="{003CF2AA-8884-4C36-88CB-5F0850865977}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Sitisi, papapona gia bullying sto dimotiko</t>
+      </text>
+    </comment>
+    <comment ref="C34" authorId="19" shapeId="0" xr:uid="{1F0FEE88-81AC-4F0C-A40A-208A40518123}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Sitisi, stiriksi
+</t>
+      </text>
+    </comment>
+    <comment ref="C35" authorId="20" shapeId="0" xr:uid="{BAD03DE3-79F7-4ED6-BBEE-A216F4A0CF81}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Didimoi me Kimona</t>
+      </text>
+    </comment>
+    <comment ref="C36" authorId="21" shapeId="0" xr:uid="{328D28C5-39DF-4E43-9191-E0347C55DC85}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Ypermetropia, astigmatismos</t>
+      </text>
+    </comment>
+    <comment ref="C38" authorId="22" shapeId="0" xr:uid="{CCF5C47C-DAC9-4163-911E-D25575FED191}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Sitisi, orfanos apo patera sti Syria</t>
+      </text>
+    </comment>
+    <comment ref="C39" authorId="23" shapeId="0" xr:uid="{1BCE4285-4670-48B9-A6C0-A7ACB02EB42C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Spazei sixna h miti tis</t>
+      </text>
+    </comment>
+    <comment ref="C43" authorId="24" shapeId="0" xr:uid="{1BA79E55-D3B6-4B95-8DA1-57CBF311C4CC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Xorismeni, apoklisitiki h mitera</t>
+      </text>
+    </comment>
+    <comment ref="C44" authorId="25" shapeId="0" xr:uid="{2B329A84-0BDF-4381-88A4-81550D5EEF38}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    indefferent</t>
+      </text>
+    </comment>
+    <comment ref="C45" authorId="26" shapeId="0" xr:uid="{AAFA0838-65EA-4623-BC08-12544B2903FB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Depy, sitisi, sinesthimatikes diskolies</t>
+      </text>
+    </comment>
+    <comment ref="C46" authorId="27" shapeId="0" xr:uid="{4D05AFA5-576B-4955-8CD5-510AFC85FC66}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Stiriksi, sitisi, menei me patera, oxi epaphi me mitera, o pateras fetos irthe, emenas me giagia kai pappou</t>
+      </text>
+    </comment>
+    <comment ref="C50" authorId="28" shapeId="0" xr:uid="{C94A78CF-2F80-4B38-B2A4-3CC0C4D9E0E4}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Dropalos, thelei enisxisi</t>
+      </text>
+    </comment>
+    <comment ref="C51" authorId="29" shapeId="0" xr:uid="{D7EB80D4-5CFD-425F-B3B4-EB0A0BE048F6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Stiriksi, mathisiakes adinamies</t>
+      </text>
+    </comment>
+    <comment ref="C52" authorId="30" shapeId="0" xr:uid="{222055CB-C6B5-4FA3-91EE-184B465B0798}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Little guy with glasses
+Reply:
+    alpabitismos</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="349">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1745,13 +2186,34 @@
   </si>
   <si>
     <t>Erevna - Kahoot B41M9 aksiologisis</t>
+  </si>
+  <si>
+    <t>how DNS works</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/5ZCvW1XSX_E</t>
+  </si>
+  <si>
+    <t>send email</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ΧΑΤΖΗΣΟΛΩΜΟΥ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ΓΙΩΡΓΟΣ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Α2</t>
+  </si>
+  <si>
+    <t>hw. Sent me email</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1805,6 +2267,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="14">
@@ -2016,16 +2484,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2381,66 +2849,66 @@
   <threadedComment ref="C22" dT="2026-09-22T09:31:53.95" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AD4C8F15-E890-4B85-B1C2-93D5114E713A}">
     <text>Special, pontios</text>
   </threadedComment>
-  <threadedComment ref="C24" dT="2026-10-02T08:21:35.28" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{8F76B8B8-18EE-496F-A335-0321C1189047}">
+  <threadedComment ref="C23" dT="2026-10-02T08:22:39.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3D2570EE-C1C0-4D2F-A268-8D52210E5513}">
+    <text>Stiriksi</text>
+  </threadedComment>
+  <threadedComment ref="C26" dT="2026-10-02T08:21:35.28" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{8F76B8B8-18EE-496F-A335-0321C1189047}">
     <text>stiriksi</text>
   </threadedComment>
-  <threadedComment ref="C25" dT="2026-10-02T08:22:39.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{E74507EC-BC04-4A9B-B15C-32C7F44E6109}">
-    <text>Stiriksi</text>
-  </threadedComment>
-  <threadedComment ref="C28" dT="2026-10-05T07:13:32.27" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{0E374CA0-3C13-436D-9FAC-14F6B920C675}">
+  <threadedComment ref="C30" dT="2026-10-05T07:13:32.27" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{0E374CA0-3C13-436D-9FAC-14F6B920C675}">
     <text>Roumania, diskolies sta ellinika</text>
   </threadedComment>
-  <threadedComment ref="C29" dT="2026-10-05T07:13:44.64" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{0E1BF347-0EA3-4549-B042-BCD495D8C495}">
+  <threadedComment ref="C31" dT="2026-10-05T07:13:44.64" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{0E1BF347-0EA3-4549-B042-BCD495D8C495}">
     <text>Xorismenoi goneis</text>
   </threadedComment>
-  <threadedComment ref="C30" dT="2026-10-05T07:14:01.31" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{77742E87-EB5D-4747-811D-D6052514F58A}">
+  <threadedComment ref="C32" dT="2026-10-05T07:14:01.31" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{77742E87-EB5D-4747-811D-D6052514F58A}">
     <text>Skaki, mathimatika olympiades</text>
   </threadedComment>
-  <threadedComment ref="C31" dT="2026-10-05T07:14:18.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{221FDEED-1145-48B8-93A0-518076128BE1}">
+  <threadedComment ref="C33" dT="2026-10-05T07:14:18.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{221FDEED-1145-48B8-93A0-518076128BE1}">
     <text>Sitisi, papapona gia bullying sto dimotiko</text>
   </threadedComment>
-  <threadedComment ref="C32" dT="2026-10-05T07:14:34.50" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{06E68A77-02D9-459A-AE13-BD4D2460CF82}">
+  <threadedComment ref="C34" dT="2026-10-05T07:14:34.50" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{06E68A77-02D9-459A-AE13-BD4D2460CF82}">
     <text xml:space="preserve">Sitisi, stiriksi
 </text>
   </threadedComment>
-  <threadedComment ref="C33" dT="2026-10-05T07:14:51.75" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B3A23F0F-0E01-41A2-8966-76A587BA515C}">
+  <threadedComment ref="C35" dT="2026-10-05T07:14:51.75" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B3A23F0F-0E01-41A2-8966-76A587BA515C}">
     <text>Didimoi me Kimona</text>
   </threadedComment>
-  <threadedComment ref="C34" dT="2026-10-05T07:15:08.05" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AA3BDBA2-8267-4A69-A689-551224F645D9}">
+  <threadedComment ref="C36" dT="2026-10-05T07:15:08.05" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AA3BDBA2-8267-4A69-A689-551224F645D9}">
     <text>Ypermetropia, astigmatismos</text>
   </threadedComment>
-  <threadedComment ref="C36" dT="2026-10-05T07:15:27.54" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{FCE8BE01-CFDB-4E54-9051-44ADC799EE83}">
+  <threadedComment ref="C38" dT="2026-10-05T07:15:27.54" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{FCE8BE01-CFDB-4E54-9051-44ADC799EE83}">
     <text>Sitisi, orfanos apo patera sti Syria</text>
   </threadedComment>
-  <threadedComment ref="C37" dT="2026-10-05T07:15:40.47" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{98BD6B5F-37EB-41FA-B971-80255C43C024}">
+  <threadedComment ref="C39" dT="2026-10-05T07:15:40.47" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{98BD6B5F-37EB-41FA-B971-80255C43C024}">
     <text>Spazei sixna h miti tis</text>
   </threadedComment>
-  <threadedComment ref="C41" dT="2026-10-05T09:04:32.37" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3FB9C602-3AA9-40D1-97B5-331230499AE8}">
+  <threadedComment ref="C43" dT="2026-10-05T09:04:32.37" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3FB9C602-3AA9-40D1-97B5-331230499AE8}">
     <text>Xorismeni, apoklisitiki h mitera</text>
   </threadedComment>
-  <threadedComment ref="C42" dT="2026-09-25T14:55:37.89" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
+  <threadedComment ref="C44" dT="2026-09-25T14:55:37.89" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
     <text>indefferent</text>
   </threadedComment>
-  <threadedComment ref="C43" dT="2026-10-05T09:04:58.84" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{86B9678A-C29A-446D-AACA-74A7C503B71B}">
+  <threadedComment ref="C45" dT="2026-10-05T09:04:58.84" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{86B9678A-C29A-446D-AACA-74A7C503B71B}">
     <text>Depy, sitisi, sinesthimatikes diskolies</text>
   </threadedComment>
-  <threadedComment ref="E43" dT="2026-09-15T15:29:00.38" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{720F20F5-2744-4E03-9112-5151AF4ED353}">
+  <threadedComment ref="E45" dT="2026-09-15T15:29:00.38" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{720F20F5-2744-4E03-9112-5151AF4ED353}">
     <text>Indifferent, don't take book.</text>
   </threadedComment>
-  <threadedComment ref="C44" dT="2026-10-05T09:05:48.06" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}">
+  <threadedComment ref="C46" dT="2026-10-05T09:05:48.06" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}">
     <text>Stiriksi, sitisi, menei me patera, oxi epaphi me mitera, o pateras fetos irthe, emenas me giagia kai pappou</text>
   </threadedComment>
-  <threadedComment ref="C48" dT="2026-10-05T09:06:03.45" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{8F4D57B3-2C90-4744-BFEF-99E499E55142}">
+  <threadedComment ref="C50" dT="2026-10-05T09:06:03.45" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{8F4D57B3-2C90-4744-BFEF-99E499E55142}">
     <text>Dropalos, thelei enisxisi</text>
   </threadedComment>
-  <threadedComment ref="C49" dT="2026-10-05T09:06:27.63" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{37F71BFC-AE14-49EC-B2B2-49697A83F48F}">
+  <threadedComment ref="C51" dT="2026-10-05T09:06:27.63" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{37F71BFC-AE14-49EC-B2B2-49697A83F48F}">
     <text>Stiriksi, mathisiakes adinamies</text>
   </threadedComment>
-  <threadedComment ref="C50" dT="2026-09-21T06:24:16.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
+  <threadedComment ref="C52" dT="2026-09-21T06:24:16.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
     <text xml:space="preserve">Little guy with glasses
 </text>
   </threadedComment>
-  <threadedComment ref="C50" dT="2026-10-05T09:06:44.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{98AF0D30-4238-4DB6-AEB6-E46495700012}" parentId="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
+  <threadedComment ref="C52" dT="2026-10-05T09:06:44.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{98AF0D30-4238-4DB6-AEB6-E46495700012}" parentId="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
     <text>alpabitismos</text>
   </threadedComment>
 </ThreadedComments>
@@ -2485,6 +2953,13 @@
   <threadedComment ref="C20" dT="2026-09-23T07:05:00.47" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{08EEC001-3001-4E58-A957-556D8883327A}">
     <text>Mono me mitera</text>
   </threadedComment>
+  <threadedComment ref="C23" dT="2026-10-14T06:13:20.12" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{A89EB0FE-9FD4-49AE-BB82-4055CE84C862}">
+    <text xml:space="preserve">Diefkolinseis, stiriksi
+</text>
+  </threadedComment>
+  <threadedComment ref="C23" dT="2026-10-14T06:13:27.30" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{61D9969E-ED7A-42EB-8233-251AAA73D2C0}" parentId="{A89EB0FE-9FD4-49AE-BB82-4055CE84C862}">
+    <text>Mitera karkino</text>
+  </threadedComment>
   <threadedComment ref="C24" dT="2026-09-23T07:02:08.99" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{8AC19454-30E3-45D9-9597-E3A2E37CFF9A}">
     <text>Aporos, sitisis</text>
   </threadedComment>
@@ -2575,6 +3050,179 @@
   </threadedComment>
   <threadedComment ref="C43" dT="2026-09-17T05:55:56.16" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{BEA4804D-72CD-494C-BE39-4999EABE6959}">
     <text>With glasses</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C5" dT="2026-09-24T08:32:38.60" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{376EB8CC-624A-4905-943C-003667EB4EEA}">
+    <text>Seems like  a good kid</text>
+  </threadedComment>
+  <threadedComment ref="C11" dT="2026-09-17T05:16:36.12" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{DC46CFF3-F130-4C35-ADEF-5A1F821781A9}">
+    <text>indifferent</text>
+  </threadedComment>
+  <threadedComment ref="C11" dT="2026-09-24T08:31:57.09" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B1FACE89-3856-4A2A-8CF7-8A8F34BC936B}" parentId="{DC46CFF3-F130-4C35-ADEF-5A1F821781A9}">
+    <text xml:space="preserve">Mourmouros
+</text>
+  </threadedComment>
+  <threadedComment ref="C12" dT="2026-09-24T08:32:16.02" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B7A43FBB-5038-4FC3-8FAD-07EE5143A1F8}">
+    <text>Fili tou konstantinou</text>
+  </threadedComment>
+  <threadedComment ref="C15" dT="2026-09-24T08:33:03.46" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{63C17029-8F90-4253-9CA7-E994CFD5D5A2}">
+    <text>Quiet but tries</text>
+  </threadedComment>
+  <threadedComment ref="C16" dT="2026-09-17T05:12:57.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AA276D36-BF21-4BF1-B4EE-CFB1644CC25A}">
+    <text>Blond, quiet</text>
+  </threadedComment>
+  <threadedComment ref="C23" dT="2026-09-22T09:31:23.10" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{E15DDDED-B2BA-4607-867F-BB836742B4CF}">
+    <text>Good student</text>
+  </threadedComment>
+  <threadedComment ref="C33" dT="2026-09-17T05:56:45.08" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{959932C7-E7CF-4613-A506-DF1AB6866DD6}">
+    <text>Not very careful</text>
+  </threadedComment>
+  <threadedComment ref="C33" dT="2026-09-22T09:33:55.26" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{48E5F015-F678-4100-8FB0-B8FDE14A53C9}" parentId="{959932C7-E7CF-4613-A506-DF1AB6866DD6}">
+    <text>Ligo prixtissa, alla kali.</text>
+  </threadedComment>
+  <threadedComment ref="C34" dT="2026-09-17T05:57:00.11" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{A44E3110-99FE-4968-95C4-FBBC90EA44AB}">
+    <text>Get bored, starts playing games</text>
+  </threadedComment>
+  <threadedComment ref="C34" dT="2026-09-22T09:34:55.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{6C394EC6-CD60-4FD2-B817-AEE1AA8F5E74}" parentId="{A44E3110-99FE-4968-95C4-FBBC90EA44AB}">
+    <text>Not paying attention</text>
+  </threadedComment>
+  <threadedComment ref="C34" dT="2026-09-22T15:27:55.30" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{97C347F3-F520-41A1-8319-2B94782E47F2}" parentId="{A44E3110-99FE-4968-95C4-FBBC90EA44AB}">
+    <text>Keep an eye on him.</text>
+  </threadedComment>
+  <threadedComment ref="C35" dT="2026-09-17T05:56:20.80" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2FB97B2F-685A-47AD-B451-26CE099B5CDE}">
+    <text>Fenete filotimos, with some knowledge</text>
+  </threadedComment>
+  <threadedComment ref="C38" dT="2026-09-22T09:33:38.73" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{49700AAE-FBF5-4AF6-8413-5CA5A784A6FE}">
+    <text>Kori tis Lelias</text>
+  </threadedComment>
+  <threadedComment ref="C42" dT="2026-09-17T05:53:15.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{C1108176-F43A-484D-8C9A-1ABAB3DE80B2}">
+    <text xml:space="preserve">Filotimos
+</text>
+  </threadedComment>
+  <threadedComment ref="C43" dT="2026-09-17T05:55:56.16" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{F444680E-9CC4-4A89-898A-5ABDCDB06F58}">
+    <text>With glasses</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment6.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A3" dT="2026-09-21T06:34:38.10" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2D3AFF17-C5DC-42F1-900D-6D2DDCDEDE40}">
+    <text>Seems good class</text>
+  </threadedComment>
+  <threadedComment ref="C4" dT="2026-10-01T18:49:32.40" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{5AEB12AC-CF6F-4769-B6EC-6CD91A0CD2B2}">
+    <text>Bulgaria, thema me apousies</text>
+  </threadedComment>
+  <threadedComment ref="C5" dT="2026-10-01T18:50:02.22" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{378E7594-8484-4AB0-9234-B7D16F63965E}">
+    <text>Menei me mitera, vlepei patera.</text>
+  </threadedComment>
+  <threadedComment ref="C5" dT="2026-10-01T18:50:07.72" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3AAD6C3F-6FD4-486A-A434-BF0409807853}" parentId="{378E7594-8484-4AB0-9234-B7D16F63965E}">
+    <text>sitisis</text>
+  </threadedComment>
+  <threadedComment ref="C5" dT="2026-10-01T18:52:00.24" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{FF203A26-000B-4ACB-8D3A-838AE02700B4}" parentId="{378E7594-8484-4AB0-9234-B7D16F63965E}">
+    <text>Mitera kypria</text>
+  </threadedComment>
+  <threadedComment ref="C6" dT="2026-10-01T18:50:40.65" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{411A9399-939F-4CF3-84DE-E99276BDD5F1}">
+    <text>Xorismenos me mitera</text>
+  </threadedComment>
+  <threadedComment ref="C7" dT="2026-10-01T18:50:55.97" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{653A25CE-F853-41CD-A80C-071E9A56C03D}">
+    <text>Isos themata me ti glossa</text>
+  </threadedComment>
+  <threadedComment ref="C7" dT="2026-10-01T18:52:12.55" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{9E380D5B-CD0D-461E-92F2-DBB3C3E05ED0}" parentId="{653A25CE-F853-41CD-A80C-071E9A56C03D}">
+    <text>roumania</text>
+  </threadedComment>
+  <threadedComment ref="C8" dT="2026-10-01T18:51:09.16" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{CBC4FE66-6F10-4A75-8F50-45357D88B4F9}">
+    <text>monaxikos</text>
+  </threadedComment>
+  <threadedComment ref="C8" dT="2026-10-01T18:51:20.32" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D5D5BB80-7936-4579-858D-BA760330281A}" parentId="{CBC4FE66-6F10-4A75-8F50-45357D88B4F9}">
+    <text>roumania</text>
+  </threadedComment>
+  <threadedComment ref="C10" dT="2026-10-01T18:52:40.56" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3CE025BD-885B-4BB4-8153-5BC45D96E63A}">
+    <text>roumania</text>
+  </threadedComment>
+  <threadedComment ref="C12" dT="2026-10-01T18:53:07.17" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{59815D4B-84E2-4C30-910E-50D01C3C6ED7}">
+    <text>Xasimoto, elleipsi prosoxis, astheneia cushing</text>
+  </threadedComment>
+  <threadedComment ref="C17" dT="2026-09-22T09:38:48.85" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{4647EABC-BD0A-4287-98AE-93002CBD969E}">
+    <text>Exei voitho</text>
+  </threadedComment>
+  <threadedComment ref="C17" dT="2026-10-02T08:19:54.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{6A555735-0A59-4459-B3B9-993E6176570B}" parentId="{4647EABC-BD0A-4287-98AE-93002CBD969E}">
+    <text>stiriksi</text>
+  </threadedComment>
+  <threadedComment ref="C18" dT="2026-10-02T08:20:20.01" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D0C2496A-FD3A-4795-86E4-65A32C49D3BB}">
+    <text>Noxelikos, pithanos ethismos sta electronica paixnidia</text>
+  </threadedComment>
+  <threadedComment ref="C20" dT="2026-10-02T08:21:02.61" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{CD7FCC05-427C-4B42-A9A7-2AFEEF3F93F9}">
+    <text>Poli evesthiti, kleei eukola, politekni</text>
+  </threadedComment>
+  <threadedComment ref="C22" dT="2026-10-02T08:21:14.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{61FB07C0-0E78-4C8B-AA14-9FC2FF75EB53}">
+    <text>vogotonia</text>
+  </threadedComment>
+  <threadedComment ref="C23" dT="2026-09-22T09:31:53.95" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{A20A5040-4856-4E57-BDA4-AE16EF61198C}">
+    <text>Special, pontios</text>
+  </threadedComment>
+  <threadedComment ref="C24" dT="2026-10-02T08:22:39.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{5B59CB62-C4AC-414E-99F2-9D3F0BAE7F43}">
+    <text>Stiriksi</text>
+  </threadedComment>
+  <threadedComment ref="C27" dT="2026-10-02T08:21:35.28" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{0F457041-30F1-42D5-86AA-827F66CF5BFF}">
+    <text>stiriksi</text>
+  </threadedComment>
+  <threadedComment ref="C30" dT="2026-10-05T07:13:32.27" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3AB30EA2-F1F4-4B35-A695-4BD343EDA7AB}">
+    <text>Roumania, diskolies sta ellinika</text>
+  </threadedComment>
+  <threadedComment ref="C31" dT="2026-10-05T07:13:44.64" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{43A0AE65-034A-43EB-BC59-C4E0B72EF263}">
+    <text>Xorismenoi goneis</text>
+  </threadedComment>
+  <threadedComment ref="C32" dT="2026-10-05T07:14:01.31" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D4F088E1-432B-4086-AA01-1CA80A1DAD01}">
+    <text>Skaki, mathimatika olympiades</text>
+  </threadedComment>
+  <threadedComment ref="C33" dT="2026-10-05T07:14:18.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{003CF2AA-8884-4C36-88CB-5F0850865977}">
+    <text>Sitisi, papapona gia bullying sto dimotiko</text>
+  </threadedComment>
+  <threadedComment ref="C34" dT="2026-10-05T07:14:34.50" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{1F0FEE88-81AC-4F0C-A40A-208A40518123}">
+    <text xml:space="preserve">Sitisi, stiriksi
+</text>
+  </threadedComment>
+  <threadedComment ref="C35" dT="2026-10-05T07:14:51.75" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{BAD03DE3-79F7-4ED6-BBEE-A216F4A0CF81}">
+    <text>Didimoi me Kimona</text>
+  </threadedComment>
+  <threadedComment ref="C36" dT="2026-10-05T07:15:08.05" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{328D28C5-39DF-4E43-9191-E0347C55DC85}">
+    <text>Ypermetropia, astigmatismos</text>
+  </threadedComment>
+  <threadedComment ref="C38" dT="2026-10-05T07:15:27.54" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{CCF5C47C-DAC9-4163-911E-D25575FED191}">
+    <text>Sitisi, orfanos apo patera sti Syria</text>
+  </threadedComment>
+  <threadedComment ref="C39" dT="2026-10-05T07:15:40.47" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{1BCE4285-4670-48B9-A6C0-A7ACB02EB42C}">
+    <text>Spazei sixna h miti tis</text>
+  </threadedComment>
+  <threadedComment ref="C43" dT="2026-10-05T09:04:32.37" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{1BA79E55-D3B6-4B95-8DA1-57CBF311C4CC}">
+    <text>Xorismeni, apoklisitiki h mitera</text>
+  </threadedComment>
+  <threadedComment ref="C44" dT="2026-09-25T14:55:37.89" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2B329A84-0BDF-4381-88A4-81550D5EEF38}">
+    <text>indefferent</text>
+  </threadedComment>
+  <threadedComment ref="C45" dT="2026-10-05T09:04:58.84" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AAFA0838-65EA-4623-BC08-12544B2903FB}">
+    <text>Depy, sitisi, sinesthimatikes diskolies</text>
+  </threadedComment>
+  <threadedComment ref="C46" dT="2026-10-05T09:05:48.06" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{4D05AFA5-576B-4955-8CD5-510AFC85FC66}">
+    <text>Stiriksi, sitisi, menei me patera, oxi epaphi me mitera, o pateras fetos irthe, emenas me giagia kai pappou</text>
+  </threadedComment>
+  <threadedComment ref="C50" dT="2026-10-05T09:06:03.45" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{C94A78CF-2F80-4B38-B2A4-3CC0C4D9E0E4}">
+    <text>Dropalos, thelei enisxisi</text>
+  </threadedComment>
+  <threadedComment ref="C51" dT="2026-10-05T09:06:27.63" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D7EB80D4-5CFD-425F-B3B4-EB0A0BE048F6}">
+    <text>Stiriksi, mathisiakes adinamies</text>
+  </threadedComment>
+  <threadedComment ref="C52" dT="2026-09-21T06:24:16.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{222055CB-C6B5-4FA3-91EE-184B465B0798}">
+    <text xml:space="preserve">Little guy with glasses
+</text>
+  </threadedComment>
+  <threadedComment ref="C52" dT="2026-10-05T09:06:44.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{51D69F72-37C6-4888-83C5-CA1EA9ED6E7D}" parentId="{222055CB-C6B5-4FA3-91EE-184B465B0798}">
+    <text>alpabitismos</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -2594,7 +3242,7 @@
     <col min="10" max="10" width="58.5859375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="65.5859375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="61.87890625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="64.234375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="64.234375" style="1" customWidth="1"/>
     <col min="14" max="14" width="43.05859375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="47.8203125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="41.64453125" style="1" bestFit="1" customWidth="1"/>
@@ -2604,34 +3252,34 @@
   <sheetData>
     <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="7"/>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="36" t="s">
+      <c r="C1" s="35"/>
+      <c r="D1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="36" t="s">
+      <c r="E1" s="35"/>
+      <c r="F1" s="34" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="37"/>
-      <c r="H1" s="36" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>242</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="36" t="s">
+      <c r="I1" s="35"/>
+      <c r="J1" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="K1" s="37"/>
-      <c r="L1" s="36" t="s">
+      <c r="K1" s="35"/>
+      <c r="L1" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="M1" s="37"/>
-      <c r="N1" s="36" t="s">
+      <c r="M1" s="35"/>
+      <c r="N1" s="34" t="s">
         <v>250</v>
       </c>
-      <c r="O1" s="37"/>
+      <c r="O1" s="35"/>
     </row>
     <row r="2" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A2" s="1" t="s">
@@ -2686,8 +3334,11 @@
       <c r="L4" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="19" t="s">
         <v>338</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.5">
@@ -2892,7 +3543,7 @@
       <c r="L13" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="M13" s="19" t="s">
         <v>341</v>
       </c>
       <c r="N13" s="1" t="s">
@@ -3312,12 +3963,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0C9DD2-633E-44CA-9A93-86B2E2731C82}">
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.3515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.46875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.52734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5859375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5859375" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.17578125" style="9" customWidth="1"/>
     <col min="5" max="5" width="9.05859375" style="9"/>
     <col min="6" max="6" width="13.52734375" style="9" bestFit="1" customWidth="1"/>
@@ -3327,7 +3978,8 @@
     <col min="10" max="10" width="14.52734375" style="9" customWidth="1"/>
     <col min="11" max="11" width="18.9375" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.64453125" style="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.05859375" style="9"/>
+    <col min="13" max="13" width="16.87890625" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.05859375" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -3345,22 +3997,22 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="36" t="s">
         <v>289</v>
       </c>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34" t="s">
+      <c r="G2" s="36"/>
+      <c r="H2" s="36" t="s">
         <v>290</v>
       </c>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34" t="s">
+      <c r="I2" s="36"/>
+      <c r="J2" s="36" t="s">
         <v>303</v>
       </c>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34" t="s">
+      <c r="K2" s="36"/>
+      <c r="L2" s="36" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="34"/>
+      <c r="M2" s="36"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9" t="s">
@@ -3368,6 +4020,9 @@
       </c>
       <c r="I3" s="9" t="s">
         <v>294</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3394,6 +4049,9 @@
       <c r="L4" s="17" t="s">
         <v>240</v>
       </c>
+      <c r="M4" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="9">
@@ -3423,6 +4081,9 @@
       <c r="L5" s="17" t="s">
         <v>240</v>
       </c>
+      <c r="M5" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="9">
@@ -3452,6 +4113,9 @@
       <c r="L6" s="17" t="s">
         <v>240</v>
       </c>
+      <c r="M6" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="9">
@@ -3481,6 +4145,9 @@
       <c r="L7" s="17" t="s">
         <v>240</v>
       </c>
+      <c r="M7" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="9">
@@ -3510,6 +4177,9 @@
       <c r="L8" s="17" t="s">
         <v>240</v>
       </c>
+      <c r="M8" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="9">
@@ -3539,6 +4209,9 @@
       <c r="L9" s="17" t="s">
         <v>240</v>
       </c>
+      <c r="M9" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="9">
@@ -3568,6 +4241,9 @@
       <c r="L10" s="17" t="s">
         <v>240</v>
       </c>
+      <c r="M10" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="9">
@@ -3597,6 +4273,9 @@
       <c r="L11" s="17" t="s">
         <v>240</v>
       </c>
+      <c r="M11" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="9">
@@ -3626,6 +4305,9 @@
       <c r="L12" s="17" t="s">
         <v>240</v>
       </c>
+      <c r="M12" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="9">
@@ -3653,6 +4335,9 @@
       <c r="L13" s="17" t="s">
         <v>240</v>
       </c>
+      <c r="M13" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="9" t="s">
@@ -3894,16 +4579,16 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="9">
-        <v>4424904</v>
+        <v>4332504</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>50</v>
+        <v>295</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>87</v>
+        <v>296</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>75</v>
+        <v>297</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>173</v>
@@ -3926,13 +4611,13 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="9">
-        <v>4934404</v>
+        <v>4424904</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>75</v>
@@ -3957,106 +4642,77 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="9">
+        <v>3257704</v>
+      </c>
       <c r="B25" s="9" t="s">
-        <v>295</v>
+        <v>345</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>296</v>
+        <v>346</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="I25" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="L25" s="12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="L25" s="12"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="9">
+        <v>4934404</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F29" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H29" s="9" t="s">
         <v>294</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="9">
-        <v>9189004</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="9">
-        <v>5682904</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="9">
-        <v>9217204</v>
+        <v>9189004</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>143</v>
@@ -4064,21 +4720,25 @@
       <c r="E30" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="F30" s="22"/>
-      <c r="H30" s="22"/>
+      <c r="F30" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="I30" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="9">
-        <v>7319504</v>
+        <v>5682904</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>143</v>
@@ -4098,13 +4758,13 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="9">
-        <v>9254304</v>
+        <v>9217204</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>143</v>
@@ -4112,25 +4772,21 @@
       <c r="E32" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="F32" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H32" s="12" t="s">
-        <v>173</v>
-      </c>
+      <c r="F32" s="22"/>
+      <c r="H32" s="22"/>
       <c r="I32" s="12" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="9">
-        <v>2428404</v>
+        <v>7319504</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>152</v>
+        <v>49</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>143</v>
@@ -4150,13 +4806,13 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="9">
-        <v>2427904</v>
+        <v>9254304</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>143</v>
@@ -4176,13 +4832,13 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="9">
-        <v>8373704</v>
+        <v>2428404</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>151</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>143</v>
@@ -4202,13 +4858,13 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="9">
-        <v>5155004</v>
+        <v>2427904</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>143</v>
@@ -4228,13 +4884,13 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="9">
-        <v>1006390</v>
+        <v>8373704</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>143</v>
@@ -4252,120 +4908,96 @@
         <v>173</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="9" t="s">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="9">
+        <v>5155004</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="9">
+        <v>1006390</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="H40" s="9" t="s">
+      <c r="H42" s="9" t="s">
         <v>291</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="9">
-        <v>5324204</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H41" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="K41" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="L41" s="17" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="9">
-        <v>5996604</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="I42" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="J42" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="K42" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="L42" s="17" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="9">
-        <v>7153704</v>
+        <v>5324204</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>161</v>
+        <v>49</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>234</v>
+        <v>173</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>234</v>
+        <v>173</v>
       </c>
       <c r="G43" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="H43" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="I43" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="J43" s="24" t="s">
-        <v>234</v>
+      <c r="H43" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J43" s="12" t="s">
+        <v>173</v>
       </c>
       <c r="K43" s="17" t="s">
         <v>240</v>
@@ -4376,13 +5008,13 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="9">
-        <v>9185204</v>
+        <v>5996604</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>162</v>
+        <v>48</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>163</v>
+        <v>77</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>159</v>
@@ -4391,19 +5023,19 @@
         <v>173</v>
       </c>
       <c r="F44" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G44" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="G44" s="25" t="s">
-        <v>268</v>
-      </c>
       <c r="H44" s="12" t="s">
         <v>173</v>
       </c>
       <c r="I44" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="J44" s="24" t="s">
-        <v>234</v>
+      <c r="J44" s="12" t="s">
+        <v>173</v>
       </c>
       <c r="K44" s="17" t="s">
         <v>240</v>
@@ -4414,19 +5046,19 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="9">
-        <v>9185504</v>
+        <v>7153704</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>159</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>173</v>
+        <v>234</v>
       </c>
       <c r="F45" s="12" t="s">
         <v>234</v>
@@ -4434,11 +5066,11 @@
       <c r="G45" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="H45" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="I45" s="12" t="s">
-        <v>173</v>
+      <c r="H45" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="I45" s="24" t="s">
+        <v>234</v>
       </c>
       <c r="J45" s="24" t="s">
         <v>234</v>
@@ -4452,13 +5084,13 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="9">
-        <v>4913604</v>
+        <v>9185204</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>159</v>
@@ -4466,11 +5098,11 @@
       <c r="E46" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="F46" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="G46" s="28" t="s">
-        <v>264</v>
+      <c r="F46" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="G46" s="25" t="s">
+        <v>268</v>
       </c>
       <c r="H46" s="12" t="s">
         <v>173</v>
@@ -4478,8 +5110,8 @@
       <c r="I46" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="J46" s="12" t="s">
-        <v>173</v>
+      <c r="J46" s="24" t="s">
+        <v>234</v>
       </c>
       <c r="K46" s="17" t="s">
         <v>240</v>
@@ -4490,13 +5122,13 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="9">
-        <v>5436204</v>
+        <v>9185504</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>159</v>
@@ -4505,7 +5137,7 @@
         <v>173</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>173</v>
+        <v>234</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>173</v>
@@ -4516,8 +5148,8 @@
       <c r="I47" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="J47" s="12" t="s">
-        <v>173</v>
+      <c r="J47" s="24" t="s">
+        <v>234</v>
       </c>
       <c r="K47" s="17" t="s">
         <v>240</v>
@@ -4528,13 +5160,13 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="9">
-        <v>3506004</v>
+        <v>4913604</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>50</v>
+        <v>166</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>159</v>
@@ -4542,11 +5174,11 @@
       <c r="E48" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="F48" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="G48" s="12" t="s">
-        <v>173</v>
+      <c r="F48" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="G48" s="28" t="s">
+        <v>264</v>
       </c>
       <c r="H48" s="12" t="s">
         <v>173</v>
@@ -4566,13 +5198,13 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="9">
-        <v>6757304</v>
+        <v>5436204</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>169</v>
+        <v>99</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>159</v>
@@ -4604,13 +5236,13 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="9">
-        <v>6390804</v>
+        <v>3506004</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>159</v>
@@ -4640,55 +5272,131 @@
         <v>240</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="22"/>
-      <c r="B54" s="12" t="s">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="9">
+        <v>6757304</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H51" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="K51" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L51" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="9">
+        <v>6390804</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="I52" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="J52" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="K52" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L52" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="22"/>
+      <c r="B56" s="12" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="B55" s="12" t="s">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B57" s="12" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="28" t="s">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B58" s="12" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="31"/>
-      <c r="B57" s="12" t="s">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="31"/>
+      <c r="B59" s="12" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="24" t="s">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B60" s="12" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="25" t="s">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="25" t="s">
         <v>268</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B61" s="12" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="26" t="s">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B62" s="12" t="s">
         <v>270</v>
       </c>
     </row>
@@ -4707,7 +5415,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23D143C4-24B5-4F25-A9AC-CA5F9ACC8C3E}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="49.87890625" bestFit="1" customWidth="1"/>
@@ -4764,6 +5472,14 @@
       </c>
       <c r="C9" t="s">
         <v>336</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A10" t="s">
+        <v>342</v>
+      </c>
+      <c r="C10" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -4804,22 +5520,22 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="36" t="s">
         <v>289</v>
       </c>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34" t="s">
+      <c r="G2" s="36"/>
+      <c r="H2" s="36" t="s">
         <v>290</v>
       </c>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34" t="s">
+      <c r="I2" s="36"/>
+      <c r="J2" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34" t="s">
+      <c r="K2" s="36"/>
+      <c r="L2" s="36" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="34"/>
+      <c r="M2" s="36"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9" t="s">
@@ -5857,18 +6573,18 @@
       <c r="D1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="36" t="s">
         <v>289</v>
       </c>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34" t="s">
+      <c r="F1" s="36"/>
+      <c r="G1" s="36" t="s">
         <v>290</v>
       </c>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34" t="s">
+      <c r="H1" s="36"/>
+      <c r="I1" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="J1" s="34"/>
+      <c r="J1" s="36"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="9">
@@ -5990,7 +6706,8 @@
     <col min="3" max="3" width="17.9375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.17578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.29296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.3515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.41015625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.3515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -6006,22 +6723,22 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="36" t="s">
         <v>289</v>
       </c>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34" t="s">
+      <c r="H1" s="36"/>
+      <c r="I1" s="36" t="s">
         <v>290</v>
       </c>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34" t="s">
+      <c r="J1" s="36"/>
+      <c r="K1" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="L1" s="34"/>
-      <c r="M1" s="35" t="s">
+      <c r="L1" s="36"/>
+      <c r="M1" s="37" t="s">
         <v>337</v>
       </c>
-      <c r="N1" s="35"/>
+      <c r="N1" s="37"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
@@ -7411,4 +8128,1252 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{836E3DAF-4660-4453-8445-CAEF205E5F1E}">
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="7.703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.41015625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.9375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.17578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.3515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A4">
+        <v>4206804</v>
+      </c>
+      <c r="B4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A5">
+        <v>9307104</v>
+      </c>
+      <c r="B5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A6">
+        <v>2173704</v>
+      </c>
+      <c r="B6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A7">
+        <v>9257304</v>
+      </c>
+      <c r="B7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C7" t="s">
+        <v>214</v>
+      </c>
+      <c r="D7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A8">
+        <v>2915404</v>
+      </c>
+      <c r="B8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A9">
+        <v>2836604</v>
+      </c>
+      <c r="B9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A10">
+        <v>1274904</v>
+      </c>
+      <c r="B10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D10" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A11">
+        <v>3863304</v>
+      </c>
+      <c r="B11" t="s">
+        <v>220</v>
+      </c>
+      <c r="C11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D11" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A12">
+        <v>3403504</v>
+      </c>
+      <c r="B12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A13">
+        <v>4721304</v>
+      </c>
+      <c r="B13" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A14">
+        <v>3924304</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D14" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A15">
+        <v>4041704</v>
+      </c>
+      <c r="B15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" t="s">
+        <v>226</v>
+      </c>
+      <c r="D15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A16">
+        <v>9280704</v>
+      </c>
+      <c r="B16" t="s">
+        <v>227</v>
+      </c>
+      <c r="C16" t="s">
+        <v>228</v>
+      </c>
+      <c r="D16" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="C17" t="s">
+        <v>229</v>
+      </c>
+      <c r="D17" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="B18" t="s">
+        <v>230</v>
+      </c>
+      <c r="C18" t="s">
+        <v>231</v>
+      </c>
+      <c r="D18" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A22">
+        <v>9693404</v>
+      </c>
+      <c r="B22" t="s">
+        <v>197</v>
+      </c>
+      <c r="C22" t="s">
+        <v>198</v>
+      </c>
+      <c r="D22" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A23">
+        <v>222222</v>
+      </c>
+      <c r="B23" t="s">
+        <v>200</v>
+      </c>
+      <c r="C23" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A24">
+        <v>9743804</v>
+      </c>
+      <c r="B24" t="s">
+        <v>202</v>
+      </c>
+      <c r="C24" t="s">
+        <v>203</v>
+      </c>
+      <c r="D24" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A25">
+        <v>111111</v>
+      </c>
+      <c r="B25" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D25" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A26">
+        <v>9662304</v>
+      </c>
+      <c r="B26" t="s">
+        <v>206</v>
+      </c>
+      <c r="C26" t="s">
+        <v>207</v>
+      </c>
+      <c r="D26" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="B27" t="s">
+        <v>274</v>
+      </c>
+      <c r="C27" t="s">
+        <v>275</v>
+      </c>
+      <c r="D27" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="B28" t="s">
+        <v>274</v>
+      </c>
+      <c r="C28" t="s">
+        <v>276</v>
+      </c>
+      <c r="D28" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A32">
+        <v>3578804</v>
+      </c>
+      <c r="B32" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A33">
+        <v>9289704</v>
+      </c>
+      <c r="B33" t="s">
+        <v>179</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A34">
+        <v>9344404</v>
+      </c>
+      <c r="B34" t="s">
+        <v>180</v>
+      </c>
+      <c r="C34" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A35">
+        <v>6746404</v>
+      </c>
+      <c r="B35" t="s">
+        <v>182</v>
+      </c>
+      <c r="C35" t="s">
+        <v>183</v>
+      </c>
+      <c r="D35" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A36">
+        <v>9257604</v>
+      </c>
+      <c r="B36" t="s">
+        <v>184</v>
+      </c>
+      <c r="C36" t="s">
+        <v>185</v>
+      </c>
+      <c r="D36" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A37">
+        <v>9717204</v>
+      </c>
+      <c r="B37" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A38">
+        <v>2298204</v>
+      </c>
+      <c r="B38" t="s">
+        <v>188</v>
+      </c>
+      <c r="C38" t="s">
+        <v>189</v>
+      </c>
+      <c r="D38" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A39">
+        <v>5784804</v>
+      </c>
+      <c r="B39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" t="s">
+        <v>190</v>
+      </c>
+      <c r="D39" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A40">
+        <v>9321704</v>
+      </c>
+      <c r="B40" t="s">
+        <v>191</v>
+      </c>
+      <c r="C40" t="s">
+        <v>192</v>
+      </c>
+      <c r="D40" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A41">
+        <v>9720304</v>
+      </c>
+      <c r="B41" t="s">
+        <v>193</v>
+      </c>
+      <c r="C41" t="s">
+        <v>194</v>
+      </c>
+      <c r="D41" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A42">
+        <v>9317404</v>
+      </c>
+      <c r="B42" t="s">
+        <v>195</v>
+      </c>
+      <c r="C42" t="s">
+        <v>67</v>
+      </c>
+      <c r="D42" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43">
+        <v>8333604</v>
+      </c>
+      <c r="B43" t="s">
+        <v>196</v>
+      </c>
+      <c r="C43" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" t="s">
+        <v>178</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FEE7927-B2CB-4F8C-B929-249864A39417}">
+  <dimension ref="A1:E62"/>
+  <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="8.3515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5859375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5859375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.17578125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="10.234375" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.05859375" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="9">
+        <v>9285104</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="9">
+        <v>8324104</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="9">
+        <v>6811804</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="9">
+        <v>5436904</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="9">
+        <v>7025704</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="9">
+        <v>8435804</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="9">
+        <v>5069104</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="9">
+        <v>5222304</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="9">
+        <v>1981204</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="9">
+        <v>3766704</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="9">
+        <v>5551204</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="9">
+        <v>2056004</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="9">
+        <v>3318504</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="9">
+        <v>4926804</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="9">
+        <v>7568204</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="9">
+        <v>5111404</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="9">
+        <v>4332504</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="9">
+        <v>4332504</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="9">
+        <v>4424904</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="9">
+        <v>3257704</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="9">
+        <v>4934404</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="29" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="9">
+        <v>9189004</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="9">
+        <v>5682904</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="9">
+        <v>9217204</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="9">
+        <v>7319504</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="9">
+        <v>9254304</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="9">
+        <v>2428404</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="9">
+        <v>2427904</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="9">
+        <v>8373704</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="9">
+        <v>5155004</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="9">
+        <v>1006390</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="9">
+        <v>5324204</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="9">
+        <v>5996604</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="9">
+        <v>7153704</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="9">
+        <v>9185204</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="9">
+        <v>9185504</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="9">
+        <v>4913604</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="9">
+        <v>5436204</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="9">
+        <v>3506004</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="9">
+        <v>6757304</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="9">
+        <v>6390804</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="22"/>
+      <c r="B56" s="12" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="31"/>
+      <c r="B59" s="12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1434" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49EC3DE6-B934-409B-A7D3-E5F64B1E9A4C}"/>
+  <xr:revisionPtr revIDLastSave="1515" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FC68A78-307E-4C42-B7D7-367EC2EB1997}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
     HW: p40, ex.7</t>
       </text>
     </comment>
-    <comment ref="A13" authorId="1" shapeId="0" xr:uid="{166B4807-79FD-403D-9189-ED88B5EDB4C9}">
+    <comment ref="A11" authorId="1" shapeId="0" xr:uid="{166B4807-79FD-403D-9189-ED88B5EDB4C9}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1160,7 +1160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="363">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1909,9 +1909,6 @@
     <t>week 12 October</t>
   </si>
   <si>
-    <t>week 17 October</t>
-  </si>
-  <si>
     <t>TEST</t>
   </si>
   <si>
@@ -2005,12 +2002,6 @@
     <t>A1: border/watermark/add image in word</t>
   </si>
   <si>
-    <t>In class</t>
-  </si>
-  <si>
-    <t>check homework on both</t>
-  </si>
-  <si>
     <t>ΕΚΛΟΓΕΣ</t>
   </si>
   <si>
@@ -2053,9 +2044,6 @@
     <t>A2</t>
   </si>
   <si>
-    <t>A5.2 Μ1 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου</t>
-  </si>
-  <si>
     <t>A5.2 Μ2 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου</t>
   </si>
   <si>
@@ -2092,9 +2080,6 @@
     <t>powerpoint introduction</t>
   </si>
   <si>
-    <t>REDO - CREATE MY OWN FYLLO ERGASIAS</t>
-  </si>
-  <si>
     <t>na ginei erevna sto B1, B2</t>
   </si>
   <si>
@@ -2213,13 +2198,64 @@
   </si>
   <si>
     <t>A5.1 Μ2 - Πλοήγηση στο Διαδίκτυο + A5.1 Μ3 - Εντοπισμός Πληροφοριών από το Διαδίκτυο</t>
+  </si>
+  <si>
+    <t>Α5.2 Μ1 - Εναλλακτικό Φύλλο Εργασίας - Ηλεκτρονικό Ταχυδρομείο</t>
+  </si>
+  <si>
+    <t>A5.2 Μ2 + A5.2 M3</t>
+  </si>
+  <si>
+    <t>A5.2 Μ1 - Proton mail - Νοήτικό στήριγμα - Δημιουργία και αποστολή εμαιλ - mono ena atomo katafere na kenei email</t>
+  </si>
+  <si>
+    <t>excel min max sum</t>
+  </si>
+  <si>
+    <t>week 19 October</t>
+  </si>
+  <si>
+    <t>week 26 October</t>
+  </si>
+  <si>
+    <t>Erevna - B41M8 - Επεξεργασία αριθμητικών δεδομένων και αναφορές κελιών</t>
+  </si>
+  <si>
+    <t>week 2 November</t>
+  </si>
+  <si>
+    <t>week 9 November</t>
+  </si>
+  <si>
+    <t>week 16 November</t>
+  </si>
+  <si>
+    <t>week 23 November</t>
+  </si>
+  <si>
+    <t>week 30 November</t>
+  </si>
+  <si>
+    <t>A5.3 Μ1 - Κίνδυνοι στο Διαδίκτυο</t>
+  </si>
+  <si>
+    <t>A5.3 Μ2 - Κίνδυνοι στο Διαδίκτυο</t>
+  </si>
+  <si>
+    <t>A2Μ1 - Κατηγορίες Υπολογιστών</t>
+  </si>
+  <si>
+    <t>A2Μ2 - Μονάδες και Περιφερειακά του Υπολογιστή - Μέρος 1</t>
+  </si>
+  <si>
+    <t>A2Μ2 - Μονάδες και Περιφερειακά του Υπολογιστή - Μέρος 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2270,6 +2306,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2409,7 +2452,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2465,19 +2508,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2524,6 +2555,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2815,7 +2861,7 @@
   <threadedComment ref="F7" dT="2026-09-21T07:31:36.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{41FD7CA7-2390-44D2-8B22-26BF56BE8599}">
     <text>HW: p40, ex.7</text>
   </threadedComment>
-  <threadedComment ref="A13" dT="2026-09-16T08:45:14.77" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{166B4807-79FD-403D-9189-ED88B5EDB4C9}">
+  <threadedComment ref="A11" dT="2026-09-16T08:45:14.77" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{166B4807-79FD-403D-9189-ED88B5EDB4C9}">
     <text xml:space="preserve">Good class
 </text>
   </threadedComment>
@@ -3258,831 +3304,872 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH36"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="11.41015625" style="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.9375" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1171875" style="29" customWidth="1"/>
-    <col min="4" max="4" width="35.52734375" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="41.9375" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42.17578125" style="29" customWidth="1"/>
-    <col min="10" max="10" width="58.5859375" style="29" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="65.5859375" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="61.87890625" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="53.1171875" style="29" customWidth="1"/>
-    <col min="14" max="14" width="43.05859375" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="47.8203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="41.64453125" style="29" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.52734375" style="29" bestFit="1" customWidth="1"/>
-    <col min="18" max="60" width="9.05859375" style="29"/>
+    <col min="1" max="1" width="11.41015625" style="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.9375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1171875" style="25" customWidth="1"/>
+    <col min="4" max="4" width="35.52734375" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="41.9375" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42.17578125" style="25" customWidth="1"/>
+    <col min="10" max="10" width="58.5859375" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="65.5859375" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="61.87890625" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="53.1171875" style="25" customWidth="1"/>
+    <col min="14" max="14" width="43.05859375" style="25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="47.8203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.41015625" style="25" customWidth="1"/>
+    <col min="17" max="17" width="24.41015625" style="25" customWidth="1"/>
+    <col min="18" max="18" width="26.41015625" style="25" customWidth="1"/>
+    <col min="19" max="19" width="25.64453125" style="25" customWidth="1"/>
+    <col min="20" max="20" width="31.5859375" style="25" customWidth="1"/>
+    <col min="21" max="21" width="32.29296875" style="25" customWidth="1"/>
+    <col min="22" max="22" width="18.3515625" style="25" customWidth="1"/>
+    <col min="23" max="23" width="14.76171875" style="25" customWidth="1"/>
+    <col min="24" max="24" width="14.3515625" style="25" customWidth="1"/>
+    <col min="25" max="25" width="14.234375" style="25" customWidth="1"/>
+    <col min="26" max="60" width="9.05859375" style="25"/>
     <col min="61" max="16384" width="9.05859375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="32"/>
-      <c r="B1" s="26" t="s">
+      <c r="A1" s="28"/>
+      <c r="B1" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="26" t="s">
+      <c r="C1" s="41"/>
+      <c r="D1" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="27"/>
-      <c r="F1" s="26" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="40" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="26" t="s">
+      <c r="G1" s="41"/>
+      <c r="H1" s="40" t="s">
         <v>241</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="26" t="s">
+      <c r="I1" s="41"/>
+      <c r="J1" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="26" t="s">
+      <c r="K1" s="41"/>
+      <c r="L1" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="M1" s="27"/>
-      <c r="N1" s="26" t="s">
+      <c r="M1" s="41"/>
+      <c r="N1" s="40" t="s">
+        <v>350</v>
+      </c>
+      <c r="O1" s="41"/>
+      <c r="P1" s="40" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="40" t="s">
+        <v>353</v>
+      </c>
+      <c r="S1" s="41"/>
+      <c r="T1" s="40" t="s">
+        <v>354</v>
+      </c>
+      <c r="U1" s="41"/>
+      <c r="V1" s="40" t="s">
+        <v>355</v>
+      </c>
+      <c r="W1" s="41"/>
+      <c r="X1" s="40" t="s">
+        <v>356</v>
+      </c>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="40" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA1" s="41"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
+      <c r="AH1" s="29"/>
+      <c r="AI1" s="29"/>
+      <c r="AJ1" s="29"/>
+      <c r="AK1" s="29"/>
+      <c r="AL1" s="29"/>
+      <c r="AM1" s="29"/>
+      <c r="AN1" s="29"/>
+      <c r="AO1" s="29"/>
+      <c r="AP1" s="29"/>
+      <c r="AQ1" s="29"/>
+      <c r="AR1" s="29"/>
+      <c r="AS1" s="29"/>
+      <c r="AT1" s="29"/>
+      <c r="AU1" s="29"/>
+      <c r="AV1" s="29"/>
+      <c r="AW1" s="29"/>
+      <c r="AX1" s="29"/>
+      <c r="AY1" s="29"/>
+      <c r="AZ1" s="29"/>
+      <c r="BA1" s="29"/>
+      <c r="BB1" s="29"/>
+      <c r="BC1" s="29"/>
+      <c r="BD1" s="29"/>
+      <c r="BE1" s="29"/>
+      <c r="BF1" s="29"/>
+      <c r="BG1" s="29"/>
+      <c r="BH1" s="29"/>
+    </row>
+    <row r="2" spans="1:60" s="2" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="24"/>
+      <c r="AA2" s="24"/>
+      <c r="AB2" s="24"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="24"/>
+      <c r="AH2" s="24"/>
+      <c r="AI2" s="24"/>
+      <c r="AJ2" s="24"/>
+      <c r="AK2" s="24"/>
+      <c r="AL2" s="24"/>
+      <c r="AM2" s="24"/>
+      <c r="AN2" s="24"/>
+      <c r="AO2" s="24"/>
+      <c r="AP2" s="24"/>
+      <c r="AQ2" s="24"/>
+      <c r="AR2" s="24"/>
+      <c r="AS2" s="24"/>
+      <c r="AT2" s="24"/>
+      <c r="AU2" s="24"/>
+      <c r="AV2" s="24"/>
+      <c r="AW2" s="24"/>
+      <c r="AX2" s="24"/>
+      <c r="AY2" s="24"/>
+      <c r="AZ2" s="24"/>
+      <c r="BA2" s="24"/>
+      <c r="BB2" s="24"/>
+      <c r="BC2" s="24"/>
+      <c r="BD2" s="24"/>
+      <c r="BE2" s="24"/>
+      <c r="BF2" s="24"/>
+      <c r="BG2" s="24"/>
+      <c r="BH2" s="24"/>
+    </row>
+    <row r="3" spans="1:60" x14ac:dyDescent="0.5">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A4" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="K4" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="M4" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="N4" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="Y4" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="O1" s="27"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="33"/>
-      <c r="AI1" s="33"/>
-      <c r="AJ1" s="33"/>
-      <c r="AK1" s="33"/>
-      <c r="AL1" s="33"/>
-      <c r="AM1" s="33"/>
-      <c r="AN1" s="33"/>
-      <c r="AO1" s="33"/>
-      <c r="AP1" s="33"/>
-      <c r="AQ1" s="33"/>
-      <c r="AR1" s="33"/>
-      <c r="AS1" s="33"/>
-      <c r="AT1" s="33"/>
-      <c r="AU1" s="33"/>
-      <c r="AV1" s="33"/>
-      <c r="AW1" s="33"/>
-      <c r="AX1" s="33"/>
-      <c r="AY1" s="33"/>
-      <c r="AZ1" s="33"/>
-      <c r="BA1" s="33"/>
-      <c r="BB1" s="33"/>
-      <c r="BC1" s="33"/>
-      <c r="BD1" s="33"/>
-      <c r="BE1" s="33"/>
-      <c r="BF1" s="33"/>
-      <c r="BG1" s="33"/>
-      <c r="BH1" s="33"/>
-    </row>
-    <row r="2" spans="1:60" s="2" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="28"/>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
-      <c r="AG2" s="28"/>
-      <c r="AH2" s="28"/>
-      <c r="AI2" s="28"/>
-      <c r="AJ2" s="28"/>
-      <c r="AK2" s="28"/>
-      <c r="AL2" s="28"/>
-      <c r="AM2" s="28"/>
-      <c r="AN2" s="28"/>
-      <c r="AO2" s="28"/>
-      <c r="AP2" s="28"/>
-      <c r="AQ2" s="28"/>
-      <c r="AR2" s="28"/>
-      <c r="AS2" s="28"/>
-      <c r="AT2" s="28"/>
-      <c r="AU2" s="28"/>
-      <c r="AV2" s="28"/>
-      <c r="AW2" s="28"/>
-      <c r="AX2" s="28"/>
-      <c r="AY2" s="28"/>
-      <c r="AZ2" s="28"/>
-      <c r="BA2" s="28"/>
-      <c r="BB2" s="28"/>
-      <c r="BC2" s="28"/>
-      <c r="BD2" s="28"/>
-      <c r="BE2" s="28"/>
-      <c r="BF2" s="28"/>
-      <c r="BG2" s="28"/>
-      <c r="BH2" s="28"/>
-    </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.5">
-      <c r="A3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="29" t="s">
+    </row>
+    <row r="5" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A5" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="J5" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="L5" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="N5" s="25" t="s">
+        <v>347</v>
+      </c>
+      <c r="X5" s="39" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:60" ht="28.7" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="L6" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="N6" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="O6" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="P6" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q6" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="R6" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="S6" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="T6" s="25" t="s">
+        <v>361</v>
+      </c>
+      <c r="U6" s="25" t="s">
+        <v>362</v>
+      </c>
+      <c r="X6" s="39" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A7" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="K7" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="L7" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="X7" s="39" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:60" x14ac:dyDescent="0.5">
+      <c r="A10" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="29" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="4" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A4" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>261</v>
-      </c>
-      <c r="C4" s="36" t="s">
+      <c r="C10" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="M10" s="25" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A11" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>253</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>254</v>
-      </c>
-      <c r="I4" s="25" t="s">
+      <c r="C11" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="J4" s="25" t="s">
-        <v>255</v>
-      </c>
-      <c r="K4" s="25" t="s">
+      <c r="G11" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="L11" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="M11" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="N11" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="O11" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="P11" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="V11" s="39" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A12" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="K12" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="L12" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="M12" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="N12" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="V12" s="39" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A13" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="L13" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="N13" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="O13" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="P13" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="V13" s="39" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" spans="1:60" x14ac:dyDescent="0.5">
+      <c r="A16" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="H17" s="33" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A18" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="F18" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="I18" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="L18" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="N18" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="O18" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="P18" s="36" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q18" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="R18" s="27" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A19" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="F19" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="G19" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="I19" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="J19" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="K19" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="L19" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="M19" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="N19" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="O19" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="P19" s="36" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q19" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="R19" s="27" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A20" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="E20" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I20" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="K20" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="L20" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="M20" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="N20" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="O20" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="P20" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q20" s="36" t="s">
+        <v>249</v>
+      </c>
+      <c r="R20" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="S20" s="27" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="B21" s="32"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="26"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="27"/>
+      <c r="Q21" s="27"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="A22" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="G22" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="J22" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="K22" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="L22" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="M22" s="23" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="B25" s="37"/>
+      <c r="C25" s="25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="B26" s="34"/>
+      <c r="C26" s="25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="B27" s="27"/>
+      <c r="C27" s="25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="B31" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="B32" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="25" t="s">
         <v>256</v>
       </c>
-      <c r="L4" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="M4" s="25" t="s">
-        <v>336</v>
-      </c>
-      <c r="N4" s="31" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.5">
-      <c r="A5" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>253</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>254</v>
-      </c>
-      <c r="I5" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="J5" s="25" t="s">
-        <v>255</v>
-      </c>
-      <c r="K5" s="25" t="s">
-        <v>256</v>
-      </c>
-      <c r="L5" s="25" t="s">
-        <v>336</v>
-      </c>
-      <c r="M5" s="25" t="s">
-        <v>297</v>
-      </c>
-      <c r="N5" s="29" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="6" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A6" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>253</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>254</v>
-      </c>
-      <c r="H6" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>255</v>
-      </c>
-      <c r="J6" s="25" t="s">
-        <v>256</v>
-      </c>
-      <c r="K6" s="25" t="s">
-        <v>349</v>
-      </c>
-      <c r="L6" s="25" t="s">
-        <v>317</v>
-      </c>
-      <c r="M6" s="31" t="s">
-        <v>336</v>
-      </c>
-      <c r="N6" s="31" t="s">
-        <v>297</v>
-      </c>
-      <c r="O6" s="29" t="s">
-        <v>298</v>
-      </c>
-      <c r="P6" s="29" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="7" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A7" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>261</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>272</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>253</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>254</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="K7" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="L7" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="M7" s="31" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="9" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="B9" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>256</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.5">
-      <c r="B10" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.5">
-      <c r="A12" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>348</v>
-      </c>
-      <c r="M12" s="29" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.5">
-      <c r="A13" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>252</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>258</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="J13" s="25" t="s">
-        <v>300</v>
-      </c>
-      <c r="K13" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="L13" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="M13" s="25" t="s">
-        <v>339</v>
-      </c>
-      <c r="N13" s="29" t="s">
-        <v>330</v>
-      </c>
-      <c r="O13" s="29" t="s">
-        <v>331</v>
-      </c>
-      <c r="P13" s="29" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="14" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A14" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>252</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>258</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="K14" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="L14" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="M14" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="N14" s="29" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.5">
-      <c r="A15" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" s="25" t="s">
-        <v>252</v>
-      </c>
-      <c r="H15" s="25" t="s">
-        <v>258</v>
-      </c>
-      <c r="I15" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="J15" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="K15" s="25" t="s">
-        <v>300</v>
-      </c>
-      <c r="L15" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="M15" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="N15" s="29" t="s">
-        <v>330</v>
-      </c>
-      <c r="O15" s="29" t="s">
-        <v>331</v>
-      </c>
-      <c r="P15" s="29" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A18" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="H19" s="37" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" ht="43" x14ac:dyDescent="0.5">
-      <c r="A20" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="E20" s="39" t="s">
-        <v>234</v>
-      </c>
-      <c r="F20" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="G20" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="H20" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="I20" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="J20" s="25" t="s">
-        <v>242</v>
-      </c>
-      <c r="K20" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="L20" s="25" t="s">
-        <v>327</v>
-      </c>
-      <c r="M20" s="25" t="s">
-        <v>328</v>
-      </c>
-      <c r="N20" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="O20" s="31" t="s">
-        <v>303</v>
-      </c>
-      <c r="P20" s="40" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q20" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="R20" s="31" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="43" x14ac:dyDescent="0.5">
-      <c r="A21" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="E21" s="39" t="s">
-        <v>234</v>
-      </c>
-      <c r="F21" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="H21" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="I21" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="J21" s="25" t="s">
-        <v>242</v>
-      </c>
-      <c r="K21" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="L21" s="25" t="s">
-        <v>327</v>
-      </c>
-      <c r="M21" s="25" t="s">
-        <v>328</v>
-      </c>
-      <c r="N21" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="O21" s="31" t="s">
-        <v>303</v>
-      </c>
-      <c r="P21" s="40" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q21" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="R21" s="31" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="71.7" x14ac:dyDescent="0.5">
-      <c r="A22" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="E22" s="39" t="s">
-        <v>234</v>
-      </c>
-      <c r="F22" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="G22" s="30" t="s">
+    </row>
+    <row r="33" spans="2:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="B33" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="B34" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="H22" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="I22" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="K22" s="25" t="s">
-        <v>242</v>
-      </c>
-      <c r="L22" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="M22" s="25" t="s">
-        <v>327</v>
-      </c>
-      <c r="N22" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="O22" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="P22" s="31" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q22" s="40" t="s">
-        <v>250</v>
-      </c>
-      <c r="R22" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="S22" s="31" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="B23" s="36"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="30"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="40"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="31"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A24" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="E24" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>280</v>
-      </c>
-      <c r="G24" s="39" t="s">
-        <v>284</v>
-      </c>
-      <c r="J24" s="25" t="s">
-        <v>309</v>
-      </c>
-      <c r="K24" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="B27" s="41"/>
-      <c r="C27" s="29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="B28" s="38"/>
-      <c r="C28" s="29" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="B29" s="31"/>
-      <c r="C29" s="29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B33" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B34" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="29" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="B35" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B36" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="29" t="s">
-        <v>286</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="13">
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="B1:C1"/>
@@ -4090,6 +4177,11 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4134,32 +4226,32 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23" t="s">
-        <v>302</v>
-      </c>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="M2" s="23"/>
+      <c r="F2" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42" t="s">
+        <v>324</v>
+      </c>
+      <c r="M2" s="42"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>121</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4481,19 +4573,19 @@
         <v>72</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4719,13 +4811,13 @@
         <v>4332504</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>173</v>
@@ -4783,13 +4875,13 @@
         <v>3257704</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -4835,10 +4927,10 @@
         <v>140</v>
       </c>
       <c r="F29" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="H29" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -5102,7 +5194,7 @@
         <v>157</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -5239,7 +5331,7 @@
         <v>233</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>173</v>
@@ -5312,10 +5404,10 @@
         <v>173</v>
       </c>
       <c r="F48" s="18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>173</v>
@@ -5488,7 +5580,7 @@
     <row r="56" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="12"/>
       <c r="B56" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -5496,21 +5588,21 @@
         <v>173</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>263</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="20"/>
       <c r="B59" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -5518,23 +5610,23 @@
         <v>233</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -5563,60 +5655,60 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C6" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C7" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C8" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C10" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -5657,22 +5749,22 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="M2" s="23"/>
+      <c r="F2" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42" t="s">
+        <v>324</v>
+      </c>
+      <c r="M2" s="42"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -5702,10 +5794,10 @@
         <v>173</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L4" s="11" t="s">
         <v>239</v>
@@ -5767,7 +5859,7 @@
         <v>173</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L6" s="11" t="s">
         <v>239</v>
@@ -6049,7 +6141,7 @@
         <v>233</v>
       </c>
       <c r="J17" s="16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>239</v>
@@ -6078,7 +6170,7 @@
         <v>233</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>239</v>
@@ -6107,7 +6199,7 @@
         <v>233</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>239</v>
@@ -6268,10 +6360,10 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>39</v>
@@ -6710,18 +6802,18 @@
       <c r="D1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="J1" s="23"/>
+      <c r="E1" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="J1" s="42"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
@@ -6861,32 +6953,32 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="L1" s="23"/>
-      <c r="M1" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="N1" s="24"/>
+      <c r="G1" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="L1" s="42"/>
+      <c r="M1" s="43" t="s">
+        <v>330</v>
+      </c>
+      <c r="N1" s="43"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="K3" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="L3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -6918,7 +7010,7 @@
         <v>173</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>173</v>
@@ -6959,7 +7051,7 @@
         <v>173</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K5" s="8" t="s">
         <v>173</v>
@@ -7000,7 +7092,7 @@
         <v>173</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>173</v>
@@ -7041,7 +7133,7 @@
         <v>173</v>
       </c>
       <c r="J7" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>173</v>
@@ -7082,7 +7174,7 @@
         <v>173</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>173</v>
@@ -7123,7 +7215,7 @@
         <v>173</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>173</v>
@@ -7164,7 +7256,7 @@
         <v>173</v>
       </c>
       <c r="J10" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>173</v>
@@ -7205,7 +7297,7 @@
         <v>173</v>
       </c>
       <c r="J11" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K11" s="12"/>
       <c r="L11" s="14" t="s">
@@ -7244,7 +7336,7 @@
         <v>173</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K12" s="8" t="s">
         <v>173</v>
@@ -7285,7 +7377,7 @@
         <v>173</v>
       </c>
       <c r="J13" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>173</v>
@@ -7324,7 +7416,7 @@
         <v>173</v>
       </c>
       <c r="J14" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>173</v>
@@ -7365,7 +7457,7 @@
         <v>173</v>
       </c>
       <c r="J15" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K15" s="8" t="s">
         <v>173</v>
@@ -7406,7 +7498,7 @@
         <v>173</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>173</v>
@@ -7441,7 +7533,7 @@
         <v>173</v>
       </c>
       <c r="J17" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>173</v>
@@ -7479,7 +7571,7 @@
         <v>173</v>
       </c>
       <c r="J18" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>173</v>
@@ -7510,13 +7602,13 @@
         <v>60</v>
       </c>
       <c r="L21" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="M21" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="N21" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7542,13 +7634,13 @@
         <v>173</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>173</v>
       </c>
       <c r="J22" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>173</v>
@@ -7586,13 +7678,13 @@
         <v>173</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>173</v>
       </c>
       <c r="J23" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>173</v>
@@ -7630,22 +7722,22 @@
         <v>173</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>173</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>173</v>
       </c>
       <c r="L24" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M24" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N24" s="8" t="s">
         <v>173</v>
@@ -7674,11 +7766,11 @@
         <v>173</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I25" s="20"/>
       <c r="J25" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K25" s="12"/>
       <c r="L25" s="8" t="s">
@@ -7712,13 +7804,13 @@
         <v>173</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>173</v>
       </c>
       <c r="J26" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>173</v>
@@ -7735,13 +7827,13 @@
     </row>
     <row r="27" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C27" t="s">
         <v>273</v>
       </c>
-      <c r="C27" t="s">
-        <v>274</v>
-      </c>
       <c r="D27" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
@@ -7749,32 +7841,32 @@
         <v>173</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I27" s="20"/>
       <c r="J27" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K27" s="8" t="s">
         <v>173</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M27" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N27" s="12"/>
     </row>
     <row r="28" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
@@ -7782,11 +7874,11 @@
         <v>173</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I28" s="20"/>
       <c r="J28" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>173</v>
@@ -7801,7 +7893,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.5">
       <c r="L30" s="8" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.5">
@@ -7809,7 +7901,7 @@
         <v>16</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7838,7 +7930,7 @@
         <v>173</v>
       </c>
       <c r="J32" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K32" s="8" t="s">
         <v>173</v>
@@ -7874,7 +7966,7 @@
       </c>
       <c r="I33" s="12"/>
       <c r="J33" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K33" s="8" t="s">
         <v>173</v>
@@ -7910,7 +8002,7 @@
       </c>
       <c r="I34" s="20"/>
       <c r="J34" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K34" s="8" t="s">
         <v>173</v>
@@ -7944,7 +8036,7 @@
       </c>
       <c r="I35" s="12"/>
       <c r="J35" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K35" s="8" t="s">
         <v>173</v>
@@ -7982,7 +8074,7 @@
         <v>173</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K36" s="8" t="s">
         <v>173</v>
@@ -8018,7 +8110,7 @@
       </c>
       <c r="I37" s="12"/>
       <c r="J37" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K37" s="8" t="s">
         <v>173</v>
@@ -8054,7 +8146,7 @@
       </c>
       <c r="I38" s="12"/>
       <c r="J38" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K38" s="12"/>
       <c r="L38" s="8" t="s">
@@ -8090,7 +8182,7 @@
         <v>173</v>
       </c>
       <c r="J39" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K39" s="8" t="s">
         <v>173</v>
@@ -8128,7 +8220,7 @@
         <v>173</v>
       </c>
       <c r="J40" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K40" s="12"/>
       <c r="L40" s="8" t="s">
@@ -8161,10 +8253,10 @@
         <v>173</v>
       </c>
       <c r="I41" s="18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J41" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>173</v>
@@ -8200,7 +8292,7 @@
       </c>
       <c r="I42" s="12"/>
       <c r="J42" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K42" s="8" t="s">
         <v>173</v>
@@ -8238,7 +8330,7 @@
         <v>173</v>
       </c>
       <c r="J43" s="19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K43" s="8" t="s">
         <v>173</v>
@@ -8275,10 +8367,10 @@
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B3" t="s">
         <v>270</v>
-      </c>
-      <c r="B3" t="s">
-        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -8523,7 +8615,7 @@
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.5">
@@ -8612,24 +8704,24 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C27" t="s">
         <v>273</v>
       </c>
-      <c r="C27" t="s">
-        <v>274</v>
-      </c>
       <c r="D27" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.5">
@@ -8844,7 +8936,7 @@
         <v>121</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8998,7 +9090,7 @@
         <v>72</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9125,13 +9217,13 @@
         <v>4332504</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E24" s="19" t="s">
         <v>233</v>
@@ -9159,13 +9251,13 @@
         <v>3257704</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>173</v>
@@ -9481,7 +9573,7 @@
     <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="12"/>
       <c r="B56" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -9489,21 +9581,21 @@
         <v>173</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>263</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="20"/>
       <c r="B59" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -9511,23 +9603,23 @@
         <v>233</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1515" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FC68A78-307E-4C42-B7D7-367EC2EB1997}"/>
+  <xr:revisionPtr revIDLastSave="1553" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EF9DBFE-67D6-4304-BA9F-3FF5D5DD4A73}"/>
   <bookViews>
     <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,9 +19,9 @@
     <sheet name="B Gymnasiou" sheetId="3" r:id="rId4"/>
     <sheet name="Monada" sheetId="5" r:id="rId5"/>
     <sheet name="A Lyceum" sheetId="4" r:id="rId6"/>
-    <sheet name="anapliroseis" sheetId="7" r:id="rId7"/>
-    <sheet name="A Lyceum - tests" sheetId="12" r:id="rId8"/>
-    <sheet name="A Gymansiou - tests" sheetId="11" r:id="rId9"/>
+    <sheet name="A Gymansiou - tests" sheetId="11" r:id="rId7"/>
+    <sheet name="B Gymnasiou -tests" sheetId="13" r:id="rId8"/>
+    <sheet name="A Lyceum - tests" sheetId="12" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -734,133 +734,6 @@
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={376EB8CC-624A-4905-943C-003667EB4EEA}</author>
-    <author>tc={DC46CFF3-F130-4C35-ADEF-5A1F821781A9}</author>
-    <author>tc={B7A43FBB-5038-4FC3-8FAD-07EE5143A1F8}</author>
-    <author>tc={63C17029-8F90-4253-9CA7-E994CFD5D5A2}</author>
-    <author>tc={AA276D36-BF21-4BF1-B4EE-CFB1644CC25A}</author>
-    <author>tc={E15DDDED-B2BA-4607-867F-BB836742B4CF}</author>
-    <author>tc={959932C7-E7CF-4613-A506-DF1AB6866DD6}</author>
-    <author>tc={A44E3110-99FE-4968-95C4-FBBC90EA44AB}</author>
-    <author>tc={2FB97B2F-685A-47AD-B451-26CE099B5CDE}</author>
-    <author>tc={49700AAE-FBF5-4AF6-8413-5CA5A784A6FE}</author>
-    <author>tc={C1108176-F43A-484D-8C9A-1ABAB3DE80B2}</author>
-    <author>tc={F444680E-9CC4-4A89-898A-5ABDCDB06F58}</author>
-  </authors>
-  <commentList>
-    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{376EB8CC-624A-4905-943C-003667EB4EEA}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Seems like  a good kid</t>
-      </text>
-    </comment>
-    <comment ref="C11" authorId="1" shapeId="0" xr:uid="{DC46CFF3-F130-4C35-ADEF-5A1F821781A9}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    indifferent
-Reply:
-    Mourmouros
-</t>
-      </text>
-    </comment>
-    <comment ref="C12" authorId="2" shapeId="0" xr:uid="{B7A43FBB-5038-4FC3-8FAD-07EE5143A1F8}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Fili tou konstantinou</t>
-      </text>
-    </comment>
-    <comment ref="C15" authorId="3" shapeId="0" xr:uid="{63C17029-8F90-4253-9CA7-E994CFD5D5A2}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Quiet but tries</t>
-      </text>
-    </comment>
-    <comment ref="C16" authorId="4" shapeId="0" xr:uid="{AA276D36-BF21-4BF1-B4EE-CFB1644CC25A}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Blond, quiet</t>
-      </text>
-    </comment>
-    <comment ref="C23" authorId="5" shapeId="0" xr:uid="{E15DDDED-B2BA-4607-867F-BB836742B4CF}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Good student</t>
-      </text>
-    </comment>
-    <comment ref="C33" authorId="6" shapeId="0" xr:uid="{959932C7-E7CF-4613-A506-DF1AB6866DD6}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Not very careful
-Reply:
-    Ligo prixtissa, alla kali.</t>
-      </text>
-    </comment>
-    <comment ref="C34" authorId="7" shapeId="0" xr:uid="{A44E3110-99FE-4968-95C4-FBBC90EA44AB}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Get bored, starts playing games
-Reply:
-    Not paying attention
-Reply:
-    Keep an eye on him.</t>
-      </text>
-    </comment>
-    <comment ref="C35" authorId="8" shapeId="0" xr:uid="{2FB97B2F-685A-47AD-B451-26CE099B5CDE}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Fenete filotimos, with some knowledge</t>
-      </text>
-    </comment>
-    <comment ref="C38" authorId="9" shapeId="0" xr:uid="{49700AAE-FBF5-4AF6-8413-5CA5A784A6FE}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Kori tis Lelias</t>
-      </text>
-    </comment>
-    <comment ref="C42" authorId="10" shapeId="0" xr:uid="{C1108176-F43A-484D-8C9A-1ABAB3DE80B2}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Filotimos
-</t>
-      </text>
-    </comment>
-    <comment ref="C43" authorId="11" shapeId="0" xr:uid="{F444680E-9CC4-4A89-898A-5ABDCDB06F58}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    With glasses</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
     <author>tc={2D3AFF17-C5DC-42F1-900D-6D2DDCDEDE40}</author>
     <author>tc={5AEB12AC-CF6F-4769-B6EC-6CD91A0CD2B2}</author>
     <author>tc={378E7594-8484-4AB0-9234-B7D16F63965E}</author>
@@ -1159,8 +1032,304 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={02E09D9F-73B6-42D2-A88A-7FB22A220EAC}</author>
+    <author>tc={D871E194-7686-4A8E-AA34-9F5FE736F131}</author>
+    <author>tc={0ABDEEB8-D801-4B94-87AF-914F44B6EB44}</author>
+    <author>tc={44350621-1C7F-4CAB-91B7-BC42B5B5F3E1}</author>
+    <author>tc={7F582BE2-437F-4E5F-8684-10ABFFDFD6F7}</author>
+    <author>tc={B30330F8-36F5-449C-B3EF-7316426C3D39}</author>
+    <author>tc={DE369BCE-E951-4D3D-B696-A0B745FB367C}</author>
+    <author>tc={1C405871-D3B3-4708-915A-C81B17038734}</author>
+    <author>tc={180CAB41-849D-4B46-B0A0-6807989F4E8B}</author>
+    <author>tc={CF862BB4-B280-43CF-BC50-070DF19CFEDF}</author>
+    <author>tc={7B9034F7-D941-4755-B17F-6920DB73F21F}</author>
+    <author>tc={B74D269D-917B-477D-938C-1FAAFC80A986}</author>
+    <author>tc={7571CE34-42F6-4EC0-9871-3093D24137C2}</author>
+    <author>tc={709FC418-2E61-4993-B73C-DE235D2E2E3E}</author>
+    <author>tc={85A14A6F-A725-4F26-ADE9-3D826555456B}</author>
+    <author>tc={51132668-AA75-4B59-A3A0-32414C71B7A1}</author>
+    <author>tc={C1BAB494-D823-4BDF-A8D1-C43CDB1FB14A}</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{02E09D9F-73B6-42D2-A88A-7FB22A220EAC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Good class</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="1" shapeId="0" xr:uid="{D871E194-7686-4A8E-AA34-9F5FE736F131}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Talks funny, good kid, tries</t>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="2" shapeId="0" xr:uid="{0ABDEEB8-D801-4B94-87AF-914F44B6EB44}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Has phone, oreo mou...</t>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="3" shapeId="0" xr:uid="{44350621-1C7F-4CAB-91B7-BC42B5B5F3E1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    psilos</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="4" shapeId="0" xr:uid="{7F582BE2-437F-4E5F-8684-10ABFFDFD6F7}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Mikrokamomeni, isixi
+</t>
+      </text>
+    </comment>
+    <comment ref="C17" authorId="5" shapeId="0" xr:uid="{B30330F8-36F5-449C-B3EF-7316426C3D39}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    yperkinitiki
+Reply:
+    Pateras sto eksoteriko</t>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="6" shapeId="0" xr:uid="{DE369BCE-E951-4D3D-B696-A0B745FB367C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Me mitera, oxi epaphi me patera.</t>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="7" shapeId="0" xr:uid="{1C405871-D3B3-4708-915A-C81B17038734}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Mono me mitera</t>
+      </text>
+    </comment>
+    <comment ref="C23" authorId="8" shapeId="0" xr:uid="{180CAB41-849D-4B46-B0A0-6807989F4E8B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Diefkolinseis, stiriksi
+Reply:
+    Mitera karkino</t>
+      </text>
+    </comment>
+    <comment ref="C24" authorId="9" shapeId="0" xr:uid="{CF862BB4-B280-43CF-BC50-070DF19CFEDF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Aporos, sitisis</t>
+      </text>
+    </comment>
+    <comment ref="C29" authorId="10" shapeId="0" xr:uid="{7B9034F7-D941-4755-B17F-6920DB73F21F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Ntrepete, xamilon tonon</t>
+      </text>
+    </comment>
+    <comment ref="C32" authorId="11" shapeId="0" xr:uid="{B74D269D-917B-477D-938C-1FAAFC80A986}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Isixi, thelei entharinsi</t>
+      </text>
+    </comment>
+    <comment ref="C33" authorId="12" shapeId="0" xr:uid="{7571CE34-42F6-4EC0-9871-3093D24137C2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Xasimoto, pernei thiroksini</t>
+      </text>
+    </comment>
+    <comment ref="C35" authorId="13" shapeId="0" xr:uid="{709FC418-2E61-4993-B73C-DE235D2E2E3E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Mila arketa, kinito, oriothetisi</t>
+      </text>
+    </comment>
+    <comment ref="C36" authorId="14" shapeId="0" xr:uid="{85A14A6F-A725-4F26-ADE9-3D826555456B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Oreo m.
+Reply:
+    Miazei tis Melias</t>
+      </text>
+    </comment>
+    <comment ref="C37" authorId="15" shapeId="0" xr:uid="{51132668-AA75-4B59-A3A0-32414C71B7A1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    zoiros</t>
+      </text>
+    </comment>
+    <comment ref="C38" authorId="16" shapeId="0" xr:uid="{C1BAB494-D823-4BDF-A8D1-C43CDB1FB14A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    zoiros</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={376EB8CC-624A-4905-943C-003667EB4EEA}</author>
+    <author>tc={DC46CFF3-F130-4C35-ADEF-5A1F821781A9}</author>
+    <author>tc={B7A43FBB-5038-4FC3-8FAD-07EE5143A1F8}</author>
+    <author>tc={63C17029-8F90-4253-9CA7-E994CFD5D5A2}</author>
+    <author>tc={AA276D36-BF21-4BF1-B4EE-CFB1644CC25A}</author>
+    <author>tc={E15DDDED-B2BA-4607-867F-BB836742B4CF}</author>
+    <author>tc={959932C7-E7CF-4613-A506-DF1AB6866DD6}</author>
+    <author>tc={A44E3110-99FE-4968-95C4-FBBC90EA44AB}</author>
+    <author>tc={2FB97B2F-685A-47AD-B451-26CE099B5CDE}</author>
+    <author>tc={49700AAE-FBF5-4AF6-8413-5CA5A784A6FE}</author>
+    <author>tc={C1108176-F43A-484D-8C9A-1ABAB3DE80B2}</author>
+    <author>tc={F444680E-9CC4-4A89-898A-5ABDCDB06F58}</author>
+  </authors>
+  <commentList>
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{376EB8CC-624A-4905-943C-003667EB4EEA}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Seems like  a good kid</t>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="1" shapeId="0" xr:uid="{DC46CFF3-F130-4C35-ADEF-5A1F821781A9}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    indifferent
+Reply:
+    Mourmouros
+</t>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="2" shapeId="0" xr:uid="{B7A43FBB-5038-4FC3-8FAD-07EE5143A1F8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Fili tou konstantinou</t>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="3" shapeId="0" xr:uid="{63C17029-8F90-4253-9CA7-E994CFD5D5A2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Quiet but tries</t>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="4" shapeId="0" xr:uid="{AA276D36-BF21-4BF1-B4EE-CFB1644CC25A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Blond, quiet</t>
+      </text>
+    </comment>
+    <comment ref="C23" authorId="5" shapeId="0" xr:uid="{E15DDDED-B2BA-4607-867F-BB836742B4CF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Good student</t>
+      </text>
+    </comment>
+    <comment ref="C33" authorId="6" shapeId="0" xr:uid="{959932C7-E7CF-4613-A506-DF1AB6866DD6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Not very careful
+Reply:
+    Ligo prixtissa, alla kali.</t>
+      </text>
+    </comment>
+    <comment ref="C34" authorId="7" shapeId="0" xr:uid="{A44E3110-99FE-4968-95C4-FBBC90EA44AB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Get bored, starts playing games
+Reply:
+    Not paying attention
+Reply:
+    Keep an eye on him.</t>
+      </text>
+    </comment>
+    <comment ref="C35" authorId="8" shapeId="0" xr:uid="{2FB97B2F-685A-47AD-B451-26CE099B5CDE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Fenete filotimos, with some knowledge</t>
+      </text>
+    </comment>
+    <comment ref="C38" authorId="9" shapeId="0" xr:uid="{49700AAE-FBF5-4AF6-8413-5CA5A784A6FE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Kori tis Lelias</t>
+      </text>
+    </comment>
+    <comment ref="C42" authorId="10" shapeId="0" xr:uid="{C1108176-F43A-484D-8C9A-1ABAB3DE80B2}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Filotimos
+</t>
+      </text>
+    </comment>
+    <comment ref="C43" authorId="11" shapeId="0" xr:uid="{F444680E-9CC4-4A89-898A-5ABDCDB06F58}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    With glasses</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="365">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2044,9 +2213,6 @@
     <t>A2</t>
   </si>
   <si>
-    <t>A5.2 Μ2 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου</t>
-  </si>
-  <si>
     <t>A5.2 Μ3 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου</t>
   </si>
   <si>
@@ -2203,9 +2369,6 @@
     <t>Α5.2 Μ1 - Εναλλακτικό Φύλλο Εργασίας - Ηλεκτρονικό Ταχυδρομείο</t>
   </si>
   <si>
-    <t>A5.2 Μ2 + A5.2 M3</t>
-  </si>
-  <si>
     <t>A5.2 Μ1 - Proton mail - Νοήτικό στήριγμα - Δημιουργία και αποστολή εμαιλ - mono ena atomo katafere na kenei email</t>
   </si>
   <si>
@@ -2249,13 +2412,25 @@
   </si>
   <si>
     <t>A2Μ2 - Μονάδες και Περιφερειακά του Υπολογιστή - Μέρος 2</t>
+  </si>
+  <si>
+    <t>A5.2 Μ2 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου - hw.ask.26 p137</t>
+  </si>
+  <si>
+    <t>CREATE EMAIL WITH HOTSPOT - Α5.2 Μ1 - Εναλλακτικό Φύλλο Εργασίας - Ηλεκτρονικό Ταχυδρομείο</t>
+  </si>
+  <si>
+    <t>kahoot 14-10-2026</t>
+  </si>
+  <si>
+    <t>ANAPLIROSEIS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2316,6 +2491,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="14">
@@ -3131,173 +3312,240 @@
 
 <file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C5" dT="2026-09-24T08:32:38.60" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{376EB8CC-624A-4905-943C-003667EB4EEA}">
-    <text>Seems like  a good kid</text>
-  </threadedComment>
-  <threadedComment ref="C11" dT="2026-09-17T05:16:36.12" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{DC46CFF3-F130-4C35-ADEF-5A1F821781A9}">
-    <text>indifferent</text>
-  </threadedComment>
-  <threadedComment ref="C11" dT="2026-09-24T08:31:57.09" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B1FACE89-3856-4A2A-8CF7-8A8F34BC936B}" parentId="{DC46CFF3-F130-4C35-ADEF-5A1F821781A9}">
-    <text xml:space="preserve">Mourmouros
+  <threadedComment ref="A3" dT="2026-09-21T06:34:38.10" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2D3AFF17-C5DC-42F1-900D-6D2DDCDEDE40}">
+    <text>Seems good class</text>
+  </threadedComment>
+  <threadedComment ref="C4" dT="2026-10-01T18:49:32.40" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{5AEB12AC-CF6F-4769-B6EC-6CD91A0CD2B2}">
+    <text>Bulgaria, thema me apousies</text>
+  </threadedComment>
+  <threadedComment ref="C5" dT="2026-10-01T18:50:02.22" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{378E7594-8484-4AB0-9234-B7D16F63965E}">
+    <text>Menei me mitera, vlepei patera.</text>
+  </threadedComment>
+  <threadedComment ref="C5" dT="2026-10-01T18:50:07.72" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3AAD6C3F-6FD4-486A-A434-BF0409807853}" parentId="{378E7594-8484-4AB0-9234-B7D16F63965E}">
+    <text>sitisis</text>
+  </threadedComment>
+  <threadedComment ref="C5" dT="2026-10-01T18:52:00.24" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{FF203A26-000B-4ACB-8D3A-838AE02700B4}" parentId="{378E7594-8484-4AB0-9234-B7D16F63965E}">
+    <text>Mitera kypria</text>
+  </threadedComment>
+  <threadedComment ref="C6" dT="2026-10-01T18:50:40.65" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{411A9399-939F-4CF3-84DE-E99276BDD5F1}">
+    <text>Xorismenos me mitera</text>
+  </threadedComment>
+  <threadedComment ref="C7" dT="2026-10-01T18:50:55.97" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{653A25CE-F853-41CD-A80C-071E9A56C03D}">
+    <text>Isos themata me ti glossa</text>
+  </threadedComment>
+  <threadedComment ref="C7" dT="2026-10-01T18:52:12.55" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{9E380D5B-CD0D-461E-92F2-DBB3C3E05ED0}" parentId="{653A25CE-F853-41CD-A80C-071E9A56C03D}">
+    <text>roumania</text>
+  </threadedComment>
+  <threadedComment ref="C8" dT="2026-10-01T18:51:09.16" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{CBC4FE66-6F10-4A75-8F50-45357D88B4F9}">
+    <text>monaxikos</text>
+  </threadedComment>
+  <threadedComment ref="C8" dT="2026-10-01T18:51:20.32" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D5D5BB80-7936-4579-858D-BA760330281A}" parentId="{CBC4FE66-6F10-4A75-8F50-45357D88B4F9}">
+    <text>roumania</text>
+  </threadedComment>
+  <threadedComment ref="C10" dT="2026-10-01T18:52:40.56" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3CE025BD-885B-4BB4-8153-5BC45D96E63A}">
+    <text>roumania</text>
+  </threadedComment>
+  <threadedComment ref="C12" dT="2026-10-01T18:53:07.17" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{59815D4B-84E2-4C30-910E-50D01C3C6ED7}">
+    <text>Xasimoto, elleipsi prosoxis, astheneia cushing</text>
+  </threadedComment>
+  <threadedComment ref="C17" dT="2026-09-22T09:38:48.85" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{4647EABC-BD0A-4287-98AE-93002CBD969E}">
+    <text>Exei voitho</text>
+  </threadedComment>
+  <threadedComment ref="C17" dT="2026-10-02T08:19:54.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{6A555735-0A59-4459-B3B9-993E6176570B}" parentId="{4647EABC-BD0A-4287-98AE-93002CBD969E}">
+    <text>stiriksi</text>
+  </threadedComment>
+  <threadedComment ref="C18" dT="2026-10-02T08:20:20.01" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D0C2496A-FD3A-4795-86E4-65A32C49D3BB}">
+    <text>Noxelikos, pithanos ethismos sta electronica paixnidia</text>
+  </threadedComment>
+  <threadedComment ref="C20" dT="2026-10-02T08:21:02.61" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{CD7FCC05-427C-4B42-A9A7-2AFEEF3F93F9}">
+    <text>Poli evesthiti, kleei eukola, politekni</text>
+  </threadedComment>
+  <threadedComment ref="C22" dT="2026-10-02T08:21:14.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{61FB07C0-0E78-4C8B-AA14-9FC2FF75EB53}">
+    <text>vogotonia</text>
+  </threadedComment>
+  <threadedComment ref="C23" dT="2026-09-22T09:31:53.95" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{A20A5040-4856-4E57-BDA4-AE16EF61198C}">
+    <text>Special, pontios</text>
+  </threadedComment>
+  <threadedComment ref="C24" dT="2026-10-02T08:22:39.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{5B59CB62-C4AC-414E-99F2-9D3F0BAE7F43}">
+    <text>Stiriksi</text>
+  </threadedComment>
+  <threadedComment ref="C27" dT="2026-10-02T08:21:35.28" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{0F457041-30F1-42D5-86AA-827F66CF5BFF}">
+    <text>stiriksi</text>
+  </threadedComment>
+  <threadedComment ref="C30" dT="2026-10-05T07:13:32.27" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3AB30EA2-F1F4-4B35-A695-4BD343EDA7AB}">
+    <text>Roumania, diskolies sta ellinika</text>
+  </threadedComment>
+  <threadedComment ref="C31" dT="2026-10-05T07:13:44.64" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{43A0AE65-034A-43EB-BC59-C4E0B72EF263}">
+    <text>Xorismenoi goneis</text>
+  </threadedComment>
+  <threadedComment ref="C32" dT="2026-10-05T07:14:01.31" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D4F088E1-432B-4086-AA01-1CA80A1DAD01}">
+    <text>Skaki, mathimatika olympiades</text>
+  </threadedComment>
+  <threadedComment ref="C33" dT="2026-10-05T07:14:18.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{003CF2AA-8884-4C36-88CB-5F0850865977}">
+    <text>Sitisi, papapona gia bullying sto dimotiko</text>
+  </threadedComment>
+  <threadedComment ref="C34" dT="2026-10-05T07:14:34.50" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{1F0FEE88-81AC-4F0C-A40A-208A40518123}">
+    <text xml:space="preserve">Sitisi, stiriksi
 </text>
   </threadedComment>
-  <threadedComment ref="C12" dT="2026-09-24T08:32:16.02" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B7A43FBB-5038-4FC3-8FAD-07EE5143A1F8}">
-    <text>Fili tou konstantinou</text>
-  </threadedComment>
-  <threadedComment ref="C15" dT="2026-09-24T08:33:03.46" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{63C17029-8F90-4253-9CA7-E994CFD5D5A2}">
-    <text>Quiet but tries</text>
-  </threadedComment>
-  <threadedComment ref="C16" dT="2026-09-17T05:12:57.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AA276D36-BF21-4BF1-B4EE-CFB1644CC25A}">
-    <text>Blond, quiet</text>
-  </threadedComment>
-  <threadedComment ref="C23" dT="2026-09-22T09:31:23.10" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{E15DDDED-B2BA-4607-867F-BB836742B4CF}">
-    <text>Good student</text>
-  </threadedComment>
-  <threadedComment ref="C33" dT="2026-09-17T05:56:45.08" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{959932C7-E7CF-4613-A506-DF1AB6866DD6}">
-    <text>Not very careful</text>
-  </threadedComment>
-  <threadedComment ref="C33" dT="2026-09-22T09:33:55.26" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{48E5F015-F678-4100-8FB0-B8FDE14A53C9}" parentId="{959932C7-E7CF-4613-A506-DF1AB6866DD6}">
-    <text>Ligo prixtissa, alla kali.</text>
-  </threadedComment>
-  <threadedComment ref="C34" dT="2026-09-17T05:57:00.11" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{A44E3110-99FE-4968-95C4-FBBC90EA44AB}">
-    <text>Get bored, starts playing games</text>
-  </threadedComment>
-  <threadedComment ref="C34" dT="2026-09-22T09:34:55.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{6C394EC6-CD60-4FD2-B817-AEE1AA8F5E74}" parentId="{A44E3110-99FE-4968-95C4-FBBC90EA44AB}">
-    <text>Not paying attention</text>
-  </threadedComment>
-  <threadedComment ref="C34" dT="2026-09-22T15:27:55.30" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{97C347F3-F520-41A1-8319-2B94782E47F2}" parentId="{A44E3110-99FE-4968-95C4-FBBC90EA44AB}">
-    <text>Keep an eye on him.</text>
-  </threadedComment>
-  <threadedComment ref="C35" dT="2026-09-17T05:56:20.80" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2FB97B2F-685A-47AD-B451-26CE099B5CDE}">
-    <text>Fenete filotimos, with some knowledge</text>
-  </threadedComment>
-  <threadedComment ref="C38" dT="2026-09-22T09:33:38.73" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{49700AAE-FBF5-4AF6-8413-5CA5A784A6FE}">
-    <text>Kori tis Lelias</text>
-  </threadedComment>
-  <threadedComment ref="C42" dT="2026-09-17T05:53:15.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{C1108176-F43A-484D-8C9A-1ABAB3DE80B2}">
-    <text xml:space="preserve">Filotimos
+  <threadedComment ref="C35" dT="2026-10-05T07:14:51.75" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{BAD03DE3-79F7-4ED6-BBEE-A216F4A0CF81}">
+    <text>Didimoi me Kimona</text>
+  </threadedComment>
+  <threadedComment ref="C36" dT="2026-10-05T07:15:08.05" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{328D28C5-39DF-4E43-9191-E0347C55DC85}">
+    <text>Ypermetropia, astigmatismos</text>
+  </threadedComment>
+  <threadedComment ref="C38" dT="2026-10-05T07:15:27.54" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{CCF5C47C-DAC9-4163-911E-D25575FED191}">
+    <text>Sitisi, orfanos apo patera sti Syria</text>
+  </threadedComment>
+  <threadedComment ref="C39" dT="2026-10-05T07:15:40.47" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{1BCE4285-4670-48B9-A6C0-A7ACB02EB42C}">
+    <text>Spazei sixna h miti tis</text>
+  </threadedComment>
+  <threadedComment ref="C43" dT="2026-10-05T09:04:32.37" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{1BA79E55-D3B6-4B95-8DA1-57CBF311C4CC}">
+    <text>Xorismeni, apoklisitiki h mitera</text>
+  </threadedComment>
+  <threadedComment ref="C44" dT="2026-09-25T14:55:37.89" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2B329A84-0BDF-4381-88A4-81550D5EEF38}">
+    <text>indefferent</text>
+  </threadedComment>
+  <threadedComment ref="C45" dT="2026-10-05T09:04:58.84" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AAFA0838-65EA-4623-BC08-12544B2903FB}">
+    <text>Depy, sitisi, sinesthimatikes diskolies</text>
+  </threadedComment>
+  <threadedComment ref="C46" dT="2026-10-05T09:05:48.06" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{4D05AFA5-576B-4955-8CD5-510AFC85FC66}">
+    <text>Stiriksi, sitisi, menei me patera, oxi epaphi me mitera, o pateras fetos irthe, emenas me giagia kai pappou</text>
+  </threadedComment>
+  <threadedComment ref="C50" dT="2026-10-05T09:06:03.45" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{C94A78CF-2F80-4B38-B2A4-3CC0C4D9E0E4}">
+    <text>Dropalos, thelei enisxisi</text>
+  </threadedComment>
+  <threadedComment ref="C51" dT="2026-10-05T09:06:27.63" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D7EB80D4-5CFD-425F-B3B4-EB0A0BE048F6}">
+    <text>Stiriksi, mathisiakes adinamies</text>
+  </threadedComment>
+  <threadedComment ref="C52" dT="2026-09-21T06:24:16.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{222055CB-C6B5-4FA3-91EE-184B465B0798}">
+    <text xml:space="preserve">Little guy with glasses
 </text>
   </threadedComment>
-  <threadedComment ref="C43" dT="2026-09-17T05:55:56.16" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{F444680E-9CC4-4A89-898A-5ABDCDB06F58}">
-    <text>With glasses</text>
+  <threadedComment ref="C52" dT="2026-10-05T09:06:44.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{51D69F72-37C6-4888-83C5-CA1EA9ED6E7D}" parentId="{222055CB-C6B5-4FA3-91EE-184B465B0798}">
+    <text>alpabitismos</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/threadedComments/threadedComment6.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A3" dT="2026-09-21T06:34:38.10" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2D3AFF17-C5DC-42F1-900D-6D2DDCDEDE40}">
-    <text>Seems good class</text>
-  </threadedComment>
-  <threadedComment ref="C4" dT="2026-10-01T18:49:32.40" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{5AEB12AC-CF6F-4769-B6EC-6CD91A0CD2B2}">
-    <text>Bulgaria, thema me apousies</text>
-  </threadedComment>
-  <threadedComment ref="C5" dT="2026-10-01T18:50:02.22" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{378E7594-8484-4AB0-9234-B7D16F63965E}">
-    <text>Menei me mitera, vlepei patera.</text>
-  </threadedComment>
-  <threadedComment ref="C5" dT="2026-10-01T18:50:07.72" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3AAD6C3F-6FD4-486A-A434-BF0409807853}" parentId="{378E7594-8484-4AB0-9234-B7D16F63965E}">
-    <text>sitisis</text>
-  </threadedComment>
-  <threadedComment ref="C5" dT="2026-10-01T18:52:00.24" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{FF203A26-000B-4ACB-8D3A-838AE02700B4}" parentId="{378E7594-8484-4AB0-9234-B7D16F63965E}">
-    <text>Mitera kypria</text>
-  </threadedComment>
-  <threadedComment ref="C6" dT="2026-10-01T18:50:40.65" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{411A9399-939F-4CF3-84DE-E99276BDD5F1}">
-    <text>Xorismenos me mitera</text>
-  </threadedComment>
-  <threadedComment ref="C7" dT="2026-10-01T18:50:55.97" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{653A25CE-F853-41CD-A80C-071E9A56C03D}">
-    <text>Isos themata me ti glossa</text>
-  </threadedComment>
-  <threadedComment ref="C7" dT="2026-10-01T18:52:12.55" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{9E380D5B-CD0D-461E-92F2-DBB3C3E05ED0}" parentId="{653A25CE-F853-41CD-A80C-071E9A56C03D}">
-    <text>roumania</text>
-  </threadedComment>
-  <threadedComment ref="C8" dT="2026-10-01T18:51:09.16" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{CBC4FE66-6F10-4A75-8F50-45357D88B4F9}">
-    <text>monaxikos</text>
-  </threadedComment>
-  <threadedComment ref="C8" dT="2026-10-01T18:51:20.32" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D5D5BB80-7936-4579-858D-BA760330281A}" parentId="{CBC4FE66-6F10-4A75-8F50-45357D88B4F9}">
-    <text>roumania</text>
-  </threadedComment>
-  <threadedComment ref="C10" dT="2026-10-01T18:52:40.56" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3CE025BD-885B-4BB4-8153-5BC45D96E63A}">
-    <text>roumania</text>
-  </threadedComment>
-  <threadedComment ref="C12" dT="2026-10-01T18:53:07.17" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{59815D4B-84E2-4C30-910E-50D01C3C6ED7}">
-    <text>Xasimoto, elleipsi prosoxis, astheneia cushing</text>
-  </threadedComment>
-  <threadedComment ref="C17" dT="2026-09-22T09:38:48.85" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{4647EABC-BD0A-4287-98AE-93002CBD969E}">
-    <text>Exei voitho</text>
-  </threadedComment>
-  <threadedComment ref="C17" dT="2026-10-02T08:19:54.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{6A555735-0A59-4459-B3B9-993E6176570B}" parentId="{4647EABC-BD0A-4287-98AE-93002CBD969E}">
-    <text>stiriksi</text>
-  </threadedComment>
-  <threadedComment ref="C18" dT="2026-10-02T08:20:20.01" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D0C2496A-FD3A-4795-86E4-65A32C49D3BB}">
-    <text>Noxelikos, pithanos ethismos sta electronica paixnidia</text>
-  </threadedComment>
-  <threadedComment ref="C20" dT="2026-10-02T08:21:02.61" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{CD7FCC05-427C-4B42-A9A7-2AFEEF3F93F9}">
-    <text>Poli evesthiti, kleei eukola, politekni</text>
-  </threadedComment>
-  <threadedComment ref="C22" dT="2026-10-02T08:21:14.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{61FB07C0-0E78-4C8B-AA14-9FC2FF75EB53}">
-    <text>vogotonia</text>
-  </threadedComment>
-  <threadedComment ref="C23" dT="2026-09-22T09:31:53.95" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{A20A5040-4856-4E57-BDA4-AE16EF61198C}">
-    <text>Special, pontios</text>
-  </threadedComment>
-  <threadedComment ref="C24" dT="2026-10-02T08:22:39.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{5B59CB62-C4AC-414E-99F2-9D3F0BAE7F43}">
-    <text>Stiriksi</text>
-  </threadedComment>
-  <threadedComment ref="C27" dT="2026-10-02T08:21:35.28" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{0F457041-30F1-42D5-86AA-827F66CF5BFF}">
-    <text>stiriksi</text>
-  </threadedComment>
-  <threadedComment ref="C30" dT="2026-10-05T07:13:32.27" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3AB30EA2-F1F4-4B35-A695-4BD343EDA7AB}">
-    <text>Roumania, diskolies sta ellinika</text>
-  </threadedComment>
-  <threadedComment ref="C31" dT="2026-10-05T07:13:44.64" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{43A0AE65-034A-43EB-BC59-C4E0B72EF263}">
-    <text>Xorismenoi goneis</text>
-  </threadedComment>
-  <threadedComment ref="C32" dT="2026-10-05T07:14:01.31" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D4F088E1-432B-4086-AA01-1CA80A1DAD01}">
-    <text>Skaki, mathimatika olympiades</text>
-  </threadedComment>
-  <threadedComment ref="C33" dT="2026-10-05T07:14:18.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{003CF2AA-8884-4C36-88CB-5F0850865977}">
-    <text>Sitisi, papapona gia bullying sto dimotiko</text>
-  </threadedComment>
-  <threadedComment ref="C34" dT="2026-10-05T07:14:34.50" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{1F0FEE88-81AC-4F0C-A40A-208A40518123}">
-    <text xml:space="preserve">Sitisi, stiriksi
+  <threadedComment ref="A3" dT="2026-09-20T18:12:21.73" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{02E09D9F-73B6-42D2-A88A-7FB22A220EAC}">
+    <text>Good class</text>
+  </threadedComment>
+  <threadedComment ref="C7" dT="2026-09-21T14:39:09.50" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D871E194-7686-4A8E-AA34-9F5FE736F131}">
+    <text>Talks funny, good kid, tries</text>
+  </threadedComment>
+  <threadedComment ref="C10" dT="2026-09-21T14:39:50.86" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{0ABDEEB8-D801-4B94-87AF-914F44B6EB44}">
+    <text>Has phone, oreo mou...</text>
+  </threadedComment>
+  <threadedComment ref="C12" dT="2026-09-23T06:55:28.24" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{44350621-1C7F-4CAB-91B7-BC42B5B5F3E1}">
+    <text>psilos</text>
+  </threadedComment>
+  <threadedComment ref="C13" dT="2026-09-23T06:55:09.83" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7F582BE2-437F-4E5F-8684-10ABFFDFD6F7}">
+    <text xml:space="preserve">Mikrokamomeni, isixi
 </text>
   </threadedComment>
-  <threadedComment ref="C35" dT="2026-10-05T07:14:51.75" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{BAD03DE3-79F7-4ED6-BBEE-A216F4A0CF81}">
-    <text>Didimoi me Kimona</text>
-  </threadedComment>
-  <threadedComment ref="C36" dT="2026-10-05T07:15:08.05" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{328D28C5-39DF-4E43-9191-E0347C55DC85}">
-    <text>Ypermetropia, astigmatismos</text>
-  </threadedComment>
-  <threadedComment ref="C38" dT="2026-10-05T07:15:27.54" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{CCF5C47C-DAC9-4163-911E-D25575FED191}">
-    <text>Sitisi, orfanos apo patera sti Syria</text>
-  </threadedComment>
-  <threadedComment ref="C39" dT="2026-10-05T07:15:40.47" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{1BCE4285-4670-48B9-A6C0-A7ACB02EB42C}">
-    <text>Spazei sixna h miti tis</text>
-  </threadedComment>
-  <threadedComment ref="C43" dT="2026-10-05T09:04:32.37" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{1BA79E55-D3B6-4B95-8DA1-57CBF311C4CC}">
-    <text>Xorismeni, apoklisitiki h mitera</text>
-  </threadedComment>
-  <threadedComment ref="C44" dT="2026-09-25T14:55:37.89" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2B329A84-0BDF-4381-88A4-81550D5EEF38}">
-    <text>indefferent</text>
-  </threadedComment>
-  <threadedComment ref="C45" dT="2026-10-05T09:04:58.84" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AAFA0838-65EA-4623-BC08-12544B2903FB}">
-    <text>Depy, sitisi, sinesthimatikes diskolies</text>
-  </threadedComment>
-  <threadedComment ref="C46" dT="2026-10-05T09:05:48.06" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{4D05AFA5-576B-4955-8CD5-510AFC85FC66}">
-    <text>Stiriksi, sitisi, menei me patera, oxi epaphi me mitera, o pateras fetos irthe, emenas me giagia kai pappou</text>
-  </threadedComment>
-  <threadedComment ref="C50" dT="2026-10-05T09:06:03.45" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{C94A78CF-2F80-4B38-B2A4-3CC0C4D9E0E4}">
-    <text>Dropalos, thelei enisxisi</text>
-  </threadedComment>
-  <threadedComment ref="C51" dT="2026-10-05T09:06:27.63" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D7EB80D4-5CFD-425F-B3B4-EB0A0BE048F6}">
-    <text>Stiriksi, mathisiakes adinamies</text>
-  </threadedComment>
-  <threadedComment ref="C52" dT="2026-09-21T06:24:16.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{222055CB-C6B5-4FA3-91EE-184B465B0798}">
-    <text xml:space="preserve">Little guy with glasses
+  <threadedComment ref="C17" dT="2026-09-23T07:02:26.50" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B30330F8-36F5-449C-B3EF-7316426C3D39}">
+    <text>yperkinitiki</text>
+  </threadedComment>
+  <threadedComment ref="C17" dT="2026-09-23T07:03:34.08" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{85A80761-C4B7-49C6-92F5-3DCB301BD107}" parentId="{B30330F8-36F5-449C-B3EF-7316426C3D39}">
+    <text>Pateras sto eksoteriko</text>
+  </threadedComment>
+  <threadedComment ref="C19" dT="2026-09-23T07:03:19.98" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{DE369BCE-E951-4D3D-B696-A0B745FB367C}">
+    <text>Me mitera, oxi epaphi me patera.</text>
+  </threadedComment>
+  <threadedComment ref="C20" dT="2026-09-23T07:05:00.47" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{1C405871-D3B3-4708-915A-C81B17038734}">
+    <text>Mono me mitera</text>
+  </threadedComment>
+  <threadedComment ref="C23" dT="2026-10-14T06:13:20.12" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{180CAB41-849D-4B46-B0A0-6807989F4E8B}">
+    <text xml:space="preserve">Diefkolinseis, stiriksi
 </text>
   </threadedComment>
-  <threadedComment ref="C52" dT="2026-10-05T09:06:44.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{51D69F72-37C6-4888-83C5-CA1EA9ED6E7D}" parentId="{222055CB-C6B5-4FA3-91EE-184B465B0798}">
-    <text>alpabitismos</text>
+  <threadedComment ref="C23" dT="2026-10-14T06:13:27.30" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{040DA3A9-BCDA-4E43-BC6D-2236293099C0}" parentId="{180CAB41-849D-4B46-B0A0-6807989F4E8B}">
+    <text>Mitera karkino</text>
+  </threadedComment>
+  <threadedComment ref="C24" dT="2026-09-23T07:02:08.99" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{CF862BB4-B280-43CF-BC50-070DF19CFEDF}">
+    <text>Aporos, sitisis</text>
+  </threadedComment>
+  <threadedComment ref="C29" dT="2026-09-20T17:09:45.79" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7B9034F7-D941-4755-B17F-6920DB73F21F}">
+    <text>Ntrepete, xamilon tonon</text>
+  </threadedComment>
+  <threadedComment ref="C32" dT="2026-09-20T17:10:08.12" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B74D269D-917B-477D-938C-1FAAFC80A986}">
+    <text>Isixi, thelei entharinsi</text>
+  </threadedComment>
+  <threadedComment ref="C33" dT="2026-09-20T17:10:27.77" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7571CE34-42F6-4EC0-9871-3093D24137C2}">
+    <text>Xasimoto, pernei thiroksini</text>
+  </threadedComment>
+  <threadedComment ref="C35" dT="2026-09-20T17:10:57.03" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{709FC418-2E61-4993-B73C-DE235D2E2E3E}">
+    <text>Mila arketa, kinito, oriothetisi</text>
+  </threadedComment>
+  <threadedComment ref="C36" dT="2026-09-22T09:37:54.19" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{85A14A6F-A725-4F26-ADE9-3D826555456B}">
+    <text>Oreo m.</text>
+  </threadedComment>
+  <threadedComment ref="C36" dT="2026-09-28T13:49:17.74" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{9A1ADE66-6BEB-4348-B407-32AD3B5B7D78}" parentId="{85A14A6F-A725-4F26-ADE9-3D826555456B}">
+    <text>Miazei tis Melias</text>
+  </threadedComment>
+  <threadedComment ref="C37" dT="2026-09-20T17:11:14.69" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{51132668-AA75-4B59-A3A0-32414C71B7A1}">
+    <text>zoiros</text>
+  </threadedComment>
+  <threadedComment ref="C38" dT="2026-09-20T17:11:23.87" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{C1BAB494-D823-4BDF-A8D1-C43CDB1FB14A}">
+    <text>zoiros</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment7.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C5" dT="2026-09-24T08:32:38.60" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{376EB8CC-624A-4905-943C-003667EB4EEA}">
+    <text>Seems like  a good kid</text>
+  </threadedComment>
+  <threadedComment ref="C11" dT="2026-09-17T05:16:36.12" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{DC46CFF3-F130-4C35-ADEF-5A1F821781A9}">
+    <text>indifferent</text>
+  </threadedComment>
+  <threadedComment ref="C11" dT="2026-09-24T08:31:57.09" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B1FACE89-3856-4A2A-8CF7-8A8F34BC936B}" parentId="{DC46CFF3-F130-4C35-ADEF-5A1F821781A9}">
+    <text xml:space="preserve">Mourmouros
+</text>
+  </threadedComment>
+  <threadedComment ref="C12" dT="2026-09-24T08:32:16.02" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B7A43FBB-5038-4FC3-8FAD-07EE5143A1F8}">
+    <text>Fili tou konstantinou</text>
+  </threadedComment>
+  <threadedComment ref="C15" dT="2026-09-24T08:33:03.46" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{63C17029-8F90-4253-9CA7-E994CFD5D5A2}">
+    <text>Quiet but tries</text>
+  </threadedComment>
+  <threadedComment ref="C16" dT="2026-09-17T05:12:57.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AA276D36-BF21-4BF1-B4EE-CFB1644CC25A}">
+    <text>Blond, quiet</text>
+  </threadedComment>
+  <threadedComment ref="C23" dT="2026-09-22T09:31:23.10" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{E15DDDED-B2BA-4607-867F-BB836742B4CF}">
+    <text>Good student</text>
+  </threadedComment>
+  <threadedComment ref="C33" dT="2026-09-17T05:56:45.08" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{959932C7-E7CF-4613-A506-DF1AB6866DD6}">
+    <text>Not very careful</text>
+  </threadedComment>
+  <threadedComment ref="C33" dT="2026-09-22T09:33:55.26" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{48E5F015-F678-4100-8FB0-B8FDE14A53C9}" parentId="{959932C7-E7CF-4613-A506-DF1AB6866DD6}">
+    <text>Ligo prixtissa, alla kali.</text>
+  </threadedComment>
+  <threadedComment ref="C34" dT="2026-09-17T05:57:00.11" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{A44E3110-99FE-4968-95C4-FBBC90EA44AB}">
+    <text>Get bored, starts playing games</text>
+  </threadedComment>
+  <threadedComment ref="C34" dT="2026-09-22T09:34:55.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{6C394EC6-CD60-4FD2-B817-AEE1AA8F5E74}" parentId="{A44E3110-99FE-4968-95C4-FBBC90EA44AB}">
+    <text>Not paying attention</text>
+  </threadedComment>
+  <threadedComment ref="C34" dT="2026-09-22T15:27:55.30" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{97C347F3-F520-41A1-8319-2B94782E47F2}" parentId="{A44E3110-99FE-4968-95C4-FBBC90EA44AB}">
+    <text>Keep an eye on him.</text>
+  </threadedComment>
+  <threadedComment ref="C35" dT="2026-09-17T05:56:20.80" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2FB97B2F-685A-47AD-B451-26CE099B5CDE}">
+    <text>Fenete filotimos, with some knowledge</text>
+  </threadedComment>
+  <threadedComment ref="C38" dT="2026-09-22T09:33:38.73" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{49700AAE-FBF5-4AF6-8413-5CA5A784A6FE}">
+    <text>Kori tis Lelias</text>
+  </threadedComment>
+  <threadedComment ref="C42" dT="2026-09-17T05:53:15.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{C1108176-F43A-484D-8C9A-1ABAB3DE80B2}">
+    <text xml:space="preserve">Filotimos
+</text>
+  </threadedComment>
+  <threadedComment ref="C43" dT="2026-09-17T05:55:56.16" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{F444680E-9CC4-4A89-898A-5ABDCDB06F58}">
+    <text>With glasses</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -3361,31 +3609,31 @@
       </c>
       <c r="M1" s="41"/>
       <c r="N1" s="40" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="O1" s="41"/>
       <c r="P1" s="40" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q1" s="41"/>
       <c r="R1" s="40" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="S1" s="41"/>
       <c r="T1" s="40" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="U1" s="41"/>
       <c r="V1" s="40" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="W1" s="41"/>
       <c r="X1" s="40" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="41"/>
       <c r="Z1" s="40" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AA1" s="41"/>
       <c r="AB1" s="29"/>
@@ -3497,7 +3745,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:60" ht="43" x14ac:dyDescent="0.5">
       <c r="A4" s="30" t="s">
         <v>2</v>
       </c>
@@ -3535,16 +3783,19 @@
         <v>239</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>346</v>
+        <v>362</v>
+      </c>
+      <c r="O4" s="25" t="s">
+        <v>361</v>
       </c>
       <c r="Y4" s="39" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="5" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:60" ht="43" x14ac:dyDescent="0.5">
       <c r="A5" s="30" t="s">
         <v>3</v>
       </c>
@@ -3579,13 +3830,16 @@
         <v>255</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>346</v>
-      </c>
-      <c r="N5" s="25" t="s">
-        <v>347</v>
+        <v>345</v>
+      </c>
+      <c r="N5" s="27" t="s">
+        <v>362</v>
+      </c>
+      <c r="O5" s="25" t="s">
+        <v>361</v>
       </c>
       <c r="X5" s="39" t="s">
         <v>249</v>
@@ -3623,37 +3877,37 @@
         <v>255</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="N6" s="27" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="O6" s="25" t="s">
+        <v>361</v>
+      </c>
+      <c r="P6" s="25" t="s">
         <v>294</v>
       </c>
-      <c r="P6" s="25" t="s">
-        <v>295</v>
-      </c>
       <c r="Q6" s="25" t="s">
+        <v>356</v>
+      </c>
+      <c r="R6" s="25" t="s">
+        <v>357</v>
+      </c>
+      <c r="S6" s="25" t="s">
         <v>358</v>
       </c>
-      <c r="R6" s="25" t="s">
+      <c r="T6" s="25" t="s">
         <v>359</v>
       </c>
-      <c r="S6" s="25" t="s">
+      <c r="U6" s="25" t="s">
         <v>360</v>
-      </c>
-      <c r="T6" s="25" t="s">
-        <v>361</v>
-      </c>
-      <c r="U6" s="25" t="s">
-        <v>362</v>
       </c>
       <c r="X6" s="39" t="s">
         <v>249</v>
@@ -3697,7 +3951,13 @@
         <v>239</v>
       </c>
       <c r="M7" s="23" t="s">
-        <v>345</v>
+        <v>344</v>
+      </c>
+      <c r="N7" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="O7" s="27" t="s">
+        <v>362</v>
       </c>
       <c r="X7" s="39" t="s">
         <v>249</v>
@@ -3711,10 +3971,10 @@
         <v>35</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M10" s="25" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
@@ -3746,25 +4006,25 @@
         <v>259</v>
       </c>
       <c r="J11" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="K11" s="23" t="s">
         <v>296</v>
-      </c>
-      <c r="K11" s="23" t="s">
-        <v>297</v>
       </c>
       <c r="L11" s="26" t="s">
         <v>239</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="N11" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="O11" s="25" t="s">
         <v>325</v>
       </c>
-      <c r="O11" s="25" t="s">
+      <c r="P11" s="25" t="s">
         <v>326</v>
-      </c>
-      <c r="P11" s="25" t="s">
-        <v>327</v>
       </c>
       <c r="V11" s="39" t="s">
         <v>249</v>
@@ -3808,9 +4068,12 @@
         <v>239</v>
       </c>
       <c r="M12" s="23" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="N12" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="O12" s="25" t="s">
         <v>296</v>
       </c>
       <c r="V12" s="39" t="s">
@@ -3849,22 +4112,22 @@
         <v>259</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L13" s="26" t="s">
         <v>239</v>
       </c>
       <c r="M13" s="23" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N13" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="O13" s="25" t="s">
         <v>325</v>
       </c>
-      <c r="O13" s="25" t="s">
+      <c r="P13" s="25" t="s">
         <v>326</v>
-      </c>
-      <c r="P13" s="25" t="s">
-        <v>327</v>
       </c>
       <c r="V13" s="39" t="s">
         <v>249</v>
@@ -3921,16 +4184,16 @@
         <v>243</v>
       </c>
       <c r="L18" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="M18" s="23" t="s">
         <v>322</v>
-      </c>
-      <c r="M18" s="23" t="s">
-        <v>323</v>
       </c>
       <c r="N18" s="27" t="s">
         <v>244</v>
       </c>
       <c r="O18" s="27" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P18" s="36" t="s">
         <v>249</v>
@@ -3977,16 +4240,16 @@
         <v>243</v>
       </c>
       <c r="L19" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="M19" s="23" t="s">
         <v>322</v>
-      </c>
-      <c r="M19" s="23" t="s">
-        <v>323</v>
       </c>
       <c r="N19" s="27" t="s">
         <v>244</v>
       </c>
       <c r="O19" s="27" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P19" s="36" t="s">
         <v>249</v>
@@ -4036,16 +4299,16 @@
         <v>243</v>
       </c>
       <c r="M20" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="N20" s="27" t="s">
         <v>322</v>
-      </c>
-      <c r="N20" s="27" t="s">
-        <v>323</v>
       </c>
       <c r="O20" s="27" t="s">
         <v>244</v>
       </c>
       <c r="P20" s="27" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q20" s="36" t="s">
         <v>249</v>
@@ -4094,16 +4357,16 @@
         <v>281</v>
       </c>
       <c r="J22" s="23" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K22" s="23" t="s">
         <v>172</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.5">
@@ -4235,11 +4498,11 @@
       </c>
       <c r="I2" s="42"/>
       <c r="J2" s="42" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K2" s="42"/>
       <c r="L2" s="42" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M2" s="42"/>
     </row>
@@ -4251,7 +4514,7 @@
         <v>290</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4582,10 +4845,10 @@
         <v>290</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4875,13 +5138,13 @@
         <v>3257704</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>340</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -5644,7 +5907,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23D143C4-24B5-4F25-A9AC-CA5F9ACC8C3E}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="49.87890625" bestFit="1" customWidth="1"/>
@@ -5655,60 +5918,73 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C3" s="22" t="s">
         <v>309</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
+        <v>315</v>
+      </c>
+      <c r="C7" t="s">
         <v>316</v>
-      </c>
-      <c r="C7" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C9" t="s">
         <v>328</v>
-      </c>
-      <c r="C9" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
+        <v>334</v>
+      </c>
+      <c r="C10" t="s">
         <v>335</v>
       </c>
-      <c r="C10" t="s">
-        <v>336</v>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A16" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A17" t="s">
+        <v>269</v>
+      </c>
+      <c r="B17" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -5758,11 +6034,11 @@
       </c>
       <c r="I2" s="42"/>
       <c r="J2" s="42" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K2" s="42"/>
       <c r="L2" s="42" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M2" s="42"/>
     </row>
@@ -6360,10 +6636,10 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>304</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>39</v>
@@ -6811,7 +7087,7 @@
       </c>
       <c r="H1" s="42"/>
       <c r="I1" s="42" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J1" s="42"/>
     </row>
@@ -6962,11 +7238,11 @@
       </c>
       <c r="J1" s="42"/>
       <c r="K1" s="42" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L1" s="42"/>
       <c r="M1" s="43" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N1" s="43"/>
     </row>
@@ -6975,10 +7251,10 @@
         <v>14</v>
       </c>
       <c r="K3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7602,13 +7878,13 @@
         <v>60</v>
       </c>
       <c r="L21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7893,7 +8169,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.5">
       <c r="L30" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.5">
@@ -7901,7 +8177,7 @@
         <v>16</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8357,554 +8633,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC563BF-C300-44C1-88F1-5244DF9366D6}">
-  <dimension ref="A3:B3"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
-  <cols>
-    <col min="1" max="1" width="10.703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.64453125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{836E3DAF-4660-4453-8445-CAEF205E5F1E}">
-  <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
-  <cols>
-    <col min="1" max="1" width="7.703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.41015625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.9375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.17578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.3515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A4">
-        <v>4206804</v>
-      </c>
-      <c r="B4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A5">
-        <v>9307104</v>
-      </c>
-      <c r="B5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A6">
-        <v>2173704</v>
-      </c>
-      <c r="B6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A7">
-        <v>9257304</v>
-      </c>
-      <c r="B7" t="s">
-        <v>212</v>
-      </c>
-      <c r="C7" t="s">
-        <v>213</v>
-      </c>
-      <c r="D7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A8">
-        <v>2915404</v>
-      </c>
-      <c r="B8" t="s">
-        <v>214</v>
-      </c>
-      <c r="C8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A9">
-        <v>2836604</v>
-      </c>
-      <c r="B9" t="s">
-        <v>215</v>
-      </c>
-      <c r="C9" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A10">
-        <v>1274904</v>
-      </c>
-      <c r="B10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C10" t="s">
-        <v>218</v>
-      </c>
-      <c r="D10" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A11">
-        <v>3863304</v>
-      </c>
-      <c r="B11" t="s">
-        <v>219</v>
-      </c>
-      <c r="C11" t="s">
-        <v>220</v>
-      </c>
-      <c r="D11" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A12">
-        <v>3403504</v>
-      </c>
-      <c r="B12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D12" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A13">
-        <v>4721304</v>
-      </c>
-      <c r="B13" t="s">
-        <v>223</v>
-      </c>
-      <c r="C13" t="s">
-        <v>191</v>
-      </c>
-      <c r="D13" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A14">
-        <v>3924304</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>224</v>
-      </c>
-      <c r="D14" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A15">
-        <v>4041704</v>
-      </c>
-      <c r="B15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" t="s">
-        <v>225</v>
-      </c>
-      <c r="D15" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A16">
-        <v>9280704</v>
-      </c>
-      <c r="B16" t="s">
-        <v>226</v>
-      </c>
-      <c r="C16" t="s">
-        <v>227</v>
-      </c>
-      <c r="D16" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="C17" t="s">
-        <v>228</v>
-      </c>
-      <c r="D17" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="B18" t="s">
-        <v>229</v>
-      </c>
-      <c r="C18" t="s">
-        <v>230</v>
-      </c>
-      <c r="D18" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A22">
-        <v>9693404</v>
-      </c>
-      <c r="B22" t="s">
-        <v>196</v>
-      </c>
-      <c r="C22" t="s">
-        <v>197</v>
-      </c>
-      <c r="D22" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A23">
-        <v>222222</v>
-      </c>
-      <c r="B23" t="s">
-        <v>199</v>
-      </c>
-      <c r="C23" t="s">
-        <v>200</v>
-      </c>
-      <c r="D23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A24">
-        <v>9743804</v>
-      </c>
-      <c r="B24" t="s">
-        <v>201</v>
-      </c>
-      <c r="C24" t="s">
-        <v>202</v>
-      </c>
-      <c r="D24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A25">
-        <v>111111</v>
-      </c>
-      <c r="B25" t="s">
-        <v>203</v>
-      </c>
-      <c r="C25" t="s">
-        <v>204</v>
-      </c>
-      <c r="D25" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A26">
-        <v>9662304</v>
-      </c>
-      <c r="B26" t="s">
-        <v>205</v>
-      </c>
-      <c r="C26" t="s">
-        <v>206</v>
-      </c>
-      <c r="D26" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="B27" t="s">
-        <v>272</v>
-      </c>
-      <c r="C27" t="s">
-        <v>273</v>
-      </c>
-      <c r="D27" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="B28" t="s">
-        <v>272</v>
-      </c>
-      <c r="C28" t="s">
-        <v>274</v>
-      </c>
-      <c r="D28" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A32">
-        <v>3578804</v>
-      </c>
-      <c r="B32" t="s">
-        <v>176</v>
-      </c>
-      <c r="C32" t="s">
-        <v>128</v>
-      </c>
-      <c r="D32" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A33">
-        <v>9289704</v>
-      </c>
-      <c r="B33" t="s">
-        <v>178</v>
-      </c>
-      <c r="C33" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A34">
-        <v>9344404</v>
-      </c>
-      <c r="B34" t="s">
-        <v>179</v>
-      </c>
-      <c r="C34" t="s">
-        <v>180</v>
-      </c>
-      <c r="D34" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A35">
-        <v>6746404</v>
-      </c>
-      <c r="B35" t="s">
-        <v>181</v>
-      </c>
-      <c r="C35" t="s">
-        <v>182</v>
-      </c>
-      <c r="D35" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A36">
-        <v>9257604</v>
-      </c>
-      <c r="B36" t="s">
-        <v>183</v>
-      </c>
-      <c r="C36" t="s">
-        <v>184</v>
-      </c>
-      <c r="D36" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A37">
-        <v>9717204</v>
-      </c>
-      <c r="B37" t="s">
-        <v>185</v>
-      </c>
-      <c r="C37" t="s">
-        <v>186</v>
-      </c>
-      <c r="D37" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A38">
-        <v>2298204</v>
-      </c>
-      <c r="B38" t="s">
-        <v>187</v>
-      </c>
-      <c r="C38" t="s">
-        <v>188</v>
-      </c>
-      <c r="D38" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A39">
-        <v>5784804</v>
-      </c>
-      <c r="B39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A40">
-        <v>9321704</v>
-      </c>
-      <c r="B40" t="s">
-        <v>190</v>
-      </c>
-      <c r="C40" t="s">
-        <v>191</v>
-      </c>
-      <c r="D40" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A41">
-        <v>9720304</v>
-      </c>
-      <c r="B41" t="s">
-        <v>192</v>
-      </c>
-      <c r="C41" t="s">
-        <v>193</v>
-      </c>
-      <c r="D41" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A42">
-        <v>9317404</v>
-      </c>
-      <c r="B42" t="s">
-        <v>194</v>
-      </c>
-      <c r="C42" t="s">
-        <v>67</v>
-      </c>
-      <c r="D42" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A43">
-        <v>8333604</v>
-      </c>
-      <c r="B43" t="s">
-        <v>195</v>
-      </c>
-      <c r="C43" t="s">
-        <v>67</v>
-      </c>
-      <c r="D43" t="s">
-        <v>177</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FEE7927-B2CB-4F8C-B929-249864A39417}">
   <dimension ref="A1:E62"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
@@ -8936,7 +8664,7 @@
         <v>121</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9251,13 +8979,13 @@
         <v>3257704</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>340</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>173</v>
@@ -9620,6 +9348,1031 @@
       </c>
       <c r="B62" s="6" t="s">
         <v>268</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BDA3CBB-27EB-4CB5-A822-4D20093FF9BE}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="8.3515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.05859375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.8203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="6.703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.29296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.05859375" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="4">
+        <v>1025518</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="4">
+        <v>4298104</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="4">
+        <v>1033606</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="4">
+        <v>1033506</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="4">
+        <v>1026254</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="4">
+        <v>1028366</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="4">
+        <v>1033023</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="4">
+        <v>1032554</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="4">
+        <v>1026281</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="4">
+        <v>1029057</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="4">
+        <v>1035828</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="4">
+        <v>1031619</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="4">
+        <v>1037608</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="4">
+        <v>1035515</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="4">
+        <v>1030772</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="4">
+        <v>1026742</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="4">
+        <v>1038924</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="4">
+        <v>1029508</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="4">
+        <v>1028849</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="4">
+        <v>1027008</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="4">
+        <v>1026200</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="4">
+        <v>1025833</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="4">
+        <v>1036053</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="4">
+        <v>1029029</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="4">
+        <v>1028278</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="4">
+        <v>1025603</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="4">
+        <v>1028053</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="4">
+        <v>1027036</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="4">
+        <v>1032361</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{836E3DAF-4660-4453-8445-CAEF205E5F1E}">
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="7.703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.41015625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.9375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.17578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.3515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A4">
+        <v>4206804</v>
+      </c>
+      <c r="B4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A5">
+        <v>9307104</v>
+      </c>
+      <c r="B5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A6">
+        <v>2173704</v>
+      </c>
+      <c r="B6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A7">
+        <v>9257304</v>
+      </c>
+      <c r="B7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A8">
+        <v>2915404</v>
+      </c>
+      <c r="B8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A9">
+        <v>2836604</v>
+      </c>
+      <c r="B9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" t="s">
+        <v>216</v>
+      </c>
+      <c r="D9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A10">
+        <v>1274904</v>
+      </c>
+      <c r="B10" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10" t="s">
+        <v>218</v>
+      </c>
+      <c r="D10" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A11">
+        <v>3863304</v>
+      </c>
+      <c r="B11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D11" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A12">
+        <v>3403504</v>
+      </c>
+      <c r="B12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A13">
+        <v>4721304</v>
+      </c>
+      <c r="B13" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" t="s">
+        <v>191</v>
+      </c>
+      <c r="D13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A14">
+        <v>3924304</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D14" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A15">
+        <v>4041704</v>
+      </c>
+      <c r="B15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" t="s">
+        <v>225</v>
+      </c>
+      <c r="D15" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A16">
+        <v>9280704</v>
+      </c>
+      <c r="B16" t="s">
+        <v>226</v>
+      </c>
+      <c r="C16" t="s">
+        <v>227</v>
+      </c>
+      <c r="D16" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="C17" t="s">
+        <v>228</v>
+      </c>
+      <c r="D17" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="B18" t="s">
+        <v>229</v>
+      </c>
+      <c r="C18" t="s">
+        <v>230</v>
+      </c>
+      <c r="D18" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A22">
+        <v>9693404</v>
+      </c>
+      <c r="B22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" t="s">
+        <v>197</v>
+      </c>
+      <c r="D22" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A23">
+        <v>222222</v>
+      </c>
+      <c r="B23" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" t="s">
+        <v>200</v>
+      </c>
+      <c r="D23" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A24">
+        <v>9743804</v>
+      </c>
+      <c r="B24" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24" t="s">
+        <v>202</v>
+      </c>
+      <c r="D24" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A25">
+        <v>111111</v>
+      </c>
+      <c r="B25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C25" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A26">
+        <v>9662304</v>
+      </c>
+      <c r="B26" t="s">
+        <v>205</v>
+      </c>
+      <c r="C26" t="s">
+        <v>206</v>
+      </c>
+      <c r="D26" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="B27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C27" t="s">
+        <v>273</v>
+      </c>
+      <c r="D27" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="B28" t="s">
+        <v>272</v>
+      </c>
+      <c r="C28" t="s">
+        <v>274</v>
+      </c>
+      <c r="D28" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A32">
+        <v>3578804</v>
+      </c>
+      <c r="B32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C32" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A33">
+        <v>9289704</v>
+      </c>
+      <c r="B33" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A34">
+        <v>9344404</v>
+      </c>
+      <c r="B34" t="s">
+        <v>179</v>
+      </c>
+      <c r="C34" t="s">
+        <v>180</v>
+      </c>
+      <c r="D34" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A35">
+        <v>6746404</v>
+      </c>
+      <c r="B35" t="s">
+        <v>181</v>
+      </c>
+      <c r="C35" t="s">
+        <v>182</v>
+      </c>
+      <c r="D35" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A36">
+        <v>9257604</v>
+      </c>
+      <c r="B36" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A37">
+        <v>9717204</v>
+      </c>
+      <c r="B37" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" t="s">
+        <v>186</v>
+      </c>
+      <c r="D37" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A38">
+        <v>2298204</v>
+      </c>
+      <c r="B38" t="s">
+        <v>187</v>
+      </c>
+      <c r="C38" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A39">
+        <v>5784804</v>
+      </c>
+      <c r="B39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A40">
+        <v>9321704</v>
+      </c>
+      <c r="B40" t="s">
+        <v>190</v>
+      </c>
+      <c r="C40" t="s">
+        <v>191</v>
+      </c>
+      <c r="D40" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A41">
+        <v>9720304</v>
+      </c>
+      <c r="B41" t="s">
+        <v>192</v>
+      </c>
+      <c r="C41" t="s">
+        <v>193</v>
+      </c>
+      <c r="D41" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A42">
+        <v>9317404</v>
+      </c>
+      <c r="B42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C42" t="s">
+        <v>67</v>
+      </c>
+      <c r="D42" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A43">
+        <v>8333604</v>
+      </c>
+      <c r="B43" t="s">
+        <v>195</v>
+      </c>
+      <c r="C43" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1553" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EF9DBFE-67D6-4304-BA9F-3FF5D5DD4A73}"/>
+  <xr:revisionPtr revIDLastSave="1568" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD66E263-E629-4BBD-9B95-1A6C4D2A685F}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
     <sheet name="A Gymansiou" sheetId="2" r:id="rId2"/>
-    <sheet name="notes" sheetId="10" r:id="rId3"/>
-    <sheet name="B Gymnasiou" sheetId="3" r:id="rId4"/>
-    <sheet name="Monada" sheetId="5" r:id="rId5"/>
-    <sheet name="A Lyceum" sheetId="4" r:id="rId6"/>
+    <sheet name="B Gymnasiou" sheetId="3" r:id="rId3"/>
+    <sheet name="A Lyceum" sheetId="4" r:id="rId4"/>
+    <sheet name="notes" sheetId="10" r:id="rId5"/>
+    <sheet name="Monada" sheetId="5" r:id="rId6"/>
     <sheet name="A Gymansiou - tests" sheetId="11" r:id="rId7"/>
     <sheet name="B Gymnasiou -tests" sheetId="13" r:id="rId8"/>
     <sheet name="A Lyceum - tests" sheetId="12" r:id="rId9"/>
@@ -1329,7 +1329,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="370">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2424,13 +2424,28 @@
   </si>
   <si>
     <t>ANAPLIROSEIS</t>
+  </si>
+  <si>
+    <t>https://youtu.be/F7pYHN9iC9I?si=SpZ8-YBTWozvd4E5</t>
+  </si>
+  <si>
+    <t>Amazing mind reader reveals his 'gift'</t>
+  </si>
+  <si>
+    <t>phising</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8aLJe9gsOxs</t>
+  </si>
+  <si>
+    <t>19-23/10 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2491,12 +2506,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="14">
@@ -4432,6 +4441,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4440,11 +4454,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4455,7 +4464,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0C9DD2-633E-44CA-9A93-86B2E2731C82}">
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.3515625" style="4" bestFit="1" customWidth="1"/>
@@ -4471,10 +4480,12 @@
     <col min="11" max="11" width="18.9375" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.64453125" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.87890625" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.05859375" style="4"/>
+    <col min="14" max="14" width="9.05859375" style="4"/>
+    <col min="15" max="15" width="16.87890625" style="4" customWidth="1"/>
+    <col min="16" max="16384" width="9.05859375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="7" t="s">
         <v>57</v>
       </c>
@@ -4488,7 +4499,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="F2" s="42" t="s">
         <v>285</v>
       </c>
@@ -4505,8 +4516,12 @@
         <v>323</v>
       </c>
       <c r="M2" s="42"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="N2" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="O2" s="42"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>121</v>
       </c>
@@ -4517,7 +4532,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4">
         <v>9285104</v>
       </c>
@@ -4545,7 +4560,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4">
         <v>8324104</v>
       </c>
@@ -4577,7 +4592,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4">
         <v>6811804</v>
       </c>
@@ -4609,7 +4624,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="4">
         <v>5436904</v>
       </c>
@@ -4641,7 +4656,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4">
         <v>7025704</v>
       </c>
@@ -4673,7 +4688,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="4">
         <v>8435804</v>
       </c>
@@ -4705,7 +4720,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4">
         <v>5069104</v>
       </c>
@@ -4737,7 +4752,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4">
         <v>5222304</v>
       </c>
@@ -4769,7 +4784,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4">
         <v>1981204</v>
       </c>
@@ -4801,7 +4816,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="4">
         <v>3766704</v>
       </c>
@@ -4831,7 +4846,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="4" t="s">
         <v>72</v>
       </c>
@@ -4851,7 +4866,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4">
         <v>5551204</v>
       </c>
@@ -5893,11 +5908,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5906,8 +5922,2509 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A321353-3FB1-4427-84C3-E63782B65799}">
+  <dimension ref="A1:O38"/>
+  <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="8.3515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.05859375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.8203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="6.703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="9.05859375" style="4"/>
+    <col min="11" max="11" width="9.8203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="9.05859375" style="4"/>
+    <col min="15" max="15" width="15" style="4" customWidth="1"/>
+    <col min="16" max="16384" width="9.05859375" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="F2" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42" t="s">
+        <v>323</v>
+      </c>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="O2" s="42"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="4">
+        <v>1025518</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="4">
+        <v>4298104</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I5" s="12"/>
+      <c r="L5" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="4">
+        <v>1033606</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="4">
+        <v>1033506</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="4">
+        <v>1026254</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="4">
+        <v>1028366</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="4">
+        <v>1033023</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="4">
+        <v>1032554</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="4">
+        <v>1026281</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="4">
+        <v>1029057</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="4">
+        <v>1035828</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="4">
+        <v>1031619</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="4">
+        <v>1037608</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="4">
+        <v>1035515</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="4">
+        <v>1030772</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="4">
+        <v>1026742</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="4">
+        <v>1038924</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="4">
+        <v>1029508</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="4">
+        <v>1028849</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="4">
+        <v>1027008</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="4">
+        <v>1026200</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="4">
+        <v>1025833</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="4">
+        <v>1036053</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="M32" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="4">
+        <v>1029029</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="4">
+        <v>1028278</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="4">
+        <v>1025603</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="J35" s="12"/>
+      <c r="K35" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="4">
+        <v>1028053</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="4">
+        <v>1027036</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="4">
+        <v>1032361</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF640171-D19A-4A22-AEE9-A5E7AF0F79D2}">
+  <dimension ref="A1:P43"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="7.703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.41015625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.9375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.17578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.29296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.41015625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.3515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5859375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="L1" s="42"/>
+      <c r="M1" s="43" t="s">
+        <v>329</v>
+      </c>
+      <c r="N1" s="43"/>
+      <c r="O1" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="P1" s="42"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" t="s">
+        <v>300</v>
+      </c>
+      <c r="L3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>4206804</v>
+      </c>
+      <c r="B4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>9307104</v>
+      </c>
+      <c r="B5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>208</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>2173704</v>
+      </c>
+      <c r="B6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>9257304</v>
+      </c>
+      <c r="B7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>2915404</v>
+      </c>
+      <c r="B8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>208</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <v>2836604</v>
+      </c>
+      <c r="B9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" t="s">
+        <v>216</v>
+      </c>
+      <c r="D9" t="s">
+        <v>208</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>1274904</v>
+      </c>
+      <c r="B10" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10" t="s">
+        <v>218</v>
+      </c>
+      <c r="D10" t="s">
+        <v>208</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>3863304</v>
+      </c>
+      <c r="B11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K11" s="12"/>
+      <c r="L11" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="M11" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>3403504</v>
+      </c>
+      <c r="B12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>4721304</v>
+      </c>
+      <c r="B13" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" t="s">
+        <v>191</v>
+      </c>
+      <c r="D13" t="s">
+        <v>208</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="M13" s="20"/>
+    </row>
+    <row r="14" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>3924304</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D14" t="s">
+        <v>208</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>4041704</v>
+      </c>
+      <c r="B15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" t="s">
+        <v>225</v>
+      </c>
+      <c r="D15" t="s">
+        <v>208</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>9280704</v>
+      </c>
+      <c r="B16" t="s">
+        <v>226</v>
+      </c>
+      <c r="C16" t="s">
+        <v>227</v>
+      </c>
+      <c r="D16" t="s">
+        <v>208</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="C17" t="s">
+        <v>228</v>
+      </c>
+      <c r="D17" t="s">
+        <v>231</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" t="s">
+        <v>229</v>
+      </c>
+      <c r="C18" t="s">
+        <v>230</v>
+      </c>
+      <c r="D18" t="s">
+        <v>208</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.5">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.5">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L21" t="s">
+        <v>312</v>
+      </c>
+      <c r="M21" t="s">
+        <v>312</v>
+      </c>
+      <c r="N21" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22">
+        <v>9693404</v>
+      </c>
+      <c r="B22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" t="s">
+        <v>197</v>
+      </c>
+      <c r="D22" t="s">
+        <v>198</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23">
+        <v>222222</v>
+      </c>
+      <c r="B23" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" t="s">
+        <v>200</v>
+      </c>
+      <c r="D23" t="s">
+        <v>198</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24">
+        <v>9743804</v>
+      </c>
+      <c r="B24" t="s">
+        <v>201</v>
+      </c>
+      <c r="C24" t="s">
+        <v>202</v>
+      </c>
+      <c r="D24" t="s">
+        <v>198</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25">
+        <v>111111</v>
+      </c>
+      <c r="B25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C25" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" t="s">
+        <v>198</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="I25" s="20"/>
+      <c r="J25" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K25" s="12"/>
+      <c r="L25" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="N25" s="12"/>
+    </row>
+    <row r="26" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26">
+        <v>9662304</v>
+      </c>
+      <c r="B26" t="s">
+        <v>205</v>
+      </c>
+      <c r="C26" t="s">
+        <v>206</v>
+      </c>
+      <c r="D26" t="s">
+        <v>198</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J26" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C27" t="s">
+        <v>273</v>
+      </c>
+      <c r="D27" t="s">
+        <v>275</v>
+      </c>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="I27" s="20"/>
+      <c r="J27" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L27" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="M27" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="N27" s="12"/>
+    </row>
+    <row r="28" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" t="s">
+        <v>272</v>
+      </c>
+      <c r="C28" t="s">
+        <v>274</v>
+      </c>
+      <c r="D28" t="s">
+        <v>276</v>
+      </c>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="I28" s="20"/>
+      <c r="J28" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="N28" s="12"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.5">
+      <c r="L30" s="8" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.5">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32">
+        <v>3578804</v>
+      </c>
+      <c r="B32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C32" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" t="s">
+        <v>177</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33">
+        <v>9289704</v>
+      </c>
+      <c r="B33" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" t="s">
+        <v>177</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I33" s="12"/>
+      <c r="J33" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M33" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34">
+        <v>9344404</v>
+      </c>
+      <c r="B34" t="s">
+        <v>179</v>
+      </c>
+      <c r="C34" t="s">
+        <v>180</v>
+      </c>
+      <c r="D34" t="s">
+        <v>177</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="I34" s="20"/>
+      <c r="J34" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L34" s="12"/>
+      <c r="M34" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35">
+        <v>6746404</v>
+      </c>
+      <c r="B35" t="s">
+        <v>181</v>
+      </c>
+      <c r="C35" t="s">
+        <v>182</v>
+      </c>
+      <c r="D35" t="s">
+        <v>177</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="I35" s="12"/>
+      <c r="J35" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M35" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36">
+        <v>9257604</v>
+      </c>
+      <c r="B36" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" t="s">
+        <v>177</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J36" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M36" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37">
+        <v>9717204</v>
+      </c>
+      <c r="B37" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" t="s">
+        <v>186</v>
+      </c>
+      <c r="D37" t="s">
+        <v>177</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="I37" s="12"/>
+      <c r="J37" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M37" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38">
+        <v>2298204</v>
+      </c>
+      <c r="B38" t="s">
+        <v>187</v>
+      </c>
+      <c r="C38" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" t="s">
+        <v>177</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I38" s="12"/>
+      <c r="J38" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K38" s="12"/>
+      <c r="L38" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M38" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39">
+        <v>5784804</v>
+      </c>
+      <c r="B39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" t="s">
+        <v>177</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40">
+        <v>9321704</v>
+      </c>
+      <c r="B40" t="s">
+        <v>190</v>
+      </c>
+      <c r="C40" t="s">
+        <v>191</v>
+      </c>
+      <c r="D40" t="s">
+        <v>177</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J40" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K40" s="12"/>
+      <c r="L40" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M40" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41">
+        <v>9720304</v>
+      </c>
+      <c r="B41" t="s">
+        <v>192</v>
+      </c>
+      <c r="C41" t="s">
+        <v>193</v>
+      </c>
+      <c r="D41" t="s">
+        <v>177</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I41" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="J41" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42">
+        <v>9317404</v>
+      </c>
+      <c r="B42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C42" t="s">
+        <v>67</v>
+      </c>
+      <c r="D42" t="s">
+        <v>177</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I42" s="12"/>
+      <c r="J42" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M42" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43">
+        <v>8333604</v>
+      </c>
+      <c r="B43" t="s">
+        <v>195</v>
+      </c>
+      <c r="C43" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" t="s">
+        <v>177</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J43" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="M43" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23D143C4-24B5-4F25-A9AC-CA5F9ACC8C3E}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="49.87890625" bestFit="1" customWidth="1"/>
@@ -5987,6 +8504,22 @@
         <v>270</v>
       </c>
     </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A18" t="s">
+        <v>366</v>
+      </c>
+      <c r="B18" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A19" t="s">
+        <v>367</v>
+      </c>
+      <c r="B19" t="s">
+        <v>368</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" xr:uid="{2329A344-AF26-4B9C-98D4-47024E1629FE}"/>
@@ -5996,1065 +8529,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A321353-3FB1-4427-84C3-E63782B65799}">
-  <dimension ref="A1:M38"/>
-  <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="8.3515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.05859375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.8203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="6.703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="9.05859375" style="4"/>
-    <col min="11" max="11" width="9.8203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.05859375" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="42" t="s">
-        <v>285</v>
-      </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42" t="s">
-        <v>286</v>
-      </c>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42" t="s">
-        <v>299</v>
-      </c>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42" t="s">
-        <v>323</v>
-      </c>
-      <c r="M2" s="42"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="4">
-        <v>1025518</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="4">
-        <v>4298104</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I5" s="12"/>
-      <c r="L5" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="4">
-        <v>1033606</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="4">
-        <v>1033506</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="4">
-        <v>1026254</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="4">
-        <v>1028366</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="4">
-        <v>1033023</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="4">
-        <v>1032554</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="4">
-        <v>1026281</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L12" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="4">
-        <v>1029057</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="4">
-        <v>1035828</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="L16" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="4">
-        <v>1031619</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="J17" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="L17" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="4">
-        <v>1037608</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="J18" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="4">
-        <v>1035515</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="K19" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="L19" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="4">
-        <v>1030772</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="L20" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="4">
-        <v>1026742</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="4">
-        <v>1038924</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K22" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="L22" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="4">
-        <v>1029508</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="4">
-        <v>1028849</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="L24" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L28" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="4">
-        <v>1027008</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K29" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L29" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="M29" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="4">
-        <v>1026200</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L30" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="M30" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="4">
-        <v>1025833</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K31" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L31" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="M31" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="4">
-        <v>1036053</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L32" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="M32" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="4">
-        <v>1029029</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L33" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="M33" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="4">
-        <v>1028278</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L34" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="M34" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="4">
-        <v>1025603</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="J35" s="12"/>
-      <c r="K35" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L35" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="M35" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="4">
-        <v>1028053</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L36" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="M36" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="4">
-        <v>1027036</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K37" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L37" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="M37" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="4">
-        <v>1032361</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K38" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="L38" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="M38" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82B87684-E387-4B51-9ECE-3C23F4BC9CBD}">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
@@ -7198,1437 +8673,6 @@
     <mergeCell ref="I1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF640171-D19A-4A22-AEE9-A5E7AF0F79D2}">
-  <dimension ref="A1:N43"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
-  <cols>
-    <col min="1" max="1" width="7.703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.41015625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.9375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.17578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.29296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.41015625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.3515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5859375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="42" t="s">
-        <v>285</v>
-      </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42" t="s">
-        <v>286</v>
-      </c>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42" t="s">
-        <v>299</v>
-      </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="43" t="s">
-        <v>329</v>
-      </c>
-      <c r="N1" s="43"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" t="s">
-        <v>300</v>
-      </c>
-      <c r="L3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
-        <v>4206804</v>
-      </c>
-      <c r="B4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" t="s">
-        <v>208</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
-        <v>9307104</v>
-      </c>
-      <c r="B5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" t="s">
-        <v>208</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J5" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
-        <v>2173704</v>
-      </c>
-      <c r="B6" t="s">
-        <v>210</v>
-      </c>
-      <c r="C6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D6" t="s">
-        <v>208</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
-        <v>9257304</v>
-      </c>
-      <c r="B7" t="s">
-        <v>212</v>
-      </c>
-      <c r="C7" t="s">
-        <v>213</v>
-      </c>
-      <c r="D7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8">
-        <v>2915404</v>
-      </c>
-      <c r="B8" t="s">
-        <v>214</v>
-      </c>
-      <c r="C8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" t="s">
-        <v>208</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J8" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9">
-        <v>2836604</v>
-      </c>
-      <c r="B9" t="s">
-        <v>215</v>
-      </c>
-      <c r="C9" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" t="s">
-        <v>208</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10">
-        <v>1274904</v>
-      </c>
-      <c r="B10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C10" t="s">
-        <v>218</v>
-      </c>
-      <c r="D10" t="s">
-        <v>208</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11">
-        <v>3863304</v>
-      </c>
-      <c r="B11" t="s">
-        <v>219</v>
-      </c>
-      <c r="C11" t="s">
-        <v>220</v>
-      </c>
-      <c r="D11" t="s">
-        <v>208</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K11" s="12"/>
-      <c r="L11" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="M11" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12">
-        <v>3403504</v>
-      </c>
-      <c r="B12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13">
-        <v>4721304</v>
-      </c>
-      <c r="B13" t="s">
-        <v>223</v>
-      </c>
-      <c r="C13" t="s">
-        <v>191</v>
-      </c>
-      <c r="D13" t="s">
-        <v>208</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J13" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="M13" s="20"/>
-    </row>
-    <row r="14" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14">
-        <v>3924304</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="s">
-        <v>224</v>
-      </c>
-      <c r="D14" t="s">
-        <v>208</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15">
-        <v>4041704</v>
-      </c>
-      <c r="B15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" t="s">
-        <v>225</v>
-      </c>
-      <c r="D15" t="s">
-        <v>208</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J15" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16">
-        <v>9280704</v>
-      </c>
-      <c r="B16" t="s">
-        <v>226</v>
-      </c>
-      <c r="C16" t="s">
-        <v>227</v>
-      </c>
-      <c r="D16" t="s">
-        <v>208</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="C17" t="s">
-        <v>228</v>
-      </c>
-      <c r="D17" t="s">
-        <v>231</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J17" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" t="s">
-        <v>229</v>
-      </c>
-      <c r="C18" t="s">
-        <v>230</v>
-      </c>
-      <c r="D18" t="s">
-        <v>208</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J18" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M18" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" t="s">
-        <v>60</v>
-      </c>
-      <c r="L21" t="s">
-        <v>312</v>
-      </c>
-      <c r="M21" t="s">
-        <v>312</v>
-      </c>
-      <c r="N21" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22">
-        <v>9693404</v>
-      </c>
-      <c r="B22" t="s">
-        <v>196</v>
-      </c>
-      <c r="C22" t="s">
-        <v>197</v>
-      </c>
-      <c r="D22" t="s">
-        <v>198</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J22" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M22" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23">
-        <v>222222</v>
-      </c>
-      <c r="B23" t="s">
-        <v>199</v>
-      </c>
-      <c r="C23" t="s">
-        <v>200</v>
-      </c>
-      <c r="D23" t="s">
-        <v>198</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J23" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M23" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24">
-        <v>9743804</v>
-      </c>
-      <c r="B24" t="s">
-        <v>201</v>
-      </c>
-      <c r="C24" t="s">
-        <v>202</v>
-      </c>
-      <c r="D24" t="s">
-        <v>198</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J24" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L24" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="M24" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25">
-        <v>111111</v>
-      </c>
-      <c r="B25" t="s">
-        <v>203</v>
-      </c>
-      <c r="C25" t="s">
-        <v>204</v>
-      </c>
-      <c r="D25" t="s">
-        <v>198</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="I25" s="20"/>
-      <c r="J25" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K25" s="12"/>
-      <c r="L25" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="N25" s="12"/>
-    </row>
-    <row r="26" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26">
-        <v>9662304</v>
-      </c>
-      <c r="B26" t="s">
-        <v>205</v>
-      </c>
-      <c r="C26" t="s">
-        <v>206</v>
-      </c>
-      <c r="D26" t="s">
-        <v>198</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J26" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="N26" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" t="s">
-        <v>272</v>
-      </c>
-      <c r="C27" t="s">
-        <v>273</v>
-      </c>
-      <c r="D27" t="s">
-        <v>275</v>
-      </c>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="I27" s="20"/>
-      <c r="J27" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L27" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="M27" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="N27" s="12"/>
-    </row>
-    <row r="28" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" t="s">
-        <v>272</v>
-      </c>
-      <c r="C28" t="s">
-        <v>274</v>
-      </c>
-      <c r="D28" t="s">
-        <v>276</v>
-      </c>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="I28" s="20"/>
-      <c r="J28" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M28" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="N28" s="12"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="L30" s="8" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A31" t="s">
-        <v>16</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32">
-        <v>3578804</v>
-      </c>
-      <c r="B32" t="s">
-        <v>176</v>
-      </c>
-      <c r="C32" t="s">
-        <v>128</v>
-      </c>
-      <c r="D32" t="s">
-        <v>177</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J32" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M32" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33">
-        <v>9289704</v>
-      </c>
-      <c r="B33" t="s">
-        <v>178</v>
-      </c>
-      <c r="C33" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" t="s">
-        <v>177</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I33" s="12"/>
-      <c r="J33" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M33" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34">
-        <v>9344404</v>
-      </c>
-      <c r="B34" t="s">
-        <v>179</v>
-      </c>
-      <c r="C34" t="s">
-        <v>180</v>
-      </c>
-      <c r="D34" t="s">
-        <v>177</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="I34" s="20"/>
-      <c r="J34" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L34" s="12"/>
-      <c r="M34" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35">
-        <v>6746404</v>
-      </c>
-      <c r="B35" t="s">
-        <v>181</v>
-      </c>
-      <c r="C35" t="s">
-        <v>182</v>
-      </c>
-      <c r="D35" t="s">
-        <v>177</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="I35" s="12"/>
-      <c r="J35" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M35" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36">
-        <v>9257604</v>
-      </c>
-      <c r="B36" t="s">
-        <v>183</v>
-      </c>
-      <c r="C36" t="s">
-        <v>184</v>
-      </c>
-      <c r="D36" t="s">
-        <v>177</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J36" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L36" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M36" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37">
-        <v>9717204</v>
-      </c>
-      <c r="B37" t="s">
-        <v>185</v>
-      </c>
-      <c r="C37" t="s">
-        <v>186</v>
-      </c>
-      <c r="D37" t="s">
-        <v>177</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="I37" s="12"/>
-      <c r="J37" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K37" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L37" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M37" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38">
-        <v>2298204</v>
-      </c>
-      <c r="B38" t="s">
-        <v>187</v>
-      </c>
-      <c r="C38" t="s">
-        <v>188</v>
-      </c>
-      <c r="D38" t="s">
-        <v>177</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I38" s="12"/>
-      <c r="J38" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K38" s="12"/>
-      <c r="L38" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M38" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39">
-        <v>5784804</v>
-      </c>
-      <c r="B39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" t="s">
-        <v>177</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J39" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L39" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M39" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40">
-        <v>9321704</v>
-      </c>
-      <c r="B40" t="s">
-        <v>190</v>
-      </c>
-      <c r="C40" t="s">
-        <v>191</v>
-      </c>
-      <c r="D40" t="s">
-        <v>177</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J40" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K40" s="12"/>
-      <c r="L40" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M40" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41">
-        <v>9720304</v>
-      </c>
-      <c r="B41" t="s">
-        <v>192</v>
-      </c>
-      <c r="C41" t="s">
-        <v>193</v>
-      </c>
-      <c r="D41" t="s">
-        <v>177</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I41" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="J41" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L41" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M41" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42">
-        <v>9317404</v>
-      </c>
-      <c r="B42" t="s">
-        <v>194</v>
-      </c>
-      <c r="C42" t="s">
-        <v>67</v>
-      </c>
-      <c r="D42" t="s">
-        <v>177</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I42" s="12"/>
-      <c r="J42" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L42" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M42" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43">
-        <v>8333604</v>
-      </c>
-      <c r="B43" t="s">
-        <v>195</v>
-      </c>
-      <c r="C43" t="s">
-        <v>67</v>
-      </c>
-      <c r="D43" t="s">
-        <v>177</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J43" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="K43" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="L43" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M43" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-  </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1568" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD66E263-E629-4BBD-9B95-1A6C4D2A685F}"/>
+  <xr:revisionPtr revIDLastSave="1569" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21D04BB2-B47C-48B6-B7EA-114F0ED501C0}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -2749,17 +2749,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3593,58 +3593,58 @@
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="28"/>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="40" t="s">
+      <c r="C1" s="43"/>
+      <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="40" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="41"/>
-      <c r="H1" s="40" t="s">
+      <c r="G1" s="43"/>
+      <c r="H1" s="42" t="s">
         <v>241</v>
       </c>
-      <c r="I1" s="41"/>
-      <c r="J1" s="40" t="s">
+      <c r="I1" s="43"/>
+      <c r="J1" s="42" t="s">
         <v>245</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="40" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="42" t="s">
         <v>248</v>
       </c>
-      <c r="M1" s="41"/>
-      <c r="N1" s="40" t="s">
+      <c r="M1" s="43"/>
+      <c r="N1" s="42" t="s">
         <v>348</v>
       </c>
-      <c r="O1" s="41"/>
-      <c r="P1" s="40" t="s">
+      <c r="O1" s="43"/>
+      <c r="P1" s="42" t="s">
         <v>349</v>
       </c>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="40" t="s">
+      <c r="Q1" s="43"/>
+      <c r="R1" s="42" t="s">
         <v>351</v>
       </c>
-      <c r="S1" s="41"/>
-      <c r="T1" s="40" t="s">
+      <c r="S1" s="43"/>
+      <c r="T1" s="42" t="s">
         <v>352</v>
       </c>
-      <c r="U1" s="41"/>
-      <c r="V1" s="40" t="s">
+      <c r="U1" s="43"/>
+      <c r="V1" s="42" t="s">
         <v>353</v>
       </c>
-      <c r="W1" s="41"/>
-      <c r="X1" s="40" t="s">
+      <c r="W1" s="43"/>
+      <c r="X1" s="42" t="s">
         <v>354</v>
       </c>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="40" t="s">
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="42" t="s">
         <v>355</v>
       </c>
-      <c r="AA1" s="41"/>
+      <c r="AA1" s="43"/>
       <c r="AB1" s="29"/>
       <c r="AC1" s="29"/>
       <c r="AD1" s="29"/>
@@ -3797,7 +3797,7 @@
       <c r="N4" s="27" t="s">
         <v>362</v>
       </c>
-      <c r="O4" s="25" t="s">
+      <c r="O4" s="27" t="s">
         <v>361</v>
       </c>
       <c r="Y4" s="39" t="s">
@@ -3847,7 +3847,7 @@
       <c r="N5" s="27" t="s">
         <v>362</v>
       </c>
-      <c r="O5" s="25" t="s">
+      <c r="O5" s="27" t="s">
         <v>361</v>
       </c>
       <c r="X5" s="39" t="s">
@@ -3897,7 +3897,7 @@
       <c r="N6" s="27" t="s">
         <v>362</v>
       </c>
-      <c r="O6" s="25" t="s">
+      <c r="O6" s="27" t="s">
         <v>361</v>
       </c>
       <c r="P6" s="25" t="s">
@@ -4441,11 +4441,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4454,6 +4449,11 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4500,26 +4500,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42" t="s">
+      <c r="G2" s="40"/>
+      <c r="H2" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42" t="s">
+      <c r="I2" s="40"/>
+      <c r="J2" s="40" t="s">
         <v>297</v>
       </c>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42" t="s">
+      <c r="K2" s="40"/>
+      <c r="L2" s="40" t="s">
         <v>323</v>
       </c>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42" t="s">
+      <c r="M2" s="40"/>
+      <c r="N2" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="O2" s="42"/>
+      <c r="O2" s="40"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -5952,26 +5952,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42" t="s">
+      <c r="G2" s="40"/>
+      <c r="H2" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42" t="s">
+      <c r="I2" s="40"/>
+      <c r="J2" s="40" t="s">
         <v>299</v>
       </c>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42" t="s">
+      <c r="K2" s="40"/>
+      <c r="L2" s="40" t="s">
         <v>323</v>
       </c>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42" t="s">
+      <c r="M2" s="40"/>
+      <c r="N2" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="O2" s="42"/>
+      <c r="O2" s="40"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -7014,26 +7014,26 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42" t="s">
+      <c r="H1" s="40"/>
+      <c r="I1" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42" t="s">
+      <c r="J1" s="40"/>
+      <c r="K1" s="40" t="s">
         <v>299</v>
       </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="43" t="s">
+      <c r="L1" s="40"/>
+      <c r="M1" s="41" t="s">
         <v>329</v>
       </c>
-      <c r="N1" s="43"/>
-      <c r="O1" s="42" t="s">
+      <c r="N1" s="41"/>
+      <c r="O1" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="P1" s="42"/>
+      <c r="P1" s="40"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
@@ -8553,18 +8553,18 @@
       <c r="D1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42" t="s">
+      <c r="F1" s="40"/>
+      <c r="G1" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42" t="s">
+      <c r="H1" s="40"/>
+      <c r="I1" s="40" t="s">
         <v>299</v>
       </c>
-      <c r="J1" s="42"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1569" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21D04BB2-B47C-48B6-B7EA-114F0ED501C0}"/>
+  <xr:revisionPtr revIDLastSave="1571" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58EC4C9C-D83B-4BD6-ADC2-1487D8BB051C}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -1329,7 +1329,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="370">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2749,17 +2749,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3593,58 +3593,58 @@
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="28"/>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="42" t="s">
+      <c r="C1" s="41"/>
+      <c r="D1" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="43"/>
-      <c r="F1" s="42" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="40" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="42" t="s">
+      <c r="G1" s="41"/>
+      <c r="H1" s="40" t="s">
         <v>241</v>
       </c>
-      <c r="I1" s="43"/>
-      <c r="J1" s="42" t="s">
+      <c r="I1" s="41"/>
+      <c r="J1" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="42" t="s">
+      <c r="K1" s="41"/>
+      <c r="L1" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="M1" s="43"/>
-      <c r="N1" s="42" t="s">
+      <c r="M1" s="41"/>
+      <c r="N1" s="40" t="s">
         <v>348</v>
       </c>
-      <c r="O1" s="43"/>
-      <c r="P1" s="42" t="s">
+      <c r="O1" s="41"/>
+      <c r="P1" s="40" t="s">
         <v>349</v>
       </c>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="42" t="s">
+      <c r="Q1" s="41"/>
+      <c r="R1" s="40" t="s">
         <v>351</v>
       </c>
-      <c r="S1" s="43"/>
-      <c r="T1" s="42" t="s">
+      <c r="S1" s="41"/>
+      <c r="T1" s="40" t="s">
         <v>352</v>
       </c>
-      <c r="U1" s="43"/>
-      <c r="V1" s="42" t="s">
+      <c r="U1" s="41"/>
+      <c r="V1" s="40" t="s">
         <v>353</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="42" t="s">
+      <c r="W1" s="41"/>
+      <c r="X1" s="40" t="s">
         <v>354</v>
       </c>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="42" t="s">
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="40" t="s">
         <v>355</v>
       </c>
-      <c r="AA1" s="43"/>
+      <c r="AA1" s="41"/>
       <c r="AB1" s="29"/>
       <c r="AC1" s="29"/>
       <c r="AD1" s="29"/>
@@ -4441,6 +4441,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4449,11 +4454,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4500,26 +4500,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="42" t="s">
         <v>285</v>
       </c>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40" t="s">
+      <c r="G2" s="42"/>
+      <c r="H2" s="42" t="s">
         <v>286</v>
       </c>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40" t="s">
+      <c r="I2" s="42"/>
+      <c r="J2" s="42" t="s">
         <v>297</v>
       </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40" t="s">
+      <c r="K2" s="42"/>
+      <c r="L2" s="42" t="s">
         <v>323</v>
       </c>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40" t="s">
+      <c r="M2" s="42"/>
+      <c r="N2" s="42" t="s">
         <v>369</v>
       </c>
-      <c r="O2" s="40"/>
+      <c r="O2" s="42"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -5952,26 +5952,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="42" t="s">
         <v>285</v>
       </c>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40" t="s">
+      <c r="G2" s="42"/>
+      <c r="H2" s="42" t="s">
         <v>286</v>
       </c>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40" t="s">
+      <c r="I2" s="42"/>
+      <c r="J2" s="42" t="s">
         <v>299</v>
       </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40" t="s">
+      <c r="K2" s="42"/>
+      <c r="L2" s="42" t="s">
         <v>323</v>
       </c>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40" t="s">
+      <c r="M2" s="42"/>
+      <c r="N2" s="42" t="s">
         <v>369</v>
       </c>
-      <c r="O2" s="40"/>
+      <c r="O2" s="42"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -7014,26 +7014,26 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="42" t="s">
         <v>285</v>
       </c>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40" t="s">
+      <c r="H1" s="42"/>
+      <c r="I1" s="42" t="s">
         <v>286</v>
       </c>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40" t="s">
+      <c r="J1" s="42"/>
+      <c r="K1" s="42" t="s">
         <v>299</v>
       </c>
-      <c r="L1" s="40"/>
-      <c r="M1" s="41" t="s">
+      <c r="L1" s="42"/>
+      <c r="M1" s="43" t="s">
         <v>329</v>
       </c>
-      <c r="N1" s="41"/>
-      <c r="O1" s="40" t="s">
+      <c r="N1" s="43"/>
+      <c r="O1" s="42" t="s">
         <v>369</v>
       </c>
-      <c r="P1" s="40"/>
+      <c r="P1" s="42"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
@@ -8553,18 +8553,18 @@
       <c r="D1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="42" t="s">
         <v>285</v>
       </c>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40" t="s">
+      <c r="F1" s="42"/>
+      <c r="G1" s="42" t="s">
         <v>286</v>
       </c>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40" t="s">
+      <c r="H1" s="42"/>
+      <c r="I1" s="42" t="s">
         <v>299</v>
       </c>
-      <c r="J1" s="40"/>
+      <c r="J1" s="42"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
@@ -8856,6 +8856,9 @@
       <c r="D13" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="E13" s="6" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4" t="s">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1571" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58EC4C9C-D83B-4BD6-ADC2-1487D8BB051C}"/>
+  <xr:revisionPtr revIDLastSave="1575" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DF63F48-ED06-446B-B508-CD0C9A5B6D76}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -1329,7 +1329,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="370">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -4441,11 +4441,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4454,6 +4449,11 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8724,6 +8724,9 @@
       <c r="D4" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="E4" s="6" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4">
@@ -8842,6 +8845,9 @@
       <c r="D12" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="E12" s="6" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="4">
@@ -9102,7 +9108,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="4">
         <v>7319504</v>
       </c>
@@ -9116,7 +9122,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="4">
         <v>9254304</v>
       </c>
@@ -9130,7 +9136,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="4">
         <v>2428404</v>
       </c>
@@ -9144,7 +9150,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="4">
         <v>2427904</v>
       </c>
@@ -9158,7 +9164,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4">
         <v>8373704</v>
       </c>
@@ -9172,7 +9178,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="4">
         <v>5155004</v>
       </c>
@@ -9186,7 +9192,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="4">
         <v>1006390</v>
       </c>
@@ -9200,12 +9206,12 @@
         <v>143</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="4">
         <v>5324204</v>
       </c>
@@ -9219,7 +9225,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="4">
         <v>5996604</v>
       </c>
@@ -9233,7 +9239,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="4">
         <v>7153704</v>
       </c>
@@ -9247,7 +9253,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="4">
         <v>9185204</v>
       </c>
@@ -9260,8 +9266,11 @@
       <c r="D46" s="4" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E46" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="4">
         <v>9185504</v>
       </c>
@@ -9274,8 +9283,11 @@
       <c r="D47" s="4" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E47" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="4">
         <v>4913604</v>
       </c>
@@ -9287,6 +9299,9 @@
       </c>
       <c r="D48" s="4" t="s">
         <v>159</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1575" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DF63F48-ED06-446B-B508-CD0C9A5B6D76}"/>
+  <xr:revisionPtr revIDLastSave="1633" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA31D332-0949-494F-84E5-91158F4B66FD}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -1329,7 +1329,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="372">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2213,9 +2213,6 @@
     <t>A2</t>
   </si>
   <si>
-    <t>A5.2 Μ3 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου</t>
-  </si>
-  <si>
     <t>B41M8 - Επεξεργασία αριθμητικών δεδομένων και αναφορές κελιών</t>
   </si>
   <si>
@@ -2414,9 +2411,6 @@
     <t>A2Μ2 - Μονάδες και Περιφερειακά του Υπολογιστή - Μέρος 2</t>
   </si>
   <si>
-    <t>A5.2 Μ2 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου - hw.ask.26 p137</t>
-  </si>
-  <si>
     <t>CREATE EMAIL WITH HOTSPOT - Α5.2 Μ1 - Εναλλακτικό Φύλλο Εργασίας - Ηλεκτρονικό Ταχυδρομείο</t>
   </si>
   <si>
@@ -2439,6 +2433,18 @@
   </si>
   <si>
     <t>19-23/10 2026</t>
+  </si>
+  <si>
+    <t>kahoot 19-10-2026</t>
+  </si>
+  <si>
+    <t>B41M9 - Εισαγωγή στις Συναρτήσεις - ξανα σχετική και απόλυτη αναφορά</t>
+  </si>
+  <si>
+    <t>A5.2 Μ2 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου - give A5.2 Μ2 και Μ3 - Ενιαίο Δισέλιδο Φύλλο Εργασίας</t>
+  </si>
+  <si>
+    <t>A5.2 Μ3 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου - use A5.2 Μ2 και Μ3 - Ενιαίο Δισέλιδο Φύλλο Εργασίας</t>
   </si>
 </sst>
 </file>
@@ -3577,7 +3583,7 @@
     <col min="13" max="13" width="53.1171875" style="25" customWidth="1"/>
     <col min="14" max="14" width="43.05859375" style="25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="47.8203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37.41015625" style="25" customWidth="1"/>
+    <col min="16" max="16" width="40.3515625" style="25" customWidth="1"/>
     <col min="17" max="17" width="24.41015625" style="25" customWidth="1"/>
     <col min="18" max="18" width="26.41015625" style="25" customWidth="1"/>
     <col min="19" max="19" width="25.64453125" style="25" customWidth="1"/>
@@ -3618,31 +3624,31 @@
       </c>
       <c r="M1" s="41"/>
       <c r="N1" s="40" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O1" s="41"/>
       <c r="P1" s="40" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q1" s="41"/>
       <c r="R1" s="40" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="S1" s="41"/>
       <c r="T1" s="40" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="U1" s="41"/>
       <c r="V1" s="40" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="W1" s="41"/>
       <c r="X1" s="40" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Y1" s="41"/>
       <c r="Z1" s="40" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AA1" s="41"/>
       <c r="AB1" s="29"/>
@@ -3792,13 +3798,13 @@
         <v>239</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="N4" s="27" t="s">
-        <v>362</v>
+        <v>329</v>
+      </c>
+      <c r="N4" s="23" t="s">
+        <v>360</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="Y4" s="39" t="s">
         <v>249</v>
@@ -3839,22 +3845,22 @@
         <v>255</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N5" s="27" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="O5" s="27" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="X5" s="39" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="6" spans="1:60" ht="28.7" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:60" ht="61" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="30" t="s">
         <v>4</v>
       </c>
@@ -3886,37 +3892,37 @@
         <v>255</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="N6" s="27" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="O6" s="27" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="P6" s="25" t="s">
-        <v>294</v>
+        <v>371</v>
       </c>
       <c r="Q6" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="R6" s="25" t="s">
         <v>356</v>
       </c>
-      <c r="R6" s="25" t="s">
+      <c r="S6" s="25" t="s">
         <v>357</v>
       </c>
-      <c r="S6" s="25" t="s">
+      <c r="T6" s="25" t="s">
         <v>358</v>
       </c>
-      <c r="T6" s="25" t="s">
+      <c r="U6" s="25" t="s">
         <v>359</v>
-      </c>
-      <c r="U6" s="25" t="s">
-        <v>360</v>
       </c>
       <c r="X6" s="39" t="s">
         <v>249</v>
@@ -3960,13 +3966,13 @@
         <v>239</v>
       </c>
       <c r="M7" s="23" t="s">
-        <v>344</v>
-      </c>
-      <c r="N7" s="27" t="s">
-        <v>330</v>
+        <v>343</v>
+      </c>
+      <c r="N7" s="23" t="s">
+        <v>256</v>
       </c>
       <c r="O7" s="27" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="X7" s="39" t="s">
         <v>249</v>
@@ -3980,13 +3986,13 @@
         <v>35</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M10" s="25" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="11" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="11" spans="1:60" x14ac:dyDescent="0.5">
       <c r="A11" s="30" t="s">
         <v>6</v>
       </c>
@@ -4015,25 +4021,25 @@
         <v>259</v>
       </c>
       <c r="J11" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="K11" s="23" t="s">
         <v>295</v>
-      </c>
-      <c r="K11" s="23" t="s">
-        <v>296</v>
       </c>
       <c r="L11" s="26" t="s">
         <v>239</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="N11" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="N11" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="O11" s="25" t="s">
         <v>324</v>
       </c>
-      <c r="O11" s="25" t="s">
+      <c r="P11" s="25" t="s">
         <v>325</v>
-      </c>
-      <c r="P11" s="25" t="s">
-        <v>326</v>
       </c>
       <c r="V11" s="39" t="s">
         <v>249</v>
@@ -4077,19 +4083,19 @@
         <v>239</v>
       </c>
       <c r="M12" s="23" t="s">
-        <v>350</v>
-      </c>
-      <c r="N12" s="25" t="s">
-        <v>295</v>
+        <v>349</v>
+      </c>
+      <c r="N12" s="23" t="s">
+        <v>294</v>
       </c>
       <c r="O12" s="25" t="s">
-        <v>296</v>
+        <v>369</v>
       </c>
       <c r="V12" s="39" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="13" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:60" x14ac:dyDescent="0.5">
       <c r="A13" s="30" t="s">
         <v>8</v>
       </c>
@@ -4121,22 +4127,22 @@
         <v>259</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L13" s="26" t="s">
         <v>239</v>
       </c>
       <c r="M13" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="N13" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="N13" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="O13" s="25" t="s">
         <v>324</v>
       </c>
-      <c r="O13" s="25" t="s">
+      <c r="P13" s="25" t="s">
         <v>325</v>
-      </c>
-      <c r="P13" s="25" t="s">
-        <v>326</v>
       </c>
       <c r="V13" s="39" t="s">
         <v>249</v>
@@ -4193,16 +4199,16 @@
         <v>243</v>
       </c>
       <c r="L18" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="M18" s="23" t="s">
         <v>321</v>
-      </c>
-      <c r="M18" s="23" t="s">
-        <v>322</v>
       </c>
       <c r="N18" s="27" t="s">
         <v>244</v>
       </c>
       <c r="O18" s="27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P18" s="36" t="s">
         <v>249</v>
@@ -4249,16 +4255,16 @@
         <v>243</v>
       </c>
       <c r="L19" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="M19" s="23" t="s">
         <v>321</v>
-      </c>
-      <c r="M19" s="23" t="s">
-        <v>322</v>
       </c>
       <c r="N19" s="27" t="s">
         <v>244</v>
       </c>
       <c r="O19" s="27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P19" s="36" t="s">
         <v>249</v>
@@ -4308,16 +4314,16 @@
         <v>243</v>
       </c>
       <c r="M20" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="N20" s="27" t="s">
         <v>321</v>
-      </c>
-      <c r="N20" s="27" t="s">
-        <v>322</v>
       </c>
       <c r="O20" s="27" t="s">
         <v>244</v>
       </c>
       <c r="P20" s="27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q20" s="36" t="s">
         <v>249</v>
@@ -4366,16 +4372,16 @@
         <v>281</v>
       </c>
       <c r="J22" s="23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K22" s="23" t="s">
         <v>172</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.5">
@@ -4441,6 +4447,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4449,11 +4460,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4509,15 +4515,15 @@
       </c>
       <c r="I2" s="42"/>
       <c r="J2" s="42" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K2" s="42"/>
       <c r="L2" s="42" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M2" s="42"/>
       <c r="N2" s="42" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="O2" s="42"/>
     </row>
@@ -4529,7 +4535,7 @@
         <v>290</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -4860,10 +4866,10 @@
         <v>290</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -5153,13 +5159,13 @@
         <v>3257704</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>338</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>339</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -5961,15 +5967,15 @@
       </c>
       <c r="I2" s="42"/>
       <c r="J2" s="42" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K2" s="42"/>
       <c r="L2" s="42" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M2" s="42"/>
       <c r="N2" s="42" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="O2" s="42"/>
     </row>
@@ -6567,10 +6573,10 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>303</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>39</v>
@@ -7023,15 +7029,15 @@
       </c>
       <c r="J1" s="42"/>
       <c r="K1" s="42" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L1" s="42"/>
       <c r="M1" s="43" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N1" s="43"/>
       <c r="O1" s="42" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="P1" s="42"/>
     </row>
@@ -7040,10 +7046,10 @@
         <v>14</v>
       </c>
       <c r="K3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7667,13 +7673,13 @@
         <v>60</v>
       </c>
       <c r="L21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M21" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="N21" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7958,7 +7964,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.5">
       <c r="L30" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.5">
@@ -7966,7 +7972,7 @@
         <v>16</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8435,65 +8441,65 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C3" s="22" t="s">
         <v>308</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" t="s">
         <v>315</v>
-      </c>
-      <c r="C7" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C9" t="s">
         <v>327</v>
-      </c>
-      <c r="C9" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
+        <v>333</v>
+      </c>
+      <c r="C10" t="s">
         <v>334</v>
-      </c>
-      <c r="C10" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.5">
@@ -8506,18 +8512,18 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B18" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B19" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -8562,7 +8568,7 @@
       </c>
       <c r="H1" s="42"/>
       <c r="I1" s="42" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J1" s="42"/>
     </row>
@@ -8708,7 +8714,7 @@
         <v>121</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8741,6 +8747,7 @@
       <c r="D5" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="E5" s="20"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4">
@@ -8755,6 +8762,7 @@
       <c r="D6" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="E6" s="20"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="4">
@@ -8786,6 +8794,9 @@
       <c r="D8" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="E8" s="6" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="4">
@@ -8800,6 +8811,7 @@
       <c r="D9" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="E9" s="20"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4">
@@ -8831,6 +8843,7 @@
       <c r="D11" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4">
@@ -9032,13 +9045,13 @@
         <v>3257704</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>338</v>
-      </c>
       <c r="D26" s="4" t="s">
-        <v>339</v>
+        <v>75</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>173</v>
@@ -9224,6 +9237,7 @@
       <c r="D43" s="4" t="s">
         <v>159</v>
       </c>
+      <c r="E43" s="20"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="4">
@@ -9238,6 +9252,7 @@
       <c r="D44" s="4" t="s">
         <v>159</v>
       </c>
+      <c r="E44" s="20"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="4">
@@ -9252,6 +9267,7 @@
       <c r="D45" s="4" t="s">
         <v>159</v>
       </c>
+      <c r="E45" s="20"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="4">
@@ -9304,7 +9320,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="4">
         <v>5436204</v>
       </c>
@@ -9317,8 +9333,9 @@
       <c r="D49" s="4" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E49" s="20"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="4">
         <v>3506004</v>
       </c>
@@ -9331,8 +9348,9 @@
       <c r="D50" s="4" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E50" s="20"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="4">
         <v>6757304</v>
       </c>
@@ -9345,8 +9363,9 @@
       <c r="D51" s="4" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E51" s="20"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="4">
         <v>6390804</v>
       </c>
@@ -9359,14 +9378,15 @@
       <c r="D52" s="4" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E52" s="20"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="12"/>
       <c r="B56" s="6" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="17" t="s">
         <v>173</v>
       </c>
@@ -9374,7 +9394,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="18" t="s">
         <v>262</v>
       </c>
@@ -9382,13 +9402,13 @@
         <v>263</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="20"/>
       <c r="B59" s="6" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="14" t="s">
         <v>233</v>
       </c>
@@ -9396,7 +9416,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="15" t="s">
         <v>266</v>
       </c>
@@ -9404,7 +9424,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="16" t="s">
         <v>267</v>
       </c>
@@ -9429,7 +9449,8 @@
     <col min="3" max="3" width="18.8203125" style="4" customWidth="1"/>
     <col min="4" max="4" width="6.703125" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.29296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.05859375" style="4"/>
+    <col min="6" max="6" width="13.703125" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="9.05859375" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -9451,7 +9472,7 @@
         <v>90</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9484,8 +9505,8 @@
       <c r="D5" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>233</v>
+      <c r="E5" s="6" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9501,8 +9522,8 @@
       <c r="D6" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>233</v>
+      <c r="E6" s="6" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9628,6 +9649,9 @@
       <c r="A15" s="4" t="s">
         <v>108</v>
       </c>
+      <c r="E15" s="4" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4">
@@ -9642,8 +9666,11 @@
       <c r="D16" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E16" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="4">
         <v>1031619</v>
       </c>
@@ -9656,8 +9683,11 @@
       <c r="D17" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E17" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="4">
         <v>1037608</v>
       </c>
@@ -9670,8 +9700,11 @@
       <c r="D18" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E18" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="4">
         <v>1035515</v>
       </c>
@@ -9684,8 +9717,11 @@
       <c r="D19" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E19" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="4">
         <v>1030772</v>
       </c>
@@ -9698,8 +9734,11 @@
       <c r="D20" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E20" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4">
         <v>1026742</v>
       </c>
@@ -9712,8 +9751,11 @@
       <c r="D21" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E21" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="4">
         <v>1038924</v>
       </c>
@@ -9726,8 +9768,11 @@
       <c r="D22" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E22" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="4">
         <v>1029508</v>
       </c>
@@ -9740,8 +9785,11 @@
       <c r="D23" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E23" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="4">
         <v>1028849</v>
       </c>
@@ -9754,24 +9802,33 @@
       <c r="D24" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E24" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E27" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>303</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E28" s="4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4">
         <v>1027008</v>
       </c>
@@ -9784,8 +9841,11 @@
       <c r="D29" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E29" s="4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4">
         <v>1026200</v>
       </c>
@@ -9798,8 +9858,11 @@
       <c r="D30" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E30" s="4">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4">
         <v>1025833</v>
       </c>
@@ -9812,8 +9875,11 @@
       <c r="D31" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E31" s="4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4">
         <v>1036053</v>
       </c>
@@ -9826,8 +9892,11 @@
       <c r="D32" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E32" s="4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="4">
         <v>1029029</v>
       </c>
@@ -9840,8 +9909,11 @@
       <c r="D33" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E33" s="4">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="4">
         <v>1028278</v>
       </c>
@@ -9854,8 +9926,11 @@
       <c r="D34" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E34" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="4">
         <v>1025603</v>
       </c>
@@ -9868,8 +9943,11 @@
       <c r="D35" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="4">
         <v>1028053</v>
       </c>
@@ -9882,8 +9960,11 @@
       <c r="D36" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E36" s="4">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4">
         <v>1027036</v>
       </c>
@@ -9896,8 +9977,11 @@
       <c r="D37" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E37" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="4">
         <v>1032361</v>
       </c>
@@ -9909,6 +9993,9 @@
       </c>
       <c r="D38" s="4" t="s">
         <v>39</v>
+      </c>
+      <c r="E38" s="4">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -10155,7 +10242,7 @@
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.5">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1633" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA31D332-0949-494F-84E5-91158F4B66FD}"/>
+  <xr:revisionPtr revIDLastSave="1666" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFE28220-83F5-47F7-B96D-980A73522A79}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -1207,6 +1207,7 @@
     <author>tc={376EB8CC-624A-4905-943C-003667EB4EEA}</author>
     <author>tc={DC46CFF3-F130-4C35-ADEF-5A1F821781A9}</author>
     <author>tc={B7A43FBB-5038-4FC3-8FAD-07EE5143A1F8}</author>
+    <author>tc={F5563291-8843-4D02-B160-A8886F3E2F55}</author>
     <author>tc={63C17029-8F90-4253-9CA7-E994CFD5D5A2}</author>
     <author>tc={AA276D36-BF21-4BF1-B4EE-CFB1644CC25A}</author>
     <author>tc={E15DDDED-B2BA-4607-867F-BB836742B4CF}</author>
@@ -1245,7 +1246,15 @@
     Fili tou konstantinou</t>
       </text>
     </comment>
-    <comment ref="C15" authorId="3" shapeId="0" xr:uid="{63C17029-8F90-4253-9CA7-E994CFD5D5A2}">
+    <comment ref="E13" authorId="3" shapeId="0" xr:uid="{F5563291-8843-4D02-B160-A8886F3E2F55}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Sleeping</t>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="4" shapeId="0" xr:uid="{63C17029-8F90-4253-9CA7-E994CFD5D5A2}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1253,7 +1262,7 @@
     Quiet but tries</t>
       </text>
     </comment>
-    <comment ref="C16" authorId="4" shapeId="0" xr:uid="{AA276D36-BF21-4BF1-B4EE-CFB1644CC25A}">
+    <comment ref="C16" authorId="5" shapeId="0" xr:uid="{AA276D36-BF21-4BF1-B4EE-CFB1644CC25A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1261,7 +1270,7 @@
     Blond, quiet</t>
       </text>
     </comment>
-    <comment ref="C23" authorId="5" shapeId="0" xr:uid="{E15DDDED-B2BA-4607-867F-BB836742B4CF}">
+    <comment ref="C23" authorId="6" shapeId="0" xr:uid="{E15DDDED-B2BA-4607-867F-BB836742B4CF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1269,7 +1278,7 @@
     Good student</t>
       </text>
     </comment>
-    <comment ref="C33" authorId="6" shapeId="0" xr:uid="{959932C7-E7CF-4613-A506-DF1AB6866DD6}">
+    <comment ref="C33" authorId="7" shapeId="0" xr:uid="{959932C7-E7CF-4613-A506-DF1AB6866DD6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1279,7 +1288,7 @@
     Ligo prixtissa, alla kali.</t>
       </text>
     </comment>
-    <comment ref="C34" authorId="7" shapeId="0" xr:uid="{A44E3110-99FE-4968-95C4-FBBC90EA44AB}">
+    <comment ref="C34" authorId="8" shapeId="0" xr:uid="{A44E3110-99FE-4968-95C4-FBBC90EA44AB}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1291,7 +1300,7 @@
     Keep an eye on him.</t>
       </text>
     </comment>
-    <comment ref="C35" authorId="8" shapeId="0" xr:uid="{2FB97B2F-685A-47AD-B451-26CE099B5CDE}">
+    <comment ref="C35" authorId="9" shapeId="0" xr:uid="{2FB97B2F-685A-47AD-B451-26CE099B5CDE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1299,7 +1308,7 @@
     Fenete filotimos, with some knowledge</t>
       </text>
     </comment>
-    <comment ref="C38" authorId="9" shapeId="0" xr:uid="{49700AAE-FBF5-4AF6-8413-5CA5A784A6FE}">
+    <comment ref="C38" authorId="10" shapeId="0" xr:uid="{49700AAE-FBF5-4AF6-8413-5CA5A784A6FE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1307,7 +1316,7 @@
     Kori tis Lelias</t>
       </text>
     </comment>
-    <comment ref="C42" authorId="10" shapeId="0" xr:uid="{C1108176-F43A-484D-8C9A-1ABAB3DE80B2}">
+    <comment ref="C42" authorId="11" shapeId="0" xr:uid="{C1108176-F43A-484D-8C9A-1ABAB3DE80B2}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1316,7 +1325,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="C43" authorId="11" shapeId="0" xr:uid="{F444680E-9CC4-4A89-898A-5ABDCDB06F58}">
+    <comment ref="C43" authorId="12" shapeId="0" xr:uid="{F444680E-9CC4-4A89-898A-5ABDCDB06F58}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1329,7 +1338,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="378">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2445,13 +2454,31 @@
   </si>
   <si>
     <t>A5.2 Μ3 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου - use A5.2 Μ2 και Μ3 - Ενιαίο Δισέλιδο Φύλλο Εργασίας</t>
+  </si>
+  <si>
+    <t>put hw. 1-11 A5M5</t>
+  </si>
+  <si>
+    <t>hw. 1-12 A5M2</t>
+  </si>
+  <si>
+    <t>kahoot 20-10-26</t>
+  </si>
+  <si>
+    <t>A5.2 Μ2 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου - give A5.2 Μ2 - ΦΕ Εμπέδωσης</t>
+  </si>
+  <si>
+    <t>A5.2 Μ3 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου - give A5.2 Μ3 -Φύλλο Εργασίας - Επισύναψη</t>
+  </si>
+  <si>
+    <t>REVISION - Επανάληψη A5 Δίκτυα και Ασφάλεια</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2512,6 +2539,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="14">
@@ -3525,6 +3558,9 @@
   <threadedComment ref="C12" dT="2026-09-24T08:32:16.02" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B7A43FBB-5038-4FC3-8FAD-07EE5143A1F8}">
     <text>Fili tou konstantinou</text>
   </threadedComment>
+  <threadedComment ref="E13" dT="2026-10-20T14:51:00.89" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{F5563291-8843-4D02-B160-A8886F3E2F55}">
+    <text>Sleeping</text>
+  </threadedComment>
   <threadedComment ref="C15" dT="2026-09-24T08:33:03.46" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{63C17029-8F90-4253-9CA7-E994CFD5D5A2}">
     <text>Quiet but tries</text>
   </threadedComment>
@@ -3804,13 +3840,13 @@
         <v>360</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="Y4" s="39" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="5" spans="1:60" ht="43" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A5" s="30" t="s">
         <v>3</v>
       </c>
@@ -3850,11 +3886,11 @@
       <c r="M5" s="23" t="s">
         <v>344</v>
       </c>
-      <c r="N5" s="27" t="s">
-        <v>370</v>
+      <c r="N5" s="23" t="s">
+        <v>375</v>
       </c>
       <c r="O5" s="27" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="X5" s="39" t="s">
         <v>249</v>
@@ -4138,7 +4174,7 @@
       <c r="N13" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="O13" s="25" t="s">
+      <c r="O13" s="23" t="s">
         <v>324</v>
       </c>
       <c r="P13" s="25" t="s">
@@ -4204,11 +4240,11 @@
       <c r="M18" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="N18" s="27" t="s">
+      <c r="N18" s="23" t="s">
         <v>244</v>
       </c>
       <c r="O18" s="27" t="s">
-        <v>297</v>
+        <v>377</v>
       </c>
       <c r="P18" s="36" t="s">
         <v>249</v>
@@ -4260,11 +4296,11 @@
       <c r="M19" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="N19" s="27" t="s">
+      <c r="N19" s="23" t="s">
         <v>244</v>
       </c>
       <c r="O19" s="27" t="s">
-        <v>297</v>
+        <v>377</v>
       </c>
       <c r="P19" s="36" t="s">
         <v>249</v>
@@ -4316,7 +4352,7 @@
       <c r="M20" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="N20" s="27" t="s">
+      <c r="N20" s="23" t="s">
         <v>321</v>
       </c>
       <c r="O20" s="27" t="s">
@@ -7005,6 +7041,7 @@
     <col min="12" max="12" width="17.41015625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.3515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.5859375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.9375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7051,6 +7088,9 @@
       <c r="L3" t="s">
         <v>309</v>
       </c>
+      <c r="O3" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="4" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
@@ -7092,6 +7132,9 @@
       <c r="M4" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="O4" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
@@ -7133,6 +7176,9 @@
       <c r="M5" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="O5" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
@@ -7174,6 +7220,9 @@
       <c r="M6" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="O6" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
@@ -7215,6 +7264,9 @@
       <c r="M7" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="O7" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
@@ -7256,6 +7308,9 @@
       <c r="M8" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="O8" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
@@ -7297,6 +7352,9 @@
       <c r="M9" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="O9" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
@@ -7338,6 +7396,9 @@
       <c r="M10" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="O10" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
@@ -7377,6 +7438,9 @@
       <c r="M11" s="14" t="s">
         <v>233</v>
       </c>
+      <c r="O11" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
@@ -7418,6 +7482,9 @@
       <c r="M12" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="O12" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
@@ -7457,6 +7524,7 @@
         <v>233</v>
       </c>
       <c r="M13" s="20"/>
+      <c r="O13" s="20"/>
     </row>
     <row r="14" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
@@ -7498,6 +7566,9 @@
       <c r="M14" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="O14" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
@@ -7539,6 +7610,9 @@
       <c r="M15" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="O15" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
@@ -7580,8 +7654,11 @@
       <c r="M16" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O16" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="C17" t="s">
         <v>228</v>
       </c>
@@ -7615,8 +7692,11 @@
       <c r="M17" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O17" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
         <v>229</v>
       </c>
@@ -7653,13 +7733,16 @@
       <c r="M18" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.5">
+      <c r="O18" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -7681,8 +7764,11 @@
       <c r="N21" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O21" s="8" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>9693404</v>
       </c>
@@ -7725,8 +7811,11 @@
       <c r="N22" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O22" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>222222</v>
       </c>
@@ -7769,8 +7858,11 @@
       <c r="N23" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O23" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>9743804</v>
       </c>
@@ -7813,8 +7905,11 @@
       <c r="N24" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O24" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>111111</v>
       </c>
@@ -7851,8 +7946,11 @@
         <v>173</v>
       </c>
       <c r="N25" s="12"/>
-    </row>
-    <row r="26" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O25" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>9662304</v>
       </c>
@@ -7895,8 +7993,11 @@
       <c r="N26" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O26" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" t="s">
         <v>272</v>
       </c>
@@ -7928,8 +8029,11 @@
         <v>266</v>
       </c>
       <c r="N27" s="12"/>
-    </row>
-    <row r="28" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O27" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
         <v>272</v>
       </c>
@@ -7961,13 +8065,16 @@
         <v>173</v>
       </c>
       <c r="N28" s="12"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.5">
+      <c r="O28" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.5">
       <c r="L30" s="8" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -7975,7 +8082,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>3578804</v>
       </c>
@@ -8012,8 +8119,11 @@
       <c r="M32" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O32" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>9289704</v>
       </c>
@@ -8048,8 +8158,11 @@
       <c r="M33" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O33" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>9344404</v>
       </c>
@@ -8082,8 +8195,11 @@
       <c r="M34" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O34" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>6746404</v>
       </c>
@@ -8118,8 +8234,11 @@
       <c r="M35" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O35" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>9257604</v>
       </c>
@@ -8156,8 +8275,11 @@
       <c r="M36" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O36" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>9717204</v>
       </c>
@@ -8192,8 +8314,11 @@
       <c r="M37" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O37" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>2298204</v>
       </c>
@@ -8226,8 +8351,11 @@
       <c r="M38" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O38" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>5784804</v>
       </c>
@@ -8264,8 +8392,11 @@
       <c r="M39" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O39" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>9321704</v>
       </c>
@@ -8300,8 +8431,11 @@
       <c r="M40" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O40" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>9720304</v>
       </c>
@@ -8338,8 +8472,11 @@
       <c r="M41" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O41" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>9317404</v>
       </c>
@@ -8374,8 +8511,11 @@
       <c r="M42" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O42" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>8333604</v>
       </c>
@@ -8410,6 +8550,9 @@
         <v>173</v>
       </c>
       <c r="M43" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="O43" s="14" t="s">
         <v>233</v>
       </c>
     </row>
@@ -8917,8 +9060,8 @@
       <c r="D18" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="19" t="s">
-        <v>233</v>
+      <c r="E18" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -10017,7 +10160,7 @@
     <col min="5" max="5" width="14.3515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -10031,12 +10174,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="E3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A4">
         <v>4206804</v>
       </c>
@@ -10049,8 +10195,11 @@
       <c r="D4" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A5">
         <v>9307104</v>
       </c>
@@ -10063,8 +10212,11 @@
       <c r="D5" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A6">
         <v>2173704</v>
       </c>
@@ -10077,8 +10229,11 @@
       <c r="D6" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A7">
         <v>9257304</v>
       </c>
@@ -10091,8 +10246,11 @@
       <c r="D7" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A8">
         <v>2915404</v>
       </c>
@@ -10105,8 +10263,11 @@
       <c r="D8" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="E8">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A9">
         <v>2836604</v>
       </c>
@@ -10119,8 +10280,11 @@
       <c r="D9" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="E9">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A10">
         <v>1274904</v>
       </c>
@@ -10133,8 +10297,11 @@
       <c r="D10" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A11">
         <v>3863304</v>
       </c>
@@ -10147,8 +10314,11 @@
       <c r="D11" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A12">
         <v>3403504</v>
       </c>
@@ -10161,8 +10331,11 @@
       <c r="D12" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A13">
         <v>4721304</v>
       </c>
@@ -10175,8 +10348,11 @@
       <c r="D13" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A14">
         <v>3924304</v>
       </c>
@@ -10189,8 +10365,11 @@
       <c r="D14" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A15">
         <v>4041704</v>
       </c>
@@ -10203,8 +10382,11 @@
       <c r="D15" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A16">
         <v>9280704</v>
       </c>
@@ -10216,6 +10398,9 @@
       </c>
       <c r="D16" t="s">
         <v>208</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.5">
@@ -10225,6 +10410,9 @@
       <c r="D17" t="s">
         <v>231</v>
       </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B18" t="s">
@@ -10235,6 +10423,9 @@
       </c>
       <c r="D18" t="s">
         <v>208</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.5">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1666" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFE28220-83F5-47F7-B96D-980A73522A79}"/>
+  <xr:revisionPtr revIDLastSave="1668" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6179019C-1A3B-4CF6-BDEB-43C061997408}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -1338,7 +1338,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="378">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2478,7 +2478,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2539,12 +2539,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="14">
@@ -4483,11 +4477,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4496,6 +4485,11 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8890,7 +8884,9 @@
       <c r="D5" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E5" s="20"/>
+      <c r="E5" s="6" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4">
@@ -8986,7 +8982,9 @@
       <c r="D11" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E11" s="20"/>
+      <c r="E11" s="6" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1668" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6179019C-1A3B-4CF6-BDEB-43C061997408}"/>
+  <xr:revisionPtr revIDLastSave="1671" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95644075-F484-4776-B224-C9E8D98C66F7}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -1338,7 +1338,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="378">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -3833,7 +3833,7 @@
       <c r="N4" s="23" t="s">
         <v>360</v>
       </c>
-      <c r="O4" s="27" t="s">
+      <c r="O4" s="23" t="s">
         <v>375</v>
       </c>
       <c r="Y4" s="39" t="s">
@@ -4065,7 +4065,7 @@
       <c r="N11" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="O11" s="25" t="s">
+      <c r="O11" s="23" t="s">
         <v>324</v>
       </c>
       <c r="P11" s="25" t="s">
@@ -4477,6 +4477,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4485,11 +4490,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8950,7 +8950,9 @@
       <c r="D9" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E9" s="20"/>
+      <c r="E9" s="6" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1671" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95644075-F484-4776-B224-C9E8D98C66F7}"/>
+  <xr:revisionPtr revIDLastSave="1689" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43699234-F7EC-4E93-84EF-9ABE861AD094}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -1338,7 +1338,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="381">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2472,6 +2472,15 @@
   </si>
   <si>
     <t>REVISION - Επανάληψη A5 Δίκτυα και Ασφάλεια</t>
+  </si>
+  <si>
+    <t>send attachment</t>
+  </si>
+  <si>
+    <t>powerpoint - create star</t>
+  </si>
+  <si>
+    <t>CREATE EMAIL WITH HOTSPOT - Α5.2 Μ1 - Εναλλακτικό Φύλλο Εργασίας - Ηλεκτρονικό Ταχυδρομείο - only 3 boys were in class</t>
   </si>
 </sst>
 </file>
@@ -3883,7 +3892,7 @@
       <c r="N5" s="23" t="s">
         <v>375</v>
       </c>
-      <c r="O5" s="27" t="s">
+      <c r="O5" s="23" t="s">
         <v>376</v>
       </c>
       <c r="X5" s="39" t="s">
@@ -3930,8 +3939,8 @@
       <c r="M6" s="23" t="s">
         <v>345</v>
       </c>
-      <c r="N6" s="27" t="s">
-        <v>360</v>
+      <c r="N6" s="23" t="s">
+        <v>380</v>
       </c>
       <c r="O6" s="27" t="s">
         <v>370</v>
@@ -4413,6 +4422,9 @@
       <c r="M22" s="23" t="s">
         <v>346</v>
       </c>
+      <c r="N22" s="23" t="s">
+        <v>379</v>
+      </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B23" s="32"/>
@@ -4477,11 +4489,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4490,6 +4497,11 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8821,7 +8833,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FEE7927-B2CB-4F8C-B929-249864A39417}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.3515625" style="4" bestFit="1" customWidth="1"/>
@@ -8829,10 +8841,11 @@
     <col min="3" max="3" width="22.5859375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.17578125" style="4" customWidth="1"/>
     <col min="5" max="5" width="10.234375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.05859375" style="4"/>
+    <col min="6" max="6" width="15.41015625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.05859375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="7" t="s">
         <v>57</v>
       </c>
@@ -8846,15 +8859,18 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>121</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F3" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4">
         <v>9285104</v>
       </c>
@@ -8871,7 +8887,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4">
         <v>8324104</v>
       </c>
@@ -8888,7 +8904,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4">
         <v>6811804</v>
       </c>
@@ -8903,7 +8919,7 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="4">
         <v>5436904</v>
       </c>
@@ -8920,7 +8936,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4">
         <v>7025704</v>
       </c>
@@ -8937,7 +8953,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="4">
         <v>8435804</v>
       </c>
@@ -8954,7 +8970,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4">
         <v>5069104</v>
       </c>
@@ -8971,7 +8987,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4">
         <v>5222304</v>
       </c>
@@ -8988,7 +9004,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4">
         <v>1981204</v>
       </c>
@@ -9005,7 +9021,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="4">
         <v>3766704</v>
       </c>
@@ -9022,7 +9038,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4" t="s">
         <v>72</v>
       </c>
@@ -9030,7 +9046,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="4">
         <v>5551204</v>
       </c>
@@ -9046,8 +9062,11 @@
       <c r="E17" s="6" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F17" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="4">
         <v>2056004</v>
       </c>
@@ -9063,8 +9082,11 @@
       <c r="E18" s="6" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F18" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="4">
         <v>3318504</v>
       </c>
@@ -9080,8 +9102,11 @@
       <c r="E19" s="6" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F19" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="4">
         <v>4926804</v>
       </c>
@@ -9097,8 +9122,11 @@
       <c r="E20" s="6" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F20" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4">
         <v>7568204</v>
       </c>
@@ -9114,8 +9142,11 @@
       <c r="E21" s="6" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F21" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="4">
         <v>5111404</v>
       </c>
@@ -9131,8 +9162,11 @@
       <c r="E22" s="6" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F22" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="4">
         <v>4332504</v>
       </c>
@@ -9148,8 +9182,11 @@
       <c r="E23" s="6" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F23" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="4">
         <v>4332504</v>
       </c>
@@ -9166,7 +9203,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4">
         <v>4424904</v>
       </c>
@@ -9183,7 +9220,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4">
         <v>3257704</v>
       </c>
@@ -9199,8 +9236,11 @@
       <c r="E26" s="6" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F26" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4">
         <v>4934404</v>
       </c>
@@ -9217,12 +9257,12 @@
         <v>233</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4">
         <v>9189004</v>
       </c>
@@ -9236,7 +9276,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4">
         <v>5682904</v>
       </c>
@@ -9250,7 +9290,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4">
         <v>9217204</v>
       </c>
@@ -9291,6 +9331,9 @@
       <c r="D34" s="4" t="s">
         <v>143</v>
       </c>
+      <c r="E34" s="6" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="4">
@@ -9319,6 +9362,9 @@
       <c r="D36" s="4" t="s">
         <v>143</v>
       </c>
+      <c r="E36" s="6" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4">
@@ -9346,6 +9392,9 @@
       </c>
       <c r="D38" s="4" t="s">
         <v>143</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1689" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43699234-F7EC-4E93-84EF-9ABE861AD094}"/>
+  <xr:revisionPtr revIDLastSave="1690" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3101BF5D-F319-4CCD-8F8A-23B711E42EE5}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -4246,7 +4246,7 @@
       <c r="N18" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="O18" s="27" t="s">
+      <c r="O18" s="23" t="s">
         <v>377</v>
       </c>
       <c r="P18" s="36" t="s">
@@ -4489,6 +4489,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4497,11 +4502,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1690" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3101BF5D-F319-4CCD-8F8A-23B711E42EE5}"/>
+  <xr:revisionPtr revIDLastSave="1711" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D17FFA99-9734-4131-9A42-E53403D817C9}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -1338,7 +1338,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="381">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2487,7 +2487,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2547,6 +2547,15 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2684,7 +2693,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2801,6 +2810,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4302,7 +4314,7 @@
       <c r="N19" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="O19" s="27" t="s">
+      <c r="O19" s="23" t="s">
         <v>377</v>
       </c>
       <c r="P19" s="36" t="s">
@@ -4358,10 +4370,10 @@
       <c r="N20" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="O20" s="27" t="s">
+      <c r="O20" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="P20" s="27" t="s">
+      <c r="P20" s="36" t="s">
         <v>297</v>
       </c>
       <c r="Q20" s="36" t="s">
@@ -4489,11 +4501,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4502,6 +4509,11 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7141,6 +7153,9 @@
       <c r="O4" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="P4" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
@@ -7185,6 +7200,9 @@
       <c r="O5" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="P5" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
@@ -7229,6 +7247,9 @@
       <c r="O6" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="P6" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
@@ -7273,6 +7294,9 @@
       <c r="O7" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="P7" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
@@ -7317,6 +7341,9 @@
       <c r="O8" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="P8" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
@@ -7361,6 +7388,9 @@
       <c r="O9" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="P9" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
@@ -7405,6 +7435,9 @@
       <c r="O10" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="P10" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
@@ -7447,6 +7480,9 @@
       <c r="O11" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="P11" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
@@ -7491,6 +7527,9 @@
       <c r="O12" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="P12" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
@@ -7530,7 +7569,12 @@
         <v>233</v>
       </c>
       <c r="M13" s="20"/>
-      <c r="O13" s="20"/>
+      <c r="O13" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
@@ -7575,6 +7619,9 @@
       <c r="O14" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="P14" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
@@ -7619,6 +7666,9 @@
       <c r="O15" s="8" t="s">
         <v>173</v>
       </c>
+      <c r="P15" s="8" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
@@ -7663,8 +7713,11 @@
       <c r="O16" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P16" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="C17" t="s">
         <v>228</v>
       </c>
@@ -7701,8 +7754,11 @@
       <c r="O17" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P17" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
         <v>229</v>
       </c>
@@ -7742,13 +7798,16 @@
       <c r="O18" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.5">
+      <c r="P18" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -7774,7 +7833,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>9693404</v>
       </c>
@@ -7820,8 +7879,11 @@
       <c r="O22" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P22" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>222222</v>
       </c>
@@ -7867,8 +7929,11 @@
       <c r="O23" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P23" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>9743804</v>
       </c>
@@ -7914,8 +7979,11 @@
       <c r="O24" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P24" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>111111</v>
       </c>
@@ -7955,8 +8023,11 @@
       <c r="O25" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P25" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>9662304</v>
       </c>
@@ -8002,8 +8073,11 @@
       <c r="O26" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P26" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" t="s">
         <v>272</v>
       </c>
@@ -8038,8 +8112,11 @@
       <c r="O27" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P27" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
         <v>272</v>
       </c>
@@ -8074,13 +8151,16 @@
       <c r="O28" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.5">
+      <c r="P28" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.5">
       <c r="L30" s="8" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -8088,7 +8168,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>3578804</v>
       </c>
@@ -8125,11 +8205,14 @@
       <c r="M32" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="O32" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="O32" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="P32" s="44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>9289704</v>
       </c>
@@ -8167,8 +8250,11 @@
       <c r="O33" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P33" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>9344404</v>
       </c>
@@ -8204,8 +8290,11 @@
       <c r="O34" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P34" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>6746404</v>
       </c>
@@ -8243,8 +8332,11 @@
       <c r="O35" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P35" s="44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>9257604</v>
       </c>
@@ -8284,8 +8376,11 @@
       <c r="O36" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P36" s="44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>9717204</v>
       </c>
@@ -8323,8 +8418,11 @@
       <c r="O37" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P37" s="44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>2298204</v>
       </c>
@@ -8360,8 +8458,11 @@
       <c r="O38" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P38" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>5784804</v>
       </c>
@@ -8401,8 +8502,11 @@
       <c r="O39" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P39" s="44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>9321704</v>
       </c>
@@ -8440,8 +8544,11 @@
       <c r="O40" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P40" s="44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>9720304</v>
       </c>
@@ -8481,8 +8588,11 @@
       <c r="O41" s="8" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P41" s="44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>9317404</v>
       </c>
@@ -8520,8 +8630,11 @@
       <c r="O42" s="14" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="P42" s="44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>8333604</v>
       </c>
@@ -8560,6 +8673,9 @@
       </c>
       <c r="O43" s="14" t="s">
         <v>233</v>
+      </c>
+      <c r="P43" s="44" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1711" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D17FFA99-9734-4131-9A42-E53403D817C9}"/>
+  <xr:revisionPtr revIDLastSave="1717" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36E5D0C3-8C58-49B8-8BCD-7019D9A3CB26}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -1338,7 +1338,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="380">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2448,9 +2448,6 @@
   </si>
   <si>
     <t>B41M9 - Εισαγωγή στις Συναρτήσεις - ξανα σχετική και απόλυτη αναφορά</t>
-  </si>
-  <si>
-    <t>A5.2 Μ2 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου - give A5.2 Μ2 και Μ3 - Ενιαίο Δισέλιδο Φύλλο Εργασίας</t>
   </si>
   <si>
     <t>A5.2 Μ3 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου - use A5.2 Μ2 και Μ3 - Ενιαίο Δισέλιδο Φύλλο Εργασίας</t>
@@ -2693,7 +2690,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2800,11 +2797,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2812,8 +2806,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3650,58 +3650,58 @@
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="28"/>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="40" t="s">
+      <c r="C1" s="44"/>
+      <c r="D1" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="40" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="43" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="41"/>
-      <c r="H1" s="40" t="s">
+      <c r="G1" s="44"/>
+      <c r="H1" s="43" t="s">
         <v>241</v>
       </c>
-      <c r="I1" s="41"/>
-      <c r="J1" s="40" t="s">
+      <c r="I1" s="44"/>
+      <c r="J1" s="43" t="s">
         <v>245</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="40" t="s">
+      <c r="K1" s="44"/>
+      <c r="L1" s="43" t="s">
         <v>248</v>
       </c>
-      <c r="M1" s="41"/>
-      <c r="N1" s="40" t="s">
+      <c r="M1" s="44"/>
+      <c r="N1" s="43" t="s">
         <v>347</v>
       </c>
-      <c r="O1" s="41"/>
-      <c r="P1" s="40" t="s">
+      <c r="O1" s="44"/>
+      <c r="P1" s="43" t="s">
         <v>348</v>
       </c>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="40" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="43" t="s">
         <v>350</v>
       </c>
-      <c r="S1" s="41"/>
-      <c r="T1" s="40" t="s">
+      <c r="S1" s="44"/>
+      <c r="T1" s="43" t="s">
         <v>351</v>
       </c>
-      <c r="U1" s="41"/>
-      <c r="V1" s="40" t="s">
+      <c r="U1" s="44"/>
+      <c r="V1" s="43" t="s">
         <v>352</v>
       </c>
-      <c r="W1" s="41"/>
-      <c r="X1" s="40" t="s">
+      <c r="W1" s="44"/>
+      <c r="X1" s="43" t="s">
         <v>353</v>
       </c>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="40" t="s">
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="43" t="s">
         <v>354</v>
       </c>
-      <c r="AA1" s="41"/>
+      <c r="AA1" s="44"/>
       <c r="AB1" s="29"/>
       <c r="AC1" s="29"/>
       <c r="AD1" s="29"/>
@@ -3855,7 +3855,7 @@
         <v>360</v>
       </c>
       <c r="O4" s="23" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Y4" s="39" t="s">
         <v>249</v>
@@ -3902,10 +3902,10 @@
         <v>344</v>
       </c>
       <c r="N5" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="O5" s="23" t="s">
         <v>375</v>
-      </c>
-      <c r="O5" s="23" t="s">
-        <v>376</v>
       </c>
       <c r="X5" s="39" t="s">
         <v>249</v>
@@ -3952,13 +3952,13 @@
         <v>345</v>
       </c>
       <c r="N6" s="23" t="s">
-        <v>380</v>
-      </c>
-      <c r="O6" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="O6" s="45" t="s">
+        <v>374</v>
+      </c>
+      <c r="P6" s="25" t="s">
         <v>370</v>
-      </c>
-      <c r="P6" s="25" t="s">
-        <v>371</v>
       </c>
       <c r="Q6" s="25" t="s">
         <v>355</v>
@@ -3979,7 +3979,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="7" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:60" ht="43" x14ac:dyDescent="0.5">
       <c r="A7" s="30" t="s">
         <v>5</v>
       </c>
@@ -4020,10 +4020,10 @@
         <v>343</v>
       </c>
       <c r="N7" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="O7" s="27" t="s">
-        <v>360</v>
+        <v>345</v>
+      </c>
+      <c r="O7" s="45" t="s">
+        <v>374</v>
       </c>
       <c r="X7" s="39" t="s">
         <v>249</v>
@@ -4139,7 +4139,7 @@
       <c r="N12" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="O12" s="25" t="s">
+      <c r="O12" s="45" t="s">
         <v>369</v>
       </c>
       <c r="V12" s="39" t="s">
@@ -4259,7 +4259,7 @@
         <v>244</v>
       </c>
       <c r="O18" s="23" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P18" s="36" t="s">
         <v>249</v>
@@ -4315,7 +4315,7 @@
         <v>244</v>
       </c>
       <c r="O19" s="23" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P19" s="36" t="s">
         <v>249</v>
@@ -4435,7 +4435,7 @@
         <v>346</v>
       </c>
       <c r="N22" s="23" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.5">
@@ -4501,6 +4501,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4509,11 +4514,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4560,26 +4560,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="41" t="s">
         <v>285</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42" t="s">
+      <c r="G2" s="41"/>
+      <c r="H2" s="41" t="s">
         <v>286</v>
       </c>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42" t="s">
+      <c r="I2" s="41"/>
+      <c r="J2" s="41" t="s">
         <v>296</v>
       </c>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42" t="s">
+      <c r="K2" s="41"/>
+      <c r="L2" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42" t="s">
+      <c r="M2" s="41"/>
+      <c r="N2" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="O2" s="42"/>
+      <c r="O2" s="41"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -6012,26 +6012,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="41" t="s">
         <v>285</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42" t="s">
+      <c r="G2" s="41"/>
+      <c r="H2" s="41" t="s">
         <v>286</v>
       </c>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42" t="s">
+      <c r="I2" s="41"/>
+      <c r="J2" s="41" t="s">
         <v>298</v>
       </c>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42" t="s">
+      <c r="K2" s="41"/>
+      <c r="L2" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42" t="s">
+      <c r="M2" s="41"/>
+      <c r="N2" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="O2" s="42"/>
+      <c r="O2" s="41"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -7075,26 +7075,26 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="G1" s="41" t="s">
         <v>285</v>
       </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42" t="s">
+      <c r="H1" s="41"/>
+      <c r="I1" s="41" t="s">
         <v>286</v>
       </c>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42" t="s">
+      <c r="J1" s="41"/>
+      <c r="K1" s="41" t="s">
         <v>298</v>
       </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="43" t="s">
+      <c r="L1" s="41"/>
+      <c r="M1" s="42" t="s">
         <v>328</v>
       </c>
-      <c r="N1" s="43"/>
-      <c r="O1" s="42" t="s">
+      <c r="N1" s="42"/>
+      <c r="O1" s="41" t="s">
         <v>367</v>
       </c>
-      <c r="P1" s="42"/>
+      <c r="P1" s="41"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
@@ -7107,7 +7107,7 @@
         <v>309</v>
       </c>
       <c r="O3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7830,7 +7830,7 @@
         <v>340</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8205,10 +8205,10 @@
       <c r="M32" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="O32" s="44" t="s">
-        <v>173</v>
-      </c>
-      <c r="P32" s="44" t="s">
+      <c r="O32" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="P32" s="40" t="s">
         <v>173</v>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       <c r="O35" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="P35" s="44" t="s">
+      <c r="P35" s="40" t="s">
         <v>173</v>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       <c r="O36" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="P36" s="44" t="s">
+      <c r="P36" s="40" t="s">
         <v>173</v>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       <c r="O37" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="P37" s="44" t="s">
+      <c r="P37" s="40" t="s">
         <v>173</v>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       <c r="O39" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="P39" s="44" t="s">
+      <c r="P39" s="40" t="s">
         <v>173</v>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
       <c r="O40" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="P40" s="44" t="s">
+      <c r="P40" s="40" t="s">
         <v>173</v>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       <c r="O41" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="P41" s="44" t="s">
+      <c r="P41" s="40" t="s">
         <v>173</v>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       <c r="O42" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="P42" s="44" t="s">
+      <c r="P42" s="40" t="s">
         <v>173</v>
       </c>
     </row>
@@ -8674,7 +8674,7 @@
       <c r="O43" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="P43" s="44" t="s">
+      <c r="P43" s="40" t="s">
         <v>173</v>
       </c>
     </row>
@@ -8824,18 +8824,18 @@
       <c r="D1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="41" t="s">
         <v>285</v>
       </c>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42" t="s">
+      <c r="F1" s="41"/>
+      <c r="G1" s="41" t="s">
         <v>286</v>
       </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42" t="s">
+      <c r="H1" s="41"/>
+      <c r="I1" s="41" t="s">
         <v>298</v>
       </c>
-      <c r="J1" s="42"/>
+      <c r="J1" s="41"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
@@ -8983,7 +8983,7 @@
         <v>335</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -10344,7 +10344,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.5">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1717" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36E5D0C3-8C58-49B8-8BCD-7019D9A3CB26}"/>
+  <xr:revisionPtr revIDLastSave="1718" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C299AF1-F0B2-49E4-98A0-CFD7BCA66B9A}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -1338,7 +1338,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="380">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2800,11 +2800,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2812,8 +2809,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3650,58 +3650,58 @@
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="28"/>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="43" t="s">
+      <c r="C1" s="43"/>
+      <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="43" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="44"/>
-      <c r="H1" s="43" t="s">
+      <c r="G1" s="43"/>
+      <c r="H1" s="42" t="s">
         <v>241</v>
       </c>
-      <c r="I1" s="44"/>
-      <c r="J1" s="43" t="s">
+      <c r="I1" s="43"/>
+      <c r="J1" s="42" t="s">
         <v>245</v>
       </c>
-      <c r="K1" s="44"/>
-      <c r="L1" s="43" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="42" t="s">
         <v>248</v>
       </c>
-      <c r="M1" s="44"/>
-      <c r="N1" s="43" t="s">
+      <c r="M1" s="43"/>
+      <c r="N1" s="42" t="s">
         <v>347</v>
       </c>
-      <c r="O1" s="44"/>
-      <c r="P1" s="43" t="s">
+      <c r="O1" s="43"/>
+      <c r="P1" s="42" t="s">
         <v>348</v>
       </c>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="43" t="s">
+      <c r="Q1" s="43"/>
+      <c r="R1" s="42" t="s">
         <v>350</v>
       </c>
-      <c r="S1" s="44"/>
-      <c r="T1" s="43" t="s">
+      <c r="S1" s="43"/>
+      <c r="T1" s="42" t="s">
         <v>351</v>
       </c>
-      <c r="U1" s="44"/>
-      <c r="V1" s="43" t="s">
+      <c r="U1" s="43"/>
+      <c r="V1" s="42" t="s">
         <v>352</v>
       </c>
-      <c r="W1" s="44"/>
-      <c r="X1" s="43" t="s">
+      <c r="W1" s="43"/>
+      <c r="X1" s="42" t="s">
         <v>353</v>
       </c>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="43" t="s">
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="42" t="s">
         <v>354</v>
       </c>
-      <c r="AA1" s="44"/>
+      <c r="AA1" s="43"/>
       <c r="AB1" s="29"/>
       <c r="AC1" s="29"/>
       <c r="AD1" s="29"/>
@@ -3954,7 +3954,7 @@
       <c r="N6" s="23" t="s">
         <v>379</v>
       </c>
-      <c r="O6" s="45" t="s">
+      <c r="O6" s="41" t="s">
         <v>374</v>
       </c>
       <c r="P6" s="25" t="s">
@@ -4022,7 +4022,7 @@
       <c r="N7" s="23" t="s">
         <v>345</v>
       </c>
-      <c r="O7" s="45" t="s">
+      <c r="O7" s="41" t="s">
         <v>374</v>
       </c>
       <c r="X7" s="39" t="s">
@@ -4139,7 +4139,7 @@
       <c r="N12" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="O12" s="45" t="s">
+      <c r="O12" s="41" t="s">
         <v>369</v>
       </c>
       <c r="V12" s="39" t="s">
@@ -4501,11 +4501,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4514,6 +4509,11 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4560,26 +4560,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="44" t="s">
         <v>285</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41" t="s">
+      <c r="G2" s="44"/>
+      <c r="H2" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41" t="s">
+      <c r="I2" s="44"/>
+      <c r="J2" s="44" t="s">
         <v>296</v>
       </c>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41" t="s">
+      <c r="K2" s="44"/>
+      <c r="L2" s="44" t="s">
         <v>322</v>
       </c>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41" t="s">
+      <c r="M2" s="44"/>
+      <c r="N2" s="44" t="s">
         <v>367</v>
       </c>
-      <c r="O2" s="41"/>
+      <c r="O2" s="44"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -6012,26 +6012,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="44" t="s">
         <v>285</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41" t="s">
+      <c r="G2" s="44"/>
+      <c r="H2" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41" t="s">
+      <c r="I2" s="44"/>
+      <c r="J2" s="44" t="s">
         <v>298</v>
       </c>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41" t="s">
+      <c r="K2" s="44"/>
+      <c r="L2" s="44" t="s">
         <v>322</v>
       </c>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41" t="s">
+      <c r="M2" s="44"/>
+      <c r="N2" s="44" t="s">
         <v>367</v>
       </c>
-      <c r="O2" s="41"/>
+      <c r="O2" s="44"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -7075,26 +7075,26 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="G1" s="44" t="s">
         <v>285</v>
       </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41" t="s">
+      <c r="H1" s="44"/>
+      <c r="I1" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41" t="s">
+      <c r="J1" s="44"/>
+      <c r="K1" s="44" t="s">
         <v>298</v>
       </c>
-      <c r="L1" s="41"/>
-      <c r="M1" s="42" t="s">
+      <c r="L1" s="44"/>
+      <c r="M1" s="45" t="s">
         <v>328</v>
       </c>
-      <c r="N1" s="42"/>
-      <c r="O1" s="41" t="s">
+      <c r="N1" s="45"/>
+      <c r="O1" s="44" t="s">
         <v>367</v>
       </c>
-      <c r="P1" s="41"/>
+      <c r="P1" s="44"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
@@ -8824,18 +8824,18 @@
       <c r="D1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="E1" s="44" t="s">
         <v>285</v>
       </c>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41" t="s">
+      <c r="F1" s="44"/>
+      <c r="G1" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41" t="s">
+      <c r="H1" s="44"/>
+      <c r="I1" s="44" t="s">
         <v>298</v>
       </c>
-      <c r="J1" s="41"/>
+      <c r="J1" s="44"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
@@ -9671,7 +9671,9 @@
       <c r="D51" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E51" s="20"/>
+      <c r="E51" s="6" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="4">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1718" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C299AF1-F0B2-49E4-98A0-CFD7BCA66B9A}"/>
+  <xr:revisionPtr revIDLastSave="1732" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C794B012-5CC6-479E-B323-3024BF4D3A80}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -100,8 +100,6 @@
     <author>tc={98BD6B5F-37EB-41FA-B971-80255C43C024}</author>
     <author>tc={3FB9C602-3AA9-40D1-97B5-331230499AE8}</author>
     <author>tc={009D741D-5339-4620-BEF3-C76ECC0C19D0}</author>
-    <author>tc={86B9678A-C29A-446D-AACA-74A7C503B71B}</author>
-    <author>tc={720F20F5-2744-4E03-9112-5151AF4ED353}</author>
     <author>tc={7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}</author>
     <author>tc={8F4D57B3-2C90-4744-BFEF-99E499E55142}</author>
     <author>tc={37F71BFC-AE14-49EC-B2B2-49697A83F48F}</author>
@@ -327,23 +325,7 @@
     indefferent</t>
       </text>
     </comment>
-    <comment ref="C45" authorId="26" shapeId="0" xr:uid="{86B9678A-C29A-446D-AACA-74A7C503B71B}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Depy, sitisi, sinesthimatikes diskolies</t>
-      </text>
-    </comment>
-    <comment ref="E45" authorId="27" shapeId="0" xr:uid="{720F20F5-2744-4E03-9112-5151AF4ED353}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Indifferent, don't take book.</t>
-      </text>
-    </comment>
-    <comment ref="C46" authorId="28" shapeId="0" xr:uid="{7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}">
+    <comment ref="C45" authorId="26" shapeId="0" xr:uid="{7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -351,7 +333,7 @@
     Stiriksi, sitisi, menei me patera, oxi epaphi me mitera, o pateras fetos irthe, emenas me giagia kai pappou</t>
       </text>
     </comment>
-    <comment ref="C50" authorId="29" shapeId="0" xr:uid="{8F4D57B3-2C90-4744-BFEF-99E499E55142}">
+    <comment ref="C49" authorId="27" shapeId="0" xr:uid="{8F4D57B3-2C90-4744-BFEF-99E499E55142}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -359,7 +341,7 @@
     Dropalos, thelei enisxisi</t>
       </text>
     </comment>
-    <comment ref="C51" authorId="30" shapeId="0" xr:uid="{37F71BFC-AE14-49EC-B2B2-49697A83F48F}">
+    <comment ref="C50" authorId="28" shapeId="0" xr:uid="{37F71BFC-AE14-49EC-B2B2-49697A83F48F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -367,7 +349,7 @@
     Stiriksi, mathisiakes adinamies</t>
       </text>
     </comment>
-    <comment ref="C52" authorId="31" shapeId="0" xr:uid="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
+    <comment ref="C51" authorId="29" shapeId="0" xr:uid="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -760,7 +742,6 @@
     <author>tc={1BCE4285-4670-48B9-A6C0-A7ACB02EB42C}</author>
     <author>tc={1BA79E55-D3B6-4B95-8DA1-57CBF311C4CC}</author>
     <author>tc={2B329A84-0BDF-4381-88A4-81550D5EEF38}</author>
-    <author>tc={AAFA0838-65EA-4623-BC08-12544B2903FB}</author>
     <author>tc={4D05AFA5-576B-4955-8CD5-510AFC85FC66}</author>
     <author>tc={C94A78CF-2F80-4B38-B2A4-3CC0C4D9E0E4}</author>
     <author>tc={D7EB80D4-5CFD-425F-B3B4-EB0A0BE048F6}</author>
@@ -986,15 +967,7 @@
     indefferent</t>
       </text>
     </comment>
-    <comment ref="C45" authorId="26" shapeId="0" xr:uid="{AAFA0838-65EA-4623-BC08-12544B2903FB}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Depy, sitisi, sinesthimatikes diskolies</t>
-      </text>
-    </comment>
-    <comment ref="C46" authorId="27" shapeId="0" xr:uid="{4D05AFA5-576B-4955-8CD5-510AFC85FC66}">
+    <comment ref="C45" authorId="26" shapeId="0" xr:uid="{4D05AFA5-576B-4955-8CD5-510AFC85FC66}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1002,7 +975,7 @@
     Stiriksi, sitisi, menei me patera, oxi epaphi me mitera, o pateras fetos irthe, emenas me giagia kai pappou</t>
       </text>
     </comment>
-    <comment ref="C50" authorId="28" shapeId="0" xr:uid="{C94A78CF-2F80-4B38-B2A4-3CC0C4D9E0E4}">
+    <comment ref="C49" authorId="27" shapeId="0" xr:uid="{C94A78CF-2F80-4B38-B2A4-3CC0C4D9E0E4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1010,7 +983,7 @@
     Dropalos, thelei enisxisi</t>
       </text>
     </comment>
-    <comment ref="C51" authorId="29" shapeId="0" xr:uid="{D7EB80D4-5CFD-425F-B3B4-EB0A0BE048F6}">
+    <comment ref="C50" authorId="28" shapeId="0" xr:uid="{D7EB80D4-5CFD-425F-B3B4-EB0A0BE048F6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1018,7 +991,7 @@
     Stiriksi, mathisiakes adinamies</t>
       </text>
     </comment>
-    <comment ref="C52" authorId="30" shapeId="0" xr:uid="{222055CB-C6B5-4FA3-91EE-184B465B0798}">
+    <comment ref="C51" authorId="29" shapeId="0" xr:uid="{222055CB-C6B5-4FA3-91EE-184B465B0798}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1338,7 +1311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="378">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -1820,12 +1793,6 @@
     <t>Α4</t>
   </si>
   <si>
-    <t>ΣΑΒΒΑ</t>
-  </si>
-  <si>
-    <t>ΑΝΝΑ ΔΑΥΙΝΙΑ</t>
-  </si>
-  <si>
     <t>ΣΑΧΠΑΖΙΔΗΣ</t>
   </si>
   <si>
@@ -2447,12 +2414,6 @@
     <t>kahoot 19-10-2026</t>
   </si>
   <si>
-    <t>B41M9 - Εισαγωγή στις Συναρτήσεις - ξανα σχετική και απόλυτη αναφορά</t>
-  </si>
-  <si>
-    <t>A5.2 Μ3 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου - use A5.2 Μ2 και Μ3 - Ενιαίο Δισέλιδο Φύλλο Εργασίας</t>
-  </si>
-  <si>
     <t>put hw. 1-11 A5M5</t>
   </si>
   <si>
@@ -2478,6 +2439,12 @@
   </si>
   <si>
     <t>CREATE EMAIL WITH HOTSPOT - Α5.2 Μ1 - Εναλλακτικό Φύλλο Εργασίας - Ηλεκτρονικό Ταχυδρομείο - only 3 boys were in class</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ξανα σχετική και απόλυτη αναφορά</t>
+  </si>
+  <si>
+    <t>sent email with material</t>
   </si>
 </sst>
 </file>
@@ -2690,7 +2657,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2799,9 +2766,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3208,26 +3172,20 @@
   <threadedComment ref="C44" dT="2026-09-25T14:55:37.89" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
     <text>indefferent</text>
   </threadedComment>
-  <threadedComment ref="C45" dT="2026-10-05T09:04:58.84" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{86B9678A-C29A-446D-AACA-74A7C503B71B}">
-    <text>Depy, sitisi, sinesthimatikes diskolies</text>
-  </threadedComment>
-  <threadedComment ref="E45" dT="2026-09-15T15:29:00.38" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{720F20F5-2744-4E03-9112-5151AF4ED353}">
-    <text>Indifferent, don't take book.</text>
-  </threadedComment>
-  <threadedComment ref="C46" dT="2026-10-05T09:05:48.06" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}">
+  <threadedComment ref="C45" dT="2026-10-05T09:05:48.06" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}">
     <text>Stiriksi, sitisi, menei me patera, oxi epaphi me mitera, o pateras fetos irthe, emenas me giagia kai pappou</text>
   </threadedComment>
-  <threadedComment ref="C50" dT="2026-10-05T09:06:03.45" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{8F4D57B3-2C90-4744-BFEF-99E499E55142}">
+  <threadedComment ref="C49" dT="2026-10-05T09:06:03.45" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{8F4D57B3-2C90-4744-BFEF-99E499E55142}">
     <text>Dropalos, thelei enisxisi</text>
   </threadedComment>
-  <threadedComment ref="C51" dT="2026-10-05T09:06:27.63" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{37F71BFC-AE14-49EC-B2B2-49697A83F48F}">
+  <threadedComment ref="C50" dT="2026-10-05T09:06:27.63" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{37F71BFC-AE14-49EC-B2B2-49697A83F48F}">
     <text>Stiriksi, mathisiakes adinamies</text>
   </threadedComment>
-  <threadedComment ref="C52" dT="2026-09-21T06:24:16.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
+  <threadedComment ref="C51" dT="2026-09-21T06:24:16.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
     <text xml:space="preserve">Little guy with glasses
 </text>
   </threadedComment>
-  <threadedComment ref="C52" dT="2026-10-05T09:06:44.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{98AF0D30-4238-4DB6-AEB6-E46495700012}" parentId="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
+  <threadedComment ref="C51" dT="2026-10-05T09:06:44.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{98AF0D30-4238-4DB6-AEB6-E46495700012}" parentId="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
     <text>alpabitismos</text>
   </threadedComment>
 </ThreadedComments>
@@ -3469,23 +3427,20 @@
   <threadedComment ref="C44" dT="2026-09-25T14:55:37.89" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2B329A84-0BDF-4381-88A4-81550D5EEF38}">
     <text>indefferent</text>
   </threadedComment>
-  <threadedComment ref="C45" dT="2026-10-05T09:04:58.84" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AAFA0838-65EA-4623-BC08-12544B2903FB}">
-    <text>Depy, sitisi, sinesthimatikes diskolies</text>
-  </threadedComment>
-  <threadedComment ref="C46" dT="2026-10-05T09:05:48.06" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{4D05AFA5-576B-4955-8CD5-510AFC85FC66}">
+  <threadedComment ref="C45" dT="2026-10-05T09:05:48.06" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{4D05AFA5-576B-4955-8CD5-510AFC85FC66}">
     <text>Stiriksi, sitisi, menei me patera, oxi epaphi me mitera, o pateras fetos irthe, emenas me giagia kai pappou</text>
   </threadedComment>
-  <threadedComment ref="C50" dT="2026-10-05T09:06:03.45" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{C94A78CF-2F80-4B38-B2A4-3CC0C4D9E0E4}">
+  <threadedComment ref="C49" dT="2026-10-05T09:06:03.45" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{C94A78CF-2F80-4B38-B2A4-3CC0C4D9E0E4}">
     <text>Dropalos, thelei enisxisi</text>
   </threadedComment>
-  <threadedComment ref="C51" dT="2026-10-05T09:06:27.63" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D7EB80D4-5CFD-425F-B3B4-EB0A0BE048F6}">
+  <threadedComment ref="C50" dT="2026-10-05T09:06:27.63" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{D7EB80D4-5CFD-425F-B3B4-EB0A0BE048F6}">
     <text>Stiriksi, mathisiakes adinamies</text>
   </threadedComment>
-  <threadedComment ref="C52" dT="2026-09-21T06:24:16.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{222055CB-C6B5-4FA3-91EE-184B465B0798}">
+  <threadedComment ref="C51" dT="2026-09-21T06:24:16.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{222055CB-C6B5-4FA3-91EE-184B465B0798}">
     <text xml:space="preserve">Little guy with glasses
 </text>
   </threadedComment>
-  <threadedComment ref="C52" dT="2026-10-05T09:06:44.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{51D69F72-37C6-4888-83C5-CA1EA9ED6E7D}" parentId="{222055CB-C6B5-4FA3-91EE-184B465B0798}">
+  <threadedComment ref="C51" dT="2026-10-05T09:06:44.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{51D69F72-37C6-4888-83C5-CA1EA9ED6E7D}" parentId="{222055CB-C6B5-4FA3-91EE-184B465B0798}">
     <text>alpabitismos</text>
   </threadedComment>
 </ThreadedComments>
@@ -3650,58 +3605,58 @@
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="28"/>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="42" t="s">
+      <c r="C1" s="42"/>
+      <c r="D1" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="43"/>
-      <c r="F1" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="42" t="s">
-        <v>241</v>
-      </c>
-      <c r="I1" s="43"/>
-      <c r="J1" s="42" t="s">
-        <v>245</v>
-      </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="42" t="s">
-        <v>248</v>
-      </c>
-      <c r="M1" s="43"/>
-      <c r="N1" s="42" t="s">
-        <v>347</v>
-      </c>
-      <c r="O1" s="43"/>
-      <c r="P1" s="42" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="G1" s="42"/>
+      <c r="H1" s="41" t="s">
+        <v>239</v>
+      </c>
+      <c r="I1" s="42"/>
+      <c r="J1" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="K1" s="42"/>
+      <c r="L1" s="41" t="s">
+        <v>246</v>
+      </c>
+      <c r="M1" s="42"/>
+      <c r="N1" s="41" t="s">
+        <v>345</v>
+      </c>
+      <c r="O1" s="42"/>
+      <c r="P1" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="41" t="s">
         <v>348</v>
       </c>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="42" t="s">
+      <c r="S1" s="42"/>
+      <c r="T1" s="41" t="s">
+        <v>349</v>
+      </c>
+      <c r="U1" s="42"/>
+      <c r="V1" s="41" t="s">
         <v>350</v>
       </c>
-      <c r="S1" s="43"/>
-      <c r="T1" s="42" t="s">
+      <c r="W1" s="42"/>
+      <c r="X1" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="U1" s="43"/>
-      <c r="V1" s="42" t="s">
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="41" t="s">
         <v>352</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="42" t="s">
-        <v>353</v>
-      </c>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="42" t="s">
-        <v>354</v>
-      </c>
-      <c r="AA1" s="43"/>
+      <c r="AA1" s="42"/>
       <c r="AB1" s="29"/>
       <c r="AC1" s="29"/>
       <c r="AD1" s="29"/>
@@ -3808,7 +3763,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:60" ht="43" x14ac:dyDescent="0.5">
@@ -3816,7 +3771,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>9</v>
@@ -3831,34 +3786,34 @@
         <v>31</v>
       </c>
       <c r="G4" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="J4" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="K4" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="I4" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="J4" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="K4" s="23" t="s">
-        <v>255</v>
-      </c>
       <c r="L4" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N4" s="23" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="O4" s="23" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="Y4" s="39" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
@@ -3875,40 +3830,40 @@
         <v>30</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>31</v>
       </c>
       <c r="G5" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="J5" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="K5" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="I5" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="J5" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="K5" s="23" t="s">
-        <v>255</v>
-      </c>
       <c r="L5" s="23" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="N5" s="23" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="O5" s="23" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="X5" s="39" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:60" ht="61" customHeight="1" x14ac:dyDescent="0.5">
@@ -3928,55 +3883,55 @@
         <v>31</v>
       </c>
       <c r="F6" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="I6" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="J6" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="H6" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="J6" s="23" t="s">
-        <v>255</v>
-      </c>
       <c r="K6" s="23" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="N6" s="23" t="s">
-        <v>379</v>
-      </c>
-      <c r="O6" s="41" t="s">
-        <v>374</v>
+        <v>375</v>
+      </c>
+      <c r="O6" s="23" t="s">
+        <v>370</v>
       </c>
       <c r="P6" s="25" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q6" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="R6" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="S6" s="25" t="s">
         <v>355</v>
       </c>
-      <c r="R6" s="25" t="s">
+      <c r="T6" s="25" t="s">
         <v>356</v>
       </c>
-      <c r="S6" s="25" t="s">
+      <c r="U6" s="25" t="s">
         <v>357</v>
       </c>
-      <c r="T6" s="25" t="s">
-        <v>358</v>
-      </c>
-      <c r="U6" s="25" t="s">
-        <v>359</v>
-      </c>
       <c r="X6" s="39" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="1:60" ht="43" x14ac:dyDescent="0.5">
@@ -3984,7 +3939,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>9</v>
@@ -3993,40 +3948,40 @@
         <v>18</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G7" s="23" t="s">
         <v>31</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K7" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L7" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M7" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="N7" s="23" t="s">
         <v>343</v>
       </c>
-      <c r="N7" s="23" t="s">
-        <v>345</v>
-      </c>
-      <c r="O7" s="41" t="s">
-        <v>374</v>
+      <c r="O7" s="23" t="s">
+        <v>370</v>
       </c>
       <c r="X7" s="39" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:60" x14ac:dyDescent="0.5">
@@ -4037,10 +3992,10 @@
         <v>35</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="M10" s="25" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:60" x14ac:dyDescent="0.5">
@@ -4060,40 +4015,40 @@
         <v>32</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G11" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="I11" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="H11" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>259</v>
-      </c>
       <c r="J11" s="23" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="L11" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="N11" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="O11" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="P11" s="25" t="s">
         <v>323</v>
       </c>
-      <c r="O11" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="P11" s="25" t="s">
-        <v>325</v>
-      </c>
       <c r="V11" s="39" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
@@ -4110,40 +4065,43 @@
         <v>28</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F12" s="23" t="s">
         <v>32</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H12" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="J12" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="I12" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="J12" s="23" t="s">
-        <v>259</v>
-      </c>
       <c r="K12" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L12" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M12" s="23" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="N12" s="23" t="s">
-        <v>294</v>
-      </c>
-      <c r="O12" s="41" t="s">
-        <v>369</v>
+        <v>292</v>
+      </c>
+      <c r="O12" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="P12" s="25" t="s">
+        <v>376</v>
       </c>
       <c r="V12" s="39" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:60" x14ac:dyDescent="0.5">
@@ -4160,43 +4118,43 @@
         <v>28</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F13" s="23" t="s">
         <v>32</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H13" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="J13" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="I13" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="J13" s="23" t="s">
-        <v>259</v>
-      </c>
       <c r="K13" s="23" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L13" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M13" s="23" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="N13" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="O13" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="P13" s="25" t="s">
         <v>323</v>
       </c>
-      <c r="O13" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="P13" s="25" t="s">
-        <v>325</v>
-      </c>
       <c r="V13" s="39" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="1:60" x14ac:dyDescent="0.5">
@@ -4207,12 +4165,12 @@
         <v>35</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.5">
       <c r="H17" s="33" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="28.7" x14ac:dyDescent="0.5">
@@ -4226,49 +4184,49 @@
         <v>19</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E18" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="F18" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="F18" s="35" t="s">
-        <v>236</v>
-      </c>
       <c r="G18" s="35" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H18" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="I18" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="J18" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="I18" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="J18" s="23" t="s">
+      <c r="K18" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="L18" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="N18" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="K18" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="L18" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="M18" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="N18" s="23" t="s">
+      <c r="O18" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="P18" s="36" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q18" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="O18" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="P18" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q18" s="27" t="s">
-        <v>246</v>
-      </c>
       <c r="R18" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="28.7" x14ac:dyDescent="0.5">
@@ -4282,49 +4240,49 @@
         <v>19</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E19" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="F19" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="F19" s="35" t="s">
-        <v>236</v>
-      </c>
       <c r="G19" s="35" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H19" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="I19" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="J19" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="I19" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="J19" s="23" t="s">
+      <c r="K19" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="L19" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="M19" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="N19" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="K19" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="L19" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="M19" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="N19" s="23" t="s">
+      <c r="O19" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="P19" s="36" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q19" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="O19" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="P19" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q19" s="27" t="s">
-        <v>246</v>
-      </c>
       <c r="R19" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="28.7" x14ac:dyDescent="0.5">
@@ -4338,52 +4296,52 @@
         <v>19</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E20" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="F20" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="F20" s="35" t="s">
-        <v>236</v>
-      </c>
       <c r="G20" s="26" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I20" s="26" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J20" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="K20" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="K20" s="23" t="s">
+      <c r="L20" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="M20" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="N20" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="O20" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="L20" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="M20" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="N20" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="O20" s="23" t="s">
+      <c r="P20" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q20" s="36" t="s">
+        <v>247</v>
+      </c>
+      <c r="R20" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="P20" s="36" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q20" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="R20" s="27" t="s">
-        <v>246</v>
-      </c>
       <c r="S20" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.5">
@@ -4411,31 +4369,31 @@
         <v>27</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F22" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="G22" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="G22" s="35" t="s">
-        <v>281</v>
-      </c>
       <c r="J22" s="23" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M22" s="23" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N22" s="23" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.5">
@@ -4480,7 +4438,7 @@
         <v>22</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="28.7" x14ac:dyDescent="0.5">
@@ -4496,11 +4454,16 @@
         <v>24</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4509,11 +4472,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4524,7 +4482,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0C9DD2-633E-44CA-9A93-86B2E2731C82}">
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.3515625" style="4" bestFit="1" customWidth="1"/>
@@ -4560,36 +4518,36 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="44" t="s">
-        <v>285</v>
-      </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44" t="s">
-        <v>286</v>
-      </c>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44" t="s">
-        <v>296</v>
-      </c>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44" t="s">
-        <v>322</v>
-      </c>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44" t="s">
-        <v>367</v>
-      </c>
-      <c r="O2" s="44"/>
+      <c r="F2" s="43" t="s">
+        <v>283</v>
+      </c>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43" t="s">
+        <v>320</v>
+      </c>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43" t="s">
+        <v>365</v>
+      </c>
+      <c r="O2" s="43"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>121</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -4606,18 +4564,18 @@
         <v>124</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -4634,22 +4592,22 @@
         <v>124</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -4666,22 +4624,22 @@
         <v>124</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -4698,22 +4656,22 @@
         <v>124</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -4730,22 +4688,22 @@
         <v>124</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -4762,22 +4720,22 @@
         <v>124</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -4794,22 +4752,22 @@
         <v>124</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -4826,22 +4784,22 @@
         <v>124</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -4858,22 +4816,22 @@
         <v>124</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -4890,20 +4848,20 @@
         <v>124</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H13" s="20"/>
       <c r="I13" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -4911,19 +4869,19 @@
         <v>72</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -4940,25 +4898,25 @@
         <v>75</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="4">
         <v>2056004</v>
       </c>
@@ -4972,23 +4930,23 @@
         <v>75</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="4">
         <v>3318504</v>
       </c>
@@ -5002,25 +4960,25 @@
         <v>75</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="4">
         <v>4926804</v>
       </c>
@@ -5034,25 +4992,25 @@
         <v>75</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="4">
         <v>7568204</v>
       </c>
@@ -5066,23 +5024,23 @@
         <v>75</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4">
         <v>5111404</v>
       </c>
@@ -5096,23 +5054,23 @@
         <v>75</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="4">
         <v>4332504</v>
       </c>
@@ -5126,57 +5084,57 @@
         <v>75</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="4">
         <v>4332504</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>293</v>
-      </c>
       <c r="E23" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="4">
         <v>4424904</v>
       </c>
@@ -5190,36 +5148,36 @@
         <v>75</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4">
         <v>3257704</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>336</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -5228,7 +5186,7 @@
       <c r="J25" s="6"/>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4">
         <v>4934404</v>
       </c>
@@ -5242,36 +5200,39 @@
         <v>75</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4" t="s">
         <v>140</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>288</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4">
         <v>9189004</v>
       </c>
@@ -5285,19 +5246,19 @@
         <v>143</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4">
         <v>5682904</v>
       </c>
@@ -5311,19 +5272,19 @@
         <v>143</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4">
         <v>9217204</v>
       </c>
@@ -5337,15 +5298,15 @@
         <v>143</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="4">
         <v>7319504</v>
       </c>
@@ -5359,19 +5320,19 @@
         <v>143</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="4">
         <v>9254304</v>
       </c>
@@ -5385,19 +5346,19 @@
         <v>143</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="4">
         <v>2428404</v>
       </c>
@@ -5411,19 +5372,19 @@
         <v>143</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="4">
         <v>2427904</v>
       </c>
@@ -5437,19 +5398,19 @@
         <v>143</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4">
         <v>8373704</v>
       </c>
@@ -5463,19 +5424,19 @@
         <v>143</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="4">
         <v>5155004</v>
       </c>
@@ -5489,19 +5450,19 @@
         <v>143</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="4">
         <v>1006390</v>
       </c>
@@ -5515,27 +5476,27 @@
         <v>143</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="4" t="s">
         <v>157</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="4">
         <v>5324204</v>
       </c>
@@ -5549,31 +5510,34 @@
         <v>159</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L43" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>237</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="4">
         <v>5996604</v>
       </c>
@@ -5587,33 +5551,33 @@
         <v>159</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L44" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="4">
-        <v>7153704</v>
+        <v>9185204</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>160</v>
@@ -5625,33 +5589,33 @@
         <v>159</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>233</v>
+        <v>171</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H45" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="I45" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="J45" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="4">
-        <v>9185204</v>
+        <v>9185504</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>162</v>
@@ -5663,185 +5627,185 @@
         <v>159</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="G46" s="15" t="s">
-        <v>266</v>
+        <v>231</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="4">
-        <v>9185504</v>
+        <v>4913604</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>164</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>159</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
+      </c>
+      <c r="F47" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>260</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J47" s="14" t="s">
-        <v>233</v>
+        <v>171</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L47" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="4">
-        <v>4913604</v>
+        <v>5436204</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>159</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F48" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="G48" s="18" t="s">
-        <v>262</v>
+        <v>171</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L48" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="4">
-        <v>5436204</v>
+        <v>3506004</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>167</v>
+        <v>50</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>159</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L49" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="4">
-        <v>3506004</v>
+        <v>6757304</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>50</v>
+        <v>166</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>159</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L50" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="4">
-        <v>6757304</v>
+        <v>6390804</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>168</v>
@@ -5853,118 +5817,80 @@
         <v>159</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L51" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="4">
-        <v>6390804</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J52" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K52" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="L52" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="12"/>
+      <c r="B55" s="6" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="12"/>
+      <c r="A56" s="17" t="s">
+        <v>171</v>
+      </c>
       <c r="B56" s="6" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="17" t="s">
-        <v>173</v>
+      <c r="A57" s="18" t="s">
+        <v>260</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="20"/>
+      <c r="B58" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="B58" s="6" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="20"/>
-      <c r="B59" s="6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="B60" s="6" t="s">
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="16" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="15" t="s">
+      <c r="B61" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -6012,26 +5938,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="44" t="s">
-        <v>285</v>
-      </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44" t="s">
-        <v>286</v>
-      </c>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44" t="s">
-        <v>298</v>
-      </c>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44" t="s">
-        <v>322</v>
-      </c>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44" t="s">
-        <v>367</v>
-      </c>
-      <c r="O2" s="44"/>
+      <c r="F2" s="43" t="s">
+        <v>283</v>
+      </c>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43" t="s">
+        <v>320</v>
+      </c>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43" t="s">
+        <v>365</v>
+      </c>
+      <c r="O2" s="43"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -6052,22 +5978,22 @@
         <v>93</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H4" s="21" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -6084,20 +6010,20 @@
         <v>93</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I5" s="12"/>
       <c r="L5" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -6114,22 +6040,22 @@
         <v>93</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -6146,20 +6072,20 @@
         <v>93</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -6176,22 +6102,22 @@
         <v>93</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -6208,22 +6134,22 @@
         <v>93</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -6240,22 +6166,22 @@
         <v>93</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -6272,22 +6198,22 @@
         <v>93</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -6304,22 +6230,22 @@
         <v>93</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -6336,22 +6262,22 @@
         <v>93</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -6373,19 +6299,19 @@
         <v>111</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6402,19 +6328,19 @@
         <v>111</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J17" s="16" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6431,19 +6357,19 @@
         <v>111</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6460,19 +6386,19 @@
         <v>111</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6489,19 +6415,19 @@
         <v>111</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6518,19 +6444,19 @@
         <v>111</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6547,19 +6473,19 @@
         <v>111</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6576,19 +6502,19 @@
         <v>111</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6605,19 +6531,19 @@
         <v>111</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6627,31 +6553,31 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6668,28 +6594,28 @@
         <v>39</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6706,28 +6632,28 @@
         <v>39</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6744,28 +6670,28 @@
         <v>39</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6782,28 +6708,28 @@
         <v>39</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M32" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6820,28 +6746,28 @@
         <v>39</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6858,28 +6784,28 @@
         <v>39</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6896,26 +6822,26 @@
         <v>39</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J35" s="12"/>
       <c r="K35" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6932,28 +6858,28 @@
         <v>39</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6970,28 +6896,28 @@
         <v>39</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -7008,28 +6934,28 @@
         <v>39</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -7075,39 +7001,39 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="44" t="s">
-        <v>285</v>
-      </c>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44" t="s">
-        <v>286</v>
-      </c>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44" t="s">
-        <v>298</v>
-      </c>
-      <c r="L1" s="44"/>
-      <c r="M1" s="45" t="s">
-        <v>328</v>
-      </c>
-      <c r="N1" s="45"/>
-      <c r="O1" s="44" t="s">
-        <v>367</v>
-      </c>
-      <c r="P1" s="44"/>
+      <c r="G1" s="43" t="s">
+        <v>283</v>
+      </c>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="L1" s="43"/>
+      <c r="M1" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="N1" s="44"/>
+      <c r="O1" s="43" t="s">
+        <v>365</v>
+      </c>
+      <c r="P1" s="43"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="K3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="O3" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7115,46 +7041,46 @@
         <v>4206804</v>
       </c>
       <c r="B4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C4" t="s">
         <v>123</v>
       </c>
       <c r="D4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7162,46 +7088,46 @@
         <v>9307104</v>
       </c>
       <c r="B5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C5" t="s">
         <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7209,46 +7135,46 @@
         <v>2173704</v>
       </c>
       <c r="B6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7256,46 +7182,46 @@
         <v>9257304</v>
       </c>
       <c r="B7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J7" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7303,46 +7229,46 @@
         <v>2915404</v>
       </c>
       <c r="B8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C8" t="s">
         <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7350,46 +7276,46 @@
         <v>2836604</v>
       </c>
       <c r="B9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7397,46 +7323,46 @@
         <v>1274904</v>
       </c>
       <c r="B10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J10" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7444,44 +7370,44 @@
         <v>3863304</v>
       </c>
       <c r="B11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J11" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K11" s="12"/>
       <c r="L11" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7489,46 +7415,46 @@
         <v>3403504</v>
       </c>
       <c r="B12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7536,44 +7462,44 @@
         <v>4721304</v>
       </c>
       <c r="B13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J13" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M13" s="20"/>
       <c r="O13" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P13" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7584,43 +7510,43 @@
         <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J14" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7631,43 +7557,43 @@
         <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J15" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7675,131 +7601,131 @@
         <v>9280704</v>
       </c>
       <c r="B16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="C17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D17" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J17" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C18" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J18" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.5">
@@ -7821,16 +7747,16 @@
         <v>60</v>
       </c>
       <c r="L21" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M21" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="N21" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7838,49 +7764,49 @@
         <v>9693404</v>
       </c>
       <c r="B22" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" t="s">
+        <v>195</v>
+      </c>
+      <c r="D22" t="s">
         <v>196</v>
       </c>
-      <c r="C22" t="s">
-        <v>197</v>
-      </c>
-      <c r="D22" t="s">
-        <v>198</v>
-      </c>
       <c r="E22" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J22" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N22" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7888,49 +7814,49 @@
         <v>222222</v>
       </c>
       <c r="B23" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J23" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P23" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7938,49 +7864,49 @@
         <v>9743804</v>
       </c>
       <c r="B24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C24" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D24" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L24" s="15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M24" s="15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P24" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -7988,43 +7914,43 @@
         <v>111111</v>
       </c>
       <c r="B25" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C25" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D25" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I25" s="20"/>
       <c r="J25" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K25" s="12"/>
       <c r="L25" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N25" s="12"/>
       <c r="O25" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8032,132 +7958,132 @@
         <v>9662304</v>
       </c>
       <c r="B26" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C26" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D26" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J26" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C27" t="s">
+        <v>271</v>
+      </c>
+      <c r="D27" t="s">
         <v>273</v>
-      </c>
-      <c r="D27" t="s">
-        <v>275</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
       <c r="G27" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I27" s="20"/>
       <c r="J27" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L27" s="15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M27" s="15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="N27" s="12"/>
       <c r="O27" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
+        <v>270</v>
+      </c>
+      <c r="C28" t="s">
         <v>272</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>274</v>
-      </c>
-      <c r="D28" t="s">
-        <v>276</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
       <c r="G28" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I28" s="20"/>
       <c r="J28" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N28" s="12"/>
       <c r="O28" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.5">
       <c r="L30" s="8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.5">
@@ -8165,7 +8091,7 @@
         <v>16</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8173,43 +8099,43 @@
         <v>3578804</v>
       </c>
       <c r="B32" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C32" t="s">
         <v>128</v>
       </c>
       <c r="D32" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J32" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O32" s="40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P32" s="40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8217,41 +8143,41 @@
         <v>9289704</v>
       </c>
       <c r="B33" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C33" t="s">
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I33" s="12"/>
       <c r="J33" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M33" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O33" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P33" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8259,39 +8185,39 @@
         <v>9344404</v>
       </c>
       <c r="B34" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C34" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D34" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I34" s="20"/>
       <c r="J34" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L34" s="12"/>
       <c r="M34" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O34" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P34" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8299,41 +8225,41 @@
         <v>6746404</v>
       </c>
       <c r="B35" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C35" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D35" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I35" s="12"/>
       <c r="J35" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M35" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O35" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P35" s="40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8341,43 +8267,43 @@
         <v>9257604</v>
       </c>
       <c r="B36" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C36" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D36" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M36" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O36" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P36" s="40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8385,41 +8311,41 @@
         <v>9717204</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C37" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D37" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I37" s="12"/>
       <c r="J37" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M37" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O37" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P37" s="40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8427,39 +8353,39 @@
         <v>2298204</v>
       </c>
       <c r="B38" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C38" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D38" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I38" s="12"/>
       <c r="J38" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K38" s="12"/>
       <c r="L38" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M38" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O38" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P38" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8470,40 +8396,40 @@
         <v>98</v>
       </c>
       <c r="C39" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D39" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J39" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O39" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P39" s="40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8511,41 +8437,41 @@
         <v>9321704</v>
       </c>
       <c r="B40" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C40" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J40" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K40" s="12"/>
       <c r="L40" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M40" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O40" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P40" s="40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8553,43 +8479,43 @@
         <v>9720304</v>
       </c>
       <c r="B41" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C41" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D41" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I41" s="18" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J41" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O41" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P41" s="40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8597,41 +8523,41 @@
         <v>9317404</v>
       </c>
       <c r="B42" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C42" t="s">
         <v>67</v>
       </c>
       <c r="D42" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I42" s="12"/>
       <c r="J42" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L42" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M42" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O42" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P42" s="40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
@@ -8639,43 +8565,43 @@
         <v>8333604</v>
       </c>
       <c r="B43" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C43" t="s">
         <v>67</v>
       </c>
       <c r="D43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J43" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M43" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O43" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P43" s="40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -8706,89 +8632,89 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C8" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C9" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C10" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B18" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B19" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -8824,18 +8750,18 @@
       <c r="D1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="44" t="s">
-        <v>285</v>
-      </c>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44" t="s">
-        <v>286</v>
-      </c>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44" t="s">
-        <v>298</v>
-      </c>
-      <c r="J1" s="44"/>
+      <c r="E1" s="43" t="s">
+        <v>283</v>
+      </c>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="J1" s="43"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
@@ -8851,10 +8777,10 @@
         <v>63</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8871,10 +8797,10 @@
         <v>63</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8891,10 +8817,10 @@
         <v>63</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8911,10 +8837,10 @@
         <v>63</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8931,10 +8857,10 @@
         <v>63</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -8949,7 +8875,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FEE7927-B2CB-4F8C-B929-249864A39417}">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.3515625" style="4" bestFit="1" customWidth="1"/>
@@ -8980,10 +8906,10 @@
         <v>121</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9000,7 +8926,7 @@
         <v>124</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9017,7 +8943,7 @@
         <v>124</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9049,7 +8975,7 @@
         <v>124</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9066,7 +8992,7 @@
         <v>124</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9083,7 +9009,7 @@
         <v>124</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9100,7 +9026,7 @@
         <v>124</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9117,7 +9043,7 @@
         <v>124</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9134,7 +9060,7 @@
         <v>124</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9151,7 +9077,7 @@
         <v>124</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9159,7 +9085,7 @@
         <v>72</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9176,10 +9102,10 @@
         <v>75</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9196,10 +9122,10 @@
         <v>75</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9216,10 +9142,10 @@
         <v>75</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9236,10 +9162,10 @@
         <v>75</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9256,10 +9182,10 @@
         <v>75</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9276,10 +9202,10 @@
         <v>75</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9296,10 +9222,10 @@
         <v>75</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9307,16 +9233,16 @@
         <v>4332504</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>293</v>
-      </c>
       <c r="E24" s="19" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9333,7 +9259,7 @@
         <v>75</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9341,19 +9267,19 @@
         <v>3257704</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>75</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9370,7 +9296,7 @@
         <v>75</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -9448,7 +9374,7 @@
         <v>143</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9479,7 +9405,7 @@
         <v>143</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9510,7 +9436,7 @@
         <v>143</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9564,7 +9490,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="4">
-        <v>7153704</v>
+        <v>9185204</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>160</v>
@@ -9575,11 +9501,13 @@
       <c r="D45" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E45" s="20"/>
+      <c r="E45" s="6" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="4">
-        <v>9185204</v>
+        <v>9185504</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>162</v>
@@ -9591,76 +9519,78 @@
         <v>159</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="4">
-        <v>9185504</v>
+        <v>4913604</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>164</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>159</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="4">
-        <v>4913604</v>
+        <v>5436204</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>173</v>
-      </c>
+      <c r="E48" s="20"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="4">
-        <v>5436204</v>
+        <v>3506004</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>167</v>
+        <v>50</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E49" s="20"/>
+      <c r="E49" s="6" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="4">
-        <v>3506004</v>
+        <v>6757304</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>50</v>
+        <v>166</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E50" s="20"/>
+      <c r="E50" s="6" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="4">
-        <v>6757304</v>
+        <v>6390804</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>168</v>
@@ -9672,74 +9602,59 @@
         <v>159</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="4">
-        <v>6390804</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E52" s="20"/>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="12"/>
+      <c r="B55" s="6" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="12"/>
+      <c r="A56" s="17" t="s">
+        <v>171</v>
+      </c>
       <c r="B56" s="6" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="17" t="s">
-        <v>173</v>
+      <c r="A57" s="18" t="s">
+        <v>260</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="20"/>
+      <c r="B58" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="B58" s="6" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="20"/>
-      <c r="B59" s="6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="B60" s="6" t="s">
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="16" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="15" t="s">
+      <c r="B61" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -9782,7 +9697,7 @@
         <v>90</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9816,7 +9731,7 @@
         <v>93</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9833,7 +9748,7 @@
         <v>93</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9960,7 +9875,7 @@
         <v>108</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -10045,7 +9960,7 @@
         <v>111</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -10121,15 +10036,15 @@
         <v>56</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>39</v>
@@ -10346,7 +10261,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.5">
@@ -10354,13 +10269,13 @@
         <v>4206804</v>
       </c>
       <c r="B4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C4" t="s">
         <v>123</v>
       </c>
       <c r="D4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -10371,13 +10286,13 @@
         <v>9307104</v>
       </c>
       <c r="B5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C5" t="s">
         <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -10388,13 +10303,13 @@
         <v>2173704</v>
       </c>
       <c r="B6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -10405,13 +10320,13 @@
         <v>9257304</v>
       </c>
       <c r="B7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -10422,13 +10337,13 @@
         <v>2915404</v>
       </c>
       <c r="B8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C8" t="s">
         <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E8">
         <v>0.67</v>
@@ -10439,13 +10354,13 @@
         <v>2836604</v>
       </c>
       <c r="B9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E9">
         <v>0.67</v>
@@ -10456,13 +10371,13 @@
         <v>1274904</v>
       </c>
       <c r="B10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -10473,13 +10388,13 @@
         <v>3863304</v>
       </c>
       <c r="B11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -10490,13 +10405,13 @@
         <v>3403504</v>
       </c>
       <c r="B12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -10507,13 +10422,13 @@
         <v>4721304</v>
       </c>
       <c r="B13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -10527,10 +10442,10 @@
         <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -10544,10 +10459,10 @@
         <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -10558,13 +10473,13 @@
         <v>9280704</v>
       </c>
       <c r="B16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -10572,10 +10487,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.5">
       <c r="C17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D17" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -10583,13 +10498,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B18" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C18" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -10600,7 +10515,7 @@
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.5">
@@ -10622,13 +10537,13 @@
         <v>9693404</v>
       </c>
       <c r="B22" t="s">
+        <v>194</v>
+      </c>
+      <c r="C22" t="s">
+        <v>195</v>
+      </c>
+      <c r="D22" t="s">
         <v>196</v>
-      </c>
-      <c r="C22" t="s">
-        <v>197</v>
-      </c>
-      <c r="D22" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.5">
@@ -10636,13 +10551,13 @@
         <v>222222</v>
       </c>
       <c r="B23" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.5">
@@ -10650,13 +10565,13 @@
         <v>9743804</v>
       </c>
       <c r="B24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C24" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D24" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.5">
@@ -10664,13 +10579,13 @@
         <v>111111</v>
       </c>
       <c r="B25" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C25" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D25" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.5">
@@ -10678,35 +10593,35 @@
         <v>9662304</v>
       </c>
       <c r="B26" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C26" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D26" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B27" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C27" t="s">
+        <v>271</v>
+      </c>
+      <c r="D27" t="s">
         <v>273</v>
-      </c>
-      <c r="D27" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.5">
       <c r="B28" t="s">
+        <v>270</v>
+      </c>
+      <c r="C28" t="s">
         <v>272</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>274</v>
-      </c>
-      <c r="D28" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.5">
@@ -10719,13 +10634,13 @@
         <v>3578804</v>
       </c>
       <c r="B32" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C32" t="s">
         <v>128</v>
       </c>
       <c r="D32" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.5">
@@ -10733,13 +10648,13 @@
         <v>9289704</v>
       </c>
       <c r="B33" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C33" t="s">
         <v>49</v>
       </c>
       <c r="D33" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.5">
@@ -10747,13 +10662,13 @@
         <v>9344404</v>
       </c>
       <c r="B34" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C34" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D34" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.5">
@@ -10761,13 +10676,13 @@
         <v>6746404</v>
       </c>
       <c r="B35" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C35" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D35" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.5">
@@ -10775,13 +10690,13 @@
         <v>9257604</v>
       </c>
       <c r="B36" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C36" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D36" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.5">
@@ -10789,13 +10704,13 @@
         <v>9717204</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C37" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D37" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.5">
@@ -10803,13 +10718,13 @@
         <v>2298204</v>
       </c>
       <c r="B38" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C38" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D38" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.5">
@@ -10820,10 +10735,10 @@
         <v>98</v>
       </c>
       <c r="C39" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D39" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.5">
@@ -10831,13 +10746,13 @@
         <v>9321704</v>
       </c>
       <c r="B40" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C40" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.5">
@@ -10845,13 +10760,13 @@
         <v>9720304</v>
       </c>
       <c r="B41" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C41" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D41" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.5">
@@ -10859,13 +10774,13 @@
         <v>9317404</v>
       </c>
       <c r="B42" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C42" t="s">
         <v>67</v>
       </c>
       <c r="D42" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.5">
@@ -10873,13 +10788,13 @@
         <v>8333604</v>
       </c>
       <c r="B43" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C43" t="s">
         <v>67</v>
       </c>
       <c r="D43" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1732" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C794B012-5CC6-479E-B323-3024BF4D3A80}"/>
+  <xr:revisionPtr revIDLastSave="1740" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08E52E7E-238B-4457-8F6A-BEA28CB84B14}"/>
   <bookViews>
     <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1311,7 +1311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="378">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -3812,6 +3812,12 @@
       <c r="O4" s="23" t="s">
         <v>370</v>
       </c>
+      <c r="P4" s="25" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q4" s="25" t="s">
+        <v>353</v>
+      </c>
       <c r="Y4" s="39" t="s">
         <v>247</v>
       </c>
@@ -3862,6 +3868,12 @@
       <c r="O5" s="23" t="s">
         <v>371</v>
       </c>
+      <c r="P5" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q5" s="25" t="s">
+        <v>354</v>
+      </c>
       <c r="X5" s="39" t="s">
         <v>247</v>
       </c>
@@ -3930,6 +3942,9 @@
       <c r="U6" s="25" t="s">
         <v>357</v>
       </c>
+      <c r="V6" s="39" t="s">
+        <v>295</v>
+      </c>
       <c r="X6" s="39" t="s">
         <v>247</v>
       </c>
@@ -3979,6 +3994,12 @@
       </c>
       <c r="O7" s="23" t="s">
         <v>370</v>
+      </c>
+      <c r="P7" s="25" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>353</v>
       </c>
       <c r="X7" s="39" t="s">
         <v>247</v>
@@ -4459,11 +4480,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4472,6 +4488,11 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1740" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08E52E7E-238B-4457-8F6A-BEA28CB84B14}"/>
+  <xr:revisionPtr revIDLastSave="1819" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{439F55AF-3511-4000-B72C-9E42DA99E471}"/>
   <bookViews>
     <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1311,7 +1311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="382">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2441,17 +2441,29 @@
     <t>CREATE EMAIL WITH HOTSPOT - Α5.2 Μ1 - Εναλλακτικό Φύλλο Εργασίας - Ηλεκτρονικό Ταχυδρομείο - only 3 boys were in class</t>
   </si>
   <si>
-    <t xml:space="preserve"> ξανα σχετική και απόλυτη αναφορά</t>
-  </si>
-  <si>
     <t>sent email with material</t>
+  </si>
+  <si>
+    <t>A7M1 - Εισαγωγή στη τεχνιτή νοημοσύνη</t>
+  </si>
+  <si>
+    <t>B41M10 - Συναρτήσεις ξανα σχετική και απόλυτη αναφορά</t>
+  </si>
+  <si>
+    <t>eueuoeuo</t>
+  </si>
+  <si>
+    <t>ueeueuo</t>
+  </si>
+  <si>
+    <t>Maria test</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2522,8 +2534,22 @@
       <charset val="161"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2602,8 +2628,19 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2652,12 +2689,64 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2779,8 +2868,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="180" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="60% - Accent6" xfId="3" builtinId="52"/>
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -3573,7 +3682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH38"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="11.41015625" style="30" bestFit="1" customWidth="1"/>
@@ -3590,7 +3699,7 @@
     <col min="14" max="14" width="43.05859375" style="25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="47.8203125" style="25" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="40.3515625" style="25" customWidth="1"/>
-    <col min="17" max="17" width="24.41015625" style="25" customWidth="1"/>
+    <col min="17" max="17" width="28.9375" style="25" customWidth="1"/>
     <col min="18" max="18" width="26.41015625" style="25" customWidth="1"/>
     <col min="19" max="19" width="25.64453125" style="25" customWidth="1"/>
     <col min="20" max="20" width="31.5859375" style="25" customWidth="1"/>
@@ -3945,6 +4054,9 @@
       <c r="V6" s="39" t="s">
         <v>295</v>
       </c>
+      <c r="W6" s="25" t="s">
+        <v>377</v>
+      </c>
       <c r="X6" s="39" t="s">
         <v>247</v>
       </c>
@@ -4019,7 +4131,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A11" s="30" t="s">
         <v>6</v>
       </c>
@@ -4066,6 +4178,9 @@
         <v>322</v>
       </c>
       <c r="P11" s="25" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q11" s="25" t="s">
         <v>323</v>
       </c>
       <c r="V11" s="39" t="s">
@@ -4119,13 +4234,16 @@
         <v>293</v>
       </c>
       <c r="P12" s="25" t="s">
-        <v>376</v>
+        <v>378</v>
+      </c>
+      <c r="Q12" s="25" t="s">
+        <v>322</v>
       </c>
       <c r="V12" s="39" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A13" s="30" t="s">
         <v>8</v>
       </c>
@@ -4172,6 +4290,9 @@
         <v>322</v>
       </c>
       <c r="P13" s="25" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q13" s="25" t="s">
         <v>323</v>
       </c>
       <c r="V13" s="39" t="s">
@@ -4442,6 +4563,28 @@
       <c r="C27" s="25" t="s">
         <v>29</v>
       </c>
+      <c r="P27" s="47"/>
+      <c r="Q27" s="47"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="O28" s="45"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="46"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="O29" s="45"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="49"/>
+      <c r="R29" s="46"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="O30" s="45"/>
+      <c r="P30" s="49"/>
+      <c r="Q30" s="49" t="s">
+        <v>380</v>
+      </c>
+      <c r="R30" s="46"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B31" s="25" t="s">
@@ -4453,33 +4596,80 @@
       <c r="E31" s="25" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.5">
+      <c r="O31" s="45"/>
+      <c r="P31" s="49"/>
+      <c r="Q31" s="49" t="s">
+        <v>379</v>
+      </c>
+      <c r="R31" s="46"/>
+    </row>
+    <row r="32" spans="1:19" ht="99" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="25" t="s">
         <v>22</v>
       </c>
       <c r="C32" s="25" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="33" spans="2:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="O32" s="45"/>
+      <c r="P32" s="50" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q32" s="49"/>
+      <c r="R32" s="46"/>
+    </row>
+    <row r="33" spans="2:18" ht="29" thickTop="1" x14ac:dyDescent="0.5">
       <c r="B33" s="25" t="s">
         <v>23</v>
       </c>
       <c r="C33" s="38" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="O33" s="45"/>
+      <c r="P33" s="49"/>
+      <c r="Q33" s="49"/>
+      <c r="R33" s="46"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B34" s="25" t="s">
         <v>24</v>
       </c>
       <c r="C34" s="25" t="s">
         <v>281</v>
       </c>
+      <c r="O34" s="45"/>
+      <c r="P34" s="49"/>
+      <c r="Q34" s="49"/>
+      <c r="R34" s="46"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="O35" s="45"/>
+      <c r="P35" s="49"/>
+      <c r="Q35" s="49"/>
+      <c r="R35" s="46"/>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="O36" s="45"/>
+      <c r="P36" s="49"/>
+      <c r="Q36" s="49"/>
+      <c r="R36" s="46"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="O37" s="45"/>
+      <c r="P37" s="49"/>
+      <c r="Q37" s="49"/>
+      <c r="R37" s="46"/>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.5">
+      <c r="P38" s="48"/>
+      <c r="Q38" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4488,11 +4678,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5250,7 +5435,7 @@
         <v>288</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -5555,7 +5740,7 @@
         <v>237</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.55000000000000004">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1819" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{439F55AF-3511-4000-B72C-9E42DA99E471}"/>
+  <xr:revisionPtr revIDLastSave="1841" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BEE3FB1-E33B-4943-9719-CC1849082F5A}"/>
   <bookViews>
     <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1311,7 +1311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="382">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2444,9 +2444,6 @@
     <t>sent email with material</t>
   </si>
   <si>
-    <t>A7M1 - Εισαγωγή στη τεχνιτή νοημοσύνη</t>
-  </si>
-  <si>
     <t>B41M10 - Συναρτήσεις ξανα σχετική και απόλυτη αναφορά</t>
   </si>
   <si>
@@ -2457,6 +2454,9 @@
   </si>
   <si>
     <t>Maria test</t>
+  </si>
+  <si>
+    <t>B41M13 - Δημιουργία Γραφημάτων</t>
   </si>
 </sst>
 </file>
@@ -2746,7 +2746,7 @@
     <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2856,18 +2856,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2885,6 +2873,27 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3699,7 +3708,7 @@
     <col min="14" max="14" width="43.05859375" style="25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="47.8203125" style="25" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="40.3515625" style="25" customWidth="1"/>
-    <col min="17" max="17" width="28.9375" style="25" customWidth="1"/>
+    <col min="17" max="17" width="28.41015625" style="25" customWidth="1"/>
     <col min="18" max="18" width="26.41015625" style="25" customWidth="1"/>
     <col min="19" max="19" width="25.64453125" style="25" customWidth="1"/>
     <col min="20" max="20" width="31.5859375" style="25" customWidth="1"/>
@@ -3714,58 +3723,58 @@
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="28"/>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="41" t="s">
+      <c r="C1" s="51"/>
+      <c r="D1" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="51"/>
+      <c r="F1" s="50" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="42"/>
-      <c r="H1" s="41" t="s">
+      <c r="G1" s="51"/>
+      <c r="H1" s="50" t="s">
         <v>239</v>
       </c>
-      <c r="I1" s="42"/>
-      <c r="J1" s="41" t="s">
+      <c r="I1" s="51"/>
+      <c r="J1" s="50" t="s">
         <v>243</v>
       </c>
-      <c r="K1" s="42"/>
-      <c r="L1" s="41" t="s">
+      <c r="K1" s="51"/>
+      <c r="L1" s="50" t="s">
         <v>246</v>
       </c>
-      <c r="M1" s="42"/>
-      <c r="N1" s="41" t="s">
+      <c r="M1" s="51"/>
+      <c r="N1" s="50" t="s">
         <v>345</v>
       </c>
-      <c r="O1" s="42"/>
-      <c r="P1" s="41" t="s">
+      <c r="O1" s="51"/>
+      <c r="P1" s="50" t="s">
         <v>346</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="41" t="s">
+      <c r="Q1" s="51"/>
+      <c r="R1" s="50" t="s">
         <v>348</v>
       </c>
-      <c r="S1" s="42"/>
-      <c r="T1" s="41" t="s">
+      <c r="S1" s="51"/>
+      <c r="T1" s="50" t="s">
         <v>349</v>
       </c>
-      <c r="U1" s="42"/>
-      <c r="V1" s="41" t="s">
+      <c r="U1" s="51"/>
+      <c r="V1" s="50" t="s">
         <v>350</v>
       </c>
-      <c r="W1" s="42"/>
-      <c r="X1" s="41" t="s">
+      <c r="W1" s="51"/>
+      <c r="X1" s="50" t="s">
         <v>351</v>
       </c>
-      <c r="Y1" s="42"/>
-      <c r="Z1" s="41" t="s">
+      <c r="Y1" s="51"/>
+      <c r="Z1" s="50" t="s">
         <v>352</v>
       </c>
-      <c r="AA1" s="42"/>
+      <c r="AA1" s="51"/>
       <c r="AB1" s="29"/>
       <c r="AC1" s="29"/>
       <c r="AD1" s="29"/>
@@ -3909,7 +3918,7 @@
       <c r="K4" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="L4" s="47" t="s">
         <v>237</v>
       </c>
       <c r="M4" s="23" t="s">
@@ -3924,7 +3933,10 @@
       <c r="P4" s="25" t="s">
         <v>371</v>
       </c>
-      <c r="Q4" s="25" t="s">
+      <c r="Q4" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>353</v>
       </c>
       <c r="Y4" s="39" t="s">
@@ -3980,7 +3992,10 @@
       <c r="P5" s="25" t="s">
         <v>353</v>
       </c>
-      <c r="Q5" s="25" t="s">
+      <c r="Q5" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="R5" s="25" t="s">
         <v>354</v>
       </c>
       <c r="X5" s="39" t="s">
@@ -4036,26 +4051,26 @@
       <c r="P6" s="25" t="s">
         <v>371</v>
       </c>
-      <c r="Q6" s="25" t="s">
+      <c r="Q6" s="48" t="s">
+        <v>282</v>
+      </c>
+      <c r="R6" s="25" t="s">
         <v>353</v>
       </c>
-      <c r="R6" s="25" t="s">
+      <c r="S6" s="25" t="s">
         <v>354</v>
       </c>
-      <c r="S6" s="25" t="s">
+      <c r="T6" s="25" t="s">
         <v>355</v>
       </c>
-      <c r="T6" s="25" t="s">
+      <c r="U6" s="25" t="s">
         <v>356</v>
       </c>
-      <c r="U6" s="25" t="s">
+      <c r="V6" s="25" t="s">
         <v>357</v>
       </c>
-      <c r="V6" s="39" t="s">
+      <c r="W6" s="39" t="s">
         <v>295</v>
-      </c>
-      <c r="W6" s="25" t="s">
-        <v>377</v>
       </c>
       <c r="X6" s="39" t="s">
         <v>247</v>
@@ -4095,7 +4110,7 @@
       <c r="K7" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="L7" s="26" t="s">
+      <c r="L7" s="47" t="s">
         <v>237</v>
       </c>
       <c r="M7" s="23" t="s">
@@ -4127,6 +4142,7 @@
       <c r="C10" s="25" t="s">
         <v>339</v>
       </c>
+      <c r="L10" s="49"/>
       <c r="M10" s="25" t="s">
         <v>302</v>
       </c>
@@ -4165,7 +4181,7 @@
       <c r="K11" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="L11" s="26" t="s">
+      <c r="L11" s="47" t="s">
         <v>237</v>
       </c>
       <c r="M11" s="23" t="s">
@@ -4180,14 +4196,17 @@
       <c r="P11" s="25" t="s">
         <v>323</v>
       </c>
-      <c r="Q11" s="25" t="s">
+      <c r="Q11" s="48" t="s">
+        <v>282</v>
+      </c>
+      <c r="R11" s="25" t="s">
         <v>323</v>
       </c>
       <c r="V11" s="39" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:60" ht="43" x14ac:dyDescent="0.5">
       <c r="A12" s="30" t="s">
         <v>7</v>
       </c>
@@ -4221,7 +4240,7 @@
       <c r="K12" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="L12" s="26" t="s">
+      <c r="L12" s="47" t="s">
         <v>237</v>
       </c>
       <c r="M12" s="23" t="s">
@@ -4234,7 +4253,7 @@
         <v>293</v>
       </c>
       <c r="P12" s="25" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q12" s="25" t="s">
         <v>322</v>
@@ -4277,7 +4296,7 @@
       <c r="K13" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="L13" s="26" t="s">
+      <c r="L13" s="47" t="s">
         <v>237</v>
       </c>
       <c r="M13" s="23" t="s">
@@ -4293,7 +4312,7 @@
         <v>323</v>
       </c>
       <c r="Q13" s="25" t="s">
-        <v>323</v>
+        <v>381</v>
       </c>
       <c r="V13" s="39" t="s">
         <v>247</v>
@@ -4563,28 +4582,28 @@
       <c r="C27" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="P27" s="47"/>
-      <c r="Q27" s="47"/>
+      <c r="P27" s="43"/>
+      <c r="Q27" s="43"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="O28" s="45"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="49"/>
-      <c r="R28" s="46"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="45"/>
+      <c r="R28" s="42"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="O29" s="45"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="49"/>
-      <c r="R29" s="46"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="45"/>
+      <c r="Q29" s="45"/>
+      <c r="R29" s="42"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="O30" s="45"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="49" t="s">
-        <v>380</v>
-      </c>
-      <c r="R30" s="46"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="45"/>
+      <c r="Q30" s="45" t="s">
+        <v>379</v>
+      </c>
+      <c r="R30" s="42"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B31" s="25" t="s">
@@ -4596,12 +4615,12 @@
       <c r="E31" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="O31" s="45"/>
-      <c r="P31" s="49"/>
-      <c r="Q31" s="49" t="s">
-        <v>379</v>
-      </c>
-      <c r="R31" s="46"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="45"/>
+      <c r="Q31" s="45" t="s">
+        <v>378</v>
+      </c>
+      <c r="R31" s="42"/>
     </row>
     <row r="32" spans="1:19" ht="99" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="25" t="s">
@@ -4610,12 +4629,12 @@
       <c r="C32" s="25" t="s">
         <v>254</v>
       </c>
-      <c r="O32" s="45"/>
-      <c r="P32" s="50" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q32" s="49"/>
-      <c r="R32" s="46"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="46" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q32" s="45"/>
+      <c r="R32" s="42"/>
     </row>
     <row r="33" spans="2:18" ht="29" thickTop="1" x14ac:dyDescent="0.5">
       <c r="B33" s="25" t="s">
@@ -4624,10 +4643,10 @@
       <c r="C33" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="O33" s="45"/>
-      <c r="P33" s="49"/>
-      <c r="Q33" s="49"/>
-      <c r="R33" s="46"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="45"/>
+      <c r="Q33" s="45"/>
+      <c r="R33" s="42"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.5">
       <c r="B34" s="25" t="s">
@@ -4636,32 +4655,32 @@
       <c r="C34" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="O34" s="45"/>
-      <c r="P34" s="49"/>
-      <c r="Q34" s="49"/>
-      <c r="R34" s="46"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="45"/>
+      <c r="Q34" s="45"/>
+      <c r="R34" s="42"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.5">
-      <c r="O35" s="45"/>
-      <c r="P35" s="49"/>
-      <c r="Q35" s="49"/>
-      <c r="R35" s="46"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="45"/>
+      <c r="Q35" s="45"/>
+      <c r="R35" s="42"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.5">
-      <c r="O36" s="45"/>
-      <c r="P36" s="49"/>
-      <c r="Q36" s="49"/>
-      <c r="R36" s="46"/>
+      <c r="O36" s="41"/>
+      <c r="P36" s="45"/>
+      <c r="Q36" s="45"/>
+      <c r="R36" s="42"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.5">
-      <c r="O37" s="45"/>
-      <c r="P37" s="49"/>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="46"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="45"/>
+      <c r="Q37" s="45"/>
+      <c r="R37" s="42"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.5">
-      <c r="P38" s="48"/>
-      <c r="Q38" s="48"/>
+      <c r="P38" s="44"/>
+      <c r="Q38" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -4724,26 +4743,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="43" t="s">
+      <c r="F2" s="52" t="s">
         <v>283</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43" t="s">
+      <c r="G2" s="52"/>
+      <c r="H2" s="52" t="s">
         <v>284</v>
       </c>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43" t="s">
+      <c r="I2" s="52"/>
+      <c r="J2" s="52" t="s">
         <v>294</v>
       </c>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43" t="s">
+      <c r="K2" s="52"/>
+      <c r="L2" s="52" t="s">
         <v>320</v>
       </c>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43" t="s">
+      <c r="M2" s="52"/>
+      <c r="N2" s="52" t="s">
         <v>365</v>
       </c>
-      <c r="O2" s="43"/>
+      <c r="O2" s="52"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -6144,26 +6163,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="43" t="s">
+      <c r="F2" s="52" t="s">
         <v>283</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43" t="s">
+      <c r="G2" s="52"/>
+      <c r="H2" s="52" t="s">
         <v>284</v>
       </c>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43" t="s">
+      <c r="I2" s="52"/>
+      <c r="J2" s="52" t="s">
         <v>296</v>
       </c>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43" t="s">
+      <c r="K2" s="52"/>
+      <c r="L2" s="52" t="s">
         <v>320</v>
       </c>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43" t="s">
+      <c r="M2" s="52"/>
+      <c r="N2" s="52" t="s">
         <v>365</v>
       </c>
-      <c r="O2" s="43"/>
+      <c r="O2" s="52"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -7207,26 +7226,26 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="52" t="s">
         <v>283</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43" t="s">
+      <c r="H1" s="52"/>
+      <c r="I1" s="52" t="s">
         <v>284</v>
       </c>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43" t="s">
+      <c r="J1" s="52"/>
+      <c r="K1" s="52" t="s">
         <v>296</v>
       </c>
-      <c r="L1" s="43"/>
-      <c r="M1" s="44" t="s">
+      <c r="L1" s="52"/>
+      <c r="M1" s="53" t="s">
         <v>326</v>
       </c>
-      <c r="N1" s="44"/>
-      <c r="O1" s="43" t="s">
+      <c r="N1" s="53"/>
+      <c r="O1" s="52" t="s">
         <v>365</v>
       </c>
-      <c r="P1" s="43"/>
+      <c r="P1" s="52"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
@@ -8956,18 +8975,18 @@
       <c r="D1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="52" t="s">
         <v>283</v>
       </c>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43" t="s">
+      <c r="F1" s="52"/>
+      <c r="G1" s="52" t="s">
         <v>284</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43" t="s">
+      <c r="H1" s="52"/>
+      <c r="I1" s="52" t="s">
         <v>296</v>
       </c>
-      <c r="J1" s="43"/>
+      <c r="J1" s="52"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1841" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BEE3FB1-E33B-4943-9719-CC1849082F5A}"/>
+  <xr:revisionPtr revIDLastSave="1861" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB0BECB4-FB79-4097-8189-605DC9F4E3FE}"/>
   <bookViews>
     <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1311,7 +1311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1866" uniqueCount="389">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2447,23 +2447,104 @@
     <t>B41M10 - Συναρτήσεις ξανα σχετική και απόλυτη αναφορά</t>
   </si>
   <si>
-    <t>eueuoeuo</t>
-  </si>
-  <si>
-    <t>ueeueuo</t>
-  </si>
-  <si>
-    <t>Maria test</t>
-  </si>
-  <si>
     <t>B41M13 - Δημιουργία Γραφημάτων</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Last chapter taught</t>
+  </si>
+  <si>
+    <r>
+      <t>A5.2 Μ2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Διαχείριση Ηλεκτρονικού Ταχυδρομείου — ΦΕ Εμπέδωσης</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A5.2 Μ3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Διαχείριση Ηλεκτρονικού Ταχυδρομείου — Επισύναψη</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B41M11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Βασική Μορφοποίηση Υπολογιστικού Φύλλου</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B41M9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Εισαγωγή στις Συναρτήσεις</t>
+    </r>
+  </si>
+  <si>
+    <t>Επανάληψη A5 – Δίκτυα και Ασφάλεια</t>
+  </si>
+  <si>
+    <r>
+      <t>Α.5.M5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Ασφάλεια</t>
+    </r>
+  </si>
+  <si>
+    <t>PowerPoint – Create star</t>
+  </si>
+  <si>
+    <t>B41M14 - Επεξεργασία Γραφημάτων</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2535,21 +2616,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="16">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2628,19 +2703,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="8">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2690,30 +2754,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -2726,25 +2766,10 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2862,17 +2887,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="180" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2881,6 +2897,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2896,9 +2921,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="60% - Accent6" xfId="3" builtinId="52"/>
-    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+  <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -3691,7 +3714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH38"/>
+  <dimension ref="A1:BH37"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="11.41015625" style="30" bestFit="1" customWidth="1"/>
@@ -3707,7 +3730,7 @@
     <col min="13" max="13" width="53.1171875" style="25" customWidth="1"/>
     <col min="14" max="14" width="43.05859375" style="25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="47.8203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="40.3515625" style="25" customWidth="1"/>
+    <col min="16" max="16" width="36.1171875" style="25" customWidth="1"/>
     <col min="17" max="17" width="28.41015625" style="25" customWidth="1"/>
     <col min="18" max="18" width="26.41015625" style="25" customWidth="1"/>
     <col min="19" max="19" width="25.64453125" style="25" customWidth="1"/>
@@ -3918,7 +3941,7 @@
       <c r="K4" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="L4" s="47" t="s">
+      <c r="L4" s="44" t="s">
         <v>237</v>
       </c>
       <c r="M4" s="23" t="s">
@@ -3933,7 +3956,7 @@
       <c r="P4" s="25" t="s">
         <v>371</v>
       </c>
-      <c r="Q4" s="47" t="s">
+      <c r="Q4" s="44" t="s">
         <v>282</v>
       </c>
       <c r="R4" s="25" t="s">
@@ -3992,7 +4015,7 @@
       <c r="P5" s="25" t="s">
         <v>353</v>
       </c>
-      <c r="Q5" s="47" t="s">
+      <c r="Q5" s="44" t="s">
         <v>282</v>
       </c>
       <c r="R5" s="25" t="s">
@@ -4048,10 +4071,10 @@
       <c r="O6" s="23" t="s">
         <v>370</v>
       </c>
-      <c r="P6" s="25" t="s">
+      <c r="P6" s="23" t="s">
         <v>371</v>
       </c>
-      <c r="Q6" s="48" t="s">
+      <c r="Q6" s="45" t="s">
         <v>282</v>
       </c>
       <c r="R6" s="25" t="s">
@@ -4110,7 +4133,7 @@
       <c r="K7" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="L7" s="47" t="s">
+      <c r="L7" s="44" t="s">
         <v>237</v>
       </c>
       <c r="M7" s="23" t="s">
@@ -4122,7 +4145,7 @@
       <c r="O7" s="23" t="s">
         <v>370</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="P7" s="23" t="s">
         <v>371</v>
       </c>
       <c r="Q7" s="25" t="s">
@@ -4142,7 +4165,7 @@
       <c r="C10" s="25" t="s">
         <v>339</v>
       </c>
-      <c r="L10" s="49"/>
+      <c r="L10" s="46"/>
       <c r="M10" s="25" t="s">
         <v>302</v>
       </c>
@@ -4181,7 +4204,7 @@
       <c r="K11" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="L11" s="47" t="s">
+      <c r="L11" s="44" t="s">
         <v>237</v>
       </c>
       <c r="M11" s="23" t="s">
@@ -4193,20 +4216,26 @@
       <c r="O11" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="P11" s="25" t="s">
+      <c r="P11" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="Q11" s="48" t="s">
+      <c r="Q11" s="45" t="s">
         <v>282</v>
       </c>
       <c r="R11" s="25" t="s">
         <v>323</v>
       </c>
+      <c r="T11" s="39" t="s">
+        <v>295</v>
+      </c>
+      <c r="U11" s="39" t="s">
+        <v>295</v>
+      </c>
       <c r="V11" s="39" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="12" spans="1:60" ht="43" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:60" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A12" s="30" t="s">
         <v>7</v>
       </c>
@@ -4240,7 +4269,7 @@
       <c r="K12" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="L12" s="47" t="s">
+      <c r="L12" s="44" t="s">
         <v>237</v>
       </c>
       <c r="M12" s="23" t="s">
@@ -4252,11 +4281,23 @@
       <c r="O12" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="P12" s="25" t="s">
+      <c r="P12" s="23" t="s">
         <v>377</v>
       </c>
       <c r="Q12" s="25" t="s">
         <v>322</v>
+      </c>
+      <c r="R12" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="S12" s="25" t="s">
+        <v>388</v>
+      </c>
+      <c r="T12" s="39" t="s">
+        <v>295</v>
+      </c>
+      <c r="U12" s="39" t="s">
+        <v>295</v>
       </c>
       <c r="V12" s="39" t="s">
         <v>247</v>
@@ -4296,7 +4337,7 @@
       <c r="K13" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="L13" s="47" t="s">
+      <c r="L13" s="44" t="s">
         <v>237</v>
       </c>
       <c r="M13" s="23" t="s">
@@ -4308,11 +4349,20 @@
       <c r="O13" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="P13" s="25" t="s">
+      <c r="P13" s="23" t="s">
         <v>323</v>
       </c>
       <c r="Q13" s="25" t="s">
-        <v>381</v>
+        <v>378</v>
+      </c>
+      <c r="R13" s="25" t="s">
+        <v>388</v>
+      </c>
+      <c r="T13" s="39" t="s">
+        <v>295</v>
+      </c>
+      <c r="U13" s="39" t="s">
+        <v>295</v>
       </c>
       <c r="V13" s="39" t="s">
         <v>247</v>
@@ -4514,12 +4564,6 @@
       <c r="G21" s="26"/>
       <c r="H21" s="23"/>
       <c r="I21" s="26"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="27"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="27"/>
-      <c r="Q21" s="27"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.5">
       <c r="A22" s="30" t="s">
@@ -4587,22 +4631,14 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.5">
       <c r="O28" s="41"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="45"/>
       <c r="R28" s="42"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.5">
       <c r="O29" s="41"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="45"/>
       <c r="R29" s="42"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.5">
       <c r="O30" s="41"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="45" t="s">
-        <v>379</v>
-      </c>
       <c r="R30" s="42"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.5">
@@ -4616,13 +4652,9 @@
         <v>26</v>
       </c>
       <c r="O31" s="41"/>
-      <c r="P31" s="45"/>
-      <c r="Q31" s="45" t="s">
-        <v>378</v>
-      </c>
       <c r="R31" s="42"/>
     </row>
-    <row r="32" spans="1:19" ht="99" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.5">
       <c r="B32" s="25" t="s">
         <v>22</v>
       </c>
@@ -4630,13 +4662,9 @@
         <v>254</v>
       </c>
       <c r="O32" s="41"/>
-      <c r="P32" s="46" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q32" s="45"/>
       <c r="R32" s="42"/>
     </row>
-    <row r="33" spans="2:18" ht="29" thickTop="1" x14ac:dyDescent="0.5">
+    <row r="33" spans="2:18" ht="28.7" x14ac:dyDescent="0.5">
       <c r="B33" s="25" t="s">
         <v>23</v>
       </c>
@@ -4644,8 +4672,6 @@
         <v>36</v>
       </c>
       <c r="O33" s="41"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="45"/>
       <c r="R33" s="42"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.5">
@@ -4656,31 +4682,19 @@
         <v>281</v>
       </c>
       <c r="O34" s="41"/>
-      <c r="P34" s="45"/>
-      <c r="Q34" s="45"/>
       <c r="R34" s="42"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.5">
       <c r="O35" s="41"/>
-      <c r="P35" s="45"/>
-      <c r="Q35" s="45"/>
       <c r="R35" s="42"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.5">
       <c r="O36" s="41"/>
-      <c r="P36" s="45"/>
-      <c r="Q36" s="45"/>
       <c r="R36" s="42"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.5">
       <c r="O37" s="41"/>
-      <c r="P37" s="45"/>
-      <c r="Q37" s="45"/>
       <c r="R37" s="42"/>
-    </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.5">
-      <c r="P38" s="44"/>
-      <c r="Q38" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -8846,10 +8860,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23D143C4-24B5-4F25-A9AC-CA5F9ACC8C3E}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="49.87890625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.76171875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="57.76171875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.9375" customWidth="1"/>
     <col min="9" max="9" width="6.5859375" customWidth="1"/>
@@ -8940,6 +8955,102 @@
       </c>
       <c r="B19" t="s">
         <v>364</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A23" s="47" t="s">
+        <v>379</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A24" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="49" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A25" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="49" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A26" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A27" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="49" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A28" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="49" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A29" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="49" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A30" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="49" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A31" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="49" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A32" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="49" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A33" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="49" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A34" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="49" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -9469,6 +9580,7 @@
       <c r="E24" s="19" t="s">
         <v>231</v>
       </c>
+      <c r="F24" s="20"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4">
@@ -9486,6 +9598,9 @@
       <c r="E25" s="6" t="s">
         <v>171</v>
       </c>
+      <c r="F25" s="6" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4">
@@ -9523,6 +9638,7 @@
       <c r="E27" s="19" t="s">
         <v>231</v>
       </c>
+      <c r="F27" s="20"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4" t="s">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1861" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB0BECB4-FB79-4097-8189-605DC9F4E3FE}"/>
+  <xr:revisionPtr revIDLastSave="1880" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61A2874D-444F-480B-9C1A-7110F256F582}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -1311,7 +1311,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1866" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="394">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2538,6 +2538,21 @@
   </si>
   <si>
     <t>B41M14 - Επεξεργασία Γραφημάτων</t>
+  </si>
+  <si>
+    <t>ΣΧΟΛΙΚΗ ΓΙΟΡΤΗ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>26-30/10 2026</t>
+  </si>
+  <si>
+    <t>hw ask.7-13, p146, via email</t>
+  </si>
+  <si>
+    <t>hw. Ex 1-17, A52M3</t>
   </si>
 </sst>
 </file>
@@ -2771,7 +2786,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2908,6 +2923,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2919,6 +2937,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3746,58 +3767,58 @@
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="28"/>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="50" t="s">
+      <c r="C1" s="52"/>
+      <c r="D1" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="50" t="s">
+      <c r="E1" s="52"/>
+      <c r="F1" s="51" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="50" t="s">
+      <c r="G1" s="52"/>
+      <c r="H1" s="51" t="s">
         <v>239</v>
       </c>
-      <c r="I1" s="51"/>
-      <c r="J1" s="50" t="s">
+      <c r="I1" s="52"/>
+      <c r="J1" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="K1" s="51"/>
-      <c r="L1" s="50" t="s">
+      <c r="K1" s="52"/>
+      <c r="L1" s="51" t="s">
         <v>246</v>
       </c>
-      <c r="M1" s="51"/>
-      <c r="N1" s="50" t="s">
+      <c r="M1" s="52"/>
+      <c r="N1" s="51" t="s">
         <v>345</v>
       </c>
-      <c r="O1" s="51"/>
-      <c r="P1" s="50" t="s">
+      <c r="O1" s="52"/>
+      <c r="P1" s="51" t="s">
         <v>346</v>
       </c>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="50" t="s">
+      <c r="Q1" s="52"/>
+      <c r="R1" s="51" t="s">
         <v>348</v>
       </c>
-      <c r="S1" s="51"/>
-      <c r="T1" s="50" t="s">
+      <c r="S1" s="52"/>
+      <c r="T1" s="51" t="s">
         <v>349</v>
       </c>
-      <c r="U1" s="51"/>
-      <c r="V1" s="50" t="s">
+      <c r="U1" s="52"/>
+      <c r="V1" s="51" t="s">
         <v>350</v>
       </c>
-      <c r="W1" s="51"/>
-      <c r="X1" s="50" t="s">
+      <c r="W1" s="52"/>
+      <c r="X1" s="51" t="s">
         <v>351</v>
       </c>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="50" t="s">
+      <c r="Y1" s="52"/>
+      <c r="Z1" s="51" t="s">
         <v>352</v>
       </c>
-      <c r="AA1" s="51"/>
+      <c r="AA1" s="52"/>
       <c r="AB1" s="29"/>
       <c r="AC1" s="29"/>
       <c r="AD1" s="29"/>
@@ -4012,7 +4033,7 @@
       <c r="O5" s="23" t="s">
         <v>371</v>
       </c>
-      <c r="P5" s="25" t="s">
+      <c r="P5" s="23" t="s">
         <v>353</v>
       </c>
       <c r="Q5" s="44" t="s">
@@ -4219,7 +4240,7 @@
       <c r="P11" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="Q11" s="45" t="s">
+      <c r="Q11" s="50" t="s">
         <v>282</v>
       </c>
       <c r="R11" s="25" t="s">
@@ -4352,8 +4373,8 @@
       <c r="P13" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="Q13" s="25" t="s">
-        <v>378</v>
+      <c r="Q13" s="23" t="s">
+        <v>390</v>
       </c>
       <c r="R13" s="25" t="s">
         <v>388</v>
@@ -4379,12 +4400,12 @@
         <v>236</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.5">
       <c r="H17" s="33" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:20" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A18" s="30" t="s">
         <v>14</v>
       </c>
@@ -4430,7 +4451,7 @@
       <c r="O18" s="23" t="s">
         <v>372</v>
       </c>
-      <c r="P18" s="36" t="s">
+      <c r="P18" s="23" t="s">
         <v>247</v>
       </c>
       <c r="Q18" s="27" t="s">
@@ -4440,7 +4461,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:20" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A19" s="30" t="s">
         <v>16</v>
       </c>
@@ -4486,17 +4507,20 @@
       <c r="O19" s="23" t="s">
         <v>372</v>
       </c>
-      <c r="P19" s="36" t="s">
-        <v>247</v>
+      <c r="P19" s="50" t="s">
+        <v>389</v>
       </c>
       <c r="Q19" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="R19" s="27" t="s">
+      <c r="R19" s="36" t="s">
+        <v>247</v>
+      </c>
+      <c r="S19" s="27" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="28.7" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:20" ht="28.7" x14ac:dyDescent="0.5">
       <c r="A20" s="30" t="s">
         <v>15</v>
       </c>
@@ -4542,20 +4566,23 @@
       <c r="O20" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="P20" s="36" t="s">
+      <c r="P20" s="50" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q20" s="36" t="s">
         <v>295</v>
       </c>
-      <c r="Q20" s="36" t="s">
+      <c r="R20" s="36" t="s">
         <v>247</v>
       </c>
-      <c r="R20" s="27" t="s">
+      <c r="S20" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="S20" s="27" t="s">
+      <c r="T20" s="27" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.5">
       <c r="B21" s="32"/>
       <c r="C21" s="34"/>
       <c r="D21" s="35"/>
@@ -4565,7 +4592,7 @@
       <c r="H21" s="23"/>
       <c r="I21" s="26"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.5">
       <c r="A22" s="30" t="s">
         <v>10</v>
       </c>
@@ -4601,27 +4628,27 @@
         <v>374</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.5">
       <c r="B23" s="32"/>
       <c r="C23" s="32"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.5">
       <c r="B24" s="32"/>
       <c r="C24" s="32"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.5">
       <c r="B25" s="37"/>
       <c r="C25" s="25" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.5">
       <c r="B26" s="34"/>
       <c r="C26" s="25" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.5">
       <c r="B27" s="27"/>
       <c r="C27" s="25" t="s">
         <v>29</v>
@@ -4629,19 +4656,19 @@
       <c r="P27" s="43"/>
       <c r="Q27" s="43"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.5">
       <c r="O28" s="41"/>
       <c r="R28" s="42"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.5">
       <c r="O29" s="41"/>
       <c r="R29" s="42"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.5">
       <c r="O30" s="41"/>
       <c r="R30" s="42"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.5">
       <c r="B31" s="25" t="s">
         <v>21</v>
       </c>
@@ -4654,7 +4681,7 @@
       <c r="O31" s="41"/>
       <c r="R31" s="42"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.5">
       <c r="B32" s="25" t="s">
         <v>22</v>
       </c>
@@ -4737,7 +4764,7 @@
     <col min="11" max="11" width="18.9375" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.64453125" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.87890625" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.05859375" style="4"/>
+    <col min="14" max="14" width="17.64453125" style="4" customWidth="1"/>
     <col min="15" max="15" width="16.87890625" style="4" customWidth="1"/>
     <col min="16" max="16384" width="9.05859375" style="4"/>
   </cols>
@@ -4757,26 +4784,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="53" t="s">
         <v>283</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52" t="s">
+      <c r="G2" s="53"/>
+      <c r="H2" s="53" t="s">
         <v>284</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52" t="s">
+      <c r="I2" s="53"/>
+      <c r="J2" s="53" t="s">
         <v>294</v>
       </c>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52" t="s">
+      <c r="K2" s="53"/>
+      <c r="L2" s="53" t="s">
         <v>320</v>
       </c>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52" t="s">
-        <v>365</v>
-      </c>
-      <c r="O2" s="52"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53" t="s">
+        <v>391</v>
+      </c>
+      <c r="O2" s="53"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -5103,7 +5130,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:15" ht="31.35" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="4" t="s">
         <v>72</v>
       </c>
@@ -5121,6 +5148,9 @@
       </c>
       <c r="L15" s="4" t="s">
         <v>328</v>
+      </c>
+      <c r="N15" s="55" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -6177,26 +6207,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="53" t="s">
         <v>283</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52" t="s">
+      <c r="G2" s="53"/>
+      <c r="H2" s="53" t="s">
         <v>284</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52" t="s">
+      <c r="I2" s="53"/>
+      <c r="J2" s="53" t="s">
         <v>296</v>
       </c>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52" t="s">
+      <c r="K2" s="53"/>
+      <c r="L2" s="53" t="s">
         <v>320</v>
       </c>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52" t="s">
+      <c r="M2" s="53"/>
+      <c r="N2" s="53" t="s">
         <v>365</v>
       </c>
-      <c r="O2" s="52"/>
+      <c r="O2" s="53"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -7240,26 +7270,26 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="52" t="s">
+      <c r="G1" s="53" t="s">
         <v>283</v>
       </c>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52" t="s">
+      <c r="H1" s="53"/>
+      <c r="I1" s="53" t="s">
         <v>284</v>
       </c>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52" t="s">
+      <c r="J1" s="53"/>
+      <c r="K1" s="53" t="s">
         <v>296</v>
       </c>
-      <c r="L1" s="52"/>
-      <c r="M1" s="53" t="s">
+      <c r="L1" s="53"/>
+      <c r="M1" s="54" t="s">
         <v>326</v>
       </c>
-      <c r="N1" s="53"/>
-      <c r="O1" s="52" t="s">
+      <c r="N1" s="54"/>
+      <c r="O1" s="53" t="s">
         <v>365</v>
       </c>
-      <c r="P1" s="52"/>
+      <c r="P1" s="53"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
@@ -9086,18 +9116,18 @@
       <c r="D1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="53" t="s">
         <v>283</v>
       </c>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52" t="s">
+      <c r="F1" s="53"/>
+      <c r="G1" s="53" t="s">
         <v>284</v>
       </c>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52" t="s">
+      <c r="H1" s="53"/>
+      <c r="I1" s="53" t="s">
         <v>296</v>
       </c>
-      <c r="J1" s="52"/>
+      <c r="J1" s="53"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
@@ -9211,7 +9241,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FEE7927-B2CB-4F8C-B929-249864A39417}">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.3515625" style="4" bestFit="1" customWidth="1"/>
@@ -9220,10 +9250,11 @@
     <col min="4" max="4" width="14.17578125" style="4" customWidth="1"/>
     <col min="5" max="5" width="10.234375" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.41015625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.05859375" style="4"/>
+    <col min="7" max="7" width="14.87890625" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="9.05859375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="7" t="s">
         <v>57</v>
       </c>
@@ -9237,7 +9268,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>121</v>
       </c>
@@ -9248,7 +9279,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4">
         <v>9285104</v>
       </c>
@@ -9265,7 +9296,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4">
         <v>8324104</v>
       </c>
@@ -9282,7 +9313,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4">
         <v>6811804</v>
       </c>
@@ -9297,7 +9328,7 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="4">
         <v>5436904</v>
       </c>
@@ -9314,7 +9345,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4">
         <v>7025704</v>
       </c>
@@ -9331,7 +9362,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="4">
         <v>8435804</v>
       </c>
@@ -9348,7 +9379,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4">
         <v>5069104</v>
       </c>
@@ -9365,7 +9396,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4">
         <v>5222304</v>
       </c>
@@ -9382,7 +9413,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4">
         <v>1981204</v>
       </c>
@@ -9399,7 +9430,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="4">
         <v>3766704</v>
       </c>
@@ -9416,12 +9447,15 @@
         <v>171</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:7" ht="47" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4" t="s">
         <v>72</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>276</v>
+      </c>
+      <c r="G16" s="55" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -10856,7 +10890,7 @@
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>309</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.5">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1880" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61A2874D-444F-480B-9C1A-7110F256F582}"/>
+  <xr:revisionPtr revIDLastSave="1970" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC5BFB8A-094B-4BE3-B44D-D5AE53FB2C31}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="15" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="A Gymansiou - tests" sheetId="11" r:id="rId7"/>
     <sheet name="B Gymnasiou -tests" sheetId="13" r:id="rId8"/>
     <sheet name="A Lyceum - tests" sheetId="12" r:id="rId9"/>
+    <sheet name="odikos diorthosis" sheetId="14" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -583,6 +584,7 @@
     <author>tc={B7F8AA97-EF7A-4346-BFE7-BFF2EEB2C1DB}</author>
     <author>tc={D7246692-A47D-44D0-B75A-AD5BAC8A45F7}</author>
     <author>tc={7768E2F5-6F98-401C-9CE0-F5514C8493B1}</author>
+    <author>tc={5A77E0AC-024E-461D-9046-EF3ADCAECE02}</author>
     <author>tc={2EB8A751-6FC9-43E4-BEFE-D7B2A37941A4}</author>
     <author>tc={BEA4804D-72CD-494C-BE39-4999EABE6959}</author>
   </authors>
@@ -692,7 +694,16 @@
     Kori tis Lelias</t>
       </text>
     </comment>
-    <comment ref="C42" authorId="12" shapeId="0" xr:uid="{2EB8A751-6FC9-43E4-BEFE-D7B2A37941A4}">
+    <comment ref="S41" authorId="12" shapeId="0" xr:uid="{5A77E0AC-024E-461D-9046-EF3ADCAECE02}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Only he brought his exercises
+</t>
+      </text>
+    </comment>
+    <comment ref="C42" authorId="13" shapeId="0" xr:uid="{2EB8A751-6FC9-43E4-BEFE-D7B2A37941A4}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -701,7 +712,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="C43" authorId="13" shapeId="0" xr:uid="{BEA4804D-72CD-494C-BE39-4999EABE6959}">
+    <comment ref="C43" authorId="14" shapeId="0" xr:uid="{BEA4804D-72CD-494C-BE39-4999EABE6959}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1311,7 +1322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="424">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2554,12 +2565,106 @@
   <si>
     <t>hw. Ex 1-17, A52M3</t>
   </si>
+  <si>
+    <t>Πρόγραμμα συνάντησης Γονέων με τους-τις Εκπαιδευτικούς - Α Τετραμήνου</t>
+  </si>
+  <si>
+    <t>2026-10-27-sxoliki-giorti-28-octombriou</t>
+  </si>
+  <si>
+    <t>ethniki-epeteios-28octovriou-2026</t>
+  </si>
+  <si>
+    <t>A Lykeiou</t>
+  </si>
+  <si>
+    <t>A Omada</t>
+  </si>
+  <si>
+    <t>B Omada</t>
+  </si>
+  <si>
+    <t>1 - LAN</t>
+  </si>
+  <si>
+    <t>2 - Switch</t>
+  </si>
+  <si>
+    <t>3 - ipconfig</t>
+  </si>
+  <si>
+    <t>4 - filewall</t>
+  </si>
+  <si>
+    <t>5 - metatrepei domain names se IP Addresses</t>
+  </si>
+  <si>
+    <t>6 - Γ - Β - Α - Δ</t>
+  </si>
+  <si>
+    <t>7. 3</t>
+  </si>
+  <si>
+    <t>8-b</t>
+  </si>
+  <si>
+    <t>13 - LAN - IP Address - Router - Phishing</t>
+  </si>
+  <si>
+    <t>14 - NO - Nai thelei router</t>
+  </si>
+  <si>
+    <t>1 - Firewall</t>
+  </si>
+  <si>
+    <t>2 - metatrepei domain names se IP Addresses</t>
+  </si>
+  <si>
+    <t>3 - switch</t>
+  </si>
+  <si>
+    <t>4 - LAN</t>
+  </si>
+  <si>
+    <t>5 - ipconfig</t>
+  </si>
+  <si>
+    <t>6- web browser</t>
+  </si>
+  <si>
+    <t>7-d</t>
+  </si>
+  <si>
+    <t>9-web browser</t>
+  </si>
+  <si>
+    <t>8-a</t>
+  </si>
+  <si>
+    <t>9 - Switch - Router - Modem - Access Point</t>
+  </si>
+  <si>
+    <t>11 - Phishing - Ip Address - LAN - Router</t>
+  </si>
+  <si>
+    <t>12 - NO - Nai thelei router</t>
+  </si>
+  <si>
+    <t>simple network</t>
+  </si>
+  <si>
+    <t>Διαβάζουμε βιβλίο και συζητούμε την ιστορία</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2638,8 +2743,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2718,6 +2838,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -2782,11 +2908,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2908,9 +3035,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2926,23 +3050,30 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -3483,6 +3614,10 @@
   <threadedComment ref="C38" dT="2026-09-22T09:33:38.73" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7768E2F5-6F98-401C-9CE0-F5514C8493B1}">
     <text>Kori tis Lelias</text>
   </threadedComment>
+  <threadedComment ref="S41" dT="2026-10-29T12:34:45.86" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{5A77E0AC-024E-461D-9046-EF3ADCAECE02}">
+    <text xml:space="preserve">Only he brought his exercises
+</text>
+  </threadedComment>
   <threadedComment ref="C42" dT="2026-09-17T05:53:15.67" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2EB8A751-6FC9-43E4-BEFE-D7B2A37941A4}">
     <text xml:space="preserve">Filotimos
 </text>
@@ -3767,58 +3902,58 @@
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="28"/>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="51" t="s">
+      <c r="C1" s="55"/>
+      <c r="D1" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="52"/>
-      <c r="F1" s="51" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="54" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="52"/>
-      <c r="H1" s="51" t="s">
+      <c r="G1" s="55"/>
+      <c r="H1" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="I1" s="52"/>
-      <c r="J1" s="51" t="s">
+      <c r="I1" s="55"/>
+      <c r="J1" s="54" t="s">
         <v>243</v>
       </c>
-      <c r="K1" s="52"/>
-      <c r="L1" s="51" t="s">
+      <c r="K1" s="55"/>
+      <c r="L1" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="M1" s="52"/>
-      <c r="N1" s="51" t="s">
+      <c r="M1" s="55"/>
+      <c r="N1" s="54" t="s">
         <v>345</v>
       </c>
-      <c r="O1" s="52"/>
-      <c r="P1" s="51" t="s">
+      <c r="O1" s="55"/>
+      <c r="P1" s="54" t="s">
         <v>346</v>
       </c>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="51" t="s">
+      <c r="Q1" s="55"/>
+      <c r="R1" s="54" t="s">
         <v>348</v>
       </c>
-      <c r="S1" s="52"/>
-      <c r="T1" s="51" t="s">
+      <c r="S1" s="55"/>
+      <c r="T1" s="54" t="s">
         <v>349</v>
       </c>
-      <c r="U1" s="52"/>
-      <c r="V1" s="51" t="s">
+      <c r="U1" s="55"/>
+      <c r="V1" s="54" t="s">
         <v>350</v>
       </c>
-      <c r="W1" s="52"/>
-      <c r="X1" s="51" t="s">
+      <c r="W1" s="55"/>
+      <c r="X1" s="54" t="s">
         <v>351</v>
       </c>
-      <c r="Y1" s="52"/>
-      <c r="Z1" s="51" t="s">
+      <c r="Y1" s="55"/>
+      <c r="Z1" s="54" t="s">
         <v>352</v>
       </c>
-      <c r="AA1" s="52"/>
+      <c r="AA1" s="55"/>
       <c r="AB1" s="29"/>
       <c r="AC1" s="29"/>
       <c r="AD1" s="29"/>
@@ -3974,7 +4109,7 @@
       <c r="O4" s="23" t="s">
         <v>370</v>
       </c>
-      <c r="P4" s="25" t="s">
+      <c r="P4" s="23" t="s">
         <v>371</v>
       </c>
       <c r="Q4" s="44" t="s">
@@ -4092,11 +4227,11 @@
       <c r="O6" s="23" t="s">
         <v>370</v>
       </c>
-      <c r="P6" s="23" t="s">
+      <c r="P6" s="44" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q6" s="25" t="s">
         <v>371</v>
-      </c>
-      <c r="Q6" s="45" t="s">
-        <v>282</v>
       </c>
       <c r="R6" s="25" t="s">
         <v>353</v>
@@ -4186,7 +4321,7 @@
       <c r="C10" s="25" t="s">
         <v>339</v>
       </c>
-      <c r="L10" s="46"/>
+      <c r="L10" s="45"/>
       <c r="M10" s="25" t="s">
         <v>302</v>
       </c>
@@ -4240,7 +4375,7 @@
       <c r="P11" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="Q11" s="50" t="s">
+      <c r="Q11" s="49" t="s">
         <v>282</v>
       </c>
       <c r="R11" s="25" t="s">
@@ -4507,7 +4642,7 @@
       <c r="O19" s="23" t="s">
         <v>372</v>
       </c>
-      <c r="P19" s="50" t="s">
+      <c r="P19" s="49" t="s">
         <v>389</v>
       </c>
       <c r="Q19" s="27" t="s">
@@ -4566,7 +4701,7 @@
       <c r="O20" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="P20" s="50" t="s">
+      <c r="P20" s="49" t="s">
         <v>389</v>
       </c>
       <c r="Q20" s="36" t="s">
@@ -4743,6 +4878,125 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B796910D-7266-49FF-ACC0-0BCFD5AA50E9}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="36.64453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A2" s="25" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A5" t="s">
+        <v>401</v>
+      </c>
+      <c r="B5" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B6" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A7" t="s">
+        <v>403</v>
+      </c>
+      <c r="B7" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A8" t="s">
+        <v>404</v>
+      </c>
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A9" t="s">
+        <v>405</v>
+      </c>
+      <c r="B9" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A10" s="51" t="s">
+        <v>406</v>
+      </c>
+      <c r="B10" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A11" t="s">
+        <v>407</v>
+      </c>
+      <c r="B11" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A12" t="s">
+        <v>417</v>
+      </c>
+      <c r="B12" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A13" t="s">
+        <v>408</v>
+      </c>
+      <c r="B13" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A14" t="s">
+        <v>409</v>
+      </c>
+      <c r="B14" t="s">
+        <v>421</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -4784,26 +5038,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="52" t="s">
         <v>283</v>
       </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53" t="s">
+      <c r="G2" s="52"/>
+      <c r="H2" s="52" t="s">
         <v>284</v>
       </c>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53" t="s">
+      <c r="I2" s="52"/>
+      <c r="J2" s="52" t="s">
         <v>294</v>
       </c>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53" t="s">
+      <c r="K2" s="52"/>
+      <c r="L2" s="52" t="s">
         <v>320</v>
       </c>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53" t="s">
+      <c r="M2" s="52"/>
+      <c r="N2" s="52" t="s">
         <v>391</v>
       </c>
-      <c r="O2" s="53"/>
+      <c r="O2" s="52"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -5149,7 +5403,7 @@
       <c r="L15" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="N15" s="55" t="s">
+      <c r="N15" s="50" t="s">
         <v>392</v>
       </c>
     </row>
@@ -6207,26 +6461,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="52" t="s">
         <v>283</v>
       </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53" t="s">
+      <c r="G2" s="52"/>
+      <c r="H2" s="52" t="s">
         <v>284</v>
       </c>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53" t="s">
+      <c r="I2" s="52"/>
+      <c r="J2" s="52" t="s">
         <v>296</v>
       </c>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53" t="s">
+      <c r="K2" s="52"/>
+      <c r="L2" s="52" t="s">
         <v>320</v>
       </c>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53" t="s">
+      <c r="M2" s="52"/>
+      <c r="N2" s="52" t="s">
         <v>365</v>
       </c>
-      <c r="O2" s="53"/>
+      <c r="O2" s="52"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -7243,7 +7497,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF640171-D19A-4A22-AEE9-A5E7AF0F79D2}">
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="7.703125" bestFit="1" customWidth="1"/>
@@ -7257,7 +7511,7 @@
     <col min="15" max="15" width="15.9375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -7270,28 +7524,32 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="53" t="s">
+      <c r="G1" s="52" t="s">
         <v>283</v>
       </c>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53" t="s">
+      <c r="H1" s="52"/>
+      <c r="I1" s="52" t="s">
         <v>284</v>
       </c>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53" t="s">
+      <c r="J1" s="52"/>
+      <c r="K1" s="52" t="s">
         <v>296</v>
       </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="54" t="s">
+      <c r="L1" s="52"/>
+      <c r="M1" s="53" t="s">
         <v>326</v>
       </c>
-      <c r="N1" s="54"/>
-      <c r="O1" s="53" t="s">
+      <c r="N1" s="53"/>
+      <c r="O1" s="52" t="s">
         <v>365</v>
       </c>
-      <c r="P1" s="53"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.5">
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52" t="s">
+        <v>391</v>
+      </c>
+      <c r="R1" s="52"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -7305,7 +7563,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>4206804</v>
       </c>
@@ -7352,7 +7610,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:18" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>9307104</v>
       </c>
@@ -7399,7 +7657,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:18" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>2173704</v>
       </c>
@@ -7446,7 +7704,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:18" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>9257304</v>
       </c>
@@ -7493,7 +7751,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:18" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>2915404</v>
       </c>
@@ -7540,7 +7798,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:18" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>2836604</v>
       </c>
@@ -7587,7 +7845,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:18" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>1274904</v>
       </c>
@@ -7634,7 +7892,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:18" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>3863304</v>
       </c>
@@ -7679,7 +7937,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:18" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>3403504</v>
       </c>
@@ -7726,7 +7984,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:18" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>4721304</v>
       </c>
@@ -7771,7 +8029,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:18" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>3924304</v>
       </c>
@@ -7818,7 +8076,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>4041704</v>
       </c>
@@ -7865,7 +8123,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:18" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>9280704</v>
       </c>
@@ -8407,7 +8665,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:19" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>9289704</v>
       </c>
@@ -8448,8 +8706,11 @@
       <c r="P33" s="14" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="S33" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>9344404</v>
       </c>
@@ -8488,8 +8749,11 @@
       <c r="P34" s="14" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="S34" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>6746404</v>
       </c>
@@ -8530,8 +8794,11 @@
       <c r="P35" s="40" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="S35" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>9257604</v>
       </c>
@@ -8574,8 +8841,11 @@
       <c r="P36" s="40" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="S36" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>9717204</v>
       </c>
@@ -8616,8 +8886,11 @@
       <c r="P37" s="40" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="S37" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>2298204</v>
       </c>
@@ -8656,8 +8929,11 @@
       <c r="P38" s="14" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="S38" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>5784804</v>
       </c>
@@ -8700,8 +8976,11 @@
       <c r="P39" s="40" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="S39" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>9321704</v>
       </c>
@@ -8742,8 +9021,11 @@
       <c r="P40" s="40" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="S40" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>9720304</v>
       </c>
@@ -8786,8 +9068,11 @@
       <c r="P41" s="40" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="S41" s="40" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>9317404</v>
       </c>
@@ -8828,8 +9113,11 @@
       <c r="P42" s="40" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" ht="15.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="S42" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="15.7" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>8333604</v>
       </c>
@@ -8872,9 +9160,13 @@
       <c r="P43" s="40" t="s">
         <v>171</v>
       </c>
+      <c r="S43" s="8" t="s">
+        <v>231</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="Q1:R1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
@@ -8895,7 +9187,7 @@
   <cols>
     <col min="1" max="1" width="49.87890625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46.76171875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.76171875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.41015625" customWidth="1"/>
     <col min="7" max="7" width="8.9375" customWidth="1"/>
     <col min="9" max="9" width="6.5859375" customWidth="1"/>
   </cols>
@@ -8958,20 +9250,31 @@
         <v>332</v>
       </c>
     </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="C15" s="56">
+        <v>6</v>
+      </c>
+    </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="C16" s="58">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="43.35" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
         <v>267</v>
       </c>
       <c r="B17" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="C17" s="57" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
         <v>362</v>
       </c>
@@ -8979,7 +9282,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
         <v>363</v>
       </c>
@@ -8987,99 +9290,112 @@
         <v>364</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A23" s="47" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A21" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A22" t="s">
+        <v>395</v>
+      </c>
+      <c r="B22" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A23" s="46" t="s">
         <v>379</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="46" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A24" s="48" t="s">
+    <row r="24" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A24" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="49" t="s">
+      <c r="B24" s="48" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A25" s="48" t="s">
+    <row r="25" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A25" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="49" t="s">
+      <c r="B25" s="48" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A26" s="48" t="s">
+    <row r="26" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A26" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="48" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="28.7" x14ac:dyDescent="0.5">
-      <c r="A27" s="48" t="s">
+    <row r="27" spans="1:3" ht="28.7" x14ac:dyDescent="0.5">
+      <c r="A27" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="48" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A28" s="48" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A28" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="49" t="s">
+      <c r="B28" s="48" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A29" s="48" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A29" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="49" t="s">
+      <c r="B29" s="48" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A30" s="48" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A30" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="49" t="s">
+      <c r="B30" s="48" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A31" s="48" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A31" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="B31" s="49" t="s">
+      <c r="B31" s="48" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A32" s="48" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A32" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="49" t="s">
+      <c r="B32" s="48" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A33" s="48" t="s">
+      <c r="A33" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="B33" s="49" t="s">
+      <c r="B33" s="48" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A34" s="48" t="s">
+      <c r="A34" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="49" t="s">
+      <c r="B34" s="48" t="s">
         <v>387</v>
       </c>
     </row>
@@ -9116,18 +9432,18 @@
       <c r="D1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="53" t="s">
+      <c r="E1" s="52" t="s">
         <v>283</v>
       </c>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53" t="s">
+      <c r="F1" s="52"/>
+      <c r="G1" s="52" t="s">
         <v>284</v>
       </c>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53" t="s">
+      <c r="H1" s="52"/>
+      <c r="I1" s="52" t="s">
         <v>296</v>
       </c>
-      <c r="J1" s="53"/>
+      <c r="J1" s="52"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
@@ -9447,14 +9763,14 @@
         <v>171</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="47" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:7" ht="31.35" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4" t="s">
         <v>72</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="G16" s="55" t="s">
+      <c r="G16" s="50" t="s">
         <v>392</v>
       </c>
     </row>
@@ -10607,7 +10923,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{836E3DAF-4660-4453-8445-CAEF205E5F1E}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="7.703125" bestFit="1" customWidth="1"/>
@@ -10617,7 +10933,7 @@
     <col min="5" max="5" width="14.3515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>57</v>
       </c>
@@ -10631,15 +10947,18 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A4">
         <v>4206804</v>
       </c>
@@ -10655,8 +10974,11 @@
       <c r="E4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A5">
         <v>9307104</v>
       </c>
@@ -10672,8 +10994,11 @@
       <c r="E5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A6">
         <v>2173704</v>
       </c>
@@ -10689,8 +11014,11 @@
       <c r="E6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A7">
         <v>9257304</v>
       </c>
@@ -10706,8 +11034,11 @@
       <c r="E7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A8">
         <v>2915404</v>
       </c>
@@ -10723,8 +11054,11 @@
       <c r="E8">
         <v>0.67</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A9">
         <v>2836604</v>
       </c>
@@ -10740,8 +11074,11 @@
       <c r="E9">
         <v>0.67</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A10">
         <v>1274904</v>
       </c>
@@ -10757,8 +11094,11 @@
       <c r="E10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A11">
         <v>3863304</v>
       </c>
@@ -10774,8 +11114,11 @@
       <c r="E11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A12">
         <v>3403504</v>
       </c>
@@ -10791,8 +11134,11 @@
       <c r="E12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A13">
         <v>4721304</v>
       </c>
@@ -10808,8 +11154,11 @@
       <c r="E13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A14">
         <v>3924304</v>
       </c>
@@ -10825,8 +11174,11 @@
       <c r="E14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A15">
         <v>4041704</v>
       </c>
@@ -10842,8 +11194,11 @@
       <c r="E15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A16">
         <v>9280704</v>
       </c>
@@ -10859,8 +11214,11 @@
       <c r="E16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.5">
       <c r="C17" t="s">
         <v>226</v>
       </c>
@@ -10870,8 +11228,11 @@
       <c r="E17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.5">
       <c r="B18" t="s">
         <v>227</v>
       </c>
@@ -10884,8 +11245,11 @@
       <c r="E18">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -10893,7 +11257,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -10907,7 +11271,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A22">
         <v>9693404</v>
       </c>
@@ -10921,7 +11285,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A23">
         <v>222222</v>
       </c>
@@ -10935,7 +11299,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A24">
         <v>9743804</v>
       </c>
@@ -10949,7 +11313,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A25">
         <v>111111</v>
       </c>
@@ -10963,7 +11327,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A26">
         <v>9662304</v>
       </c>
@@ -10977,7 +11341,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.5">
       <c r="B27" t="s">
         <v>270</v>
       </c>
@@ -10988,7 +11352,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.5">
       <c r="B28" t="s">
         <v>270</v>
       </c>
@@ -10999,12 +11363,12 @@
         <v>274</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.5">
       <c r="A32">
         <v>3578804</v>
       </c>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1970" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC5BFB8A-094B-4BE3-B44D-D5AE53FB2C31}"/>
+  <xr:revisionPtr revIDLastSave="1983" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FF10D71-B673-4F04-BF34-C64A8F3AB11D}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="15" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -47,11 +47,20 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={0EC5DC5A-F896-49D3-AC0B-D675C88CA2B5}</author>
     <author>tc={41FD7CA7-2390-44D2-8B22-26BF56BE8599}</author>
     <author>tc={166B4807-79FD-403D-9189-ED88B5EDB4C9}</author>
   </authors>
   <commentList>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{41FD7CA7-2390-44D2-8B22-26BF56BE8599}">
+    <comment ref="Q6" authorId="0" shapeId="0" xr:uid="{0EC5DC5A-F896-49D3-AC0B-D675C88CA2B5}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Only Samy Nectarios sent me attachment</t>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="1" shapeId="0" xr:uid="{41FD7CA7-2390-44D2-8B22-26BF56BE8599}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -59,7 +68,7 @@
     HW: p40, ex.7</t>
       </text>
     </comment>
-    <comment ref="A11" authorId="1" shapeId="0" xr:uid="{166B4807-79FD-403D-9189-ED88B5EDB4C9}">
+    <comment ref="A11" authorId="2" shapeId="0" xr:uid="{166B4807-79FD-403D-9189-ED88B5EDB4C9}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1322,7 +1331,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="424">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2662,9 +2671,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2757,6 +2766,12 @@
       <name val="DejaVu Sans"/>
       <family val="2"/>
       <charset val="161"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="15">
@@ -3054,23 +3069,23 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -3359,6 +3374,9 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="Q6" dT="2026-10-30T09:16:36.01" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{0EC5DC5A-F896-49D3-AC0B-D675C88CA2B5}">
+    <text>Only Samy Nectarios sent me attachment</text>
+  </threadedComment>
   <threadedComment ref="F7" dT="2026-09-21T07:31:36.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{41FD7CA7-2390-44D2-8B22-26BF56BE8599}">
     <text>HW: p40, ex.7</text>
   </threadedComment>
@@ -3902,58 +3920,58 @@
   <sheetData>
     <row r="1" spans="1:60" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="28"/>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="54" t="s">
+      <c r="C1" s="56"/>
+      <c r="D1" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="54" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="55" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="55"/>
-      <c r="H1" s="54" t="s">
+      <c r="G1" s="56"/>
+      <c r="H1" s="55" t="s">
         <v>239</v>
       </c>
-      <c r="I1" s="55"/>
-      <c r="J1" s="54" t="s">
+      <c r="I1" s="56"/>
+      <c r="J1" s="55" t="s">
         <v>243</v>
       </c>
-      <c r="K1" s="55"/>
-      <c r="L1" s="54" t="s">
+      <c r="K1" s="56"/>
+      <c r="L1" s="55" t="s">
         <v>246</v>
       </c>
-      <c r="M1" s="55"/>
-      <c r="N1" s="54" t="s">
+      <c r="M1" s="56"/>
+      <c r="N1" s="55" t="s">
         <v>345</v>
       </c>
-      <c r="O1" s="55"/>
-      <c r="P1" s="54" t="s">
+      <c r="O1" s="56"/>
+      <c r="P1" s="55" t="s">
         <v>346</v>
       </c>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="54" t="s">
+      <c r="Q1" s="56"/>
+      <c r="R1" s="55" t="s">
         <v>348</v>
       </c>
-      <c r="S1" s="55"/>
-      <c r="T1" s="54" t="s">
+      <c r="S1" s="56"/>
+      <c r="T1" s="55" t="s">
         <v>349</v>
       </c>
-      <c r="U1" s="55"/>
-      <c r="V1" s="54" t="s">
+      <c r="U1" s="56"/>
+      <c r="V1" s="55" t="s">
         <v>350</v>
       </c>
-      <c r="W1" s="55"/>
-      <c r="X1" s="54" t="s">
+      <c r="W1" s="56"/>
+      <c r="X1" s="55" t="s">
         <v>351</v>
       </c>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="54" t="s">
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="55" t="s">
         <v>352</v>
       </c>
-      <c r="AA1" s="55"/>
+      <c r="AA1" s="56"/>
       <c r="AB1" s="29"/>
       <c r="AC1" s="29"/>
       <c r="AD1" s="29"/>
@@ -4118,6 +4136,9 @@
       <c r="R4" s="25" t="s">
         <v>353</v>
       </c>
+      <c r="S4" s="25" t="s">
+        <v>353</v>
+      </c>
       <c r="Y4" s="39" t="s">
         <v>247</v>
       </c>
@@ -4177,6 +4198,9 @@
       <c r="R5" s="25" t="s">
         <v>354</v>
       </c>
+      <c r="S5" s="25" t="s">
+        <v>355</v>
+      </c>
       <c r="X5" s="39" t="s">
         <v>247</v>
       </c>
@@ -4230,7 +4254,7 @@
       <c r="P6" s="44" t="s">
         <v>282</v>
       </c>
-      <c r="Q6" s="25" t="s">
+      <c r="Q6" s="23" t="s">
         <v>371</v>
       </c>
       <c r="R6" s="25" t="s">
@@ -4306,6 +4330,12 @@
       </c>
       <c r="Q7" s="25" t="s">
         <v>353</v>
+      </c>
+      <c r="R7" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="S7" s="25" t="s">
+        <v>355</v>
       </c>
       <c r="X7" s="39" t="s">
         <v>247</v>
@@ -4860,11 +4890,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4873,6 +4898,11 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5038,26 +5068,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="57" t="s">
         <v>283</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52" t="s">
+      <c r="G2" s="57"/>
+      <c r="H2" s="57" t="s">
         <v>284</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52" t="s">
+      <c r="I2" s="57"/>
+      <c r="J2" s="57" t="s">
         <v>294</v>
       </c>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52" t="s">
+      <c r="K2" s="57"/>
+      <c r="L2" s="57" t="s">
         <v>320</v>
       </c>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52" t="s">
+      <c r="M2" s="57"/>
+      <c r="N2" s="57" t="s">
         <v>391</v>
       </c>
-      <c r="O2" s="52"/>
+      <c r="O2" s="57"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -6461,26 +6491,26 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="F2" s="52" t="s">
+      <c r="F2" s="57" t="s">
         <v>283</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52" t="s">
+      <c r="G2" s="57"/>
+      <c r="H2" s="57" t="s">
         <v>284</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52" t="s">
+      <c r="I2" s="57"/>
+      <c r="J2" s="57" t="s">
         <v>296</v>
       </c>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52" t="s">
+      <c r="K2" s="57"/>
+      <c r="L2" s="57" t="s">
         <v>320</v>
       </c>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52" t="s">
+      <c r="M2" s="57"/>
+      <c r="N2" s="57" t="s">
         <v>365</v>
       </c>
-      <c r="O2" s="52"/>
+      <c r="O2" s="57"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
@@ -7524,30 +7554,30 @@
       <c r="D1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="52" t="s">
+      <c r="G1" s="57" t="s">
         <v>283</v>
       </c>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52" t="s">
+      <c r="H1" s="57"/>
+      <c r="I1" s="57" t="s">
         <v>284</v>
       </c>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52" t="s">
+      <c r="J1" s="57"/>
+      <c r="K1" s="57" t="s">
         <v>296</v>
       </c>
-      <c r="L1" s="52"/>
-      <c r="M1" s="53" t="s">
+      <c r="L1" s="57"/>
+      <c r="M1" s="58" t="s">
         <v>326</v>
       </c>
-      <c r="N1" s="53"/>
-      <c r="O1" s="52" t="s">
+      <c r="N1" s="58"/>
+      <c r="O1" s="57" t="s">
         <v>365</v>
       </c>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52" t="s">
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57" t="s">
         <v>391</v>
       </c>
-      <c r="R1" s="52"/>
+      <c r="R1" s="57"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
@@ -9251,7 +9281,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="C15" s="56">
+      <c r="C15" s="52">
         <v>6</v>
       </c>
     </row>
@@ -9259,7 +9289,7 @@
       <c r="A16" t="s">
         <v>360</v>
       </c>
-      <c r="C16" s="58">
+      <c r="C16" s="54">
         <v>1000000</v>
       </c>
     </row>
@@ -9270,7 +9300,7 @@
       <c r="B17" t="s">
         <v>268</v>
       </c>
-      <c r="C17" s="57" t="s">
+      <c r="C17" s="53" t="s">
         <v>423</v>
       </c>
     </row>
@@ -9432,18 +9462,18 @@
       <c r="D1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="57" t="s">
         <v>283</v>
       </c>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52" t="s">
+      <c r="F1" s="57"/>
+      <c r="G1" s="57" t="s">
         <v>284</v>
       </c>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52" t="s">
+      <c r="H1" s="57"/>
+      <c r="I1" s="57" t="s">
         <v>296</v>
       </c>
-      <c r="J1" s="52"/>
+      <c r="J1" s="57"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4">
@@ -9994,6 +10024,12 @@
       <c r="A29" s="4" t="s">
         <v>140</v>
       </c>
+      <c r="E29" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4">
@@ -10008,6 +10044,7 @@
       <c r="D30" s="4" t="s">
         <v>143</v>
       </c>
+      <c r="F30" s="20"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4">
@@ -10022,6 +10059,7 @@
       <c r="D31" s="4" t="s">
         <v>143</v>
       </c>
+      <c r="F31" s="20"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4">
@@ -10036,8 +10074,12 @@
       <c r="D32" s="4" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E32" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F32" s="20"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="4">
         <v>7319504</v>
       </c>
@@ -10050,8 +10092,9 @@
       <c r="D33" s="4" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F33" s="20"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="4">
         <v>9254304</v>
       </c>
@@ -10067,8 +10110,9 @@
       <c r="E34" s="6" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F34" s="20"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="4">
         <v>2428404</v>
       </c>
@@ -10081,8 +10125,9 @@
       <c r="D35" s="4" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F35" s="20"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="4">
         <v>2427904</v>
       </c>
@@ -10098,8 +10143,9 @@
       <c r="E36" s="6" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F36" s="20"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4">
         <v>8373704</v>
       </c>
@@ -10112,8 +10158,9 @@
       <c r="D37" s="4" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F37" s="20"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="4">
         <v>5155004</v>
       </c>
@@ -10129,8 +10176,11 @@
       <c r="E38" s="6" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F38" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="4">
         <v>1006390</v>
       </c>
@@ -10143,13 +10193,14 @@
       <c r="D39" s="4" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F39" s="20"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="4">
         <v>5324204</v>
       </c>
@@ -10164,7 +10215,7 @@
       </c>
       <c r="E43" s="20"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="4">
         <v>5996604</v>
       </c>
@@ -10179,7 +10230,7 @@
       </c>
       <c r="E44" s="20"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="4">
         <v>9185204</v>
       </c>
@@ -10196,7 +10247,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="4">
         <v>9185504</v>
       </c>
@@ -10213,7 +10264,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="4">
         <v>4913604</v>
       </c>
@@ -10230,7 +10281,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="4">
         <v>5436204</v>
       </c>

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://moecyprus-my.sharepoint.com/personal/aaresti3_te_schools_ac_cy/Documents/Documents/education/schools-presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1983" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FF10D71-B673-4F04-BF34-C64A8F3AB11D}"/>
+  <xr:revisionPtr revIDLastSave="2005" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{826A9E8C-748F-402A-AB69-A6D3BD04A04C}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,6 @@
     <author>tc={3D2570EE-C1C0-4D2F-A268-8D52210E5513}</author>
     <author>tc={8F76B8B8-18EE-496F-A335-0321C1189047}</author>
     <author>tc={0E374CA0-3C13-436D-9FAC-14F6B920C675}</author>
-    <author>tc={0E1BF347-0EA3-4549-B042-BCD495D8C495}</author>
     <author>tc={77742E87-EB5D-4747-811D-D6052514F58A}</author>
     <author>tc={221FDEED-1145-48B8-93A0-518076128BE1}</author>
     <author>tc={06E68A77-02D9-459A-AE13-BD4D2460CF82}</author>
@@ -254,15 +253,7 @@
     Roumania, diskolies sta ellinika</t>
       </text>
     </comment>
-    <comment ref="C31" authorId="16" shapeId="0" xr:uid="{0E1BF347-0EA3-4549-B042-BCD495D8C495}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Xorismenoi goneis</t>
-      </text>
-    </comment>
-    <comment ref="C32" authorId="17" shapeId="0" xr:uid="{77742E87-EB5D-4747-811D-D6052514F58A}">
+    <comment ref="C31" authorId="16" shapeId="0" xr:uid="{77742E87-EB5D-4747-811D-D6052514F58A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -270,7 +261,7 @@
     Skaki, mathimatika olympiades</t>
       </text>
     </comment>
-    <comment ref="C33" authorId="18" shapeId="0" xr:uid="{221FDEED-1145-48B8-93A0-518076128BE1}">
+    <comment ref="C32" authorId="17" shapeId="0" xr:uid="{221FDEED-1145-48B8-93A0-518076128BE1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -278,7 +269,7 @@
     Sitisi, papapona gia bullying sto dimotiko</t>
       </text>
     </comment>
-    <comment ref="C34" authorId="19" shapeId="0" xr:uid="{06E68A77-02D9-459A-AE13-BD4D2460CF82}">
+    <comment ref="C33" authorId="18" shapeId="0" xr:uid="{06E68A77-02D9-459A-AE13-BD4D2460CF82}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -287,7 +278,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="C35" authorId="20" shapeId="0" xr:uid="{B3A23F0F-0E01-41A2-8966-76A587BA515C}">
+    <comment ref="C34" authorId="19" shapeId="0" xr:uid="{B3A23F0F-0E01-41A2-8966-76A587BA515C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -295,7 +286,7 @@
     Didimoi me Kimona</t>
       </text>
     </comment>
-    <comment ref="C36" authorId="21" shapeId="0" xr:uid="{AA3BDBA2-8267-4A69-A689-551224F645D9}">
+    <comment ref="C35" authorId="20" shapeId="0" xr:uid="{AA3BDBA2-8267-4A69-A689-551224F645D9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -303,7 +294,7 @@
     Ypermetropia, astigmatismos</t>
       </text>
     </comment>
-    <comment ref="C38" authorId="22" shapeId="0" xr:uid="{FCE8BE01-CFDB-4E54-9051-44ADC799EE83}">
+    <comment ref="C37" authorId="21" shapeId="0" xr:uid="{FCE8BE01-CFDB-4E54-9051-44ADC799EE83}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -311,7 +302,7 @@
     Sitisi, orfanos apo patera sti Syria</t>
       </text>
     </comment>
-    <comment ref="C39" authorId="23" shapeId="0" xr:uid="{98BD6B5F-37EB-41FA-B971-80255C43C024}">
+    <comment ref="C38" authorId="22" shapeId="0" xr:uid="{98BD6B5F-37EB-41FA-B971-80255C43C024}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -319,7 +310,7 @@
     Spazei sixna h miti tis</t>
       </text>
     </comment>
-    <comment ref="C43" authorId="24" shapeId="0" xr:uid="{3FB9C602-3AA9-40D1-97B5-331230499AE8}">
+    <comment ref="C42" authorId="23" shapeId="0" xr:uid="{3FB9C602-3AA9-40D1-97B5-331230499AE8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -327,7 +318,7 @@
     Xorismeni, apoklisitiki h mitera</t>
       </text>
     </comment>
-    <comment ref="C44" authorId="25" shapeId="0" xr:uid="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
+    <comment ref="C43" authorId="24" shapeId="0" xr:uid="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -335,7 +326,7 @@
     indefferent</t>
       </text>
     </comment>
-    <comment ref="C45" authorId="26" shapeId="0" xr:uid="{7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}">
+    <comment ref="C44" authorId="25" shapeId="0" xr:uid="{7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -343,7 +334,7 @@
     Stiriksi, sitisi, menei me patera, oxi epaphi me mitera, o pateras fetos irthe, emenas me giagia kai pappou</t>
       </text>
     </comment>
-    <comment ref="C49" authorId="27" shapeId="0" xr:uid="{8F4D57B3-2C90-4744-BFEF-99E499E55142}">
+    <comment ref="C48" authorId="26" shapeId="0" xr:uid="{8F4D57B3-2C90-4744-BFEF-99E499E55142}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -351,7 +342,7 @@
     Dropalos, thelei enisxisi</t>
       </text>
     </comment>
-    <comment ref="C50" authorId="28" shapeId="0" xr:uid="{37F71BFC-AE14-49EC-B2B2-49697A83F48F}">
+    <comment ref="C49" authorId="27" shapeId="0" xr:uid="{37F71BFC-AE14-49EC-B2B2-49697A83F48F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -359,7 +350,7 @@
     Stiriksi, mathisiakes adinamies</t>
       </text>
     </comment>
-    <comment ref="C51" authorId="29" shapeId="0" xr:uid="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
+    <comment ref="C50" authorId="28" shapeId="0" xr:uid="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1331,7 +1322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="424">
   <si>
     <t>Α Τάξη</t>
   </si>
@@ -2563,9 +2554,6 @@
     <t>ΣΧΟΛΙΚΗ ΓΙΟΡΤΗ</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>26-30/10 2026</t>
   </si>
   <si>
@@ -2650,9 +2638,6 @@
     <t>8-a</t>
   </si>
   <si>
-    <t>9 - Switch - Router - Modem - Access Point</t>
-  </si>
-  <si>
     <t>11 - Phishing - Ip Address - LAN - Router</t>
   </si>
   <si>
@@ -2663,6 +2648,12 @@
   </si>
   <si>
     <t>Διαβάζουμε βιβλίο και συζητούμε την ιστορία</t>
+  </si>
+  <si>
+    <t>hw. As 7-13, p.146</t>
+  </si>
+  <si>
+    <t>9 - A - B - Δ - Γ</t>
   </si>
 </sst>
 </file>
@@ -2673,7 +2664,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2766,12 +2757,6 @@
       <name val="DejaVu Sans"/>
       <family val="2"/>
       <charset val="161"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="15">
@@ -3452,51 +3437,48 @@
   <threadedComment ref="C30" dT="2026-10-05T07:13:32.27" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{0E374CA0-3C13-436D-9FAC-14F6B920C675}">
     <text>Roumania, diskolies sta ellinika</text>
   </threadedComment>
-  <threadedComment ref="C31" dT="2026-10-05T07:13:44.64" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{0E1BF347-0EA3-4549-B042-BCD495D8C495}">
-    <text>Xorismenoi goneis</text>
-  </threadedComment>
-  <threadedComment ref="C32" dT="2026-10-05T07:14:01.31" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{77742E87-EB5D-4747-811D-D6052514F58A}">
+  <threadedComment ref="C31" dT="2026-10-05T07:14:01.31" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{77742E87-EB5D-4747-811D-D6052514F58A}">
     <text>Skaki, mathimatika olympiades</text>
   </threadedComment>
-  <threadedComment ref="C33" dT="2026-10-05T07:14:18.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{221FDEED-1145-48B8-93A0-518076128BE1}">
+  <threadedComment ref="C32" dT="2026-10-05T07:14:18.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{221FDEED-1145-48B8-93A0-518076128BE1}">
     <text>Sitisi, papapona gia bullying sto dimotiko</text>
   </threadedComment>
-  <threadedComment ref="C34" dT="2026-10-05T07:14:34.50" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{06E68A77-02D9-459A-AE13-BD4D2460CF82}">
+  <threadedComment ref="C33" dT="2026-10-05T07:14:34.50" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{06E68A77-02D9-459A-AE13-BD4D2460CF82}">
     <text xml:space="preserve">Sitisi, stiriksi
 </text>
   </threadedComment>
-  <threadedComment ref="C35" dT="2026-10-05T07:14:51.75" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B3A23F0F-0E01-41A2-8966-76A587BA515C}">
+  <threadedComment ref="C34" dT="2026-10-05T07:14:51.75" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{B3A23F0F-0E01-41A2-8966-76A587BA515C}">
     <text>Didimoi me Kimona</text>
   </threadedComment>
-  <threadedComment ref="C36" dT="2026-10-05T07:15:08.05" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AA3BDBA2-8267-4A69-A689-551224F645D9}">
+  <threadedComment ref="C35" dT="2026-10-05T07:15:08.05" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{AA3BDBA2-8267-4A69-A689-551224F645D9}">
     <text>Ypermetropia, astigmatismos</text>
   </threadedComment>
-  <threadedComment ref="C38" dT="2026-10-05T07:15:27.54" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{FCE8BE01-CFDB-4E54-9051-44ADC799EE83}">
+  <threadedComment ref="C37" dT="2026-10-05T07:15:27.54" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{FCE8BE01-CFDB-4E54-9051-44ADC799EE83}">
     <text>Sitisi, orfanos apo patera sti Syria</text>
   </threadedComment>
-  <threadedComment ref="C39" dT="2026-10-05T07:15:40.47" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{98BD6B5F-37EB-41FA-B971-80255C43C024}">
+  <threadedComment ref="C38" dT="2026-10-05T07:15:40.47" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{98BD6B5F-37EB-41FA-B971-80255C43C024}">
     <text>Spazei sixna h miti tis</text>
   </threadedComment>
-  <threadedComment ref="C43" dT="2026-10-05T09:04:32.37" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3FB9C602-3AA9-40D1-97B5-331230499AE8}">
+  <threadedComment ref="C42" dT="2026-10-05T09:04:32.37" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{3FB9C602-3AA9-40D1-97B5-331230499AE8}">
     <text>Xorismeni, apoklisitiki h mitera</text>
   </threadedComment>
-  <threadedComment ref="C44" dT="2026-09-25T14:55:37.89" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
+  <threadedComment ref="C43" dT="2026-09-25T14:55:37.89" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{009D741D-5339-4620-BEF3-C76ECC0C19D0}">
     <text>indefferent</text>
   </threadedComment>
-  <threadedComment ref="C45" dT="2026-10-05T09:05:48.06" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}">
+  <threadedComment ref="C44" dT="2026-10-05T09:05:48.06" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{7B9E03F7-0A49-4A9A-B9C7-4DBFEDE76318}">
     <text>Stiriksi, sitisi, menei me patera, oxi epaphi me mitera, o pateras fetos irthe, emenas me giagia kai pappou</text>
   </threadedComment>
-  <threadedComment ref="C49" dT="2026-10-05T09:06:03.45" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{8F4D57B3-2C90-4744-BFEF-99E499E55142}">
+  <threadedComment ref="C48" dT="2026-10-05T09:06:03.45" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{8F4D57B3-2C90-4744-BFEF-99E499E55142}">
     <text>Dropalos, thelei enisxisi</text>
   </threadedComment>
-  <threadedComment ref="C50" dT="2026-10-05T09:06:27.63" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{37F71BFC-AE14-49EC-B2B2-49697A83F48F}">
+  <threadedComment ref="C49" dT="2026-10-05T09:06:27.63" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{37F71BFC-AE14-49EC-B2B2-49697A83F48F}">
     <text>Stiriksi, mathisiakes adinamies</text>
   </threadedComment>
-  <threadedComment ref="C51" dT="2026-09-21T06:24:16.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
+  <threadedComment ref="C50" dT="2026-09-21T06:24:16.33" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
     <text xml:space="preserve">Little guy with glasses
 </text>
   </threadedComment>
-  <threadedComment ref="C51" dT="2026-10-05T09:06:44.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{98AF0D30-4238-4DB6-AEB6-E46495700012}" parentId="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
+  <threadedComment ref="C50" dT="2026-10-05T09:06:44.41" personId="{022C90DC-4D80-4693-BF93-D8B5235DAAE3}" id="{98AF0D30-4238-4DB6-AEB6-E46495700012}" parentId="{2F7A43C1-80E7-48EF-B3B2-B25F8BB9C497}">
     <text>alpabitismos</text>
   </threadedComment>
 </ThreadedComments>
@@ -4328,7 +4310,7 @@
       <c r="P7" s="23" t="s">
         <v>371</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="23" t="s">
         <v>353</v>
       </c>
       <c r="R7" s="25" t="s">
@@ -4411,6 +4393,9 @@
       <c r="R11" s="25" t="s">
         <v>323</v>
       </c>
+      <c r="S11" s="25" t="s">
+        <v>378</v>
+      </c>
       <c r="T11" s="39" t="s">
         <v>295</v>
       </c>
@@ -4470,14 +4455,14 @@
       <c r="P12" s="23" t="s">
         <v>377</v>
       </c>
-      <c r="Q12" s="25" t="s">
+      <c r="Q12" s="23" t="s">
         <v>322</v>
       </c>
       <c r="R12" s="25" t="s">
+        <v>323</v>
+      </c>
+      <c r="S12" s="25" t="s">
         <v>378</v>
-      </c>
-      <c r="S12" s="25" t="s">
-        <v>388</v>
       </c>
       <c r="T12" s="39" t="s">
         <v>295</v>
@@ -4539,7 +4524,7 @@
         <v>323</v>
       </c>
       <c r="Q13" s="23" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="R13" s="25" t="s">
         <v>388</v>
@@ -4890,6 +4875,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4898,11 +4888,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4921,7 +4906,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.5">
@@ -4931,98 +4916,98 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B3" t="s">
         <v>398</v>
-      </c>
-      <c r="B3" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A10" s="51" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B12" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B13" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B14" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -5032,7 +5017,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0C9DD2-633E-44CA-9A93-86B2E2731C82}">
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr defaultColWidth="9.05859375" defaultRowHeight="15.7" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.3515625" style="4" bestFit="1" customWidth="1"/>
@@ -5085,7 +5070,7 @@
       </c>
       <c r="M2" s="57"/>
       <c r="N2" s="57" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="O2" s="57"/>
     </row>
@@ -5434,7 +5419,7 @@
         <v>328</v>
       </c>
       <c r="N15" s="50" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -5813,13 +5798,13 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4">
-        <v>5682904</v>
+        <v>9217204</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>143</v>
@@ -5827,25 +5812,21 @@
       <c r="E31" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>171</v>
-      </c>
+      <c r="F31" s="12"/>
+      <c r="H31" s="12"/>
       <c r="I31" s="6" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="4">
-        <v>9217204</v>
+        <v>7319504</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>143</v>
@@ -5853,21 +5834,25 @@
       <c r="E32" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F32" s="12"/>
-      <c r="H32" s="12"/>
+      <c r="F32" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>171</v>
+      </c>
       <c r="I32" s="6" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="4">
-        <v>7319504</v>
+        <v>9254304</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>143</v>
@@ -5887,13 +5872,13 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="4">
-        <v>9254304</v>
+        <v>2428404</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>143</v>
@@ -5913,13 +5898,13 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="4">
-        <v>2428404</v>
+        <v>2427904</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>151</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>143</v>
@@ -5939,13 +5924,13 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="4">
-        <v>2427904</v>
+        <v>8373704</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>151</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>143</v>
@@ -5965,13 +5950,13 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4">
-        <v>8373704</v>
+        <v>5155004</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>143</v>
@@ -5991,13 +5976,13 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="4">
-        <v>5155004</v>
+        <v>1006390</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>156</v>
+        <v>47</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>143</v>
@@ -6015,49 +6000,64 @@
         <v>171</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="4">
-        <v>1006390</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>171</v>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>285</v>
+      <c r="A42" s="4">
+        <v>5324204</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="4">
-        <v>5324204</v>
+        <v>5996604</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>159</v>
@@ -6069,7 +6069,7 @@
         <v>171</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>171</v>
@@ -6086,19 +6086,16 @@
       <c r="L43" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="O43" s="4" t="s">
-        <v>376</v>
-      </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="4">
-        <v>5996604</v>
+        <v>9185204</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>159</v>
@@ -6107,19 +6104,19 @@
         <v>171</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="G44" s="6" t="s">
         <v>231</v>
       </c>
+      <c r="G44" s="15" t="s">
+        <v>264</v>
+      </c>
       <c r="H44" s="6" t="s">
         <v>171</v>
       </c>
       <c r="I44" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="J44" s="6" t="s">
-        <v>171</v>
+      <c r="J44" s="14" t="s">
+        <v>231</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>237</v>
@@ -6130,13 +6127,13 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="4">
-        <v>9185204</v>
+        <v>9185504</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>159</v>
@@ -6147,8 +6144,8 @@
       <c r="F45" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="G45" s="15" t="s">
-        <v>264</v>
+      <c r="G45" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>171</v>
@@ -6168,13 +6165,13 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="4">
-        <v>9185504</v>
+        <v>4913604</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>159</v>
@@ -6182,11 +6179,11 @@
       <c r="E46" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>171</v>
+      <c r="F46" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="G46" s="18" t="s">
+        <v>260</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>171</v>
@@ -6194,8 +6191,8 @@
       <c r="I46" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="J46" s="14" t="s">
-        <v>231</v>
+      <c r="J46" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>237</v>
@@ -6206,13 +6203,13 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="4">
-        <v>4913604</v>
+        <v>5436204</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>159</v>
@@ -6220,11 +6217,11 @@
       <c r="E47" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F47" s="18" t="s">
-        <v>260</v>
-      </c>
-      <c r="G47" s="18" t="s">
-        <v>260</v>
+      <c r="F47" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>171</v>
@@ -6244,13 +6241,13 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="4">
-        <v>5436204</v>
+        <v>3506004</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>159</v>
@@ -6282,13 +6279,13 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="4">
-        <v>3506004</v>
+        <v>6757304</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>50</v>
+        <v>166</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>159</v>
@@ -6320,13 +6317,13 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="4">
-        <v>6757304</v>
+        <v>6390804</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>159</v>
@@ -6356,93 +6353,55 @@
         <v>237</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="4">
-        <v>6390804</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="K51" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="L51" s="11" t="s">
-        <v>237</v>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="12"/>
+      <c r="B54" s="6" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="12"/>
+      <c r="A55" s="17" t="s">
+        <v>171</v>
+      </c>
       <c r="B55" s="6" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="17" t="s">
-        <v>171</v>
+      <c r="A56" s="18" t="s">
+        <v>260</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="18" t="s">
-        <v>260</v>
-      </c>
+      <c r="A57" s="20"/>
       <c r="B57" s="6" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="20"/>
+      <c r="A58" s="14" t="s">
+        <v>231</v>
+      </c>
       <c r="B58" s="6" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="14" t="s">
-        <v>231</v>
+      <c r="A59" s="15" t="s">
+        <v>264</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="15" t="s">
-        <v>264</v>
+      <c r="A60" s="16" t="s">
+        <v>265</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="B61" s="6" t="s">
         <v>266</v>
       </c>
     </row>
@@ -7575,7 +7534,7 @@
       </c>
       <c r="P1" s="57"/>
       <c r="Q1" s="57" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="R1" s="57"/>
     </row>
@@ -9301,7 +9260,7 @@
         <v>268</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.5">
@@ -9322,15 +9281,15 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
+        <v>394</v>
+      </c>
+      <c r="B22" t="s">
         <v>395</v>
-      </c>
-      <c r="B22" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.5">
@@ -9596,7 +9555,7 @@
     <col min="4" max="4" width="14.17578125" style="4" customWidth="1"/>
     <col min="5" max="5" width="10.234375" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.41015625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.87890625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="17" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9.05859375" style="4"/>
   </cols>
   <sheetData>
@@ -9801,7 +9760,7 @@
         <v>276</v>
       </c>
       <c r="G16" s="50" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -10079,7 +10038,7 @@
       </c>
       <c r="F32" s="20"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="4">
         <v>7319504</v>
       </c>
@@ -10094,7 +10053,7 @@
       </c>
       <c r="F33" s="20"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="4">
         <v>9254304</v>
       </c>
@@ -10112,7 +10071,7 @@
       </c>
       <c r="F34" s="20"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="4">
         <v>2428404</v>
       </c>
@@ -10127,7 +10086,7 @@
       </c>
       <c r="F35" s="20"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="4">
         <v>2427904</v>
       </c>
@@ -10145,7 +10104,7 @@
       </c>
       <c r="F36" s="20"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4">
         <v>8373704</v>
       </c>
@@ -10160,7 +10119,7 @@
       </c>
       <c r="F37" s="20"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="4">
         <v>5155004</v>
       </c>
@@ -10180,7 +10139,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="4">
         <v>1006390</v>
       </c>
@@ -10195,12 +10154,15 @@
       </c>
       <c r="F39" s="20"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="4" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="G42" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="4">
         <v>5324204</v>
       </c>
@@ -10215,7 +10177,7 @@
       </c>
       <c r="E43" s="20"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="4">
         <v>5996604</v>
       </c>
@@ -10230,7 +10192,7 @@
       </c>
       <c r="E44" s="20"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="4">
         <v>9185204</v>
       </c>
@@ -10247,7 +10209,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="4">
         <v>9185504</v>
       </c>
@@ -10264,7 +10226,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="4">
         <v>4913604</v>
       </c>
@@ -10281,7 +10243,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="4">
         <v>5436204</v>
       </c>
@@ -11006,7 +10968,7 @@
         <v>369</v>
       </c>
       <c r="F3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.5">
@@ -11305,7 +11267,7 @@
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.5">

--- a/schools-presentations/A Semester - Programmatismos.xlsx
+++ b/schools-presentations/A Semester - Programmatismos.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2005" documentId="11_F25DC773A252ABDACC10485521D851725BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{826A9E8C-748F-402A-AB69-A6D3BD04A04C}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="15" windowWidth="38640" windowHeight="21120" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="17253" windowHeight="10133" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
@@ -4875,11 +4875,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
@@ -4888,6 +4883,11 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
